--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93737328-B251-414F-9B83-BE754DBA395F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF4EC13-A652-4E53-A25B-182EBBFD3A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5025" yWindow="5025" windowWidth="28800" windowHeight="15345" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="28800" windowHeight="15345" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -915,39 +915,39 @@
         <v>32</v>
       </c>
       <c r="K2" s="7">
-        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <f t="shared" ref="K2:K21" si="0">ROUND(IMDIV(B2,J2),2)</f>
         <v>0.97</v>
       </c>
       <c r="L2" s="8">
-        <f>E2/J2</f>
+        <f t="shared" ref="L2:L21" si="1">E2/J2</f>
         <v>6.25E-2</v>
       </c>
       <c r="M2" s="8">
-        <f>D2/J2</f>
+        <f t="shared" ref="M2:M21" si="2">D2/J2</f>
         <v>0.21875</v>
       </c>
       <c r="N2" s="7">
-        <f>ROUND(IMDIV(F2,J2),2)</f>
+        <f t="shared" ref="N2:N21" si="3">ROUND(IMDIV(F2,J2),2)</f>
         <v>0.44</v>
       </c>
       <c r="O2" s="7">
-        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <f t="shared" ref="O2:O21" si="4">ROUND(IMDIV(G2,J2),2)</f>
         <v>10</v>
       </c>
       <c r="P2" s="7">
-        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <f t="shared" ref="P2:P21" si="5">ROUND(IMDIV(H2,J2),2)</f>
         <v>0.38</v>
       </c>
       <c r="Q2" s="7">
-        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <f t="shared" ref="Q2:Q21" si="6">ROUND(IMDIV(B2,F2),2)</f>
         <v>2.21</v>
       </c>
       <c r="R2" s="7">
-        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <f t="shared" ref="R2:R21" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
         <v>67.739999999999995</v>
       </c>
       <c r="S2" s="7">
-        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <f t="shared" ref="S2:S21" si="8">ROUND(IMDIV(I2,J2),2)</f>
         <v>98.44</v>
       </c>
       <c r="T2" s="9" t="s">
@@ -957,7 +957,7 @@
         <v>25</v>
       </c>
       <c r="V2" s="1">
-        <f>((K2/2)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <f t="shared" ref="V2:V21" si="9">((K2/2)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
         <v>1.589047965116279</v>
       </c>
     </row>
@@ -993,39 +993,39 @@
         <v>32</v>
       </c>
       <c r="K3" s="7">
-        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="L3" s="8">
-        <f>E3/J3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M3" s="8">
-        <f>D3/J3</f>
+        <f t="shared" si="2"/>
         <v>6.25E-2</v>
       </c>
       <c r="N3" s="7">
-        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <f t="shared" si="3"/>
         <v>0.53</v>
       </c>
       <c r="O3" s="7">
-        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <f t="shared" si="4"/>
         <v>0.03</v>
       </c>
       <c r="P3" s="7">
-        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <f t="shared" si="5"/>
         <v>0.06</v>
       </c>
       <c r="Q3" s="7">
-        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <f t="shared" si="6"/>
         <v>0.94</v>
       </c>
       <c r="R3" s="7">
-        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <f t="shared" si="7"/>
         <v>56.25</v>
       </c>
       <c r="S3" s="7">
-        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <f t="shared" si="8"/>
         <v>54.34</v>
       </c>
       <c r="T3" s="9" t="s">
@@ -1035,7 +1035,7 @@
         <v>25</v>
       </c>
       <c r="V3" s="1">
-        <f>((K3/2)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.99136918604651159</v>
       </c>
     </row>
@@ -1071,39 +1071,39 @@
         <v>15</v>
       </c>
       <c r="K4" s="10">
-        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <f t="shared" si="0"/>
         <v>0.93</v>
       </c>
       <c r="L4" s="12">
-        <f>E4/J4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M4" s="12">
-        <f>D4/J4</f>
+        <f t="shared" si="2"/>
         <v>0.13333333333333333</v>
       </c>
       <c r="N4" s="10">
-        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
       <c r="O4" s="10">
-        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <f t="shared" si="4"/>
         <v>4.2</v>
       </c>
       <c r="P4" s="10">
-        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <f t="shared" si="5"/>
         <v>0.73</v>
       </c>
       <c r="Q4" s="10">
-        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <f t="shared" si="6"/>
         <v>2.33</v>
       </c>
       <c r="R4" s="10">
-        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S4" s="10">
-        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="T4" s="11" t="s">
@@ -1113,7 +1113,7 @@
         <v>25</v>
       </c>
       <c r="V4" s="1">
-        <f>((K4/2)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.5813449612403101</v>
       </c>
     </row>
@@ -1149,39 +1149,39 @@
         <v>15</v>
       </c>
       <c r="K5" s="10">
-        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <f t="shared" si="0"/>
         <v>0.53</v>
       </c>
       <c r="L5" s="12">
-        <f>E5/J5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M5" s="12">
-        <f>D5/J5</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N5" s="10">
-        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="O5" s="10">
-        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <f t="shared" si="4"/>
         <v>1.93</v>
       </c>
       <c r="P5" s="10">
-        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <f t="shared" si="5"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q5" s="10">
-        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <f t="shared" si="6"/>
         <v>0.89</v>
       </c>
       <c r="R5" s="10">
-        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <f t="shared" si="7"/>
         <v>87.5</v>
       </c>
       <c r="S5" s="10">
-        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="T5" s="11" t="s">
@@ -1191,7 +1191,7 @@
         <v>25</v>
       </c>
       <c r="V5" s="1">
-        <f>((K5/2)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.98477906976744189</v>
       </c>
     </row>
@@ -1200,13 +1200,13 @@
         <v>30</v>
       </c>
       <c r="B6" s="13">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C6" s="13">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D6" s="13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" s="13">
         <v>1</v>
@@ -1218,49 +1218,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="13">
-        <v>847</v>
+        <v>2299</v>
       </c>
       <c r="J6" s="13">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K6" s="13">
-        <f>ROUND(IMDIV(B6,J6),2)</f>
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="L6" s="14">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="M6" s="14">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="N6" s="13">
+        <f t="shared" si="3"/>
         <v>0.45</v>
       </c>
-      <c r="L6" s="14">
-        <f>E6/J6</f>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="M6" s="14">
-        <f>D6/J6</f>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="N6" s="13">
-        <f>ROUND(IMDIV(F6,J6),2)</f>
-        <v>0.82</v>
-      </c>
       <c r="O6" s="13">
-        <f>ROUND(IMDIV(G6,J6),2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P6" s="13">
-        <f>ROUND(IMDIV(H6,J6),2)</f>
-        <v>0.27</v>
+        <f t="shared" si="5"/>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="13">
-        <f>ROUND(IMDIV(B6,F6),2)</f>
-        <v>0.56000000000000005</v>
+        <f t="shared" si="6"/>
+        <v>2</v>
       </c>
       <c r="R6" s="13">
-        <f>ROUND(IMDIV(C6,B6),4)*100</f>
-        <v>80</v>
+        <f t="shared" si="7"/>
+        <v>44.440000000000005</v>
       </c>
       <c r="S6" s="13">
-        <f>ROUND(IMDIV(I6,J6),2)</f>
-        <v>77</v>
+        <f t="shared" si="8"/>
+        <v>114.95</v>
       </c>
       <c r="T6" s="15" t="s">
         <v>43</v>
@@ -1269,8 +1269,8 @@
         <v>25</v>
       </c>
       <c r="V6" s="1">
-        <f>((K6/2)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>0.84027589852008466</v>
+        <f t="shared" si="9"/>
+        <v>1.6421511627906977</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1278,13 +1278,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="13">
         <v>0</v>
@@ -1293,52 +1293,52 @@
         <v>11</v>
       </c>
       <c r="G7" s="13">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H7" s="13">
         <v>0</v>
       </c>
       <c r="I7" s="13">
-        <v>249</v>
+        <v>986</v>
       </c>
       <c r="J7" s="13">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K7" s="13">
-        <f>ROUND(IMDIV(B7,J7),2)</f>
-        <v>0.18</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="L7" s="14">
-        <f>E7/J7</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M7" s="14">
-        <f>D7/J7</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>0.05</v>
       </c>
       <c r="N7" s="13">
-        <f>ROUND(IMDIV(F7,J7),2)</f>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O7" s="13">
-        <f>ROUND(IMDIV(G7,J7),2)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3.9</v>
       </c>
       <c r="P7" s="13">
-        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q7" s="13">
-        <f>ROUND(IMDIV(B7,F7),2)</f>
-        <v>0.18</v>
+        <f t="shared" si="6"/>
+        <v>0.64</v>
       </c>
       <c r="R7" s="13">
-        <f>ROUND(IMDIV(C7,B7),4)*100</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>42.86</v>
       </c>
       <c r="S7" s="13">
-        <f>ROUND(IMDIV(I7,J7),2)</f>
-        <v>22.64</v>
+        <f t="shared" si="8"/>
+        <v>49.3</v>
       </c>
       <c r="T7" s="15" t="s">
         <v>43</v>
@@ -1347,8 +1347,8 @@
         <v>25</v>
       </c>
       <c r="V7" s="1">
-        <f>((K7/2)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
-        <v>0.19530232558139526</v>
+        <f t="shared" si="9"/>
+        <v>0.86680232558139525</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1383,39 +1383,39 @@
         <v>15</v>
       </c>
       <c r="K8" s="17">
-        <f>ROUND(IMDIV(B8,J8),2)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="L8" s="19">
-        <f>E8/J8</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="M8" s="19">
-        <f>D8/J8</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="N8" s="17">
-        <f>ROUND(IMDIV(F8,J8),2)</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="O8" s="17">
-        <f>ROUND(IMDIV(G8,J8),2)</f>
+        <f t="shared" si="4"/>
         <v>1.07</v>
       </c>
       <c r="P8" s="17">
-        <f>ROUND(IMDIV(H8,J8),2)</f>
+        <f t="shared" si="5"/>
         <v>0.27</v>
       </c>
       <c r="Q8" s="17">
-        <f>ROUND(IMDIV(B8,F8),2)</f>
+        <f t="shared" si="6"/>
         <v>1.33</v>
       </c>
       <c r="R8" s="17">
-        <f>ROUND(IMDIV(C8,B8),4)*100</f>
+        <f t="shared" si="7"/>
         <v>83.33</v>
       </c>
       <c r="S8" s="17">
-        <f>ROUND(IMDIV(I8,J8),2)</f>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="T8" s="18" t="s">
@@ -1425,7 +1425,7 @@
         <v>25</v>
       </c>
       <c r="V8" s="1">
-        <f>((K8/2)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.327531007751938</v>
       </c>
     </row>
@@ -1461,39 +1461,39 @@
         <v>15</v>
       </c>
       <c r="K9" s="17">
-        <f>ROUND(IMDIV(B9,J9),2)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="L9" s="19">
-        <f>E9/J9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M9" s="19">
-        <f>D9/J9</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N9" s="17">
-        <f>ROUND(IMDIV(F9,J9),2)</f>
+        <f t="shared" si="3"/>
         <v>0.87</v>
       </c>
       <c r="O9" s="17">
-        <f>ROUND(IMDIV(G9,J9),2)</f>
+        <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
       <c r="P9" s="17">
-        <f>ROUND(IMDIV(H9,J9),2)</f>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="Q9" s="17">
-        <f>ROUND(IMDIV(B9,F9),2)</f>
+        <f t="shared" si="6"/>
         <v>0.23</v>
       </c>
       <c r="R9" s="17">
-        <f>ROUND(IMDIV(C9,B9),4)*100</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S9" s="17">
-        <f>ROUND(IMDIV(I9,J9),2)</f>
+        <f t="shared" si="8"/>
         <v>25.33</v>
       </c>
       <c r="T9" s="18" t="s">
@@ -1503,7 +1503,7 @@
         <v>25</v>
       </c>
       <c r="V9" s="1">
-        <f>((K9/2)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.35781395348837208</v>
       </c>
     </row>
@@ -1524,55 +1524,55 @@
         <v>1</v>
       </c>
       <c r="F10" s="20">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G10" s="20">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="H10" s="20">
         <v>3</v>
       </c>
       <c r="I10" s="20">
-        <v>960</v>
+        <v>1235</v>
       </c>
       <c r="J10" s="20">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K10" s="20">
-        <f>ROUND(IMDIV(B10,J10),2)</f>
-        <v>0.56000000000000005</v>
+        <f t="shared" si="0"/>
+        <v>0.36</v>
       </c>
       <c r="L10" s="21">
-        <f>E10/J10</f>
-        <v>6.25E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.04</v>
       </c>
       <c r="M10" s="21">
-        <f>D10/J10</f>
-        <v>0.125</v>
+        <f t="shared" si="2"/>
+        <v>0.08</v>
       </c>
       <c r="N10" s="20">
-        <f>ROUND(IMDIV(F10,J10),2)</f>
-        <v>0.5</v>
+        <f t="shared" si="3"/>
+        <v>0.68</v>
       </c>
       <c r="O10" s="20">
-        <f>ROUND(IMDIV(G10,J10),2)</f>
-        <v>0.25</v>
+        <f t="shared" si="4"/>
+        <v>2.36</v>
       </c>
       <c r="P10" s="20">
-        <f>ROUND(IMDIV(H10,J10),2)</f>
-        <v>0.19</v>
+        <f t="shared" si="5"/>
+        <v>0.12</v>
       </c>
       <c r="Q10" s="20">
-        <f>ROUND(IMDIV(B10,F10),2)</f>
-        <v>1.1299999999999999</v>
+        <f t="shared" si="6"/>
+        <v>0.53</v>
       </c>
       <c r="R10" s="20">
-        <f>ROUND(IMDIV(C10,B10),4)*100</f>
+        <f t="shared" si="7"/>
         <v>66.67</v>
       </c>
       <c r="S10" s="20">
-        <f>ROUND(IMDIV(I10,J10),2)</f>
-        <v>60</v>
+        <f t="shared" si="8"/>
+        <v>49.4</v>
       </c>
       <c r="T10" s="20" t="s">
         <v>43</v>
@@ -1581,8 +1581,8 @@
         <v>25</v>
       </c>
       <c r="V10" s="1">
-        <f>((K10/2)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
-        <v>1.1123197674418606</v>
+        <f t="shared" si="9"/>
+        <v>0.76376744186046497</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1602,7 +1602,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="20">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G11" s="20">
         <v>0</v>
@@ -1611,46 +1611,46 @@
         <v>4</v>
       </c>
       <c r="I11" s="20">
-        <v>1200</v>
+        <v>1299</v>
       </c>
       <c r="J11" s="20">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K11" s="20">
-        <f>ROUND(IMDIV(B11,J11),2)</f>
-        <v>0.63</v>
+        <f t="shared" si="0"/>
+        <v>0.4</v>
       </c>
       <c r="L11" s="21">
-        <f>E11/J11</f>
-        <v>6.25E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.04</v>
       </c>
       <c r="M11" s="21">
-        <f>D11/J11</f>
-        <v>0.125</v>
+        <f t="shared" si="2"/>
+        <v>0.08</v>
       </c>
       <c r="N11" s="20">
-        <f>ROUND(IMDIV(F11,J11),2)</f>
-        <v>0.69</v>
+        <f t="shared" si="3"/>
+        <v>0.76</v>
       </c>
       <c r="O11" s="20">
-        <f>ROUND(IMDIV(G11,J11),2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P11" s="20">
-        <f>ROUND(IMDIV(H11,J11),2)</f>
-        <v>0.25</v>
+        <f t="shared" si="5"/>
+        <v>0.16</v>
       </c>
       <c r="Q11" s="20">
-        <f>ROUND(IMDIV(B11,F11),2)</f>
-        <v>0.91</v>
+        <f t="shared" si="6"/>
+        <v>0.53</v>
       </c>
       <c r="R11" s="20">
-        <f>ROUND(IMDIV(C11,B11),4)*100</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S11" s="20">
-        <f>ROUND(IMDIV(I11,J11),2)</f>
-        <v>75</v>
+        <f t="shared" si="8"/>
+        <v>51.96</v>
       </c>
       <c r="T11" s="20" t="s">
         <v>43</v>
@@ -1659,8 +1659,8 @@
         <v>25</v>
       </c>
       <c r="V11" s="1">
-        <f>((K11/2)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
-        <v>1.0300872093023257</v>
+        <f t="shared" si="9"/>
+        <v>0.71767441860465109</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1695,39 +1695,39 @@
         <v>35</v>
       </c>
       <c r="K12" s="23">
-        <f>ROUND(IMDIV(B12,J12),2)</f>
+        <f t="shared" si="0"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="L12" s="24">
-        <f>E12/J12</f>
+        <f t="shared" si="1"/>
         <v>0.11428571428571428</v>
       </c>
       <c r="M12" s="24">
-        <f>D12/J12</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="N12" s="23">
-        <f>ROUND(IMDIV(F12,J12),2)</f>
+        <f t="shared" si="3"/>
         <v>0.69</v>
       </c>
       <c r="O12" s="23">
-        <f>ROUND(IMDIV(G12,J12),2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P12" s="23">
-        <f>ROUND(IMDIV(H12,J12),2)</f>
+        <f t="shared" si="5"/>
         <v>0.09</v>
       </c>
       <c r="Q12" s="23">
-        <f>ROUND(IMDIV(B12,F12),2)</f>
+        <f t="shared" si="6"/>
         <v>0.83</v>
       </c>
       <c r="R12" s="23">
-        <f>ROUND(IMDIV(C12,B12),4)*100</f>
+        <f t="shared" si="7"/>
         <v>85</v>
       </c>
       <c r="S12" s="23">
-        <f>ROUND(IMDIV(I12,J12),2)</f>
+        <f t="shared" si="8"/>
         <v>54</v>
       </c>
       <c r="T12" s="25" t="s">
@@ -1737,7 +1737,7 @@
         <v>25</v>
       </c>
       <c r="V12" s="1">
-        <f>((K12/2)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.92351993355481732</v>
       </c>
     </row>
@@ -1773,39 +1773,39 @@
         <v>35</v>
       </c>
       <c r="K13" s="23">
-        <f>ROUND(IMDIV(B13,J13),2)</f>
+        <f t="shared" si="0"/>
         <v>0.49</v>
       </c>
       <c r="L13" s="24">
-        <f>E13/J13</f>
+        <f t="shared" si="1"/>
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="M13" s="24">
-        <f>D13/J13</f>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="N13" s="23">
-        <f>ROUND(IMDIV(F13,J13),2)</f>
+        <f t="shared" si="3"/>
         <v>0.74</v>
       </c>
       <c r="O13" s="23">
-        <f>ROUND(IMDIV(G13,J13),2)</f>
+        <f t="shared" si="4"/>
         <v>1.37</v>
       </c>
       <c r="P13" s="23">
-        <f>ROUND(IMDIV(H13,J13),2)</f>
+        <f t="shared" si="5"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Q13" s="23">
-        <f>ROUND(IMDIV(B13,F13),2)</f>
+        <f t="shared" si="6"/>
         <v>0.65</v>
       </c>
       <c r="R13" s="23">
-        <f>ROUND(IMDIV(C13,B13),4)*100</f>
+        <f t="shared" si="7"/>
         <v>41.18</v>
       </c>
       <c r="S13" s="23">
-        <f>ROUND(IMDIV(I13,J13),2)</f>
+        <f t="shared" si="8"/>
         <v>69</v>
       </c>
       <c r="T13" s="25" t="s">
@@ -1815,7 +1815,7 @@
         <v>25</v>
       </c>
       <c r="V13" s="1">
-        <f>((K13/2)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.88757308970099669</v>
       </c>
     </row>
@@ -1851,39 +1851,39 @@
         <v>10</v>
       </c>
       <c r="K14" s="27">
-        <f>ROUND(IMDIV(B14,J14),2)</f>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="L14" s="28">
-        <f>E14/J14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M14" s="28">
-        <f>D14/J14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14" s="27">
-        <f>ROUND(IMDIV(F14,J14),2)</f>
+        <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
       <c r="O14" s="27">
-        <f>ROUND(IMDIV(G14,J14),2)</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="P14" s="27">
-        <f>ROUND(IMDIV(H14,J14),2)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q14" s="27">
-        <f>ROUND(IMDIV(B14,F14),2)</f>
+        <f t="shared" si="6"/>
         <v>0.33</v>
       </c>
       <c r="R14" s="27">
-        <f>ROUND(IMDIV(C14,B14),4)*100</f>
+        <f t="shared" si="7"/>
         <v>66.67</v>
       </c>
       <c r="S14" s="27">
-        <f>ROUND(IMDIV(I14,J14),2)</f>
+        <f t="shared" si="8"/>
         <v>55</v>
       </c>
       <c r="T14" s="27" t="s">
@@ -1893,7 +1893,7 @@
         <v>25</v>
       </c>
       <c r="V14" s="1">
-        <f>((K14/2)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.5058139534883721</v>
       </c>
     </row>
@@ -1929,39 +1929,39 @@
         <v>10</v>
       </c>
       <c r="K15" s="27">
-        <f>ROUND(IMDIV(B15,J15),2)</f>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="L15" s="28">
-        <f>E15/J15</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M15" s="28">
-        <f>D15/J15</f>
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
       <c r="N15" s="27">
-        <f>ROUND(IMDIV(F15,J15),2)</f>
+        <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
       <c r="O15" s="27">
-        <f>ROUND(IMDIV(G15,J15),2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P15" s="27">
-        <f>ROUND(IMDIV(H15,J15),2)</f>
+        <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
       <c r="Q15" s="27">
-        <f>ROUND(IMDIV(B15,F15),2)</f>
+        <f t="shared" si="6"/>
         <v>0.33</v>
       </c>
       <c r="R15" s="27">
-        <f>ROUND(IMDIV(C15,B15),4)*100</f>
+        <f t="shared" si="7"/>
         <v>33.33</v>
       </c>
       <c r="S15" s="27">
-        <f>ROUND(IMDIV(I15,J15),2)</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="T15" s="27" t="s">
@@ -1971,7 +1971,7 @@
         <v>25</v>
       </c>
       <c r="V15" s="1">
-        <f>((K15/2)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.46604651162790689</v>
       </c>
     </row>
@@ -1980,67 +1980,67 @@
         <v>38</v>
       </c>
       <c r="B16" s="29">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C16" s="29">
+        <v>14</v>
+      </c>
+      <c r="D16" s="29">
         <v>3</v>
       </c>
-      <c r="D16" s="29">
-        <v>0</v>
-      </c>
       <c r="E16" s="29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16" s="29">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G16" s="29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H16" s="29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" s="29">
-        <v>1216</v>
+        <v>2848</v>
       </c>
       <c r="J16" s="29">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K16" s="30">
-        <f>ROUND(IMDIV(B16,J16),2)</f>
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="L16" s="31">
+        <f t="shared" si="1"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="M16" s="31">
+        <f t="shared" si="2"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="N16" s="30">
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="L16" s="31">
-        <f>E16/J16</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="31">
-        <f>D16/J16</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="30">
-        <f>ROUND(IMDIV(F16,J16),2)</f>
-        <v>0.56000000000000005</v>
-      </c>
       <c r="O16" s="30">
-        <f>ROUND(IMDIV(G16,J16),2)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>0.75</v>
       </c>
       <c r="P16" s="30">
-        <f>ROUND(IMDIV(H16,J16),2)</f>
-        <v>0.25</v>
+        <f t="shared" si="5"/>
+        <v>0.19</v>
       </c>
       <c r="Q16" s="30">
-        <f>ROUND(IMDIV(B16,F16),2)</f>
-        <v>0.89</v>
+        <f t="shared" si="6"/>
+        <v>1.5</v>
       </c>
       <c r="R16" s="30">
-        <f>ROUND(IMDIV(C16,B16),4)*100</f>
-        <v>37.5</v>
+        <f t="shared" si="7"/>
+        <v>58.330000000000005</v>
       </c>
       <c r="S16" s="30">
-        <f>ROUND(IMDIV(I16,J16),2)</f>
-        <v>76</v>
+        <f t="shared" si="8"/>
+        <v>89</v>
       </c>
       <c r="T16" s="29" t="s">
         <v>43</v>
@@ -2049,8 +2049,8 @@
         <v>25</v>
       </c>
       <c r="V16" s="1">
-        <f>((K16/2)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
-        <v>1.0559883720930232</v>
+        <f t="shared" si="9"/>
+        <v>1.3406409883720931</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -2058,10 +2058,10 @@
         <v>39</v>
       </c>
       <c r="B17" s="29">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C17" s="29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="29">
         <v>3</v>
@@ -2070,55 +2070,55 @@
         <v>0</v>
       </c>
       <c r="F17" s="29">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G17" s="29">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="H17" s="29">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I17" s="29">
-        <v>1136</v>
+        <v>2096</v>
       </c>
       <c r="J17" s="29">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K17" s="30">
-        <f>ROUND(IMDIV(B17,J17),2)</f>
-        <v>0.69</v>
+        <f t="shared" si="0"/>
+        <v>0.59</v>
       </c>
       <c r="L17" s="31">
-        <f>E17/J17</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M17" s="31">
-        <f>D17/J17</f>
-        <v>0.1875</v>
+        <f t="shared" si="2"/>
+        <v>9.375E-2</v>
       </c>
       <c r="N17" s="30">
-        <f>ROUND(IMDIV(F17,J17),2)</f>
-        <v>0.63</v>
+        <f t="shared" si="3"/>
+        <v>0.66</v>
       </c>
       <c r="O17" s="30">
-        <f>ROUND(IMDIV(G17,J17),2)</f>
-        <v>3.06</v>
+        <f t="shared" si="4"/>
+        <v>2.41</v>
       </c>
       <c r="P17" s="30">
-        <f>ROUND(IMDIV(H17,J17),2)</f>
-        <v>0.13</v>
+        <f t="shared" si="5"/>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Q17" s="30">
-        <f>ROUND(IMDIV(B17,F17),2)</f>
-        <v>1.1000000000000001</v>
+        <f t="shared" si="6"/>
+        <v>0.9</v>
       </c>
       <c r="R17" s="30">
-        <f>ROUND(IMDIV(C17,B17),4)*100</f>
-        <v>27.27</v>
+        <f t="shared" si="7"/>
+        <v>21.05</v>
       </c>
       <c r="S17" s="30">
-        <f>ROUND(IMDIV(I17,J17),2)</f>
-        <v>71</v>
+        <f t="shared" si="8"/>
+        <v>65.5</v>
       </c>
       <c r="T17" s="29" t="s">
         <v>43</v>
@@ -2127,8 +2127,8 @@
         <v>25</v>
       </c>
       <c r="V17" s="1">
-        <f>((K17/2)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
-        <v>1.0986075581395349</v>
+        <f t="shared" si="9"/>
+        <v>0.97708866279069762</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -2163,39 +2163,39 @@
         <v>14</v>
       </c>
       <c r="K18" s="33">
-        <f>ROUND(IMDIV(B18,J18),2)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L18" s="34">
-        <f>E18/J18</f>
+        <f t="shared" si="1"/>
         <v>7.1428571428571425E-2</v>
       </c>
       <c r="M18" s="34">
-        <f>D18/J18</f>
+        <f t="shared" si="2"/>
         <v>0.21428571428571427</v>
       </c>
       <c r="N18" s="33">
-        <f>ROUND(IMDIV(F18,J18),2)</f>
+        <f t="shared" si="3"/>
         <v>0.36</v>
       </c>
       <c r="O18" s="33">
-        <f>ROUND(IMDIV(G18,J18),2)</f>
+        <f t="shared" si="4"/>
         <v>10.71</v>
       </c>
       <c r="P18" s="33">
-        <f>ROUND(IMDIV(H18,J18),2)</f>
+        <f t="shared" si="5"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q18" s="33">
-        <f>ROUND(IMDIV(B18,F18),2)</f>
+        <f t="shared" si="6"/>
         <v>2.8</v>
       </c>
       <c r="R18" s="33">
-        <f>ROUND(IMDIV(C18,B18),4)*100</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S18" s="33">
-        <f>ROUND(IMDIV(I18,J18),2)</f>
+        <f t="shared" si="8"/>
         <v>118</v>
       </c>
       <c r="T18" s="32" t="s">
@@ -2205,7 +2205,7 @@
         <v>25</v>
       </c>
       <c r="V18" s="1">
-        <f>((K18/2)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.7601943521594685</v>
       </c>
     </row>
@@ -2241,39 +2241,39 @@
         <v>14</v>
       </c>
       <c r="K19" s="33">
-        <f>ROUND(IMDIV(B19,J19),2)</f>
+        <f t="shared" si="0"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="L19" s="34">
-        <f>E19/J19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M19" s="34">
-        <f>D19/J19</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N19" s="33">
-        <f>ROUND(IMDIV(F19,J19),2)</f>
+        <f t="shared" si="3"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="O19" s="33">
-        <f>ROUND(IMDIV(G19,J19),2)</f>
+        <f t="shared" si="4"/>
         <v>3.86</v>
       </c>
       <c r="P19" s="33">
-        <f>ROUND(IMDIV(H19,J19),2)</f>
+        <f t="shared" si="5"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="Q19" s="33">
-        <f>ROUND(IMDIV(B19,F19),2)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="R19" s="33">
-        <f>ROUND(IMDIV(C19,B19),4)*100</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S19" s="33">
-        <f>ROUND(IMDIV(I19,J19),2)</f>
+        <f t="shared" si="8"/>
         <v>57</v>
       </c>
       <c r="T19" s="32" t="s">
@@ -2283,7 +2283,7 @@
         <v>25</v>
       </c>
       <c r="V19" s="1">
-        <f>((K19/2)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.9871162790697674</v>
       </c>
     </row>
@@ -2292,67 +2292,67 @@
         <v>42</v>
       </c>
       <c r="B20" s="35">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C20" s="35">
+        <v>9</v>
+      </c>
+      <c r="D20" s="35">
+        <v>6</v>
+      </c>
+      <c r="E20" s="35">
         <v>1</v>
       </c>
-      <c r="D20" s="35">
-        <v>3</v>
-      </c>
-      <c r="E20" s="35">
-        <v>0</v>
-      </c>
       <c r="F20" s="35">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G20" s="35">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H20" s="35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I20" s="35">
-        <v>1000</v>
+        <v>2168</v>
       </c>
       <c r="J20" s="35">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K20" s="36">
-        <f>ROUND(IMDIV(B20,J20),2)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.77</v>
       </c>
       <c r="L20" s="37">
-        <f>E20/J20</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3.8461538461538464E-2</v>
       </c>
       <c r="M20" s="37">
-        <f>D20/J20</f>
-        <v>0.3</v>
+        <f t="shared" si="2"/>
+        <v>0.23076923076923078</v>
       </c>
       <c r="N20" s="36">
-        <f>ROUND(IMDIV(F20,J20),2)</f>
-        <v>0.3</v>
+        <f t="shared" si="3"/>
+        <v>0.54</v>
       </c>
       <c r="O20" s="36">
-        <f>ROUND(IMDIV(G20,J20),2)</f>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0.81</v>
       </c>
       <c r="P20" s="36">
-        <f>ROUND(IMDIV(H20,J20),2)</f>
-        <v>0.4</v>
+        <f t="shared" si="5"/>
+        <v>0.27</v>
       </c>
       <c r="Q20" s="36">
-        <f>ROUND(IMDIV(B20,F20),2)</f>
-        <v>3.33</v>
+        <f t="shared" si="6"/>
+        <v>1.43</v>
       </c>
       <c r="R20" s="36">
-        <f>ROUND(IMDIV(C20,B20),4)*100</f>
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>45</v>
       </c>
       <c r="S20" s="36">
-        <f>ROUND(IMDIV(I20,J20),2)</f>
-        <v>100</v>
+        <f t="shared" si="8"/>
+        <v>83.38</v>
       </c>
       <c r="T20" s="35" t="s">
         <v>43</v>
@@ -2361,8 +2361,8 @@
         <v>25</v>
       </c>
       <c r="V20" s="1">
-        <f>((K20/2)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
-        <v>1.7601162790697673</v>
+        <f t="shared" si="9"/>
+        <v>1.3116985688729874</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -2370,67 +2370,67 @@
         <v>27</v>
       </c>
       <c r="B21" s="35">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C21" s="35">
+        <v>7</v>
+      </c>
+      <c r="D21" s="35">
+        <v>4</v>
+      </c>
+      <c r="E21" s="35">
         <v>2</v>
       </c>
-      <c r="D21" s="35">
-        <v>2</v>
-      </c>
-      <c r="E21" s="35">
+      <c r="F21" s="35">
+        <v>16</v>
+      </c>
+      <c r="G21" s="35">
+        <v>30</v>
+      </c>
+      <c r="H21" s="35">
         <v>1</v>
       </c>
-      <c r="F21" s="35">
-        <v>3</v>
-      </c>
-      <c r="G21" s="35">
-        <v>0</v>
-      </c>
-      <c r="H21" s="35">
-        <v>0</v>
-      </c>
       <c r="I21" s="35">
-        <v>830</v>
+        <v>1758</v>
       </c>
       <c r="J21" s="35">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K21" s="36">
-        <f>ROUND(IMDIV(B21,J21),2)</f>
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>0.62</v>
       </c>
       <c r="L21" s="37">
-        <f>E21/J21</f>
-        <v>0.1</v>
+        <f t="shared" si="1"/>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="M21" s="37">
-        <f>D21/J21</f>
-        <v>0.2</v>
+        <f t="shared" si="2"/>
+        <v>0.15384615384615385</v>
       </c>
       <c r="N21" s="36">
-        <f>ROUND(IMDIV(F21,J21),2)</f>
-        <v>0.3</v>
+        <f t="shared" si="3"/>
+        <v>0.62</v>
       </c>
       <c r="O21" s="36">
-        <f>ROUND(IMDIV(G21,J21),2)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P21" s="36">
-        <f>ROUND(IMDIV(H21,J21),2)</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>0.04</v>
       </c>
       <c r="Q21" s="36">
-        <f>ROUND(IMDIV(B21,F21),2)</f>
-        <v>2.67</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="R21" s="36">
-        <f>ROUND(IMDIV(C21,B21),4)*100</f>
-        <v>25</v>
+        <f t="shared" si="7"/>
+        <v>43.75</v>
       </c>
       <c r="S21" s="36">
-        <f>ROUND(IMDIV(I21,J21),2)</f>
-        <v>83</v>
+        <f t="shared" si="8"/>
+        <v>67.62</v>
       </c>
       <c r="T21" s="35" t="s">
         <v>43</v>
@@ -2439,8 +2439,8 @@
         <v>25</v>
       </c>
       <c r="V21" s="1">
-        <f>((K21/2)+(M21/4)+(L21/5)-(N21)+(S21/215)+(P21/20))+1</f>
-        <v>1.556046511627907</v>
+        <f t="shared" si="9"/>
+        <v>1.0603577817531307</v>
       </c>
     </row>
   </sheetData>

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF4EC13-A652-4E53-A25B-182EBBFD3A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92E9A1E-64AE-40AB-A362-F487D676AB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="28800" windowHeight="15345" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="24225" windowHeight="12660" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1044,35 +1044,35 @@
         <v>32</v>
       </c>
       <c r="B4" s="10">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C4" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" s="11">
         <v>0</v>
       </c>
       <c r="F4" s="11">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G4" s="11">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="H4" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="11">
-        <v>1440</v>
+        <v>2402</v>
       </c>
       <c r="J4" s="11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K4" s="10">
         <f t="shared" si="0"/>
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="L4" s="12">
         <f t="shared" si="1"/>
@@ -1080,31 +1080,31 @@
       </c>
       <c r="M4" s="12">
         <f t="shared" si="2"/>
-        <v>0.13333333333333333</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" si="4"/>
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="P4" s="10">
         <f t="shared" si="5"/>
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="Q4" s="10">
         <f t="shared" si="6"/>
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="R4" s="10">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>85.79</v>
       </c>
       <c r="T4" s="11" t="s">
         <v>43</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="V4" s="1">
         <f t="shared" si="9"/>
-        <v>1.5813449612403101</v>
+        <v>1.3712375415282392</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1122,67 +1122,67 @@
         <v>33</v>
       </c>
       <c r="B5" s="10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D5" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="11">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5" s="11">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="H5" s="11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5" s="11">
-        <v>1020</v>
+        <v>2203</v>
       </c>
       <c r="J5" s="11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K5" s="10">
         <f t="shared" si="0"/>
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="N5" s="10">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="10">
         <f t="shared" si="4"/>
-        <v>1.93</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="P5" s="10">
         <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.21</v>
       </c>
       <c r="Q5" s="10">
         <f t="shared" si="6"/>
-        <v>0.89</v>
+        <v>1.43</v>
       </c>
       <c r="R5" s="10">
         <f t="shared" si="7"/>
-        <v>87.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="8"/>
-        <v>68</v>
+        <v>78.680000000000007</v>
       </c>
       <c r="T5" s="11" t="s">
         <v>43</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="V5" s="1">
         <f t="shared" si="9"/>
-        <v>0.98477906976744189</v>
+        <v>1.2814534883720929</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1356,67 +1356,67 @@
         <v>34</v>
       </c>
       <c r="B8" s="18">
+        <v>22</v>
+      </c>
+      <c r="C8" s="18">
+        <v>17</v>
+      </c>
+      <c r="D8" s="17">
+        <v>7</v>
+      </c>
+      <c r="E8" s="18">
+        <v>4</v>
+      </c>
+      <c r="F8" s="18">
+        <v>19</v>
+      </c>
+      <c r="G8" s="18">
+        <v>28</v>
+      </c>
+      <c r="H8" s="18">
         <v>12</v>
       </c>
-      <c r="C8" s="18">
-        <v>10</v>
-      </c>
-      <c r="D8" s="17">
-        <v>5</v>
-      </c>
-      <c r="E8" s="18">
-        <v>3</v>
-      </c>
-      <c r="F8" s="18">
-        <v>9</v>
-      </c>
-      <c r="G8" s="18">
-        <v>16</v>
-      </c>
-      <c r="H8" s="18">
-        <v>4</v>
-      </c>
       <c r="I8" s="18">
-        <v>1260</v>
+        <v>2524</v>
       </c>
       <c r="J8" s="18">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K8" s="17">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="L8" s="19">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="M8" s="19">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.22580645161290322</v>
       </c>
       <c r="N8" s="17">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="O8" s="17">
         <f t="shared" si="4"/>
-        <v>1.07</v>
+        <v>0.9</v>
       </c>
       <c r="P8" s="17">
         <f t="shared" si="5"/>
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="Q8" s="17">
         <f t="shared" si="6"/>
-        <v>1.33</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="R8" s="17">
         <f t="shared" si="7"/>
-        <v>83.33</v>
+        <v>77.27000000000001</v>
       </c>
       <c r="S8" s="17">
         <f t="shared" si="8"/>
-        <v>84</v>
+        <v>81.42</v>
       </c>
       <c r="T8" s="18" t="s">
         <v>43</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="V8" s="1">
         <f t="shared" si="9"/>
-        <v>1.327531007751938</v>
+        <v>1.2254557389347336</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1434,35 +1434,35 @@
         <v>22</v>
       </c>
       <c r="B9" s="17">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C9" s="17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="18">
         <v>0</v>
       </c>
       <c r="F9" s="18">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G9" s="18">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="H9" s="18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" s="18">
-        <v>380</v>
+        <v>1292</v>
       </c>
       <c r="J9" s="18">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K9" s="17">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="L9" s="19">
         <f t="shared" si="1"/>
@@ -1470,31 +1470,31 @@
       </c>
       <c r="M9" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.4516129032258063E-2</v>
       </c>
       <c r="N9" s="17">
         <f t="shared" si="3"/>
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="O9" s="17">
         <f t="shared" si="4"/>
-        <v>1.8</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="P9" s="17">
         <f t="shared" si="5"/>
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q9" s="17">
         <f t="shared" si="6"/>
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="R9" s="17">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>41.67</v>
       </c>
       <c r="S9" s="17">
         <f t="shared" si="8"/>
-        <v>25.33</v>
+        <v>41.68</v>
       </c>
       <c r="T9" s="18" t="s">
         <v>43</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V9" s="1">
         <f t="shared" si="9"/>
-        <v>0.35781395348837208</v>
+        <v>0.67448949737434361</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1824,35 +1824,35 @@
         <v>37</v>
       </c>
       <c r="B14" s="26">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C14" s="26">
+        <v>5</v>
+      </c>
+      <c r="D14" s="26">
         <v>2</v>
-      </c>
-      <c r="D14" s="26">
-        <v>0</v>
       </c>
       <c r="E14" s="26">
         <v>0</v>
       </c>
       <c r="F14" s="26">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G14" s="26">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="H14" s="26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" s="26">
-        <v>550</v>
+        <v>1668</v>
       </c>
       <c r="J14" s="26">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K14" s="27">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="L14" s="28">
         <f t="shared" si="1"/>
@@ -1860,31 +1860,31 @@
       </c>
       <c r="M14" s="28">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.6956521739130432E-2</v>
       </c>
       <c r="N14" s="27">
         <f t="shared" si="3"/>
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="O14" s="27">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>4.87</v>
       </c>
       <c r="P14" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="Q14" s="27">
         <f t="shared" si="6"/>
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="R14" s="27">
         <f t="shared" si="7"/>
-        <v>66.67</v>
+        <v>55.559999999999995</v>
       </c>
       <c r="S14" s="27">
         <f t="shared" si="8"/>
-        <v>55</v>
+        <v>72.52</v>
       </c>
       <c r="T14" s="27" t="s">
         <v>43</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="V14" s="1">
         <f t="shared" si="9"/>
-        <v>0.5058139534883721</v>
+        <v>0.78054145601617786</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1902,67 +1902,67 @@
         <v>26</v>
       </c>
       <c r="B15" s="26">
+        <v>9</v>
+      </c>
+      <c r="C15" s="26">
+        <v>4</v>
+      </c>
+      <c r="D15" s="26">
         <v>3</v>
       </c>
-      <c r="C15" s="26">
+      <c r="E15" s="26">
         <v>1</v>
       </c>
-      <c r="D15" s="26">
-        <v>1</v>
-      </c>
-      <c r="E15" s="26">
-        <v>0</v>
-      </c>
       <c r="F15" s="26">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G15" s="27">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H15" s="26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="26">
-        <v>400</v>
+        <v>946</v>
       </c>
       <c r="J15" s="26">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K15" s="27">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="L15" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="M15" s="28">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.13043478260869565</v>
       </c>
       <c r="N15" s="27">
         <f t="shared" si="3"/>
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="O15" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="P15" s="27">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="Q15" s="27">
         <f t="shared" si="6"/>
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R15" s="27">
         <f t="shared" si="7"/>
-        <v>33.33</v>
+        <v>44.440000000000005</v>
       </c>
       <c r="S15" s="27">
         <f t="shared" si="8"/>
-        <v>40</v>
+        <v>41.13</v>
       </c>
       <c r="T15" s="27" t="s">
         <v>43</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="V15" s="1">
         <f t="shared" si="9"/>
-        <v>0.46604651162790689</v>
+        <v>0.60410667340748248</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -2136,67 +2136,67 @@
         <v>40</v>
       </c>
       <c r="B18" s="32">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C18" s="32">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D18" s="32">
+        <v>8</v>
+      </c>
+      <c r="E18" s="32">
         <v>3</v>
       </c>
-      <c r="E18" s="32">
-        <v>1</v>
-      </c>
       <c r="F18" s="32">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G18" s="32">
-        <v>150</v>
+        <v>241</v>
       </c>
       <c r="H18" s="32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I18" s="32">
-        <v>1652</v>
+        <v>3252</v>
       </c>
       <c r="J18" s="32">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K18" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="L18" s="34">
         <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <v>0.1</v>
       </c>
       <c r="M18" s="34">
         <f t="shared" si="2"/>
-        <v>0.21428571428571427</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="N18" s="33">
         <f t="shared" si="3"/>
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="O18" s="33">
         <f t="shared" si="4"/>
-        <v>10.71</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="P18" s="33">
         <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" s="33">
         <f t="shared" si="6"/>
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="R18" s="33">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="S18" s="33">
         <f t="shared" si="8"/>
-        <v>118</v>
+        <v>108.4</v>
       </c>
       <c r="T18" s="32" t="s">
         <v>43</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="V18" s="1">
         <f t="shared" si="9"/>
-        <v>1.7601943521594685</v>
+        <v>1.6358527131782947</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -2214,35 +2214,35 @@
         <v>41</v>
       </c>
       <c r="B19" s="32">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C19" s="32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="32">
         <v>0</v>
       </c>
       <c r="F19" s="32">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G19" s="32">
         <v>54</v>
       </c>
       <c r="H19" s="32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19" s="32">
-        <v>798</v>
+        <v>1390</v>
       </c>
       <c r="J19" s="32">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K19" s="33">
         <f t="shared" si="0"/>
-        <v>0.56999999999999995</v>
+        <v>0.47</v>
       </c>
       <c r="L19" s="34">
         <f t="shared" si="1"/>
@@ -2250,31 +2250,31 @@
       </c>
       <c r="M19" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="N19" s="33">
         <f t="shared" si="3"/>
-        <v>0.56999999999999995</v>
+        <v>0.63</v>
       </c>
       <c r="O19" s="33">
         <f t="shared" si="4"/>
-        <v>3.86</v>
+        <v>1.8</v>
       </c>
       <c r="P19" s="33">
         <f t="shared" si="5"/>
-        <v>0.14000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="33">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="R19" s="33">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="S19" s="33">
         <f t="shared" si="8"/>
-        <v>57</v>
+        <v>46.33</v>
       </c>
       <c r="T19" s="32" t="s">
         <v>43</v>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="V19" s="1">
         <f t="shared" si="9"/>
-        <v>0.9871162790697674</v>
+        <v>0.83882170542635648</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92E9A1E-64AE-40AB-A362-F487D676AB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BC67EC-B548-43BF-B6FA-179D37890692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="24225" windowHeight="12660" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="3330" yWindow="4110" windowWidth="28800" windowHeight="15285" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -888,67 +888,67 @@
         <v>29</v>
       </c>
       <c r="B2" s="7">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C2" s="7">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E2" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G2" s="7">
-        <v>320</v>
+        <v>435</v>
       </c>
       <c r="H2" s="7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I2" s="7">
-        <v>3150</v>
+        <v>4686</v>
       </c>
       <c r="J2" s="7">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K2" s="7">
-        <f t="shared" ref="K2:K21" si="0">ROUND(IMDIV(B2,J2),2)</f>
-        <v>0.97</v>
+        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <v>1</v>
       </c>
       <c r="L2" s="8">
-        <f t="shared" ref="L2:L21" si="1">E2/J2</f>
-        <v>6.25E-2</v>
+        <f>E2/J2</f>
+        <v>6.8181818181818177E-2</v>
       </c>
       <c r="M2" s="8">
-        <f t="shared" ref="M2:M21" si="2">D2/J2</f>
-        <v>0.21875</v>
+        <f>D2/J2</f>
+        <v>0.27272727272727271</v>
       </c>
       <c r="N2" s="7">
-        <f t="shared" ref="N2:N21" si="3">ROUND(IMDIV(F2,J2),2)</f>
-        <v>0.44</v>
+        <f>ROUND(IMDIV(F2,J2),2)</f>
+        <v>0.39</v>
       </c>
       <c r="O2" s="7">
-        <f t="shared" ref="O2:O21" si="4">ROUND(IMDIV(G2,J2),2)</f>
-        <v>10</v>
+        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <v>9.89</v>
       </c>
       <c r="P2" s="7">
-        <f t="shared" ref="P2:P21" si="5">ROUND(IMDIV(H2,J2),2)</f>
-        <v>0.38</v>
+        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <v>0.39</v>
       </c>
       <c r="Q2" s="7">
-        <f t="shared" ref="Q2:Q21" si="6">ROUND(IMDIV(B2,F2),2)</f>
-        <v>2.21</v>
+        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <v>2.59</v>
       </c>
       <c r="R2" s="7">
-        <f t="shared" ref="R2:R21" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>67.739999999999995</v>
+        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>65.91</v>
       </c>
       <c r="S2" s="7">
-        <f t="shared" ref="S2:S21" si="8">ROUND(IMDIV(I2,J2),2)</f>
-        <v>98.44</v>
+        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <v>106.5</v>
       </c>
       <c r="T2" s="9" t="s">
         <v>43</v>
@@ -957,232 +957,232 @@
         <v>25</v>
       </c>
       <c r="V2" s="1">
-        <f t="shared" ref="V2:V21" si="9">((K2/2)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>1.589047965116279</v>
+        <f>((K2/2)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.706667019027484</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="7">
-        <v>16</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="A3" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="13">
+        <v>29</v>
+      </c>
+      <c r="C3" s="13">
         <v>9</v>
       </c>
-      <c r="D3" s="7">
-        <v>2</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>17</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="D3" s="13">
+        <v>8</v>
+      </c>
+      <c r="E3" s="13">
         <v>1</v>
       </c>
-      <c r="H3" s="7">
-        <v>2</v>
-      </c>
-      <c r="I3" s="7">
-        <v>1739</v>
-      </c>
-      <c r="J3" s="7">
+      <c r="F3" s="13">
+        <v>12</v>
+      </c>
+      <c r="G3" s="13">
+        <v>155</v>
+      </c>
+      <c r="H3" s="13">
+        <v>4</v>
+      </c>
+      <c r="I3" s="13">
+        <v>3475</v>
+      </c>
+      <c r="J3" s="13">
         <v>32</v>
       </c>
-      <c r="K3" s="7">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="L3" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
-        <f t="shared" si="2"/>
-        <v>6.25E-2</v>
-      </c>
-      <c r="N3" s="7">
-        <f t="shared" si="3"/>
-        <v>0.53</v>
-      </c>
-      <c r="O3" s="7">
-        <f t="shared" si="4"/>
-        <v>0.03</v>
-      </c>
-      <c r="P3" s="7">
-        <f t="shared" si="5"/>
-        <v>0.06</v>
-      </c>
-      <c r="Q3" s="7">
-        <f t="shared" si="6"/>
-        <v>0.94</v>
-      </c>
-      <c r="R3" s="7">
-        <f t="shared" si="7"/>
-        <v>56.25</v>
-      </c>
-      <c r="S3" s="7">
-        <f t="shared" si="8"/>
-        <v>54.34</v>
-      </c>
-      <c r="T3" s="9" t="s">
+      <c r="K3" s="13">
+        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <v>0.91</v>
+      </c>
+      <c r="L3" s="14">
+        <f>E3/J3</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="M3" s="14">
+        <f>D3/J3</f>
+        <v>0.25</v>
+      </c>
+      <c r="N3" s="13">
+        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <v>0.38</v>
+      </c>
+      <c r="O3" s="13">
+        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <v>4.84</v>
+      </c>
+      <c r="P3" s="13">
+        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q3" s="13">
+        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <v>2.42</v>
+      </c>
+      <c r="R3" s="13">
+        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <v>31.03</v>
+      </c>
+      <c r="S3" s="13">
+        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <v>108.59</v>
+      </c>
+      <c r="T3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="16" t="s">
         <v>25</v>
       </c>
       <c r="V3" s="1">
-        <f t="shared" si="9"/>
-        <v>0.99136918604651159</v>
+        <f>((K3/2)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <v>1.6553197674418605</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="10">
-        <v>21</v>
-      </c>
-      <c r="C4" s="10">
-        <v>9</v>
-      </c>
-      <c r="D4" s="10">
-        <v>4</v>
-      </c>
-      <c r="E4" s="11">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11">
+      <c r="A4" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="32">
+        <v>28</v>
+      </c>
+      <c r="C4" s="32">
+        <v>16</v>
+      </c>
+      <c r="D4" s="32">
+        <v>8</v>
+      </c>
+      <c r="E4" s="32">
+        <v>3</v>
+      </c>
+      <c r="F4" s="32">
         <v>13</v>
       </c>
-      <c r="G4" s="11">
-        <v>108</v>
-      </c>
-      <c r="H4" s="11">
-        <v>12</v>
-      </c>
-      <c r="I4" s="11">
-        <v>2402</v>
-      </c>
-      <c r="J4" s="11">
-        <v>28</v>
-      </c>
-      <c r="K4" s="10">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="L4" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="12">
-        <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="N4" s="10">
-        <f t="shared" si="3"/>
-        <v>0.46</v>
-      </c>
-      <c r="O4" s="10">
-        <f t="shared" si="4"/>
-        <v>3.86</v>
-      </c>
-      <c r="P4" s="10">
-        <f t="shared" si="5"/>
+      <c r="G4" s="32">
+        <v>241</v>
+      </c>
+      <c r="H4" s="32">
+        <v>6</v>
+      </c>
+      <c r="I4" s="32">
+        <v>3252</v>
+      </c>
+      <c r="J4" s="32">
+        <v>30</v>
+      </c>
+      <c r="K4" s="33">
+        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <v>0.93</v>
+      </c>
+      <c r="L4" s="34">
+        <f>E4/J4</f>
+        <v>0.1</v>
+      </c>
+      <c r="M4" s="34">
+        <f>D4/J4</f>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="N4" s="33">
+        <f>ROUND(IMDIV(F4,J4),2)</f>
         <v>0.43</v>
       </c>
-      <c r="Q4" s="10">
-        <f t="shared" si="6"/>
-        <v>1.62</v>
-      </c>
-      <c r="R4" s="10">
-        <f t="shared" si="7"/>
-        <v>42.86</v>
-      </c>
-      <c r="S4" s="10">
-        <f t="shared" si="8"/>
-        <v>85.79</v>
-      </c>
-      <c r="T4" s="11" t="s">
+      <c r="O4" s="33">
+        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="P4" s="33">
+        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="33">
+        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <v>2.15</v>
+      </c>
+      <c r="R4" s="33">
+        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <v>57.14</v>
+      </c>
+      <c r="S4" s="33">
+        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <v>108.4</v>
+      </c>
+      <c r="T4" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="11" t="s">
+      <c r="U4" s="32" t="s">
         <v>25</v>
       </c>
       <c r="V4" s="1">
-        <f t="shared" si="9"/>
-        <v>1.3712375415282392</v>
+        <f>((K4/2)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <v>1.6358527131782947</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="10">
         <v>4</v>
       </c>
       <c r="E5" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="11">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H5" s="11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I5" s="11">
-        <v>2203</v>
+        <v>2402</v>
       </c>
       <c r="J5" s="11">
         <v>28</v>
       </c>
       <c r="K5" s="10">
-        <f t="shared" si="0"/>
-        <v>0.71</v>
+        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <v>0.75</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <f>E5/J5</f>
+        <v>0</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" si="2"/>
+        <f>D5/J5</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="N5" s="10">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
+        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <v>0.46</v>
       </c>
       <c r="O5" s="10">
-        <f t="shared" si="4"/>
-        <v>4.6100000000000003</v>
+        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <v>3.86</v>
       </c>
       <c r="P5" s="10">
-        <f t="shared" si="5"/>
-        <v>0.21</v>
+        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <v>0.43</v>
       </c>
       <c r="Q5" s="10">
-        <f t="shared" si="6"/>
-        <v>1.43</v>
+        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <v>1.62</v>
       </c>
       <c r="R5" s="10">
-        <f t="shared" si="7"/>
-        <v>55.000000000000007</v>
+        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <v>42.86</v>
       </c>
       <c r="S5" s="10">
-        <f t="shared" si="8"/>
-        <v>78.680000000000007</v>
+        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <v>85.79</v>
       </c>
       <c r="T5" s="11" t="s">
         <v>43</v>
@@ -1191,164 +1191,164 @@
         <v>25</v>
       </c>
       <c r="V5" s="1">
-        <f t="shared" si="9"/>
-        <v>1.2814534883720929</v>
+        <f>((K5/2)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <v>1.3712375415282392</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="13">
-        <v>18</v>
-      </c>
-      <c r="C6" s="13">
-        <v>8</v>
-      </c>
-      <c r="D6" s="13">
-        <v>7</v>
-      </c>
-      <c r="E6" s="13">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13">
-        <v>9</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
-        <v>4</v>
-      </c>
-      <c r="I6" s="13">
-        <v>2299</v>
-      </c>
-      <c r="J6" s="13">
-        <v>20</v>
-      </c>
-      <c r="K6" s="13">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-      <c r="L6" s="14">
-        <f t="shared" si="1"/>
-        <v>0.05</v>
-      </c>
-      <c r="M6" s="14">
-        <f t="shared" si="2"/>
-        <v>0.35</v>
-      </c>
-      <c r="N6" s="13">
-        <f t="shared" si="3"/>
-        <v>0.45</v>
-      </c>
-      <c r="O6" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
-        <f t="shared" si="5"/>
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="13">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="R6" s="13">
-        <f t="shared" si="7"/>
-        <v>44.440000000000005</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="8"/>
-        <v>114.95</v>
-      </c>
-      <c r="T6" s="15" t="s">
+      <c r="A6" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="29">
+        <v>24</v>
+      </c>
+      <c r="C6" s="29">
+        <v>14</v>
+      </c>
+      <c r="D6" s="29">
+        <v>3</v>
+      </c>
+      <c r="E6" s="29">
+        <v>3</v>
+      </c>
+      <c r="F6" s="29">
+        <v>16</v>
+      </c>
+      <c r="G6" s="29">
+        <v>24</v>
+      </c>
+      <c r="H6" s="29">
+        <v>6</v>
+      </c>
+      <c r="I6" s="29">
+        <v>2848</v>
+      </c>
+      <c r="J6" s="29">
+        <v>32</v>
+      </c>
+      <c r="K6" s="30">
+        <f>ROUND(IMDIV(B6,J6),2)</f>
+        <v>0.75</v>
+      </c>
+      <c r="L6" s="31">
+        <f>E6/J6</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="M6" s="31">
+        <f>D6/J6</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="N6" s="30">
+        <f>ROUND(IMDIV(F6,J6),2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="O6" s="30">
+        <f>ROUND(IMDIV(G6,J6),2)</f>
+        <v>0.75</v>
+      </c>
+      <c r="P6" s="30">
+        <f>ROUND(IMDIV(H6,J6),2)</f>
+        <v>0.19</v>
+      </c>
+      <c r="Q6" s="30">
+        <f>ROUND(IMDIV(B6,F6),2)</f>
+        <v>1.5</v>
+      </c>
+      <c r="R6" s="30">
+        <f>ROUND(IMDIV(C6,B6),4)*100</f>
+        <v>58.330000000000005</v>
+      </c>
+      <c r="S6" s="30">
+        <f>ROUND(IMDIV(I6,J6),2)</f>
+        <v>89</v>
+      </c>
+      <c r="T6" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="16" t="s">
+      <c r="U6" s="29" t="s">
         <v>25</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" si="9"/>
-        <v>1.6421511627906977</v>
+        <f>((K6/2)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
+        <v>1.3406409883720931</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="13">
-        <v>7</v>
-      </c>
-      <c r="C7" s="13">
-        <v>3</v>
-      </c>
-      <c r="D7" s="13">
-        <v>1</v>
-      </c>
-      <c r="E7" s="13">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="A7" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="10">
+        <v>20</v>
+      </c>
+      <c r="C7" s="10">
         <v>11</v>
       </c>
-      <c r="G7" s="13">
-        <v>78</v>
-      </c>
-      <c r="H7" s="13">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13">
-        <v>986</v>
-      </c>
-      <c r="J7" s="13">
-        <v>20</v>
-      </c>
-      <c r="K7" s="13">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-      <c r="L7" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="14">
-        <f t="shared" si="2"/>
-        <v>0.05</v>
-      </c>
-      <c r="N7" s="13">
-        <f t="shared" si="3"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O7" s="13">
-        <f t="shared" si="4"/>
-        <v>3.9</v>
-      </c>
-      <c r="P7" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <f t="shared" si="6"/>
-        <v>0.64</v>
-      </c>
-      <c r="R7" s="13">
-        <f t="shared" si="7"/>
-        <v>42.86</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="8"/>
-        <v>49.3</v>
-      </c>
-      <c r="T7" s="15" t="s">
+      <c r="D7" s="10">
+        <v>4</v>
+      </c>
+      <c r="E7" s="11">
+        <v>2</v>
+      </c>
+      <c r="F7" s="11">
+        <v>14</v>
+      </c>
+      <c r="G7" s="11">
+        <v>129</v>
+      </c>
+      <c r="H7" s="11">
+        <v>6</v>
+      </c>
+      <c r="I7" s="11">
+        <v>2203</v>
+      </c>
+      <c r="J7" s="11">
+        <v>28</v>
+      </c>
+      <c r="K7" s="10">
+        <f>ROUND(IMDIV(B7,J7),2)</f>
+        <v>0.71</v>
+      </c>
+      <c r="L7" s="12">
+        <f>E7/J7</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="M7" s="12">
+        <f>D7/J7</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="N7" s="10">
+        <f>ROUND(IMDIV(F7,J7),2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="O7" s="10">
+        <f>ROUND(IMDIV(G7,J7),2)</f>
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="P7" s="10">
+        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <v>0.21</v>
+      </c>
+      <c r="Q7" s="10">
+        <f>ROUND(IMDIV(B7,F7),2)</f>
+        <v>1.43</v>
+      </c>
+      <c r="R7" s="10">
+        <f>ROUND(IMDIV(C7,B7),4)*100</f>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="S7" s="10">
+        <f>ROUND(IMDIV(I7,J7),2)</f>
+        <v>78.680000000000007</v>
+      </c>
+      <c r="T7" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="U7" s="16" t="s">
+      <c r="U7" s="11" t="s">
         <v>25</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" si="9"/>
-        <v>0.86680232558139525</v>
+        <f>((K7/2)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
+        <v>1.2814534883720929</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1383,39 +1383,39 @@
         <v>31</v>
       </c>
       <c r="K8" s="17">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B8,J8),2)</f>
         <v>0.71</v>
       </c>
       <c r="L8" s="19">
-        <f t="shared" si="1"/>
+        <f>E8/J8</f>
         <v>0.12903225806451613</v>
       </c>
       <c r="M8" s="19">
-        <f t="shared" si="2"/>
+        <f>D8/J8</f>
         <v>0.22580645161290322</v>
       </c>
       <c r="N8" s="17">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F8,J8),2)</f>
         <v>0.61</v>
       </c>
       <c r="O8" s="17">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G8,J8),2)</f>
         <v>0.9</v>
       </c>
       <c r="P8" s="17">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H8,J8),2)</f>
         <v>0.39</v>
       </c>
       <c r="Q8" s="17">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B8,F8),2)</f>
         <v>1.1599999999999999</v>
       </c>
       <c r="R8" s="17">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C8,B8),4)*100</f>
         <v>77.27000000000001</v>
       </c>
       <c r="S8" s="17">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I8,J8),2)</f>
         <v>81.42</v>
       </c>
       <c r="T8" s="18" t="s">
@@ -1425,388 +1425,388 @@
         <v>25</v>
       </c>
       <c r="V8" s="1">
-        <f t="shared" si="9"/>
+        <f>((K8/2)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
         <v>1.2254557389347336</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="17">
-        <v>12</v>
-      </c>
-      <c r="C9" s="17">
-        <v>5</v>
-      </c>
-      <c r="D9" s="17">
-        <v>2</v>
-      </c>
-      <c r="E9" s="18">
-        <v>0</v>
-      </c>
-      <c r="F9" s="18">
-        <v>23</v>
-      </c>
-      <c r="G9" s="18">
-        <v>70</v>
-      </c>
-      <c r="H9" s="18">
-        <v>6</v>
-      </c>
-      <c r="I9" s="18">
-        <v>1292</v>
-      </c>
-      <c r="J9" s="18">
-        <v>31</v>
-      </c>
-      <c r="K9" s="17">
-        <f t="shared" si="0"/>
-        <v>0.39</v>
-      </c>
-      <c r="L9" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="19">
-        <f t="shared" si="2"/>
-        <v>6.4516129032258063E-2</v>
-      </c>
-      <c r="N9" s="17">
-        <f t="shared" si="3"/>
-        <v>0.74</v>
-      </c>
-      <c r="O9" s="17">
-        <f t="shared" si="4"/>
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="P9" s="17">
-        <f t="shared" si="5"/>
-        <v>0.19</v>
-      </c>
-      <c r="Q9" s="17">
-        <f t="shared" si="6"/>
-        <v>0.52</v>
-      </c>
-      <c r="R9" s="17">
-        <f t="shared" si="7"/>
-        <v>41.67</v>
-      </c>
-      <c r="S9" s="17">
-        <f t="shared" si="8"/>
-        <v>41.68</v>
-      </c>
-      <c r="T9" s="18" t="s">
+      <c r="A9" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="35">
+        <v>24</v>
+      </c>
+      <c r="C9" s="35">
+        <v>11</v>
+      </c>
+      <c r="D9" s="35">
+        <v>7</v>
+      </c>
+      <c r="E9" s="35">
+        <v>1</v>
+      </c>
+      <c r="F9" s="35">
+        <v>25</v>
+      </c>
+      <c r="G9" s="35">
+        <v>64</v>
+      </c>
+      <c r="H9" s="35">
+        <v>9</v>
+      </c>
+      <c r="I9" s="35">
+        <v>3068</v>
+      </c>
+      <c r="J9" s="35">
+        <v>38</v>
+      </c>
+      <c r="K9" s="36">
+        <f>ROUND(IMDIV(B9,J9),2)</f>
+        <v>0.63</v>
+      </c>
+      <c r="L9" s="37">
+        <f>E9/J9</f>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="M9" s="37">
+        <f>D9/J9</f>
+        <v>0.18421052631578946</v>
+      </c>
+      <c r="N9" s="36">
+        <f>ROUND(IMDIV(F9,J9),2)</f>
+        <v>0.66</v>
+      </c>
+      <c r="O9" s="36">
+        <f>ROUND(IMDIV(G9,J9),2)</f>
+        <v>1.68</v>
+      </c>
+      <c r="P9" s="36">
+        <f>ROUND(IMDIV(H9,J9),2)</f>
+        <v>0.24</v>
+      </c>
+      <c r="Q9" s="36">
+        <f>ROUND(IMDIV(B9,F9),2)</f>
+        <v>0.96</v>
+      </c>
+      <c r="R9" s="36">
+        <f>ROUND(IMDIV(C9,B9),4)*100</f>
+        <v>45.83</v>
+      </c>
+      <c r="S9" s="36">
+        <f>ROUND(IMDIV(I9,J9),2)</f>
+        <v>80.739999999999995</v>
+      </c>
+      <c r="T9" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="18" t="s">
+      <c r="U9" s="35" t="s">
         <v>25</v>
       </c>
       <c r="V9" s="1">
-        <f t="shared" si="9"/>
-        <v>0.67448949737434361</v>
+        <f>((K9/2)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
+        <v>1.0938506731946143</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="20">
-        <v>9</v>
-      </c>
-      <c r="C10" s="20">
-        <v>6</v>
-      </c>
-      <c r="D10" s="20">
-        <v>2</v>
-      </c>
-      <c r="E10" s="20">
+      <c r="A10" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="13">
+        <v>16</v>
+      </c>
+      <c r="C10" s="13">
+        <v>7</v>
+      </c>
+      <c r="D10" s="13">
         <v>1</v>
       </c>
-      <c r="F10" s="20">
-        <v>17</v>
-      </c>
-      <c r="G10" s="20">
-        <v>59</v>
-      </c>
-      <c r="H10" s="20">
-        <v>3</v>
-      </c>
-      <c r="I10" s="20">
-        <v>1235</v>
-      </c>
-      <c r="J10" s="20">
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
+        <v>14</v>
+      </c>
+      <c r="G10" s="13">
+        <v>94</v>
+      </c>
+      <c r="H10" s="13">
+        <v>1</v>
+      </c>
+      <c r="I10" s="13">
+        <v>1886</v>
+      </c>
+      <c r="J10" s="13">
+        <v>32</v>
+      </c>
+      <c r="K10" s="13">
+        <f>ROUND(IMDIV(B10,J10),2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="14">
+        <f>E10/J10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="14">
+        <f>D10/J10</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="N10" s="13">
+        <f>ROUND(IMDIV(F10,J10),2)</f>
+        <v>0.44</v>
+      </c>
+      <c r="O10" s="13">
+        <f>ROUND(IMDIV(G10,J10),2)</f>
+        <v>2.94</v>
+      </c>
+      <c r="P10" s="13">
+        <f>ROUND(IMDIV(H10,J10),2)</f>
+        <v>0.03</v>
+      </c>
+      <c r="Q10" s="13">
+        <f>ROUND(IMDIV(B10,F10),2)</f>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R10" s="13">
+        <f>ROUND(IMDIV(C10,B10),4)*100</f>
+        <v>43.75</v>
+      </c>
+      <c r="S10" s="13">
+        <f>ROUND(IMDIV(I10,J10),2)</f>
+        <v>58.94</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="U10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="20">
-        <f t="shared" si="0"/>
-        <v>0.36</v>
-      </c>
-      <c r="L10" s="21">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-      <c r="M10" s="21">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="N10" s="20">
-        <f t="shared" si="3"/>
-        <v>0.68</v>
-      </c>
-      <c r="O10" s="20">
-        <f t="shared" si="4"/>
-        <v>2.36</v>
-      </c>
-      <c r="P10" s="20">
-        <f t="shared" si="5"/>
-        <v>0.12</v>
-      </c>
-      <c r="Q10" s="20">
-        <f t="shared" si="6"/>
-        <v>0.53</v>
-      </c>
-      <c r="R10" s="20">
-        <f t="shared" si="7"/>
-        <v>66.67</v>
-      </c>
-      <c r="S10" s="20">
-        <f t="shared" si="8"/>
-        <v>49.4</v>
-      </c>
-      <c r="T10" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="U10" s="20" t="s">
-        <v>25</v>
-      </c>
       <c r="V10" s="1">
-        <f t="shared" si="9"/>
-        <v>0.76376744186046497</v>
+        <f>((K10/2)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
+        <v>1.0934520348837209</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="20">
-        <v>10</v>
-      </c>
-      <c r="C11" s="20">
-        <v>5</v>
-      </c>
-      <c r="D11" s="20">
-        <v>2</v>
-      </c>
-      <c r="E11" s="20">
+      <c r="A11" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="7">
+        <v>22</v>
+      </c>
+      <c r="C11" s="7">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7">
+        <v>3</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>23</v>
+      </c>
+      <c r="G11" s="7">
         <v>1</v>
       </c>
-      <c r="F11" s="20">
-        <v>19</v>
-      </c>
-      <c r="G11" s="20">
+      <c r="H11" s="7">
+        <v>6</v>
+      </c>
+      <c r="I11" s="7">
+        <v>2267</v>
+      </c>
+      <c r="J11" s="7">
+        <v>44</v>
+      </c>
+      <c r="K11" s="7">
+        <f>ROUND(IMDIV(B11,J11),2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="L11" s="8">
+        <f>E11/J11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="20">
-        <v>4</v>
-      </c>
-      <c r="I11" s="20">
-        <v>1299</v>
-      </c>
-      <c r="J11" s="20">
+      <c r="M11" s="8">
+        <f>D11/J11</f>
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="N11" s="7">
+        <f>ROUND(IMDIV(F11,J11),2)</f>
+        <v>0.52</v>
+      </c>
+      <c r="O11" s="7">
+        <f>ROUND(IMDIV(G11,J11),2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="P11" s="7">
+        <f>ROUND(IMDIV(H11,J11),2)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q11" s="7">
+        <f>ROUND(IMDIV(B11,F11),2)</f>
+        <v>0.96</v>
+      </c>
+      <c r="R11" s="7">
+        <f>ROUND(IMDIV(C11,B11),4)*100</f>
+        <v>68.179999999999993</v>
+      </c>
+      <c r="S11" s="7">
+        <f>ROUND(IMDIV(I11,J11),2)</f>
+        <v>51.52</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="U11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="20">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="L11" s="21">
-        <f t="shared" si="1"/>
-        <v>0.04</v>
-      </c>
-      <c r="M11" s="21">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="N11" s="20">
-        <f t="shared" si="3"/>
-        <v>0.76</v>
-      </c>
-      <c r="O11" s="20">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="20">
-        <f t="shared" si="5"/>
-        <v>0.16</v>
-      </c>
-      <c r="Q11" s="20">
-        <f t="shared" si="6"/>
-        <v>0.53</v>
-      </c>
-      <c r="R11" s="20">
-        <f t="shared" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="S11" s="20">
-        <f t="shared" si="8"/>
-        <v>51.96</v>
-      </c>
-      <c r="T11" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="U11" s="20" t="s">
-        <v>25</v>
-      </c>
       <c r="V11" s="1">
-        <f t="shared" si="9"/>
-        <v>0.71767441860465109</v>
+        <f>((K11/2)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
+        <v>0.99367336152219865</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="22">
-        <v>20</v>
-      </c>
-      <c r="C12" s="22">
-        <v>17</v>
-      </c>
-      <c r="D12" s="22">
-        <v>7</v>
-      </c>
-      <c r="E12" s="22">
+      <c r="A12" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="29">
+        <v>19</v>
+      </c>
+      <c r="C12" s="29">
         <v>4</v>
       </c>
-      <c r="F12" s="22">
-        <v>24</v>
-      </c>
-      <c r="G12" s="22">
+      <c r="D12" s="29">
+        <v>3</v>
+      </c>
+      <c r="E12" s="29">
         <v>0</v>
       </c>
-      <c r="H12" s="22">
-        <v>3</v>
-      </c>
-      <c r="I12" s="22">
-        <v>1890</v>
-      </c>
-      <c r="J12" s="22">
-        <v>35</v>
-      </c>
-      <c r="K12" s="23">
-        <f t="shared" si="0"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L12" s="24">
-        <f t="shared" si="1"/>
-        <v>0.11428571428571428</v>
-      </c>
-      <c r="M12" s="24">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="N12" s="23">
-        <f t="shared" si="3"/>
-        <v>0.69</v>
-      </c>
-      <c r="O12" s="23">
-        <f t="shared" si="4"/>
+      <c r="F12" s="29">
+        <v>21</v>
+      </c>
+      <c r="G12" s="29">
+        <v>77</v>
+      </c>
+      <c r="H12" s="29">
+        <v>9</v>
+      </c>
+      <c r="I12" s="29">
+        <v>2096</v>
+      </c>
+      <c r="J12" s="29">
+        <v>32</v>
+      </c>
+      <c r="K12" s="30">
+        <f>ROUND(IMDIV(B12,J12),2)</f>
+        <v>0.59</v>
+      </c>
+      <c r="L12" s="31">
+        <f>E12/J12</f>
         <v>0</v>
       </c>
-      <c r="P12" s="23">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
-      </c>
-      <c r="Q12" s="23">
-        <f t="shared" si="6"/>
-        <v>0.83</v>
-      </c>
-      <c r="R12" s="23">
-        <f t="shared" si="7"/>
-        <v>85</v>
-      </c>
-      <c r="S12" s="23">
-        <f t="shared" si="8"/>
-        <v>54</v>
-      </c>
-      <c r="T12" s="25" t="s">
+      <c r="M12" s="31">
+        <f>D12/J12</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="N12" s="30">
+        <f>ROUND(IMDIV(F12,J12),2)</f>
+        <v>0.66</v>
+      </c>
+      <c r="O12" s="30">
+        <f>ROUND(IMDIV(G12,J12),2)</f>
+        <v>2.41</v>
+      </c>
+      <c r="P12" s="30">
+        <f>ROUND(IMDIV(H12,J12),2)</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q12" s="30">
+        <f>ROUND(IMDIV(B12,F12),2)</f>
+        <v>0.9</v>
+      </c>
+      <c r="R12" s="30">
+        <f>ROUND(IMDIV(C12,B12),4)*100</f>
+        <v>21.05</v>
+      </c>
+      <c r="S12" s="30">
+        <f>ROUND(IMDIV(I12,J12),2)</f>
+        <v>65.5</v>
+      </c>
+      <c r="T12" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="U12" s="25" t="s">
+      <c r="U12" s="29" t="s">
         <v>25</v>
       </c>
       <c r="V12" s="1">
-        <f t="shared" si="9"/>
-        <v>0.92351993355481732</v>
+        <f>((K12/2)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
+        <v>0.97708866279069762</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="22">
+        <v>20</v>
+      </c>
+      <c r="C13" s="22">
         <v>17</v>
       </c>
-      <c r="C13" s="22">
+      <c r="D13" s="22">
         <v>7</v>
       </c>
-      <c r="D13" s="22">
-        <v>5</v>
-      </c>
       <c r="E13" s="22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="22">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G13" s="22">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H13" s="22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I13" s="22">
-        <v>2415</v>
+        <v>1890</v>
       </c>
       <c r="J13" s="22">
         <v>35</v>
       </c>
       <c r="K13" s="23">
-        <f t="shared" si="0"/>
-        <v>0.49</v>
+        <f>ROUND(IMDIV(B13,J13),2)</f>
+        <v>0.56999999999999995</v>
       </c>
       <c r="L13" s="24">
-        <f t="shared" si="1"/>
-        <v>5.7142857142857141E-2</v>
+        <f>E13/J13</f>
+        <v>0.11428571428571428</v>
       </c>
       <c r="M13" s="24">
-        <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <f>D13/J13</f>
+        <v>0.2</v>
       </c>
       <c r="N13" s="23">
-        <f t="shared" si="3"/>
-        <v>0.74</v>
+        <f>ROUND(IMDIV(F13,J13),2)</f>
+        <v>0.69</v>
       </c>
       <c r="O13" s="23">
-        <f t="shared" si="4"/>
-        <v>1.37</v>
+        <f>ROUND(IMDIV(G13,J13),2)</f>
+        <v>0</v>
       </c>
       <c r="P13" s="23">
-        <f t="shared" si="5"/>
-        <v>0.28999999999999998</v>
+        <f>ROUND(IMDIV(H13,J13),2)</f>
+        <v>0.09</v>
       </c>
       <c r="Q13" s="23">
-        <f t="shared" si="6"/>
-        <v>0.65</v>
+        <f>ROUND(IMDIV(B13,F13),2)</f>
+        <v>0.83</v>
       </c>
       <c r="R13" s="23">
-        <f t="shared" si="7"/>
-        <v>41.18</v>
+        <f>ROUND(IMDIV(C13,B13),4)*100</f>
+        <v>85</v>
       </c>
       <c r="S13" s="23">
-        <f t="shared" si="8"/>
-        <v>69</v>
+        <f>ROUND(IMDIV(I13,J13),2)</f>
+        <v>54</v>
       </c>
       <c r="T13" s="25" t="s">
         <v>43</v>
@@ -1815,635 +1815,638 @@
         <v>25</v>
       </c>
       <c r="V13" s="1">
-        <f t="shared" si="9"/>
-        <v>0.88757308970099669</v>
+        <f>((K13/2)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
+        <v>0.92351993355481732</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="26">
-        <v>9</v>
-      </c>
-      <c r="C14" s="26">
+      <c r="A14" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="22">
+        <v>17</v>
+      </c>
+      <c r="C14" s="22">
+        <v>7</v>
+      </c>
+      <c r="D14" s="22">
         <v>5</v>
       </c>
-      <c r="D14" s="26">
+      <c r="E14" s="22">
         <v>2</v>
       </c>
-      <c r="E14" s="26">
-        <v>0</v>
-      </c>
-      <c r="F14" s="26">
-        <v>18</v>
-      </c>
-      <c r="G14" s="26">
-        <v>112</v>
-      </c>
-      <c r="H14" s="26">
-        <v>3</v>
-      </c>
-      <c r="I14" s="26">
-        <v>1668</v>
-      </c>
-      <c r="J14" s="26">
-        <v>23</v>
-      </c>
-      <c r="K14" s="27">
-        <f t="shared" si="0"/>
-        <v>0.39</v>
-      </c>
-      <c r="L14" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="28">
-        <f t="shared" si="2"/>
-        <v>8.6956521739130432E-2</v>
-      </c>
-      <c r="N14" s="27">
-        <f t="shared" si="3"/>
-        <v>0.78</v>
-      </c>
-      <c r="O14" s="27">
-        <f t="shared" si="4"/>
-        <v>4.87</v>
-      </c>
-      <c r="P14" s="27">
-        <f t="shared" si="5"/>
-        <v>0.13</v>
-      </c>
-      <c r="Q14" s="27">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
-      </c>
-      <c r="R14" s="27">
-        <f t="shared" si="7"/>
-        <v>55.559999999999995</v>
-      </c>
-      <c r="S14" s="27">
-        <f t="shared" si="8"/>
-        <v>72.52</v>
-      </c>
-      <c r="T14" s="27" t="s">
+      <c r="F14" s="22">
+        <v>26</v>
+      </c>
+      <c r="G14" s="22">
+        <v>48</v>
+      </c>
+      <c r="H14" s="22">
+        <v>10</v>
+      </c>
+      <c r="I14" s="22">
+        <v>2415</v>
+      </c>
+      <c r="J14" s="22">
+        <v>35</v>
+      </c>
+      <c r="K14" s="23">
+        <f>ROUND(IMDIV(B14,J14),2)</f>
+        <v>0.49</v>
+      </c>
+      <c r="L14" s="24">
+        <f>E14/J14</f>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="M14" s="24">
+        <f>D14/J14</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="N14" s="23">
+        <f>ROUND(IMDIV(F14,J14),2)</f>
+        <v>0.74</v>
+      </c>
+      <c r="O14" s="23">
+        <f>ROUND(IMDIV(G14,J14),2)</f>
+        <v>1.37</v>
+      </c>
+      <c r="P14" s="23">
+        <f>ROUND(IMDIV(H14,J14),2)</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Q14" s="23">
+        <f>ROUND(IMDIV(B14,F14),2)</f>
+        <v>0.65</v>
+      </c>
+      <c r="R14" s="23">
+        <f>ROUND(IMDIV(C14,B14),4)*100</f>
+        <v>41.18</v>
+      </c>
+      <c r="S14" s="23">
+        <f>ROUND(IMDIV(I14,J14),2)</f>
+        <v>69</v>
+      </c>
+      <c r="T14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="U14" s="27" t="s">
+      <c r="U14" s="25" t="s">
         <v>25</v>
       </c>
       <c r="V14" s="1">
-        <f t="shared" si="9"/>
-        <v>0.78054145601617786</v>
+        <f>((K14/2)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
+        <v>0.88757308970099669</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="26">
-        <v>9</v>
-      </c>
-      <c r="C15" s="26">
+      <c r="A15" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="35">
+        <v>18</v>
+      </c>
+      <c r="C15" s="35">
+        <v>7</v>
+      </c>
+      <c r="D15" s="35">
         <v>4</v>
       </c>
-      <c r="D15" s="26">
-        <v>3</v>
-      </c>
-      <c r="E15" s="26">
+      <c r="E15" s="35">
+        <v>2</v>
+      </c>
+      <c r="F15" s="35">
+        <v>25</v>
+      </c>
+      <c r="G15" s="35">
+        <v>30</v>
+      </c>
+      <c r="H15" s="35">
         <v>1</v>
       </c>
-      <c r="F15" s="26">
-        <v>19</v>
-      </c>
-      <c r="G15" s="27">
-        <v>40</v>
-      </c>
-      <c r="H15" s="26">
-        <v>3</v>
-      </c>
-      <c r="I15" s="26">
-        <v>946</v>
-      </c>
-      <c r="J15" s="26">
-        <v>23</v>
-      </c>
-      <c r="K15" s="27">
-        <f t="shared" si="0"/>
-        <v>0.39</v>
-      </c>
-      <c r="L15" s="28">
-        <f t="shared" si="1"/>
-        <v>4.3478260869565216E-2</v>
-      </c>
-      <c r="M15" s="28">
-        <f t="shared" si="2"/>
-        <v>0.13043478260869565</v>
-      </c>
-      <c r="N15" s="27">
-        <f t="shared" si="3"/>
-        <v>0.83</v>
-      </c>
-      <c r="O15" s="27">
-        <f t="shared" si="4"/>
-        <v>1.74</v>
-      </c>
-      <c r="P15" s="27">
-        <f t="shared" si="5"/>
-        <v>0.13</v>
-      </c>
-      <c r="Q15" s="27">
-        <f t="shared" si="6"/>
+      <c r="I15" s="35">
+        <v>1962</v>
+      </c>
+      <c r="J15" s="35">
+        <v>38</v>
+      </c>
+      <c r="K15" s="36">
+        <f>ROUND(IMDIV(B15,J15),2)</f>
         <v>0.47</v>
       </c>
-      <c r="R15" s="27">
-        <f t="shared" si="7"/>
-        <v>44.440000000000005</v>
-      </c>
-      <c r="S15" s="27">
-        <f t="shared" si="8"/>
-        <v>41.13</v>
-      </c>
-      <c r="T15" s="27" t="s">
+      <c r="L15" s="37">
+        <f>E15/J15</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M15" s="37">
+        <f>D15/J15</f>
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="N15" s="36">
+        <f>ROUND(IMDIV(F15,J15),2)</f>
+        <v>0.66</v>
+      </c>
+      <c r="O15" s="36">
+        <f>ROUND(IMDIV(G15,J15),2)</f>
+        <v>0.79</v>
+      </c>
+      <c r="P15" s="36">
+        <f>ROUND(IMDIV(H15,J15),2)</f>
+        <v>0.03</v>
+      </c>
+      <c r="Q15" s="36">
+        <f>ROUND(IMDIV(B15,F15),2)</f>
+        <v>0.72</v>
+      </c>
+      <c r="R15" s="36">
+        <f>ROUND(IMDIV(C15,B15),4)*100</f>
+        <v>38.89</v>
+      </c>
+      <c r="S15" s="36">
+        <f>ROUND(IMDIV(I15,J15),2)</f>
+        <v>51.63</v>
+      </c>
+      <c r="T15" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="U15" s="27" t="s">
+      <c r="U15" s="35" t="s">
         <v>25</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" si="9"/>
-        <v>0.60410667340748248</v>
+        <f>((K15/2)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
+        <v>0.85348164014687877</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="29">
-        <v>24</v>
-      </c>
-      <c r="C16" s="29">
+      <c r="A16" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="32">
         <v>14</v>
       </c>
-      <c r="D16" s="29">
-        <v>3</v>
-      </c>
-      <c r="E16" s="29">
-        <v>3</v>
-      </c>
-      <c r="F16" s="29">
-        <v>16</v>
-      </c>
-      <c r="G16" s="29">
-        <v>24</v>
-      </c>
-      <c r="H16" s="29">
+      <c r="C16" s="32">
         <v>6</v>
       </c>
-      <c r="I16" s="29">
-        <v>2848</v>
-      </c>
-      <c r="J16" s="29">
-        <v>32</v>
-      </c>
-      <c r="K16" s="30">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="L16" s="31">
-        <f t="shared" si="1"/>
-        <v>9.375E-2</v>
-      </c>
-      <c r="M16" s="31">
-        <f t="shared" si="2"/>
-        <v>9.375E-2</v>
-      </c>
-      <c r="N16" s="30">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="O16" s="30">
-        <f t="shared" si="4"/>
-        <v>0.75</v>
-      </c>
-      <c r="P16" s="30">
-        <f t="shared" si="5"/>
-        <v>0.19</v>
-      </c>
-      <c r="Q16" s="30">
-        <f t="shared" si="6"/>
-        <v>1.5</v>
-      </c>
-      <c r="R16" s="30">
-        <f t="shared" si="7"/>
-        <v>58.330000000000005</v>
-      </c>
-      <c r="S16" s="30">
-        <f t="shared" si="8"/>
-        <v>89</v>
-      </c>
-      <c r="T16" s="29" t="s">
+      <c r="D16" s="32">
+        <v>1</v>
+      </c>
+      <c r="E16" s="32">
+        <v>0</v>
+      </c>
+      <c r="F16" s="32">
+        <v>19</v>
+      </c>
+      <c r="G16" s="32">
+        <v>54</v>
+      </c>
+      <c r="H16" s="32">
+        <v>6</v>
+      </c>
+      <c r="I16" s="32">
+        <v>1390</v>
+      </c>
+      <c r="J16" s="32">
+        <v>30</v>
+      </c>
+      <c r="K16" s="33">
+        <f>ROUND(IMDIV(B16,J16),2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="L16" s="34">
+        <f>E16/J16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="34">
+        <f>D16/J16</f>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="N16" s="33">
+        <f>ROUND(IMDIV(F16,J16),2)</f>
+        <v>0.63</v>
+      </c>
+      <c r="O16" s="33">
+        <f>ROUND(IMDIV(G16,J16),2)</f>
+        <v>1.8</v>
+      </c>
+      <c r="P16" s="33">
+        <f>ROUND(IMDIV(H16,J16),2)</f>
+        <v>0.2</v>
+      </c>
+      <c r="Q16" s="33">
+        <f>ROUND(IMDIV(B16,F16),2)</f>
+        <v>0.74</v>
+      </c>
+      <c r="R16" s="33">
+        <f>ROUND(IMDIV(C16,B16),4)*100</f>
+        <v>42.86</v>
+      </c>
+      <c r="S16" s="33">
+        <f>ROUND(IMDIV(I16,J16),2)</f>
+        <v>46.33</v>
+      </c>
+      <c r="T16" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="U16" s="29" t="s">
+      <c r="U16" s="32" t="s">
         <v>25</v>
       </c>
       <c r="V16" s="1">
-        <f t="shared" si="9"/>
-        <v>1.3406409883720931</v>
+        <f>((K16/2)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
+        <v>0.83882170542635648</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="29">
-        <v>19</v>
-      </c>
-      <c r="C17" s="29">
-        <v>4</v>
-      </c>
-      <c r="D17" s="29">
+      <c r="A17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="26">
+        <v>9</v>
+      </c>
+      <c r="C17" s="26">
+        <v>5</v>
+      </c>
+      <c r="D17" s="26">
+        <v>2</v>
+      </c>
+      <c r="E17" s="26">
+        <v>0</v>
+      </c>
+      <c r="F17" s="26">
+        <v>18</v>
+      </c>
+      <c r="G17" s="26">
+        <v>112</v>
+      </c>
+      <c r="H17" s="26">
         <v>3</v>
       </c>
-      <c r="E17" s="29">
+      <c r="I17" s="26">
+        <v>1668</v>
+      </c>
+      <c r="J17" s="26">
+        <v>23</v>
+      </c>
+      <c r="K17" s="27">
+        <f>ROUND(IMDIV(B17,J17),2)</f>
+        <v>0.39</v>
+      </c>
+      <c r="L17" s="28">
+        <f>E17/J17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="29">
-        <v>21</v>
-      </c>
-      <c r="G17" s="29">
-        <v>77</v>
-      </c>
-      <c r="H17" s="29">
-        <v>9</v>
-      </c>
-      <c r="I17" s="29">
-        <v>2096</v>
-      </c>
-      <c r="J17" s="29">
-        <v>32</v>
-      </c>
-      <c r="K17" s="30">
-        <f t="shared" si="0"/>
-        <v>0.59</v>
-      </c>
-      <c r="L17" s="31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="31">
-        <f t="shared" si="2"/>
-        <v>9.375E-2</v>
-      </c>
-      <c r="N17" s="30">
-        <f t="shared" si="3"/>
-        <v>0.66</v>
-      </c>
-      <c r="O17" s="30">
-        <f t="shared" si="4"/>
-        <v>2.41</v>
-      </c>
-      <c r="P17" s="30">
-        <f t="shared" si="5"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q17" s="30">
-        <f t="shared" si="6"/>
-        <v>0.9</v>
-      </c>
-      <c r="R17" s="30">
-        <f t="shared" si="7"/>
-        <v>21.05</v>
-      </c>
-      <c r="S17" s="30">
-        <f t="shared" si="8"/>
-        <v>65.5</v>
-      </c>
-      <c r="T17" s="29" t="s">
+      <c r="M17" s="28">
+        <f>D17/J17</f>
+        <v>8.6956521739130432E-2</v>
+      </c>
+      <c r="N17" s="27">
+        <f>ROUND(IMDIV(F17,J17),2)</f>
+        <v>0.78</v>
+      </c>
+      <c r="O17" s="27">
+        <f>ROUND(IMDIV(G17,J17),2)</f>
+        <v>4.87</v>
+      </c>
+      <c r="P17" s="27">
+        <f>ROUND(IMDIV(H17,J17),2)</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q17" s="27">
+        <f>ROUND(IMDIV(B17,F17),2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="27">
+        <f>ROUND(IMDIV(C17,B17),4)*100</f>
+        <v>55.559999999999995</v>
+      </c>
+      <c r="S17" s="27">
+        <f>ROUND(IMDIV(I17,J17),2)</f>
+        <v>72.52</v>
+      </c>
+      <c r="T17" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="U17" s="29" t="s">
+      <c r="U17" s="27" t="s">
         <v>25</v>
       </c>
       <c r="V17" s="1">
-        <f t="shared" si="9"/>
-        <v>0.97708866279069762</v>
+        <f>((K17/2)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
+        <v>0.78054145601617786</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="32">
-        <v>28</v>
-      </c>
-      <c r="C18" s="32">
-        <v>16</v>
-      </c>
-      <c r="D18" s="32">
+      <c r="A18" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="20">
+        <v>12</v>
+      </c>
+      <c r="C18" s="20">
         <v>8</v>
       </c>
-      <c r="E18" s="32">
+      <c r="D18" s="20">
         <v>3</v>
       </c>
-      <c r="F18" s="32">
-        <v>13</v>
-      </c>
-      <c r="G18" s="32">
-        <v>241</v>
-      </c>
-      <c r="H18" s="32">
-        <v>6</v>
-      </c>
-      <c r="I18" s="32">
-        <v>3252</v>
-      </c>
-      <c r="J18" s="32">
-        <v>30</v>
-      </c>
-      <c r="K18" s="33">
-        <f t="shared" si="0"/>
-        <v>0.93</v>
-      </c>
-      <c r="L18" s="34">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="M18" s="34">
-        <f t="shared" si="2"/>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="N18" s="33">
-        <f t="shared" si="3"/>
-        <v>0.43</v>
-      </c>
-      <c r="O18" s="33">
-        <f t="shared" si="4"/>
-        <v>8.0299999999999994</v>
-      </c>
-      <c r="P18" s="33">
-        <f t="shared" si="5"/>
-        <v>0.2</v>
-      </c>
-      <c r="Q18" s="33">
-        <f t="shared" si="6"/>
-        <v>2.15</v>
-      </c>
-      <c r="R18" s="33">
-        <f t="shared" si="7"/>
-        <v>57.14</v>
-      </c>
-      <c r="S18" s="33">
-        <f t="shared" si="8"/>
-        <v>108.4</v>
-      </c>
-      <c r="T18" s="32" t="s">
+      <c r="E18" s="20">
+        <v>1</v>
+      </c>
+      <c r="F18" s="20">
+        <v>26</v>
+      </c>
+      <c r="G18" s="20">
+        <v>101</v>
+      </c>
+      <c r="H18" s="20">
+        <v>9</v>
+      </c>
+      <c r="I18" s="20">
+        <v>1883</v>
+      </c>
+      <c r="J18" s="20">
+        <v>37</v>
+      </c>
+      <c r="K18" s="20">
+        <f>ROUND(IMDIV(B18,J18),2)</f>
+        <v>0.32</v>
+      </c>
+      <c r="L18" s="21">
+        <f>E18/J18</f>
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="M18" s="21">
+        <f>D18/J18</f>
+        <v>8.1081081081081086E-2</v>
+      </c>
+      <c r="N18" s="20">
+        <f>ROUND(IMDIV(F18,J18),2)</f>
+        <v>0.7</v>
+      </c>
+      <c r="O18" s="20">
+        <f>ROUND(IMDIV(G18,J18),2)</f>
+        <v>2.73</v>
+      </c>
+      <c r="P18" s="20">
+        <f>ROUND(IMDIV(H18,J18),2)</f>
+        <v>0.24</v>
+      </c>
+      <c r="Q18" s="20">
+        <f>ROUND(IMDIV(B18,F18),2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="R18" s="20">
+        <f>ROUND(IMDIV(C18,B18),4)*100</f>
+        <v>66.67</v>
+      </c>
+      <c r="S18" s="20">
+        <f>ROUND(IMDIV(I18,J18),2)</f>
+        <v>50.89</v>
+      </c>
+      <c r="T18" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="U18" s="32" t="s">
+      <c r="U18" s="20" t="s">
         <v>25</v>
       </c>
       <c r="V18" s="1">
-        <f t="shared" si="9"/>
-        <v>1.6358527131782947</v>
+        <f>((K18/2)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
+        <v>0.7343733500942804</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="32">
-        <v>14</v>
-      </c>
-      <c r="C19" s="32">
-        <v>6</v>
-      </c>
-      <c r="D19" s="32">
+      <c r="A19" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="20">
+        <v>16</v>
+      </c>
+      <c r="C19" s="20">
+        <v>7</v>
+      </c>
+      <c r="D19" s="20">
+        <v>3</v>
+      </c>
+      <c r="E19" s="20">
         <v>1</v>
       </c>
-      <c r="E19" s="32">
+      <c r="F19" s="20">
+        <v>29</v>
+      </c>
+      <c r="G19" s="20">
         <v>0</v>
       </c>
-      <c r="F19" s="32">
-        <v>19</v>
-      </c>
-      <c r="G19" s="32">
-        <v>54</v>
-      </c>
-      <c r="H19" s="32">
-        <v>6</v>
-      </c>
-      <c r="I19" s="32">
-        <v>1390</v>
-      </c>
-      <c r="J19" s="32">
-        <v>30</v>
-      </c>
-      <c r="K19" s="33">
-        <f t="shared" si="0"/>
-        <v>0.47</v>
-      </c>
-      <c r="L19" s="34">
-        <f t="shared" si="1"/>
+      <c r="H19" s="20">
+        <v>5</v>
+      </c>
+      <c r="I19" s="20">
+        <v>1887</v>
+      </c>
+      <c r="J19" s="20">
+        <v>37</v>
+      </c>
+      <c r="K19" s="20">
+        <f>ROUND(IMDIV(B19,J19),2)</f>
+        <v>0.43</v>
+      </c>
+      <c r="L19" s="21">
+        <f>E19/J19</f>
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="M19" s="21">
+        <f>D19/J19</f>
+        <v>8.1081081081081086E-2</v>
+      </c>
+      <c r="N19" s="20">
+        <f>ROUND(IMDIV(F19,J19),2)</f>
+        <v>0.78</v>
+      </c>
+      <c r="O19" s="20">
+        <f>ROUND(IMDIV(G19,J19),2)</f>
         <v>0</v>
       </c>
-      <c r="M19" s="34">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="N19" s="33">
-        <f t="shared" si="3"/>
-        <v>0.63</v>
-      </c>
-      <c r="O19" s="33">
-        <f t="shared" si="4"/>
-        <v>1.8</v>
-      </c>
-      <c r="P19" s="33">
-        <f t="shared" si="5"/>
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="33">
-        <f t="shared" si="6"/>
-        <v>0.74</v>
-      </c>
-      <c r="R19" s="33">
-        <f t="shared" si="7"/>
-        <v>42.86</v>
-      </c>
-      <c r="S19" s="33">
-        <f t="shared" si="8"/>
-        <v>46.33</v>
-      </c>
-      <c r="T19" s="32" t="s">
+      <c r="P19" s="20">
+        <f>ROUND(IMDIV(H19,J19),2)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q19" s="20">
+        <f>ROUND(IMDIV(B19,F19),2)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R19" s="20">
+        <f>ROUND(IMDIV(C19,B19),4)*100</f>
+        <v>43.75</v>
+      </c>
+      <c r="S19" s="20">
+        <f>ROUND(IMDIV(I19,J19),2)</f>
+        <v>51</v>
+      </c>
+      <c r="T19" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="U19" s="32" t="s">
+      <c r="U19" s="20" t="s">
         <v>25</v>
       </c>
       <c r="V19" s="1">
-        <f t="shared" si="9"/>
-        <v>0.83882170542635648</v>
+        <f>((K19/2)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
+        <v>0.70488497800125693</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="35">
-        <v>20</v>
-      </c>
-      <c r="C20" s="35">
-        <v>9</v>
-      </c>
-      <c r="D20" s="35">
+      <c r="A20" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="17">
+        <v>12</v>
+      </c>
+      <c r="C20" s="17">
+        <v>5</v>
+      </c>
+      <c r="D20" s="17">
+        <v>2</v>
+      </c>
+      <c r="E20" s="18">
+        <v>0</v>
+      </c>
+      <c r="F20" s="18">
+        <v>23</v>
+      </c>
+      <c r="G20" s="18">
+        <v>70</v>
+      </c>
+      <c r="H20" s="18">
         <v>6</v>
       </c>
-      <c r="E20" s="35">
-        <v>1</v>
-      </c>
-      <c r="F20" s="35">
-        <v>14</v>
-      </c>
-      <c r="G20" s="35">
-        <v>21</v>
-      </c>
-      <c r="H20" s="35">
-        <v>7</v>
-      </c>
-      <c r="I20" s="35">
-        <v>2168</v>
-      </c>
-      <c r="J20" s="35">
-        <v>26</v>
-      </c>
-      <c r="K20" s="36">
-        <f t="shared" si="0"/>
-        <v>0.77</v>
-      </c>
-      <c r="L20" s="37">
-        <f t="shared" si="1"/>
-        <v>3.8461538461538464E-2</v>
-      </c>
-      <c r="M20" s="37">
-        <f t="shared" si="2"/>
-        <v>0.23076923076923078</v>
-      </c>
-      <c r="N20" s="36">
-        <f t="shared" si="3"/>
-        <v>0.54</v>
-      </c>
-      <c r="O20" s="36">
-        <f t="shared" si="4"/>
-        <v>0.81</v>
-      </c>
-      <c r="P20" s="36">
-        <f t="shared" si="5"/>
-        <v>0.27</v>
-      </c>
-      <c r="Q20" s="36">
-        <f t="shared" si="6"/>
-        <v>1.43</v>
-      </c>
-      <c r="R20" s="36">
-        <f t="shared" si="7"/>
-        <v>45</v>
-      </c>
-      <c r="S20" s="36">
-        <f t="shared" si="8"/>
-        <v>83.38</v>
-      </c>
-      <c r="T20" s="35" t="s">
+      <c r="I20" s="18">
+        <v>1292</v>
+      </c>
+      <c r="J20" s="18">
+        <v>31</v>
+      </c>
+      <c r="K20" s="17">
+        <f>ROUND(IMDIV(B20,J20),2)</f>
+        <v>0.39</v>
+      </c>
+      <c r="L20" s="19">
+        <f>E20/J20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="19">
+        <f>D20/J20</f>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="N20" s="17">
+        <f>ROUND(IMDIV(F20,J20),2)</f>
+        <v>0.74</v>
+      </c>
+      <c r="O20" s="17">
+        <f>ROUND(IMDIV(G20,J20),2)</f>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="P20" s="17">
+        <f>ROUND(IMDIV(H20,J20),2)</f>
+        <v>0.19</v>
+      </c>
+      <c r="Q20" s="17">
+        <f>ROUND(IMDIV(B20,F20),2)</f>
+        <v>0.52</v>
+      </c>
+      <c r="R20" s="17">
+        <f>ROUND(IMDIV(C20,B20),4)*100</f>
+        <v>41.67</v>
+      </c>
+      <c r="S20" s="17">
+        <f>ROUND(IMDIV(I20,J20),2)</f>
+        <v>41.68</v>
+      </c>
+      <c r="T20" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="U20" s="35" t="s">
+      <c r="U20" s="18" t="s">
         <v>25</v>
       </c>
       <c r="V20" s="1">
-        <f t="shared" si="9"/>
-        <v>1.3116985688729874</v>
+        <f>((K20/2)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
+        <v>0.67448949737434361</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="35">
-        <v>16</v>
-      </c>
-      <c r="C21" s="35">
-        <v>7</v>
-      </c>
-      <c r="D21" s="35">
+      <c r="A21" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="26">
+        <v>9</v>
+      </c>
+      <c r="C21" s="26">
         <v>4</v>
       </c>
-      <c r="E21" s="35">
-        <v>2</v>
-      </c>
-      <c r="F21" s="35">
-        <v>16</v>
-      </c>
-      <c r="G21" s="35">
-        <v>30</v>
-      </c>
-      <c r="H21" s="35">
+      <c r="D21" s="26">
+        <v>3</v>
+      </c>
+      <c r="E21" s="26">
         <v>1</v>
       </c>
-      <c r="I21" s="35">
-        <v>1758</v>
-      </c>
-      <c r="J21" s="35">
-        <v>26</v>
-      </c>
-      <c r="K21" s="36">
-        <f t="shared" si="0"/>
-        <v>0.62</v>
-      </c>
-      <c r="L21" s="37">
-        <f t="shared" si="1"/>
-        <v>7.6923076923076927E-2</v>
-      </c>
-      <c r="M21" s="37">
-        <f t="shared" si="2"/>
-        <v>0.15384615384615385</v>
-      </c>
-      <c r="N21" s="36">
-        <f t="shared" si="3"/>
-        <v>0.62</v>
-      </c>
-      <c r="O21" s="36">
-        <f t="shared" si="4"/>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="P21" s="36">
-        <f t="shared" si="5"/>
-        <v>0.04</v>
-      </c>
-      <c r="Q21" s="36">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="R21" s="36">
-        <f t="shared" si="7"/>
-        <v>43.75</v>
-      </c>
-      <c r="S21" s="36">
-        <f t="shared" si="8"/>
-        <v>67.62</v>
-      </c>
-      <c r="T21" s="35" t="s">
+      <c r="F21" s="26">
+        <v>19</v>
+      </c>
+      <c r="G21" s="27">
+        <v>40</v>
+      </c>
+      <c r="H21" s="26">
+        <v>3</v>
+      </c>
+      <c r="I21" s="26">
+        <v>946</v>
+      </c>
+      <c r="J21" s="26">
+        <v>23</v>
+      </c>
+      <c r="K21" s="27">
+        <f>ROUND(IMDIV(B21,J21),2)</f>
+        <v>0.39</v>
+      </c>
+      <c r="L21" s="28">
+        <f>E21/J21</f>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="M21" s="28">
+        <f>D21/J21</f>
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="N21" s="27">
+        <f>ROUND(IMDIV(F21,J21),2)</f>
+        <v>0.83</v>
+      </c>
+      <c r="O21" s="27">
+        <f>ROUND(IMDIV(G21,J21),2)</f>
+        <v>1.74</v>
+      </c>
+      <c r="P21" s="27">
+        <f>ROUND(IMDIV(H21,J21),2)</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q21" s="27">
+        <f>ROUND(IMDIV(B21,F21),2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="R21" s="27">
+        <f>ROUND(IMDIV(C21,B21),4)*100</f>
+        <v>44.440000000000005</v>
+      </c>
+      <c r="S21" s="27">
+        <f>ROUND(IMDIV(I21,J21),2)</f>
+        <v>41.13</v>
+      </c>
+      <c r="T21" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="U21" s="35" t="s">
+      <c r="U21" s="27" t="s">
         <v>25</v>
       </c>
       <c r="V21" s="1">
-        <f t="shared" si="9"/>
-        <v>1.0603577817531307</v>
+        <f>((K21/2)+(M21/4)+(L21/5)-(N21)+(S21/215)+(P21/20))+1</f>
+        <v>0.60410667340748248</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V21">
+    <sortCondition descending="1" ref="V21"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAAC03C-F769-43A5-B738-AE2E2A2A4A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C97E3C-B941-40F5-A0DD-368584E1E4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -817,14 +817,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C412513A-E0D1-405F-B780-5234AC262E79}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -892,72 +892,72 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>29</v>
       </c>
       <c r="B2" s="7">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C2" s="7">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D2" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" s="7">
         <v>3</v>
       </c>
       <c r="F2" s="7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G2" s="7">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="H2" s="7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I2" s="7">
-        <v>4686</v>
+        <v>6194</v>
       </c>
       <c r="J2" s="7">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K2" s="7">
-        <f t="shared" ref="K2:K21" si="0">ROUND(IMDIV(B2,J2),2)</f>
-        <v>1</v>
+        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <v>1.02</v>
       </c>
       <c r="L2" s="8">
-        <f t="shared" ref="L2:L21" si="1">E2/J2</f>
-        <v>6.8181818181818177E-2</v>
+        <f>E2/J2</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="M2" s="8">
-        <f t="shared" ref="M2:M21" si="2">D2/J2</f>
-        <v>0.27272727272727271</v>
+        <f>D2/J2</f>
+        <v>0.2807017543859649</v>
       </c>
       <c r="N2" s="7">
-        <f t="shared" ref="N2:N21" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <f>ROUND(IMDIV(F2,J2),2)</f>
         <v>0.39</v>
       </c>
       <c r="O2" s="7">
-        <f t="shared" ref="O2:O21" si="4">ROUND(IMDIV(G2,J2),2)</f>
-        <v>9.89</v>
+        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <v>8.56</v>
       </c>
       <c r="P2" s="7">
-        <f t="shared" ref="P2:P21" si="5">ROUND(IMDIV(H2,J2),2)</f>
-        <v>0.39</v>
+        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <v>0.35</v>
       </c>
       <c r="Q2" s="7">
-        <f t="shared" ref="Q2:Q21" si="6">ROUND(IMDIV(B2,F2),2)</f>
-        <v>2.59</v>
+        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <v>2.64</v>
       </c>
       <c r="R2" s="7">
-        <f t="shared" ref="R2:R21" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>65.91</v>
+        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>68.97</v>
       </c>
       <c r="S2" s="7">
-        <f t="shared" ref="S2:S21" si="8">ROUND(IMDIV(I2,J2),2)</f>
-        <v>106.5</v>
+        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <v>108.67</v>
       </c>
       <c r="T2" s="9" t="s">
         <v>43</v>
@@ -966,76 +966,76 @@
         <v>25</v>
       </c>
       <c r="V2" s="1">
-        <f t="shared" ref="V2:V21" si="9">((K2/2)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>1.706667019027484</v>
+        <f>((K2/2)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.7236436148510812</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="7">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C3" s="7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="7">
         <v>0</v>
       </c>
       <c r="F3" s="7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G3" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H3" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I3" s="7">
-        <v>2267</v>
+        <v>2891</v>
       </c>
       <c r="J3" s="7">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K3" s="7">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
+        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <v>0.49</v>
       </c>
       <c r="L3" s="8">
-        <f t="shared" si="1"/>
+        <f>E3/J3</f>
         <v>0</v>
       </c>
       <c r="M3" s="8">
-        <f t="shared" si="2"/>
-        <v>6.8181818181818177E-2</v>
+        <f>D3/J3</f>
+        <v>7.0175438596491224E-2</v>
       </c>
       <c r="N3" s="7">
-        <f t="shared" si="3"/>
-        <v>0.52</v>
+        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <v>0.51</v>
       </c>
       <c r="O3" s="7">
-        <f t="shared" si="4"/>
-        <v>0.02</v>
+        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <v>0.18</v>
       </c>
       <c r="P3" s="7">
-        <f t="shared" si="5"/>
-        <v>0.14000000000000001</v>
+        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <v>0.16</v>
       </c>
       <c r="Q3" s="7">
-        <f t="shared" si="6"/>
-        <v>0.96</v>
+        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <v>0.97</v>
       </c>
       <c r="R3" s="7">
-        <f t="shared" si="7"/>
-        <v>68.179999999999993</v>
+        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <v>67.86</v>
       </c>
       <c r="S3" s="7">
-        <f t="shared" si="8"/>
-        <v>51.52</v>
+        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <v>50.72</v>
       </c>
       <c r="T3" s="9" t="s">
         <v>43</v>
@@ -1044,76 +1044,76 @@
         <v>25</v>
       </c>
       <c r="V3" s="1">
-        <f t="shared" si="9"/>
-        <v>0.99367336152219865</v>
+        <f>((K3/2)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <v>0.99645083639330878</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="32">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C4" s="32">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D4" s="32">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" s="32">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" s="32">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="32">
-        <v>499</v>
+        <v>567</v>
       </c>
       <c r="H4" s="32">
         <v>10</v>
       </c>
       <c r="I4" s="32">
-        <v>4767</v>
+        <v>6274</v>
       </c>
       <c r="J4" s="32">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K4" s="33">
-        <f t="shared" si="0"/>
-        <v>0.93</v>
+        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <v>1</v>
       </c>
       <c r="L4" s="34">
-        <f t="shared" si="1"/>
-        <v>8.8888888888888892E-2</v>
+        <f>E4/J4</f>
+        <v>0.14285714285714285</v>
       </c>
       <c r="M4" s="34">
-        <f t="shared" si="2"/>
-        <v>0.31111111111111112</v>
+        <f>D4/J4</f>
+        <v>0.3392857142857143</v>
       </c>
       <c r="N4" s="33">
-        <f t="shared" si="3"/>
-        <v>0.44</v>
+        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <v>0.39</v>
       </c>
       <c r="O4" s="33">
-        <f t="shared" si="4"/>
-        <v>11.09</v>
+        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <v>10.130000000000001</v>
       </c>
       <c r="P4" s="33">
-        <f t="shared" si="5"/>
-        <v>0.22</v>
+        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <v>0.18</v>
       </c>
       <c r="Q4" s="33">
-        <f t="shared" si="6"/>
-        <v>2.1</v>
+        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <v>2.5499999999999998</v>
       </c>
       <c r="R4" s="33">
-        <f t="shared" si="7"/>
-        <v>64.290000000000006</v>
+        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <v>60.709999999999994</v>
       </c>
       <c r="S4" s="33">
-        <f t="shared" si="8"/>
-        <v>105.93</v>
+        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <v>112.04</v>
       </c>
       <c r="T4" s="32" t="s">
         <v>43</v>
@@ -1122,76 +1122,76 @@
         <v>25</v>
       </c>
       <c r="V4" s="1">
-        <f t="shared" si="9"/>
-        <v>1.6242532299741601</v>
+        <f>((K4/2)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <v>1.7535091362126245</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="46" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="32">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" s="32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="32">
         <v>0</v>
       </c>
       <c r="F5" s="32">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5" s="32">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="H5" s="32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="32">
-        <v>2140</v>
+        <v>2646</v>
       </c>
       <c r="J5" s="32">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K5" s="33">
-        <f t="shared" si="0"/>
-        <v>0.44</v>
+        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <v>0.45</v>
       </c>
       <c r="L5" s="34">
-        <f t="shared" si="1"/>
+        <f>E5/J5</f>
         <v>0</v>
       </c>
       <c r="M5" s="34">
-        <f t="shared" si="2"/>
-        <v>4.4444444444444446E-2</v>
+        <f>D5/J5</f>
+        <v>5.3571428571428568E-2</v>
       </c>
       <c r="N5" s="33">
-        <f t="shared" si="3"/>
-        <v>0.57999999999999996</v>
+        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <v>0.56999999999999995</v>
       </c>
       <c r="O5" s="33">
-        <f t="shared" si="4"/>
-        <v>1.98</v>
+        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <v>2.27</v>
       </c>
       <c r="P5" s="33">
-        <f t="shared" si="5"/>
-        <v>0.22</v>
+        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="33">
-        <f t="shared" si="6"/>
-        <v>0.77</v>
+        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <v>0.78</v>
       </c>
       <c r="R5" s="33">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C5,B5),4)*100</f>
         <v>40</v>
       </c>
       <c r="S5" s="33">
-        <f t="shared" si="8"/>
-        <v>47.56</v>
+        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <v>47.25</v>
       </c>
       <c r="T5" s="32" t="s">
         <v>43</v>
@@ -1200,11 +1200,11 @@
         <v>25</v>
       </c>
       <c r="V5" s="1">
-        <f t="shared" si="9"/>
-        <v>0.88332041343669254</v>
+        <f>((K5/2)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <v>0.89816029900332239</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="39" t="s">
         <v>32</v>
       </c>
@@ -1236,39 +1236,39 @@
         <v>64</v>
       </c>
       <c r="K6" s="10">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B6,J6),2)</f>
         <v>0.78</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" si="1"/>
+        <f>E6/J6</f>
         <v>6.25E-2</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" si="2"/>
+        <f>D6/J6</f>
         <v>0.15625</v>
       </c>
       <c r="N6" s="10">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F6,J6),2)</f>
         <v>0.5</v>
       </c>
       <c r="O6" s="10">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G6,J6),2)</f>
         <v>2.56</v>
       </c>
       <c r="P6" s="10">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H6,J6),2)</f>
         <v>0.42</v>
       </c>
       <c r="Q6" s="10">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B6,F6),2)</f>
         <v>1.56</v>
       </c>
       <c r="R6" s="10">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C6,B6),4)*100</f>
         <v>54</v>
       </c>
       <c r="S6" s="10">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I6,J6),2)</f>
         <v>89.8</v>
       </c>
       <c r="T6" s="11" t="s">
@@ -1278,11 +1278,11 @@
         <v>25</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" si="9"/>
+        <f>((K6/2)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
         <v>1.3802369186046513</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="39" t="s">
         <v>33</v>
       </c>
@@ -1314,39 +1314,39 @@
         <v>64</v>
       </c>
       <c r="K7" s="10">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B7,J7),2)</f>
         <v>0.52</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" si="1"/>
+        <f>E7/J7</f>
         <v>3.125E-2</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" si="2"/>
+        <f>D7/J7</f>
         <v>6.25E-2</v>
       </c>
       <c r="N7" s="10">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F7,J7),2)</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="O7" s="10">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G7,J7),2)</f>
         <v>3.69</v>
       </c>
       <c r="P7" s="10">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H7,J7),2)</f>
         <v>0.23</v>
       </c>
       <c r="Q7" s="10">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B7,F7),2)</f>
         <v>0.92</v>
       </c>
       <c r="R7" s="10">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C7,B7),4)*100</f>
         <v>48.480000000000004</v>
       </c>
       <c r="S7" s="10">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I7,J7),2)</f>
         <v>60.06</v>
       </c>
       <c r="T7" s="11" t="s">
@@ -1356,11 +1356,11 @@
         <v>25</v>
       </c>
       <c r="V7" s="1">
-        <f t="shared" si="9"/>
+        <f>((K7/2)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
         <v>1.0127238372093021</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="40" t="s">
         <v>30</v>
       </c>
@@ -1392,39 +1392,39 @@
         <v>53</v>
       </c>
       <c r="K8" s="13">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B8,J8),2)</f>
         <v>0.85</v>
       </c>
       <c r="L8" s="14">
-        <f t="shared" si="1"/>
+        <f>E8/J8</f>
         <v>7.5471698113207544E-2</v>
       </c>
       <c r="M8" s="14">
-        <f t="shared" si="2"/>
+        <f>D8/J8</f>
         <v>0.22641509433962265</v>
       </c>
       <c r="N8" s="13">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F8,J8),2)</f>
         <v>0.47</v>
       </c>
       <c r="O8" s="13">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G8,J8),2)</f>
         <v>4.79</v>
       </c>
       <c r="P8" s="13">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H8,J8),2)</f>
         <v>0.15</v>
       </c>
       <c r="Q8" s="13">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B8,F8),2)</f>
         <v>1.8</v>
       </c>
       <c r="R8" s="13">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C8,B8),4)*100</f>
         <v>46.67</v>
       </c>
       <c r="S8" s="13">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I8,J8),2)</f>
         <v>102.02</v>
       </c>
       <c r="T8" s="15" t="s">
@@ -1434,11 +1434,11 @@
         <v>25</v>
       </c>
       <c r="V8" s="1">
-        <f t="shared" si="9"/>
+        <f>((K8/2)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
         <v>1.5087097411145238</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="40" t="s">
         <v>31</v>
       </c>
@@ -1470,39 +1470,39 @@
         <v>53</v>
       </c>
       <c r="K9" s="13">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B9,J9),2)</f>
         <v>0.43</v>
       </c>
       <c r="L9" s="14">
-        <f t="shared" si="1"/>
+        <f>E9/J9</f>
         <v>0</v>
       </c>
       <c r="M9" s="14">
-        <f t="shared" si="2"/>
+        <f>D9/J9</f>
         <v>3.7735849056603772E-2</v>
       </c>
       <c r="N9" s="13">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F9,J9),2)</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O9" s="13">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G9,J9),2)</f>
         <v>1.79</v>
       </c>
       <c r="P9" s="13">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H9,J9),2)</f>
         <v>0.08</v>
       </c>
       <c r="Q9" s="13">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B9,F9),2)</f>
         <v>0.79</v>
       </c>
       <c r="R9" s="13">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C9,B9),4)*100</f>
         <v>43.480000000000004</v>
       </c>
       <c r="S9" s="13">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I9,J9),2)</f>
         <v>52.62</v>
       </c>
       <c r="T9" s="15" t="s">
@@ -1512,19 +1512,19 @@
         <v>25</v>
       </c>
       <c r="V9" s="1">
-        <f t="shared" si="9"/>
+        <f>((K9/2)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
         <v>0.92317814831066247</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="45" t="s">
         <v>38</v>
       </c>
       <c r="B10" s="29">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="29">
         <v>5</v>
@@ -1533,55 +1533,55 @@
         <v>4</v>
       </c>
       <c r="F10" s="29">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G10" s="29">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H10" s="29">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I10" s="29">
-        <v>4138</v>
+        <v>4633</v>
       </c>
       <c r="J10" s="29">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K10" s="30">
-        <f t="shared" si="0"/>
-        <v>0.7</v>
+        <f>ROUND(IMDIV(B10,J10),2)</f>
+        <v>0.6</v>
       </c>
       <c r="L10" s="31">
-        <f t="shared" si="1"/>
-        <v>8.5106382978723402E-2</v>
+        <f>E10/J10</f>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="M10" s="31">
-        <f t="shared" si="2"/>
-        <v>0.10638297872340426</v>
+        <f>D10/J10</f>
+        <v>8.6206896551724144E-2</v>
       </c>
       <c r="N10" s="30">
-        <f t="shared" si="3"/>
-        <v>0.53</v>
+        <f>ROUND(IMDIV(F10,J10),2)</f>
+        <v>0.6</v>
       </c>
       <c r="O10" s="30">
-        <f t="shared" si="4"/>
-        <v>1.1100000000000001</v>
+        <f>ROUND(IMDIV(G10,J10),2)</f>
+        <v>0.93</v>
       </c>
       <c r="P10" s="30">
-        <f t="shared" si="5"/>
-        <v>0.32</v>
+        <f>ROUND(IMDIV(H10,J10),2)</f>
+        <v>0.31</v>
       </c>
       <c r="Q10" s="30">
-        <f t="shared" si="6"/>
-        <v>1.32</v>
+        <f>ROUND(IMDIV(B10,F10),2)</f>
+        <v>1</v>
       </c>
       <c r="R10" s="30">
-        <f t="shared" si="7"/>
-        <v>63.639999999999993</v>
+        <f>ROUND(IMDIV(C10,B10),4)*100</f>
+        <v>62.860000000000007</v>
       </c>
       <c r="S10" s="30">
-        <f t="shared" si="8"/>
-        <v>88.04</v>
+        <f>ROUND(IMDIV(I10,J10),2)</f>
+        <v>79.88</v>
       </c>
       <c r="T10" s="29" t="s">
         <v>43</v>
@@ -1590,76 +1590,76 @@
         <v>25</v>
       </c>
       <c r="V10" s="1">
-        <f t="shared" si="9"/>
-        <v>1.289105393369619</v>
+        <f>((K10/2)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
+        <v>1.122379711307137</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="29">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11" s="29">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D11" s="29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="29">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G11" s="29">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="H11" s="29">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I11" s="29">
-        <v>2951</v>
+        <v>3578</v>
       </c>
       <c r="J11" s="29">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K11" s="30">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f>ROUND(IMDIV(B11,J11),2)</f>
+        <v>0.59</v>
       </c>
       <c r="L11" s="31">
-        <f t="shared" si="1"/>
-        <v>2.1276595744680851E-2</v>
+        <f>E11/J11</f>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="M11" s="31">
-        <f t="shared" si="2"/>
-        <v>0.10638297872340426</v>
+        <f>D11/J11</f>
+        <v>0.10344827586206896</v>
       </c>
       <c r="N11" s="30">
-        <f t="shared" si="3"/>
-        <v>0.64</v>
+        <f>ROUND(IMDIV(F11,J11),2)</f>
+        <v>0.67</v>
       </c>
       <c r="O11" s="30">
-        <f t="shared" si="4"/>
-        <v>3.66</v>
+        <f>ROUND(IMDIV(G11,J11),2)</f>
+        <v>3.36</v>
       </c>
       <c r="P11" s="30">
-        <f t="shared" si="5"/>
-        <v>0.32</v>
+        <f>ROUND(IMDIV(H11,J11),2)</f>
+        <v>0.31</v>
       </c>
       <c r="Q11" s="30">
-        <f t="shared" si="6"/>
-        <v>0.93</v>
+        <f>ROUND(IMDIV(B11,F11),2)</f>
+        <v>0.87</v>
       </c>
       <c r="R11" s="30">
-        <f t="shared" si="7"/>
-        <v>25</v>
+        <f>ROUND(IMDIV(C11,B11),4)*100</f>
+        <v>35.29</v>
       </c>
       <c r="S11" s="30">
-        <f t="shared" si="8"/>
-        <v>62.79</v>
+        <f>ROUND(IMDIV(I11,J11),2)</f>
+        <v>61.69</v>
       </c>
       <c r="T11" s="29" t="s">
         <v>43</v>
@@ -1668,11 +1668,11 @@
         <v>25</v>
       </c>
       <c r="V11" s="1">
-        <f t="shared" si="9"/>
-        <v>0.9988975754576942</v>
+        <f>((K11/2)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
+        <v>0.96018885324779468</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="43" t="s">
         <v>35</v>
       </c>
@@ -1704,39 +1704,39 @@
         <v>59</v>
       </c>
       <c r="K12" s="23">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B12,J12),2)</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="L12" s="24">
-        <f t="shared" si="1"/>
+        <f>E12/J12</f>
         <v>0.10169491525423729</v>
       </c>
       <c r="M12" s="24">
-        <f t="shared" si="2"/>
+        <f>D12/J12</f>
         <v>0.1864406779661017</v>
       </c>
       <c r="N12" s="23">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F12,J12),2)</f>
         <v>0.61</v>
       </c>
       <c r="O12" s="23">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G12,J12),2)</f>
         <v>1.81</v>
       </c>
       <c r="P12" s="23">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H12,J12),2)</f>
         <v>0.12</v>
       </c>
       <c r="Q12" s="23">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B12,F12),2)</f>
         <v>0.94</v>
       </c>
       <c r="R12" s="23">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C12,B12),4)*100</f>
         <v>73.53</v>
       </c>
       <c r="S12" s="23">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I12,J12),2)</f>
         <v>57.97</v>
       </c>
       <c r="T12" s="25" t="s">
@@ -1746,11 +1746,11 @@
         <v>25</v>
       </c>
       <c r="V12" s="1">
-        <f t="shared" si="9"/>
+        <f>((K12/2)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
         <v>1.022577059519117</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="43" t="s">
         <v>36</v>
       </c>
@@ -1782,39 +1782,39 @@
         <v>59</v>
       </c>
       <c r="K13" s="23">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B13,J13),2)</f>
         <v>0.53</v>
       </c>
       <c r="L13" s="24">
-        <f t="shared" si="1"/>
+        <f>E13/J13</f>
         <v>3.3898305084745763E-2</v>
       </c>
       <c r="M13" s="24">
-        <f t="shared" si="2"/>
+        <f>D13/J13</f>
         <v>0.15254237288135594</v>
       </c>
       <c r="N13" s="23">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F13,J13),2)</f>
         <v>0.71</v>
       </c>
       <c r="O13" s="23">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G13,J13),2)</f>
         <v>0.54</v>
       </c>
       <c r="P13" s="23">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H13,J13),2)</f>
         <v>0.22</v>
       </c>
       <c r="Q13" s="23">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B13,F13),2)</f>
         <v>0.74</v>
       </c>
       <c r="R13" s="23">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C13,B13),4)*100</f>
         <v>45.16</v>
       </c>
       <c r="S13" s="23">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I13,J13),2)</f>
         <v>68.489999999999995</v>
       </c>
       <c r="T13" s="25" t="s">
@@ -1824,11 +1824,11 @@
         <v>25</v>
       </c>
       <c r="V13" s="1">
-        <f t="shared" si="9"/>
+        <f>((K13/2)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
         <v>0.92947339377217186</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
         <v>42</v>
       </c>
@@ -1860,39 +1860,39 @@
         <v>51</v>
       </c>
       <c r="K14" s="36">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B14,J14),2)</f>
         <v>0.63</v>
       </c>
       <c r="L14" s="37">
-        <f t="shared" si="1"/>
+        <f>E14/J14</f>
         <v>1.9607843137254902E-2</v>
       </c>
       <c r="M14" s="37">
-        <f t="shared" si="2"/>
+        <f>D14/J14</f>
         <v>0.17647058823529413</v>
       </c>
       <c r="N14" s="36">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F14,J14),2)</f>
         <v>0.61</v>
       </c>
       <c r="O14" s="36">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G14,J14),2)</f>
         <v>2.9</v>
       </c>
       <c r="P14" s="36">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H14,J14),2)</f>
         <v>0.27</v>
       </c>
       <c r="Q14" s="36">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B14,F14),2)</f>
         <v>1.03</v>
       </c>
       <c r="R14" s="36">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C14,B14),4)*100</f>
         <v>43.75</v>
       </c>
       <c r="S14" s="36">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I14,J14),2)</f>
         <v>80.55</v>
       </c>
       <c r="T14" s="35" t="s">
@@ -1902,11 +1902,11 @@
         <v>25</v>
       </c>
       <c r="V14" s="1">
-        <f t="shared" si="9"/>
+        <f>((K14/2)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
         <v>1.1411903784769721</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="s">
         <v>27</v>
       </c>
@@ -1938,39 +1938,39 @@
         <v>51</v>
       </c>
       <c r="K15" s="36">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B15,J15),2)</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="L15" s="37">
-        <f t="shared" si="1"/>
+        <f>E15/J15</f>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="M15" s="37">
-        <f t="shared" si="2"/>
+        <f>D15/J15</f>
         <v>0.13725490196078433</v>
       </c>
       <c r="N15" s="36">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F15,J15),2)</f>
         <v>0.59</v>
       </c>
       <c r="O15" s="36">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G15,J15),2)</f>
         <v>4.96</v>
       </c>
       <c r="P15" s="36">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H15,J15),2)</f>
         <v>0.04</v>
       </c>
       <c r="Q15" s="36">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B15,F15),2)</f>
         <v>0.93</v>
       </c>
       <c r="R15" s="36">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C15,B15),4)*100</f>
         <v>46.43</v>
       </c>
       <c r="S15" s="36">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I15,J15),2)</f>
         <v>57.08</v>
       </c>
       <c r="T15" s="35" t="s">
@@ -1980,11 +1980,11 @@
         <v>25</v>
       </c>
       <c r="V15" s="1">
-        <f t="shared" si="9"/>
+        <f>((K15/2)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
         <v>0.99856680346557225</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="42" t="s">
         <v>23</v>
       </c>
@@ -2016,39 +2016,39 @@
         <v>50</v>
       </c>
       <c r="K16" s="20">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B16,J16),2)</f>
         <v>0.4</v>
       </c>
       <c r="L16" s="21">
-        <f t="shared" si="1"/>
+        <f>E16/J16</f>
         <v>0.02</v>
       </c>
       <c r="M16" s="21">
-        <f t="shared" si="2"/>
+        <f>D16/J16</f>
         <v>0.1</v>
       </c>
       <c r="N16" s="20">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F16,J16),2)</f>
         <v>0.7</v>
       </c>
       <c r="O16" s="20">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G16,J16),2)</f>
         <v>2.2599999999999998</v>
       </c>
       <c r="P16" s="20">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H16,J16),2)</f>
         <v>0.18</v>
       </c>
       <c r="Q16" s="20">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B16,F16),2)</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="R16" s="20">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C16,B16),4)*100</f>
         <v>60</v>
       </c>
       <c r="S16" s="20">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I16,J16),2)</f>
         <v>60.28</v>
       </c>
       <c r="T16" s="20" t="s">
@@ -2058,11 +2058,11 @@
         <v>25</v>
       </c>
       <c r="V16" s="1">
-        <f t="shared" si="9"/>
+        <f>((K16/2)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
         <v>0.81837209302325586</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="42" t="s">
         <v>24</v>
       </c>
@@ -2094,39 +2094,39 @@
         <v>50</v>
       </c>
       <c r="K17" s="20">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B17,J17),2)</f>
         <v>0.38</v>
       </c>
       <c r="L17" s="21">
-        <f t="shared" si="1"/>
+        <f>E17/J17</f>
         <v>0.02</v>
       </c>
       <c r="M17" s="21">
-        <f t="shared" si="2"/>
+        <f>D17/J17</f>
         <v>0.08</v>
       </c>
       <c r="N17" s="20">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F17,J17),2)</f>
         <v>0.64</v>
       </c>
       <c r="O17" s="20">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G17,J17),2)</f>
         <v>0.52</v>
       </c>
       <c r="P17" s="20">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H17,J17),2)</f>
         <v>0.2</v>
       </c>
       <c r="Q17" s="20">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B17,F17),2)</f>
         <v>0.59</v>
       </c>
       <c r="R17" s="20">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C17,B17),4)*100</f>
         <v>42.11</v>
       </c>
       <c r="S17" s="20">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I17,J17),2)</f>
         <v>48.4</v>
       </c>
       <c r="T17" s="20" t="s">
@@ -2136,11 +2136,11 @@
         <v>25</v>
       </c>
       <c r="V17" s="1">
-        <f t="shared" si="9"/>
+        <f>((K17/2)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
         <v>0.80911627906976746</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
         <v>37</v>
       </c>
@@ -2172,39 +2172,39 @@
         <v>51</v>
       </c>
       <c r="K18" s="27">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B18,J18),2)</f>
         <v>0.65</v>
       </c>
       <c r="L18" s="28">
-        <f t="shared" si="1"/>
+        <f>E18/J18</f>
         <v>1.9607843137254902E-2</v>
       </c>
       <c r="M18" s="28">
-        <f t="shared" si="2"/>
+        <f>D18/J18</f>
         <v>0.19607843137254902</v>
       </c>
       <c r="N18" s="27">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F18,J18),2)</f>
         <v>0.65</v>
       </c>
       <c r="O18" s="27">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G18,J18),2)</f>
         <v>5.12</v>
       </c>
       <c r="P18" s="27">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H18,J18),2)</f>
         <v>0.12</v>
       </c>
       <c r="Q18" s="27">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B18,F18),2)</f>
         <v>1</v>
       </c>
       <c r="R18" s="27">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C18,B18),4)*100</f>
         <v>51.519999999999996</v>
       </c>
       <c r="S18" s="27">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I18,J18),2)</f>
         <v>85.92</v>
       </c>
       <c r="T18" s="27" t="s">
@@ -2214,11 +2214,11 @@
         <v>25</v>
       </c>
       <c r="V18" s="1">
-        <f t="shared" si="9"/>
+        <f>((K18/2)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
         <v>1.1335690834473324</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
         <v>26</v>
       </c>
@@ -2250,39 +2250,39 @@
         <v>51</v>
       </c>
       <c r="K19" s="27">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B19,J19),2)</f>
         <v>0.37</v>
       </c>
       <c r="L19" s="28">
-        <f t="shared" si="1"/>
+        <f>E19/J19</f>
         <v>3.9215686274509803E-2</v>
       </c>
       <c r="M19" s="28">
-        <f t="shared" si="2"/>
+        <f>D19/J19</f>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="N19" s="27">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F19,J19),2)</f>
         <v>0.65</v>
       </c>
       <c r="O19" s="27">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G19,J19),2)</f>
         <v>1.65</v>
       </c>
       <c r="P19" s="27">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H19,J19),2)</f>
         <v>0.16</v>
       </c>
       <c r="Q19" s="27">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B19,F19),2)</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="R19" s="27">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C19,B19),4)*100</f>
         <v>52.629999999999995</v>
       </c>
       <c r="S19" s="27">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I19,J19),2)</f>
         <v>42.06</v>
       </c>
       <c r="T19" s="27" t="s">
@@ -2292,76 +2292,76 @@
         <v>25</v>
       </c>
       <c r="V19" s="1">
-        <f t="shared" si="9"/>
+        <f>((K19/2)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
         <v>0.77098084815321477</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="18">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C20" s="18">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D20" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" s="18">
         <v>4</v>
       </c>
       <c r="F20" s="18">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G20" s="18">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H20" s="18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I20" s="18">
-        <v>3074</v>
+        <v>4101</v>
       </c>
       <c r="J20" s="18">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K20" s="17">
-        <f t="shared" si="0"/>
-        <v>0.67</v>
+        <f>ROUND(IMDIV(B20,J20),2)</f>
+        <v>0.65</v>
       </c>
       <c r="L20" s="19">
-        <f t="shared" si="1"/>
-        <v>9.5238095238095233E-2</v>
+        <f>E20/J20</f>
+        <v>7.2727272727272724E-2</v>
       </c>
       <c r="M20" s="19">
-        <f t="shared" si="2"/>
-        <v>0.19047619047619047</v>
+        <f>D20/J20</f>
+        <v>0.18181818181818182</v>
       </c>
       <c r="N20" s="17">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F20,J20),2)</f>
         <v>0.69</v>
       </c>
       <c r="O20" s="17">
-        <f t="shared" si="4"/>
-        <v>0.67</v>
+        <f>ROUND(IMDIV(G20,J20),2)</f>
+        <v>0.71</v>
       </c>
       <c r="P20" s="17">
-        <f t="shared" si="5"/>
-        <v>0.28999999999999998</v>
+        <f>ROUND(IMDIV(H20,J20),2)</f>
+        <v>0.25</v>
       </c>
       <c r="Q20" s="17">
-        <f t="shared" si="6"/>
-        <v>0.97</v>
+        <f>ROUND(IMDIV(B20,F20),2)</f>
+        <v>0.95</v>
       </c>
       <c r="R20" s="17">
-        <f t="shared" si="7"/>
-        <v>75</v>
+        <f>ROUND(IMDIV(C20,B20),4)*100</f>
+        <v>80.56</v>
       </c>
       <c r="S20" s="17">
-        <f t="shared" si="8"/>
-        <v>73.19</v>
+        <f>ROUND(IMDIV(I20,J20),2)</f>
+        <v>74.56</v>
       </c>
       <c r="T20" s="18" t="s">
         <v>43</v>
@@ -2370,19 +2370,19 @@
         <v>25</v>
       </c>
       <c r="V20" s="1">
-        <f t="shared" si="9"/>
-        <v>1.0665852713178294</v>
+        <f>((K20/2)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
+        <v>1.0542906976744186</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C21" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
         <v>2</v>
@@ -2391,55 +2391,55 @@
         <v>0</v>
       </c>
       <c r="F21" s="18">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G21" s="18">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" s="18">
-        <v>1732</v>
+        <v>1940</v>
       </c>
       <c r="J21" s="18">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K21" s="17">
-        <f t="shared" si="0"/>
-        <v>0.33</v>
+        <f>ROUND(IMDIV(B21,J21),2)</f>
+        <v>0.31</v>
       </c>
       <c r="L21" s="19">
-        <f t="shared" si="1"/>
+        <f>E21/J21</f>
         <v>0</v>
       </c>
       <c r="M21" s="19">
-        <f t="shared" si="2"/>
-        <v>4.7619047619047616E-2</v>
+        <f>D21/J21</f>
+        <v>3.6363636363636362E-2</v>
       </c>
       <c r="N21" s="17">
-        <f t="shared" si="3"/>
-        <v>0.76</v>
+        <f>ROUND(IMDIV(F21,J21),2)</f>
+        <v>0.78</v>
       </c>
       <c r="O21" s="17">
-        <f t="shared" si="4"/>
-        <v>1.67</v>
+        <f>ROUND(IMDIV(G21,J21),2)</f>
+        <v>1.31</v>
       </c>
       <c r="P21" s="17">
-        <f t="shared" si="5"/>
-        <v>0.14000000000000001</v>
+        <f>ROUND(IMDIV(H21,J21),2)</f>
+        <v>0.15</v>
       </c>
       <c r="Q21" s="17">
-        <f t="shared" si="6"/>
-        <v>0.44</v>
+        <f>ROUND(IMDIV(B21,F21),2)</f>
+        <v>0.4</v>
       </c>
       <c r="R21" s="17">
-        <f t="shared" si="7"/>
-        <v>42.86</v>
+        <f>ROUND(IMDIV(C21,B21),4)*100</f>
+        <v>47.06</v>
       </c>
       <c r="S21" s="17">
-        <f t="shared" si="8"/>
-        <v>41.24</v>
+        <f>ROUND(IMDIV(I21,J21),2)</f>
+        <v>35.270000000000003</v>
       </c>
       <c r="T21" s="18" t="s">
         <v>43</v>
@@ -2448,8 +2448,8 @@
         <v>25</v>
       </c>
       <c r="V21" s="1">
-        <f t="shared" si="9"/>
-        <v>0.61571871539313405</v>
+        <f>((K21/2)+(M21/4)+(L21/5)-(N21)+(S21/215)+(P21/20))+1</f>
+        <v>0.55563742071881594</v>
       </c>
     </row>
   </sheetData>

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD717005-AA16-4174-8D22-3D5C61F0461F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12175DF-A587-44C0-97C0-193FE524A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5550" yWindow="4290" windowWidth="28800" windowHeight="15345" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
   <si>
     <t>player</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>5th</t>
+  </si>
+  <si>
+    <t>165+128</t>
   </si>
 </sst>
 </file>
@@ -494,135 +497,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1056,31 +931,31 @@
         <v>28</v>
       </c>
       <c r="B2" s="6">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C2" s="6">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D2" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="6">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G2" s="6">
-        <v>497</v>
+        <v>618</v>
       </c>
       <c r="H2" s="6">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I2" s="6">
-        <v>7151</v>
+        <v>8756</v>
       </c>
       <c r="J2" s="6">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K2" s="6">
         <f>ROUND(IMDIV(B2,J2),2)</f>
@@ -1088,35 +963,35 @@
       </c>
       <c r="L2" s="7">
         <f>E2/J2</f>
-        <v>5.8823529411764705E-2</v>
+        <v>6.0240963855421686E-2</v>
       </c>
       <c r="M2" s="7">
         <f>D2/J2</f>
-        <v>0.27941176470588236</v>
+        <v>0.28915662650602408</v>
       </c>
       <c r="N2" s="6">
         <f>ROUND(IMDIV(F2,J2),2)</f>
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="O2" s="6">
         <f>ROUND(IMDIV(G2,J2),2)</f>
-        <v>7.31</v>
+        <v>7.45</v>
       </c>
       <c r="P2" s="6">
         <f>ROUND(IMDIV(H2,J2),2)</f>
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="Q2" s="6">
         <f>ROUND(IMDIV(B2,F2),2)</f>
-        <v>2.65</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="R2" s="6">
         <f>ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>68.12</v>
+        <v>66.67</v>
       </c>
       <c r="S2" s="6">
         <f>ROUND(IMDIV(I2,J2),2)</f>
-        <v>105.16</v>
+        <v>105.49</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>47</v>
@@ -1126,7 +1001,7 @@
       </c>
       <c r="V2" s="45">
         <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>1.6107339261285909</v>
+        <v>1.595988512188288</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1134,67 +1009,67 @@
         <v>27</v>
       </c>
       <c r="B3" s="6">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C3" s="6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="6">
         <v>1</v>
       </c>
       <c r="F3" s="6">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G3" s="6">
         <v>41</v>
       </c>
       <c r="H3" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I3" s="6">
-        <v>3727</v>
+        <v>4432</v>
       </c>
       <c r="J3" s="6">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K3" s="6">
         <f>ROUND(IMDIV(B3,J3),2)</f>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="L3" s="7">
         <f>E3/J3</f>
-        <v>1.4705882352941176E-2</v>
+        <v>1.2048192771084338E-2</v>
       </c>
       <c r="M3" s="7">
         <f>D3/J3</f>
-        <v>7.3529411764705885E-2</v>
+        <v>7.2289156626506021E-2</v>
       </c>
       <c r="N3" s="6">
         <f>ROUND(IMDIV(F3,J3),2)</f>
-        <v>0.51</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O3" s="6">
         <f>ROUND(IMDIV(G3,J3),2)</f>
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="P3" s="6">
         <f>ROUND(IMDIV(H3,J3),2)</f>
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q3" s="6">
         <f>ROUND(IMDIV(B3,F3),2)</f>
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="R3" s="6">
         <f>ROUND(IMDIV(C3,B3),4)*100</f>
-        <v>62.860000000000007</v>
+        <v>58.540000000000006</v>
       </c>
       <c r="S3" s="6">
         <f>ROUND(IMDIV(I3,J3),2)</f>
-        <v>54.81</v>
+        <v>53.4</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>47</v>
@@ -1204,7 +1079,7 @@
       </c>
       <c r="V3" s="45">
         <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
-        <v>0.97775376196990427</v>
+        <v>0.92285402073409917</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1212,39 +1087,39 @@
         <v>31</v>
       </c>
       <c r="B4" s="9">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C4" s="9">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D4" s="9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" s="9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="9">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G4" s="9">
         <v>167</v>
       </c>
       <c r="H4" s="9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I4" s="9">
-        <v>8567</v>
+        <v>9617</v>
       </c>
       <c r="J4" s="9">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="K4" s="9">
         <f>ROUND(IMDIV(B4,J4),2)</f>
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="L4" s="11">
         <f>E4/J4</f>
-        <v>8.4210526315789472E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="M4" s="11">
         <f>D4/J4</f>
@@ -1252,27 +1127,27 @@
       </c>
       <c r="N4" s="9">
         <f>ROUND(IMDIV(F4,J4),2)</f>
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="O4" s="9">
         <f>ROUND(IMDIV(G4,J4),2)</f>
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="P4" s="9">
         <f>ROUND(IMDIV(H4,J4),2)</f>
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Q4" s="9">
         <f>ROUND(IMDIV(B4,F4),2)</f>
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="R4" s="9">
         <f>ROUND(IMDIV(C4,B4),4)*100</f>
-        <v>53.25</v>
+        <v>51.160000000000004</v>
       </c>
       <c r="S4" s="9">
         <f>ROUND(IMDIV(I4,J4),2)</f>
-        <v>90.18</v>
+        <v>87.43</v>
       </c>
       <c r="T4" s="9" t="s">
         <v>46</v>
@@ -1282,7 +1157,7 @@
       </c>
       <c r="V4" s="45">
         <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
-        <v>1.3157839657282742</v>
+        <v>1.2708329809725158</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1290,51 +1165,51 @@
         <v>32</v>
       </c>
       <c r="B5" s="9">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C5" s="9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D5" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="9">
         <v>4</v>
       </c>
       <c r="F5" s="9">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G5" s="9">
-        <v>398</v>
+        <v>527</v>
       </c>
       <c r="H5" s="9">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I5" s="9">
-        <v>5369</v>
+        <v>6419</v>
       </c>
       <c r="J5" s="9">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="K5" s="9">
         <f>ROUND(IMDIV(B5,J5),2)</f>
-        <v>0.54</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L5" s="11">
         <f>E5/J5</f>
-        <v>4.2105263157894736E-2</v>
+        <v>3.6363636363636362E-2</v>
       </c>
       <c r="M5" s="11">
         <f>D5/J5</f>
-        <v>9.4736842105263161E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="N5" s="9">
         <f>ROUND(IMDIV(F5,J5),2)</f>
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="O5" s="9">
         <f>ROUND(IMDIV(G5,J5),2)</f>
-        <v>4.1900000000000004</v>
+        <v>4.79</v>
       </c>
       <c r="P5" s="9">
         <f>ROUND(IMDIV(H5,J5),2)</f>
@@ -1342,15 +1217,15 @@
       </c>
       <c r="Q5" s="9">
         <f>ROUND(IMDIV(B5,F5),2)</f>
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="R5" s="9">
         <f>ROUND(IMDIV(C5,B5),4)*100</f>
-        <v>45.1</v>
+        <v>46.67</v>
       </c>
       <c r="S5" s="9">
         <f>ROUND(IMDIV(I5,J5),2)</f>
-        <v>56.52</v>
+        <v>58.35</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>46</v>
@@ -1360,319 +1235,319 @@
       </c>
       <c r="V5" s="45">
         <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
-        <v>0.93898898408812725</v>
+        <v>0.92939534883720931</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="29">
-        <v>62</v>
-      </c>
-      <c r="C6" s="29">
+      <c r="A6" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="12">
+        <v>70</v>
+      </c>
+      <c r="C6" s="12">
+        <v>30</v>
+      </c>
+      <c r="D6" s="12">
+        <v>19</v>
+      </c>
+      <c r="E6" s="12">
+        <v>5</v>
+      </c>
+      <c r="F6" s="12">
         <v>38</v>
       </c>
-      <c r="D6" s="29">
-        <v>20</v>
-      </c>
-      <c r="E6" s="29">
-        <v>8</v>
-      </c>
-      <c r="F6" s="29">
-        <v>33</v>
-      </c>
-      <c r="G6" s="29">
-        <v>580</v>
-      </c>
-      <c r="H6" s="29">
-        <v>10</v>
-      </c>
-      <c r="I6" s="29">
-        <v>7210</v>
-      </c>
-      <c r="J6" s="29">
-        <v>68</v>
-      </c>
-      <c r="K6" s="30">
+      <c r="G6" s="12">
+        <v>302</v>
+      </c>
+      <c r="H6" s="12">
+        <v>9</v>
+      </c>
+      <c r="I6" s="12">
+        <v>8290</v>
+      </c>
+      <c r="J6" s="12">
+        <v>81</v>
+      </c>
+      <c r="K6" s="12">
         <f>ROUND(IMDIV(B6,J6),2)</f>
-        <v>0.91</v>
-      </c>
-      <c r="L6" s="31">
+        <v>0.86</v>
+      </c>
+      <c r="L6" s="13">
         <f>E6/J6</f>
-        <v>0.11764705882352941</v>
-      </c>
-      <c r="M6" s="31">
+        <v>6.1728395061728392E-2</v>
+      </c>
+      <c r="M6" s="13">
         <f>D6/J6</f>
-        <v>0.29411764705882354</v>
-      </c>
-      <c r="N6" s="30">
+        <v>0.23456790123456789</v>
+      </c>
+      <c r="N6" s="12">
         <f>ROUND(IMDIV(F6,J6),2)</f>
-        <v>0.49</v>
-      </c>
-      <c r="O6" s="30">
+        <v>0.47</v>
+      </c>
+      <c r="O6" s="12">
         <f>ROUND(IMDIV(G6,J6),2)</f>
-        <v>8.5299999999999994</v>
-      </c>
-      <c r="P6" s="30">
+        <v>3.73</v>
+      </c>
+      <c r="P6" s="12">
         <f>ROUND(IMDIV(H6,J6),2)</f>
-        <v>0.15</v>
-      </c>
-      <c r="Q6" s="30">
+        <v>0.11</v>
+      </c>
+      <c r="Q6" s="12">
         <f>ROUND(IMDIV(B6,F6),2)</f>
-        <v>1.88</v>
-      </c>
-      <c r="R6" s="30">
+        <v>1.84</v>
+      </c>
+      <c r="R6" s="12">
         <f>ROUND(IMDIV(C6,B6),4)*100</f>
-        <v>61.29</v>
-      </c>
-      <c r="S6" s="30">
+        <v>42.86</v>
+      </c>
+      <c r="S6" s="12">
         <f>ROUND(IMDIV(I6,J6),2)</f>
-        <v>106.03</v>
-      </c>
-      <c r="T6" s="29" t="s">
+        <v>102.35</v>
+      </c>
+      <c r="T6" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="29" t="s">
+      <c r="U6" s="14" t="s">
         <v>24</v>
       </c>
       <c r="V6" s="45">
         <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>1.4717216142270861</v>
+        <v>1.4265341659488946</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="12">
         <v>40</v>
       </c>
-      <c r="B7" s="29">
-        <v>28</v>
-      </c>
-      <c r="C7" s="29">
-        <v>10</v>
-      </c>
-      <c r="D7" s="29">
-        <v>3</v>
-      </c>
-      <c r="E7" s="29">
-        <v>0</v>
-      </c>
-      <c r="F7" s="29">
-        <v>41</v>
-      </c>
-      <c r="G7" s="29">
-        <v>132</v>
-      </c>
-      <c r="H7" s="29">
-        <v>18</v>
-      </c>
-      <c r="I7" s="29">
-        <v>2982</v>
-      </c>
-      <c r="J7" s="29">
-        <v>68</v>
-      </c>
-      <c r="K7" s="30">
+      <c r="C7" s="12">
+        <v>19</v>
+      </c>
+      <c r="D7" s="12">
+        <v>5</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12">
+        <v>42</v>
+      </c>
+      <c r="G7" s="12">
+        <v>115</v>
+      </c>
+      <c r="H7" s="12">
+        <v>8</v>
+      </c>
+      <c r="I7" s="12">
+        <v>4641</v>
+      </c>
+      <c r="J7" s="12">
+        <v>81</v>
+      </c>
+      <c r="K7" s="12">
         <f>ROUND(IMDIV(B7,J7),2)</f>
-        <v>0.41</v>
-      </c>
-      <c r="L7" s="31">
+        <v>0.49</v>
+      </c>
+      <c r="L7" s="13">
         <f>E7/J7</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="31">
+        <v>1.2345679012345678E-2</v>
+      </c>
+      <c r="M7" s="13">
         <f>D7/J7</f>
-        <v>4.4117647058823532E-2</v>
-      </c>
-      <c r="N7" s="30">
+        <v>6.1728395061728392E-2</v>
+      </c>
+      <c r="N7" s="12">
         <f>ROUND(IMDIV(F7,J7),2)</f>
-        <v>0.6</v>
-      </c>
-      <c r="O7" s="30">
+        <v>0.52</v>
+      </c>
+      <c r="O7" s="12">
         <f>ROUND(IMDIV(G7,J7),2)</f>
-        <v>1.94</v>
-      </c>
-      <c r="P7" s="30">
+        <v>1.42</v>
+      </c>
+      <c r="P7" s="12">
         <f>ROUND(IMDIV(H7,J7),2)</f>
-        <v>0.26</v>
-      </c>
-      <c r="Q7" s="30">
+        <v>0.1</v>
+      </c>
+      <c r="Q7" s="12">
         <f>ROUND(IMDIV(B7,F7),2)</f>
-        <v>0.68</v>
-      </c>
-      <c r="R7" s="30">
+        <v>0.95</v>
+      </c>
+      <c r="R7" s="12">
         <f>ROUND(IMDIV(C7,B7),4)*100</f>
-        <v>35.709999999999994</v>
-      </c>
-      <c r="S7" s="30">
+        <v>47.5</v>
+      </c>
+      <c r="S7" s="12">
         <f>ROUND(IMDIV(I7,J7),2)</f>
-        <v>43.85</v>
-      </c>
-      <c r="T7" s="29" t="s">
+        <v>57.3</v>
+      </c>
+      <c r="T7" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="U7" s="29" t="s">
+      <c r="U7" s="14" t="s">
         <v>24</v>
       </c>
       <c r="V7" s="45">
         <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
-        <v>0.79198290013679895</v>
+        <v>0.9654128624748779</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="29">
+        <v>86</v>
+      </c>
+      <c r="C8" s="29">
+        <v>50</v>
+      </c>
+      <c r="D8" s="29">
         <v>29</v>
       </c>
-      <c r="B8" s="12">
-        <v>70</v>
-      </c>
-      <c r="C8" s="12">
-        <v>30</v>
-      </c>
-      <c r="D8" s="12">
-        <v>19</v>
-      </c>
-      <c r="E8" s="12">
-        <v>5</v>
-      </c>
-      <c r="F8" s="12">
-        <v>38</v>
-      </c>
-      <c r="G8" s="12">
-        <v>302</v>
-      </c>
-      <c r="H8" s="12">
+      <c r="E8" s="29">
         <v>9</v>
       </c>
-      <c r="I8" s="12">
-        <v>8290</v>
-      </c>
-      <c r="J8" s="12">
-        <v>81</v>
-      </c>
-      <c r="K8" s="12">
+      <c r="F8" s="29">
+        <v>42</v>
+      </c>
+      <c r="G8" s="29">
+        <v>586</v>
+      </c>
+      <c r="H8" s="29">
+        <v>15</v>
+      </c>
+      <c r="I8" s="29">
+        <v>9874</v>
+      </c>
+      <c r="J8" s="29">
+        <v>93</v>
+      </c>
+      <c r="K8" s="30">
         <f>ROUND(IMDIV(B8,J8),2)</f>
-        <v>0.86</v>
-      </c>
-      <c r="L8" s="13">
+        <v>0.92</v>
+      </c>
+      <c r="L8" s="31">
         <f>E8/J8</f>
-        <v>6.1728395061728392E-2</v>
-      </c>
-      <c r="M8" s="13">
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="M8" s="31">
         <f>D8/J8</f>
-        <v>0.23456790123456789</v>
-      </c>
-      <c r="N8" s="12">
+        <v>0.31182795698924731</v>
+      </c>
+      <c r="N8" s="30">
         <f>ROUND(IMDIV(F8,J8),2)</f>
-        <v>0.47</v>
-      </c>
-      <c r="O8" s="12">
+        <v>0.45</v>
+      </c>
+      <c r="O8" s="30">
         <f>ROUND(IMDIV(G8,J8),2)</f>
-        <v>3.73</v>
-      </c>
-      <c r="P8" s="12">
+        <v>6.3</v>
+      </c>
+      <c r="P8" s="30">
         <f>ROUND(IMDIV(H8,J8),2)</f>
-        <v>0.11</v>
-      </c>
-      <c r="Q8" s="12">
+        <v>0.16</v>
+      </c>
+      <c r="Q8" s="30">
         <f>ROUND(IMDIV(B8,F8),2)</f>
-        <v>1.84</v>
-      </c>
-      <c r="R8" s="12">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="R8" s="30">
         <f>ROUND(IMDIV(C8,B8),4)*100</f>
-        <v>42.86</v>
-      </c>
-      <c r="S8" s="12">
+        <v>58.14</v>
+      </c>
+      <c r="S8" s="30">
         <f>ROUND(IMDIV(I8,J8),2)</f>
-        <v>102.35</v>
-      </c>
-      <c r="T8" s="51" t="s">
+        <v>106.17</v>
+      </c>
+      <c r="T8" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="U8" s="14" t="s">
+      <c r="U8" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V8" s="45">
         <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
-        <v>1.4265341659488946</v>
+        <v>1.5171257814453614</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="12">
+      <c r="B9" s="29">
+        <v>34</v>
+      </c>
+      <c r="C9" s="29">
+        <v>12</v>
+      </c>
+      <c r="D9" s="29">
+        <v>3</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29">
+        <v>51</v>
+      </c>
+      <c r="G9" s="29">
+        <v>165</v>
+      </c>
+      <c r="H9" s="29">
         <v>19</v>
       </c>
-      <c r="D9" s="12">
-        <v>5</v>
-      </c>
-      <c r="E9" s="12">
-        <v>1</v>
-      </c>
-      <c r="F9" s="12">
-        <v>42</v>
-      </c>
-      <c r="G9" s="12">
-        <v>115</v>
-      </c>
-      <c r="H9" s="12">
-        <v>8</v>
-      </c>
-      <c r="I9" s="12">
-        <v>4641</v>
-      </c>
-      <c r="J9" s="12">
-        <v>81</v>
-      </c>
-      <c r="K9" s="12">
+      <c r="I9" s="29">
+        <v>3824</v>
+      </c>
+      <c r="J9" s="29">
+        <v>93</v>
+      </c>
+      <c r="K9" s="30">
         <f>ROUND(IMDIV(B9,J9),2)</f>
-        <v>0.49</v>
-      </c>
-      <c r="L9" s="13">
+        <v>0.37</v>
+      </c>
+      <c r="L9" s="31">
         <f>E9/J9</f>
-        <v>1.2345679012345678E-2</v>
-      </c>
-      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="31">
         <f>D9/J9</f>
-        <v>6.1728395061728392E-2</v>
-      </c>
-      <c r="N9" s="12">
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N9" s="30">
         <f>ROUND(IMDIV(F9,J9),2)</f>
-        <v>0.52</v>
-      </c>
-      <c r="O9" s="12">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O9" s="30">
         <f>ROUND(IMDIV(G9,J9),2)</f>
-        <v>1.42</v>
-      </c>
-      <c r="P9" s="12">
+        <v>1.77</v>
+      </c>
+      <c r="P9" s="30">
         <f>ROUND(IMDIV(H9,J9),2)</f>
-        <v>0.1</v>
-      </c>
-      <c r="Q9" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="Q9" s="30">
         <f>ROUND(IMDIV(B9,F9),2)</f>
-        <v>0.95</v>
-      </c>
-      <c r="R9" s="12">
+        <v>0.67</v>
+      </c>
+      <c r="R9" s="30">
         <f>ROUND(IMDIV(C9,B9),4)*100</f>
-        <v>47.5</v>
-      </c>
-      <c r="S9" s="12">
+        <v>35.29</v>
+      </c>
+      <c r="S9" s="30">
         <f>ROUND(IMDIV(I9,J9),2)</f>
-        <v>57.3</v>
-      </c>
-      <c r="T9" s="51" t="s">
+        <v>41.12</v>
+      </c>
+      <c r="T9" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="U9" s="14" t="s">
+      <c r="U9" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V9" s="45">
         <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
-        <v>0.9654128624748779</v>
+        <v>0.80732033008252058</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1680,39 +1555,39 @@
         <v>37</v>
       </c>
       <c r="B10" s="26">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C10" s="26">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" s="26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="26">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="26">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="H10" s="26">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I10" s="26">
-        <v>6734</v>
+        <v>7436</v>
       </c>
       <c r="J10" s="26">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K10" s="27">
         <f>ROUND(IMDIV(B10,J10),2)</f>
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="L10" s="28">
         <f>E10/J10</f>
-        <v>8.6419753086419748E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="M10" s="28">
         <f>D10/J10</f>
@@ -1720,27 +1595,27 @@
       </c>
       <c r="N10" s="27">
         <f>ROUND(IMDIV(F10,J10),2)</f>
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="O10" s="27">
         <f>ROUND(IMDIV(G10,J10),2)</f>
-        <v>1.77</v>
+        <v>2.74</v>
       </c>
       <c r="P10" s="27">
         <f>ROUND(IMDIV(H10,J10),2)</f>
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="Q10" s="27">
         <f>ROUND(IMDIV(B10,F10),2)</f>
-        <v>1.1299999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="R10" s="27">
         <f>ROUND(IMDIV(C10,B10),4)*100</f>
-        <v>50</v>
+        <v>49.18</v>
       </c>
       <c r="S10" s="27">
         <f>ROUND(IMDIV(I10,J10),2)</f>
-        <v>83.14</v>
+        <v>82.62</v>
       </c>
       <c r="T10" s="26" t="s">
         <v>46</v>
@@ -1750,7 +1625,7 @@
       </c>
       <c r="V10" s="45">
         <f>((K10/2.5)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
-        <v>1.1282594028136663</v>
+        <v>1.1798346253229974</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1758,67 +1633,67 @@
         <v>38</v>
       </c>
       <c r="B11" s="26">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C11" s="26">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" s="26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" s="26">
         <v>2</v>
       </c>
       <c r="F11" s="26">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11" s="26">
-        <v>195</v>
+        <v>304</v>
       </c>
       <c r="H11" s="26">
         <v>25</v>
       </c>
       <c r="I11" s="26">
-        <v>4801</v>
+        <v>5800</v>
       </c>
       <c r="J11" s="26">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K11" s="27">
         <f>ROUND(IMDIV(B11,J11),2)</f>
-        <v>0.56000000000000005</v>
+        <v>0.61</v>
       </c>
       <c r="L11" s="28">
         <f>E11/J11</f>
-        <v>2.4691358024691357E-2</v>
+        <v>2.2222222222222223E-2</v>
       </c>
       <c r="M11" s="28">
         <f>D11/J11</f>
-        <v>8.6419753086419748E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N11" s="27">
         <f>ROUND(IMDIV(F11,J11),2)</f>
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="O11" s="27">
         <f>ROUND(IMDIV(G11,J11),2)</f>
-        <v>2.41</v>
+        <v>3.38</v>
       </c>
       <c r="P11" s="27">
         <f>ROUND(IMDIV(H11,J11),2)</f>
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Q11" s="27">
         <f>ROUND(IMDIV(B11,F11),2)</f>
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="R11" s="27">
         <f>ROUND(IMDIV(C11,B11),4)*100</f>
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="S11" s="27">
         <f>ROUND(IMDIV(I11,J11),2)</f>
-        <v>59.27</v>
+        <v>64.44</v>
       </c>
       <c r="T11" s="26" t="s">
         <v>46</v>
@@ -1828,631 +1703,631 @@
       </c>
       <c r="V11" s="45">
         <f>((K11/2.5)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
-        <v>0.8917176284811944</v>
+        <v>0.9771653746770026</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="32">
-        <v>36</v>
-      </c>
-      <c r="C12" s="32">
-        <v>16</v>
-      </c>
-      <c r="D12" s="32">
-        <v>10</v>
-      </c>
-      <c r="E12" s="32">
-        <v>1</v>
-      </c>
-      <c r="F12" s="32">
-        <v>40</v>
-      </c>
-      <c r="G12" s="32">
-        <v>152</v>
-      </c>
-      <c r="H12" s="32">
-        <v>16</v>
-      </c>
-      <c r="I12" s="32">
-        <v>4708</v>
-      </c>
-      <c r="J12" s="32">
+      <c r="A12" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="50">
+        <v>67</v>
+      </c>
+      <c r="C12" s="50">
+        <v>47</v>
+      </c>
+      <c r="D12" s="50">
+        <v>21</v>
+      </c>
+      <c r="E12" s="50">
+        <v>8</v>
+      </c>
+      <c r="F12" s="50">
         <v>61</v>
       </c>
-      <c r="K12" s="33">
+      <c r="G12" s="50">
+        <v>473</v>
+      </c>
+      <c r="H12" s="50">
+        <v>20</v>
+      </c>
+      <c r="I12" s="50">
+        <v>7629</v>
+      </c>
+      <c r="J12" s="50">
+        <v>103</v>
+      </c>
+      <c r="K12" s="20">
         <f>ROUND(IMDIV(B12,J12),2)</f>
+        <v>0.65</v>
+      </c>
+      <c r="L12" s="21">
+        <f>E12/J12</f>
+        <v>7.7669902912621352E-2</v>
+      </c>
+      <c r="M12" s="21">
+        <f>D12/J12</f>
+        <v>0.20388349514563106</v>
+      </c>
+      <c r="N12" s="20">
+        <f>ROUND(IMDIV(F12,J12),2)</f>
         <v>0.59</v>
       </c>
-      <c r="L12" s="34">
-        <f>E12/J12</f>
-        <v>1.6393442622950821E-2</v>
-      </c>
-      <c r="M12" s="34">
-        <f>D12/J12</f>
-        <v>0.16393442622950818</v>
-      </c>
-      <c r="N12" s="33">
-        <f>ROUND(IMDIV(F12,J12),2)</f>
-        <v>0.66</v>
-      </c>
-      <c r="O12" s="33">
+      <c r="O12" s="20">
         <f>ROUND(IMDIV(G12,J12),2)</f>
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="P12" s="33">
+        <v>4.59</v>
+      </c>
+      <c r="P12" s="20">
         <f>ROUND(IMDIV(H12,J12),2)</f>
-        <v>0.26</v>
-      </c>
-      <c r="Q12" s="33">
+        <v>0.19</v>
+      </c>
+      <c r="Q12" s="20">
         <f>ROUND(IMDIV(B12,F12),2)</f>
-        <v>0.9</v>
-      </c>
-      <c r="R12" s="33">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R12" s="20">
         <f>ROUND(IMDIV(C12,B12),4)*100</f>
-        <v>44.440000000000005</v>
-      </c>
-      <c r="S12" s="33">
+        <v>70.150000000000006</v>
+      </c>
+      <c r="S12" s="20">
         <f>ROUND(IMDIV(I12,J12),2)</f>
-        <v>77.180000000000007</v>
-      </c>
-      <c r="T12" s="32" t="s">
+        <v>74.069999999999993</v>
+      </c>
+      <c r="T12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="32" t="s">
+      <c r="U12" s="22" t="s">
         <v>24</v>
       </c>
       <c r="V12" s="45">
         <f>((K12/2.5)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
-        <v>0.99223903926801371</v>
+        <v>1.0905164822759088</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="32">
-        <v>31</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="A13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="50">
+        <v>56</v>
+      </c>
+      <c r="C13" s="50">
+        <v>28</v>
+      </c>
+      <c r="D13" s="50">
         <v>16</v>
       </c>
-      <c r="D13" s="32">
-        <v>7</v>
-      </c>
-      <c r="E13" s="32">
-        <v>3</v>
-      </c>
-      <c r="F13" s="32">
-        <v>40</v>
-      </c>
-      <c r="G13" s="32">
-        <v>253</v>
-      </c>
-      <c r="H13" s="32">
-        <v>4</v>
-      </c>
-      <c r="I13" s="32">
-        <v>3281</v>
-      </c>
-      <c r="J13" s="32">
-        <v>61</v>
-      </c>
-      <c r="K13" s="33">
+      <c r="E13" s="50">
+        <v>5</v>
+      </c>
+      <c r="F13" s="50">
+        <v>66</v>
+      </c>
+      <c r="G13" s="50">
+        <v>185</v>
+      </c>
+      <c r="H13" s="50">
+        <v>25</v>
+      </c>
+      <c r="I13" s="50">
+        <v>6610</v>
+      </c>
+      <c r="J13" s="50">
+        <v>103</v>
+      </c>
+      <c r="K13" s="20">
         <f>ROUND(IMDIV(B13,J13),2)</f>
-        <v>0.51</v>
-      </c>
-      <c r="L13" s="34">
+        <v>0.54</v>
+      </c>
+      <c r="L13" s="21">
         <f>E13/J13</f>
-        <v>4.9180327868852458E-2</v>
-      </c>
-      <c r="M13" s="34">
+        <v>4.8543689320388349E-2</v>
+      </c>
+      <c r="M13" s="21">
         <f>D13/J13</f>
-        <v>0.11475409836065574</v>
-      </c>
-      <c r="N13" s="33">
+        <v>0.1553398058252427</v>
+      </c>
+      <c r="N13" s="20">
         <f>ROUND(IMDIV(F13,J13),2)</f>
-        <v>0.66</v>
-      </c>
-      <c r="O13" s="33">
+        <v>0.64</v>
+      </c>
+      <c r="O13" s="20">
         <f>ROUND(IMDIV(G13,J13),2)</f>
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="P13" s="33">
+        <v>1.8</v>
+      </c>
+      <c r="P13" s="20">
         <f>ROUND(IMDIV(H13,J13),2)</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="Q13" s="33">
+        <v>0.24</v>
+      </c>
+      <c r="Q13" s="20">
         <f>ROUND(IMDIV(B13,F13),2)</f>
-        <v>0.78</v>
-      </c>
-      <c r="R13" s="33">
+        <v>0.85</v>
+      </c>
+      <c r="R13" s="20">
         <f>ROUND(IMDIV(C13,B13),4)*100</f>
-        <v>51.61</v>
-      </c>
-      <c r="S13" s="33">
+        <v>50</v>
+      </c>
+      <c r="S13" s="20">
         <f>ROUND(IMDIV(I13,J13),2)</f>
-        <v>53.79</v>
-      </c>
-      <c r="T13" s="32" t="s">
+        <v>64.17</v>
+      </c>
+      <c r="T13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="U13" s="32" t="s">
+      <c r="U13" s="22" t="s">
         <v>24</v>
       </c>
       <c r="V13" s="45">
         <f>((K13/2.5)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
-        <v>0.83621063667556239</v>
+        <v>0.93500880559945809</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="50">
-        <v>54</v>
-      </c>
-      <c r="C14" s="50">
-        <v>37</v>
-      </c>
-      <c r="D14" s="50">
+      <c r="A14" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="32">
+        <v>40</v>
+      </c>
+      <c r="C14" s="32">
         <v>16</v>
       </c>
-      <c r="E14" s="50">
-        <v>6</v>
-      </c>
-      <c r="F14" s="50">
-        <v>54</v>
-      </c>
-      <c r="G14" s="50">
-        <v>265</v>
-      </c>
-      <c r="H14" s="50">
-        <v>15</v>
-      </c>
-      <c r="I14" s="50">
-        <v>5844</v>
-      </c>
-      <c r="J14" s="50">
-        <v>88</v>
-      </c>
-      <c r="K14" s="20">
+      <c r="D14" s="32">
+        <v>12</v>
+      </c>
+      <c r="E14" s="32">
+        <v>1</v>
+      </c>
+      <c r="F14" s="32">
+        <v>49</v>
+      </c>
+      <c r="G14" s="32">
+        <v>190</v>
+      </c>
+      <c r="H14" s="32">
+        <v>17</v>
+      </c>
+      <c r="I14" s="32">
+        <v>5224</v>
+      </c>
+      <c r="J14" s="32">
+        <v>73</v>
+      </c>
+      <c r="K14" s="33">
         <f>ROUND(IMDIV(B14,J14),2)</f>
-        <v>0.61</v>
-      </c>
-      <c r="L14" s="21">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L14" s="34">
         <f>E14/J14</f>
-        <v>6.8181818181818177E-2</v>
-      </c>
-      <c r="M14" s="21">
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="M14" s="34">
         <f>D14/J14</f>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="N14" s="20">
+        <v>0.16438356164383561</v>
+      </c>
+      <c r="N14" s="33">
         <f>ROUND(IMDIV(F14,J14),2)</f>
-        <v>0.61</v>
-      </c>
-      <c r="O14" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="O14" s="33">
         <f>ROUND(IMDIV(G14,J14),2)</f>
-        <v>3.01</v>
-      </c>
-      <c r="P14" s="20">
+        <v>2.6</v>
+      </c>
+      <c r="P14" s="33">
         <f>ROUND(IMDIV(H14,J14),2)</f>
-        <v>0.17</v>
-      </c>
-      <c r="Q14" s="20">
+        <v>0.23</v>
+      </c>
+      <c r="Q14" s="33">
         <f>ROUND(IMDIV(B14,F14),2)</f>
-        <v>1</v>
-      </c>
-      <c r="R14" s="20">
+        <v>0.82</v>
+      </c>
+      <c r="R14" s="33">
         <f>ROUND(IMDIV(C14,B14),4)*100</f>
-        <v>68.52000000000001</v>
-      </c>
-      <c r="S14" s="20">
+        <v>40</v>
+      </c>
+      <c r="S14" s="33">
         <f>ROUND(IMDIV(I14,J14),2)</f>
-        <v>66.41</v>
-      </c>
-      <c r="T14" s="20" t="s">
+        <v>71.56</v>
+      </c>
+      <c r="T14" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="U14" s="22" t="s">
+      <c r="U14" s="32" t="s">
         <v>24</v>
       </c>
       <c r="V14" s="45">
         <f>((K14/2.5)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
-        <v>1.0104746300211416</v>
+        <v>0.93817282574068173</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="50">
-        <v>47</v>
-      </c>
-      <c r="C15" s="50">
-        <v>24</v>
-      </c>
-      <c r="D15" s="50">
-        <v>13</v>
-      </c>
-      <c r="E15" s="50">
-        <v>5</v>
-      </c>
-      <c r="F15" s="50">
-        <v>58</v>
-      </c>
-      <c r="G15" s="50">
-        <v>112</v>
-      </c>
-      <c r="H15" s="50">
-        <v>20</v>
-      </c>
-      <c r="I15" s="50">
-        <v>5950</v>
-      </c>
-      <c r="J15" s="50">
-        <v>88</v>
-      </c>
-      <c r="K15" s="20">
+      <c r="A15" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="32">
+        <v>34</v>
+      </c>
+      <c r="C15" s="32">
+        <v>16</v>
+      </c>
+      <c r="D15" s="32">
+        <v>8</v>
+      </c>
+      <c r="E15" s="32">
+        <v>3</v>
+      </c>
+      <c r="F15" s="32">
+        <v>49</v>
+      </c>
+      <c r="G15" s="32">
+        <v>253</v>
+      </c>
+      <c r="H15" s="32">
+        <v>6</v>
+      </c>
+      <c r="I15" s="32">
+        <v>3677</v>
+      </c>
+      <c r="J15" s="32">
+        <v>73</v>
+      </c>
+      <c r="K15" s="33">
         <f>ROUND(IMDIV(B15,J15),2)</f>
-        <v>0.53</v>
-      </c>
-      <c r="L15" s="21">
+        <v>0.47</v>
+      </c>
+      <c r="L15" s="34">
         <f>E15/J15</f>
-        <v>5.6818181818181816E-2</v>
-      </c>
-      <c r="M15" s="21">
+        <v>4.1095890410958902E-2</v>
+      </c>
+      <c r="M15" s="34">
         <f>D15/J15</f>
-        <v>0.14772727272727273</v>
-      </c>
-      <c r="N15" s="20">
+        <v>0.1095890410958904</v>
+      </c>
+      <c r="N15" s="33">
         <f>ROUND(IMDIV(F15,J15),2)</f>
-        <v>0.66</v>
-      </c>
-      <c r="O15" s="20">
+        <v>0.67</v>
+      </c>
+      <c r="O15" s="33">
         <f>ROUND(IMDIV(G15,J15),2)</f>
-        <v>1.27</v>
-      </c>
-      <c r="P15" s="20">
+        <v>3.47</v>
+      </c>
+      <c r="P15" s="33">
         <f>ROUND(IMDIV(H15,J15),2)</f>
-        <v>0.23</v>
-      </c>
-      <c r="Q15" s="20">
+        <v>0.08</v>
+      </c>
+      <c r="Q15" s="33">
         <f>ROUND(IMDIV(B15,F15),2)</f>
-        <v>0.81</v>
-      </c>
-      <c r="R15" s="20">
+        <v>0.69</v>
+      </c>
+      <c r="R15" s="33">
         <f>ROUND(IMDIV(C15,B15),4)*100</f>
-        <v>51.06</v>
-      </c>
-      <c r="S15" s="20">
+        <v>47.06</v>
+      </c>
+      <c r="S15" s="33">
         <f>ROUND(IMDIV(I15,J15),2)</f>
-        <v>67.61</v>
-      </c>
-      <c r="T15" s="20" t="s">
+        <v>50.37</v>
+      </c>
+      <c r="T15" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="U15" s="22" t="s">
+      <c r="U15" s="32" t="s">
         <v>24</v>
       </c>
       <c r="V15" s="45">
         <f>((K15/2.5)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
-        <v>0.92626057082452429</v>
+        <v>0.79189550812360621</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="23">
+      <c r="A16" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="18">
         <v>54</v>
       </c>
-      <c r="C16" s="23">
-        <v>32</v>
-      </c>
-      <c r="D16" s="23">
-        <v>18</v>
-      </c>
-      <c r="E16" s="23">
+      <c r="C16" s="18">
+        <v>28</v>
+      </c>
+      <c r="D16" s="18">
+        <v>11</v>
+      </c>
+      <c r="E16" s="18">
         <v>2</v>
       </c>
-      <c r="F16" s="23">
-        <v>51</v>
-      </c>
-      <c r="G16" s="23">
-        <v>270</v>
-      </c>
-      <c r="H16" s="23">
-        <v>9</v>
-      </c>
-      <c r="I16" s="23">
-        <v>6978</v>
-      </c>
-      <c r="J16" s="23">
-        <v>78</v>
-      </c>
-      <c r="K16" s="24">
+      <c r="F16" s="18">
+        <v>64</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="18">
+        <v>12</v>
+      </c>
+      <c r="I16" s="18">
+        <v>6973</v>
+      </c>
+      <c r="J16" s="18">
+        <v>99</v>
+      </c>
+      <c r="K16" s="18">
         <f>ROUND(IMDIV(B16,J16),2)</f>
-        <v>0.69</v>
-      </c>
-      <c r="L16" s="25">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L16" s="19">
         <f>E16/J16</f>
-        <v>2.564102564102564E-2</v>
-      </c>
-      <c r="M16" s="25">
+        <v>2.0202020202020204E-2</v>
+      </c>
+      <c r="M16" s="19">
         <f>D16/J16</f>
-        <v>0.23076923076923078</v>
-      </c>
-      <c r="N16" s="24">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="N16" s="18">
         <f>ROUND(IMDIV(F16,J16),2)</f>
         <v>0.65</v>
       </c>
-      <c r="O16" s="24">
+      <c r="O16" s="18" t="e">
         <f>ROUND(IMDIV(G16,J16),2)</f>
-        <v>3.46</v>
-      </c>
-      <c r="P16" s="24">
+        <v>#NUM!</v>
+      </c>
+      <c r="P16" s="18">
         <f>ROUND(IMDIV(H16,J16),2)</f>
         <v>0.12</v>
       </c>
-      <c r="Q16" s="24">
+      <c r="Q16" s="18">
         <f>ROUND(IMDIV(B16,F16),2)</f>
-        <v>1.06</v>
-      </c>
-      <c r="R16" s="24">
+        <v>0.84</v>
+      </c>
+      <c r="R16" s="18">
         <f>ROUND(IMDIV(C16,B16),4)*100</f>
-        <v>59.260000000000005</v>
-      </c>
-      <c r="S16" s="24">
+        <v>51.849999999999994</v>
+      </c>
+      <c r="S16" s="18">
         <f>ROUND(IMDIV(I16,J16),2)</f>
-        <v>89.46</v>
-      </c>
-      <c r="T16" s="24" t="s">
+        <v>70.430000000000007</v>
+      </c>
+      <c r="T16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="U16" s="24" t="s">
+      <c r="U16" s="18" t="s">
         <v>24</v>
       </c>
       <c r="V16" s="45">
         <f>((K16/2.5)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
-        <v>1.1109135360763267</v>
+        <v>0.93539957716701916</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="23">
+      <c r="A17" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="23">
+      <c r="B17" s="18">
+        <v>46</v>
+      </c>
+      <c r="C17" s="18">
+        <v>18</v>
+      </c>
+      <c r="D17" s="18">
+        <v>8</v>
+      </c>
+      <c r="E17" s="18">
+        <v>1</v>
+      </c>
+      <c r="F17" s="18">
+        <v>63</v>
+      </c>
+      <c r="G17" s="18">
+        <v>66</v>
+      </c>
+      <c r="H17" s="18">
         <v>12</v>
       </c>
-      <c r="D17" s="23">
-        <v>5</v>
-      </c>
-      <c r="E17" s="23">
-        <v>2</v>
-      </c>
-      <c r="F17" s="23">
-        <v>41</v>
-      </c>
-      <c r="G17" s="24">
-        <v>84</v>
-      </c>
-      <c r="H17" s="23">
-        <v>8</v>
-      </c>
-      <c r="I17" s="23">
-        <v>2640</v>
-      </c>
-      <c r="J17" s="23">
-        <v>62</v>
-      </c>
-      <c r="K17" s="24">
+      <c r="I17" s="18">
+        <v>5547</v>
+      </c>
+      <c r="J17" s="18">
+        <v>99</v>
+      </c>
+      <c r="K17" s="18">
         <f>ROUND(IMDIV(B17,J17),2)</f>
-        <v>0.37</v>
-      </c>
-      <c r="L17" s="25">
+        <v>0.46</v>
+      </c>
+      <c r="L17" s="19">
         <f>E17/J17</f>
-        <v>3.2258064516129031E-2</v>
-      </c>
-      <c r="M17" s="25">
+        <v>1.0101010101010102E-2</v>
+      </c>
+      <c r="M17" s="19">
         <f>D17/J17</f>
-        <v>8.0645161290322578E-2</v>
-      </c>
-      <c r="N17" s="24">
+        <v>8.0808080808080815E-2</v>
+      </c>
+      <c r="N17" s="18">
         <f>ROUND(IMDIV(F17,J17),2)</f>
-        <v>0.66</v>
-      </c>
-      <c r="O17" s="24">
+        <v>0.64</v>
+      </c>
+      <c r="O17" s="18">
         <f>ROUND(IMDIV(G17,J17),2)</f>
-        <v>1.35</v>
-      </c>
-      <c r="P17" s="24">
+        <v>0.67</v>
+      </c>
+      <c r="P17" s="18">
         <f>ROUND(IMDIV(H17,J17),2)</f>
-        <v>0.13</v>
-      </c>
-      <c r="Q17" s="24">
+        <v>0.12</v>
+      </c>
+      <c r="Q17" s="18">
         <f>ROUND(IMDIV(B17,F17),2)</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="R17" s="24">
+        <v>0.73</v>
+      </c>
+      <c r="R17" s="18">
         <f>ROUND(IMDIV(C17,B17),4)*100</f>
-        <v>52.17</v>
-      </c>
-      <c r="S17" s="24">
+        <v>39.129999999999995</v>
+      </c>
+      <c r="S17" s="18">
         <f>ROUND(IMDIV(I17,J17),2)</f>
-        <v>42.58</v>
-      </c>
-      <c r="T17" s="24" t="s">
+        <v>56.03</v>
+      </c>
+      <c r="T17" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="U17" s="24" t="s">
+      <c r="U17" s="18" t="s">
         <v>24</v>
       </c>
       <c r="V17" s="45">
         <f>((K17/2.5)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
-        <v>0.71915941485371349</v>
+        <v>0.83282687338501282</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="18">
-        <v>37</v>
-      </c>
-      <c r="C18" s="18">
-        <v>24</v>
-      </c>
-      <c r="D18" s="18">
-        <v>7</v>
-      </c>
-      <c r="E18" s="18">
-        <v>1</v>
-      </c>
-      <c r="F18" s="18">
-        <v>47</v>
-      </c>
-      <c r="G18" s="18">
-        <v>165</v>
-      </c>
-      <c r="H18" s="18">
-        <v>9</v>
-      </c>
-      <c r="I18" s="18">
-        <v>4883</v>
-      </c>
-      <c r="J18" s="18">
-        <v>71</v>
-      </c>
-      <c r="K18" s="18">
+      <c r="A18" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="23">
+        <v>55</v>
+      </c>
+      <c r="C18" s="23">
+        <v>33</v>
+      </c>
+      <c r="D18" s="23">
+        <v>18</v>
+      </c>
+      <c r="E18" s="23">
+        <v>2</v>
+      </c>
+      <c r="F18" s="23">
+        <v>60</v>
+      </c>
+      <c r="G18" s="23">
+        <v>285</v>
+      </c>
+      <c r="H18" s="23">
+        <v>11</v>
+      </c>
+      <c r="I18" s="23">
+        <v>7200</v>
+      </c>
+      <c r="J18" s="23">
+        <v>87</v>
+      </c>
+      <c r="K18" s="24">
         <f>ROUND(IMDIV(B18,J18),2)</f>
-        <v>0.52</v>
-      </c>
-      <c r="L18" s="19">
+        <v>0.63</v>
+      </c>
+      <c r="L18" s="25">
         <f>E18/J18</f>
-        <v>1.4084507042253521E-2</v>
-      </c>
-      <c r="M18" s="19">
+        <v>2.2988505747126436E-2</v>
+      </c>
+      <c r="M18" s="25">
         <f>D18/J18</f>
-        <v>9.8591549295774641E-2</v>
-      </c>
-      <c r="N18" s="18">
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="N18" s="24">
         <f>ROUND(IMDIV(F18,J18),2)</f>
-        <v>0.66</v>
-      </c>
-      <c r="O18" s="18">
+        <v>0.69</v>
+      </c>
+      <c r="O18" s="24">
         <f>ROUND(IMDIV(G18,J18),2)</f>
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="P18" s="18">
+        <v>3.28</v>
+      </c>
+      <c r="P18" s="24">
         <f>ROUND(IMDIV(H18,J18),2)</f>
         <v>0.13</v>
       </c>
-      <c r="Q18" s="18">
+      <c r="Q18" s="24">
         <f>ROUND(IMDIV(B18,F18),2)</f>
-        <v>0.79</v>
-      </c>
-      <c r="R18" s="18">
+        <v>0.92</v>
+      </c>
+      <c r="R18" s="24">
         <f>ROUND(IMDIV(C18,B18),4)*100</f>
-        <v>64.86</v>
-      </c>
-      <c r="S18" s="18">
+        <v>60</v>
+      </c>
+      <c r="S18" s="24">
         <f>ROUND(IMDIV(I18,J18),2)</f>
-        <v>68.77</v>
-      </c>
-      <c r="T18" s="18" t="s">
+        <v>82.76</v>
+      </c>
+      <c r="T18" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="U18" s="18" t="s">
+      <c r="U18" s="24" t="s">
         <v>24</v>
       </c>
       <c r="V18" s="45">
         <f>((K18/2.5)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
-        <v>0.9018252538486734</v>
+        <v>1.0097520716385993</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="18">
-        <v>30</v>
-      </c>
-      <c r="C19" s="18">
+      <c r="A19" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="23">
+        <v>25</v>
+      </c>
+      <c r="C19" s="23">
         <v>13</v>
       </c>
-      <c r="D19" s="18">
-        <v>4</v>
-      </c>
-      <c r="E19" s="18">
-        <v>1</v>
-      </c>
-      <c r="F19" s="18">
+      <c r="D19" s="23">
+        <v>5</v>
+      </c>
+      <c r="E19" s="23">
+        <v>2</v>
+      </c>
+      <c r="F19" s="23">
+        <v>49</v>
+      </c>
+      <c r="G19" s="24">
+        <v>113</v>
+      </c>
+      <c r="H19" s="23">
+        <v>9</v>
+      </c>
+      <c r="I19" s="23">
+        <v>3045</v>
+      </c>
+      <c r="J19" s="23">
+        <v>71</v>
+      </c>
+      <c r="K19" s="24">
+        <f>ROUND(IMDIV(B19,J19),2)</f>
+        <v>0.35</v>
+      </c>
+      <c r="L19" s="25">
+        <f>E19/J19</f>
+        <v>2.8169014084507043E-2</v>
+      </c>
+      <c r="M19" s="25">
+        <f>D19/J19</f>
+        <v>7.0422535211267609E-2</v>
+      </c>
+      <c r="N19" s="24">
+        <f>ROUND(IMDIV(F19,J19),2)</f>
+        <v>0.69</v>
+      </c>
+      <c r="O19" s="24">
+        <f>ROUND(IMDIV(G19,J19),2)</f>
+        <v>1.59</v>
+      </c>
+      <c r="P19" s="24">
+        <f>ROUND(IMDIV(H19,J19),2)</f>
+        <v>0.13</v>
+      </c>
+      <c r="Q19" s="24">
+        <f>ROUND(IMDIV(B19,F19),2)</f>
+        <v>0.51</v>
+      </c>
+      <c r="R19" s="24">
+        <f>ROUND(IMDIV(C19,B19),4)*100</f>
+        <v>52</v>
+      </c>
+      <c r="S19" s="24">
+        <f>ROUND(IMDIV(I19,J19),2)</f>
+        <v>42.89</v>
+      </c>
+      <c r="T19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="18">
-        <v>27</v>
-      </c>
-      <c r="H19" s="18">
-        <v>11</v>
-      </c>
-      <c r="I19" s="18">
-        <v>3638</v>
-      </c>
-      <c r="J19" s="18">
-        <v>71</v>
-      </c>
-      <c r="K19" s="18">
-        <f>ROUND(IMDIV(B19,J19),2)</f>
-        <v>0.42</v>
-      </c>
-      <c r="L19" s="19">
-        <f>E19/J19</f>
-        <v>1.4084507042253521E-2</v>
-      </c>
-      <c r="M19" s="19">
-        <f>D19/J19</f>
-        <v>5.6338028169014086E-2</v>
-      </c>
-      <c r="N19" s="18">
-        <f>ROUND(IMDIV(F19,J19),2)</f>
-        <v>0.65</v>
-      </c>
-      <c r="O19" s="18">
-        <f>ROUND(IMDIV(G19,J19),2)</f>
-        <v>0.38</v>
-      </c>
-      <c r="P19" s="18">
-        <f>ROUND(IMDIV(H19,J19),2)</f>
-        <v>0.15</v>
-      </c>
-      <c r="Q19" s="18">
-        <f>ROUND(IMDIV(B19,F19),2)</f>
-        <v>0.65</v>
-      </c>
-      <c r="R19" s="18">
-        <f>ROUND(IMDIV(C19,B19),4)*100</f>
-        <v>43.33</v>
-      </c>
-      <c r="S19" s="18">
-        <f>ROUND(IMDIV(I19,J19),2)</f>
-        <v>51.24</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="U19" s="18" t="s">
+      <c r="U19" s="24" t="s">
         <v>24</v>
       </c>
       <c r="V19" s="45">
         <f>((K19/2.5)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
-        <v>0.78072698984605304</v>
+        <v>0.67922780871274169</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12175DF-A587-44C0-97C0-193FE524A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B18C827-23B8-4728-B7BE-51A8E4BD5797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="2715" yWindow="5235" windowWidth="28800" windowHeight="15285" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
   <si>
     <t>player</t>
   </si>
@@ -180,9 +180,6 @@
   </si>
   <si>
     <t>5th</t>
-  </si>
-  <si>
-    <t>165+128</t>
   </si>
 </sst>
 </file>
@@ -1243,10 +1240,10 @@
         <v>29</v>
       </c>
       <c r="B6" s="12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C6" s="12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" s="12">
         <v>19</v>
@@ -1255,39 +1252,39 @@
         <v>5</v>
       </c>
       <c r="F6" s="12">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G6" s="12">
         <v>302</v>
       </c>
       <c r="H6" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="12">
-        <v>8290</v>
+        <v>9181</v>
       </c>
       <c r="J6" s="12">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K6" s="12">
         <f>ROUND(IMDIV(B6,J6),2)</f>
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="L6" s="13">
         <f>E6/J6</f>
-        <v>6.1728395061728392E-2</v>
+        <v>5.434782608695652E-2</v>
       </c>
       <c r="M6" s="13">
         <f>D6/J6</f>
-        <v>0.23456790123456789</v>
+        <v>0.20652173913043478</v>
       </c>
       <c r="N6" s="12">
         <f>ROUND(IMDIV(F6,J6),2)</f>
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="O6" s="12">
         <f>ROUND(IMDIV(G6,J6),2)</f>
-        <v>3.73</v>
+        <v>3.28</v>
       </c>
       <c r="P6" s="12">
         <f>ROUND(IMDIV(H6,J6),2)</f>
@@ -1295,15 +1292,15 @@
       </c>
       <c r="Q6" s="12">
         <f>ROUND(IMDIV(B6,F6),2)</f>
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="R6" s="12">
         <f>ROUND(IMDIV(C6,B6),4)*100</f>
-        <v>42.86</v>
+        <v>44</v>
       </c>
       <c r="S6" s="12">
         <f>ROUND(IMDIV(I6,J6),2)</f>
-        <v>102.35</v>
+        <v>99.79</v>
       </c>
       <c r="T6" s="51" t="s">
         <v>46</v>
@@ -1313,7 +1310,7 @@
       </c>
       <c r="V6" s="45">
         <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>1.4265341659488946</v>
+        <v>1.3401395348837208</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1321,31 +1318,31 @@
         <v>30</v>
       </c>
       <c r="B7" s="12">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C7" s="12">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="12">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G7" s="12">
         <v>115</v>
       </c>
       <c r="H7" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I7" s="12">
         <v>4641</v>
       </c>
       <c r="J7" s="12">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K7" s="12">
         <f>ROUND(IMDIV(B7,J7),2)</f>
@@ -1353,35 +1350,35 @@
       </c>
       <c r="L7" s="13">
         <f>E7/J7</f>
-        <v>1.2345679012345678E-2</v>
+        <v>2.1739130434782608E-2</v>
       </c>
       <c r="M7" s="13">
         <f>D7/J7</f>
-        <v>6.1728395061728392E-2</v>
+        <v>6.5217391304347824E-2</v>
       </c>
       <c r="N7" s="12">
         <f>ROUND(IMDIV(F7,J7),2)</f>
-        <v>0.52</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O7" s="12">
         <f>ROUND(IMDIV(G7,J7),2)</f>
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="P7" s="12">
         <f>ROUND(IMDIV(H7,J7),2)</f>
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="Q7" s="12">
         <f>ROUND(IMDIV(B7,F7),2)</f>
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="R7" s="12">
         <f>ROUND(IMDIV(C7,B7),4)*100</f>
-        <v>47.5</v>
+        <v>48.89</v>
       </c>
       <c r="S7" s="12">
         <f>ROUND(IMDIV(I7,J7),2)</f>
-        <v>57.3</v>
+        <v>50.45</v>
       </c>
       <c r="T7" s="51" t="s">
         <v>46</v>
@@ -1391,7 +1388,7 @@
       </c>
       <c r="V7" s="45">
         <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
-        <v>0.9654128624748779</v>
+        <v>0.90780333670374114</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1555,67 +1552,67 @@
         <v>37</v>
       </c>
       <c r="B10" s="26">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C10" s="26">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D10" s="26">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E10" s="26">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="26">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G10" s="26">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H10" s="26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I10" s="26">
-        <v>7436</v>
+        <v>8657</v>
       </c>
       <c r="J10" s="26">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="K10" s="27">
         <f>ROUND(IMDIV(B10,J10),2)</f>
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="L10" s="28">
         <f>E10/J10</f>
-        <v>8.8888888888888892E-2</v>
+        <v>0.10891089108910891</v>
       </c>
       <c r="M10" s="28">
         <f>D10/J10</f>
-        <v>0.1111111111111111</v>
+        <v>0.13861386138613863</v>
       </c>
       <c r="N10" s="27">
         <f>ROUND(IMDIV(F10,J10),2)</f>
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="O10" s="27">
         <f>ROUND(IMDIV(G10,J10),2)</f>
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="P10" s="27">
         <f>ROUND(IMDIV(H10,J10),2)</f>
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="Q10" s="27">
         <f>ROUND(IMDIV(B10,F10),2)</f>
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="R10" s="27">
         <f>ROUND(IMDIV(C10,B10),4)*100</f>
-        <v>49.18</v>
+        <v>50.68</v>
       </c>
       <c r="S10" s="27">
         <f>ROUND(IMDIV(I10,J10),2)</f>
-        <v>82.62</v>
+        <v>85.71</v>
       </c>
       <c r="T10" s="26" t="s">
         <v>46</v>
@@ -1625,7 +1622,7 @@
       </c>
       <c r="V10" s="45">
         <f>((K10/2.5)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
-        <v>1.1798346253229974</v>
+        <v>1.2400868063550541</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -2037,8 +2034,8 @@
       <c r="F16" s="18">
         <v>64</v>
       </c>
-      <c r="G16" s="18" t="s">
-        <v>48</v>
+      <c r="G16" s="18">
+        <v>293</v>
       </c>
       <c r="H16" s="18">
         <v>12</v>
@@ -2065,9 +2062,9 @@
         <f>ROUND(IMDIV(F16,J16),2)</f>
         <v>0.65</v>
       </c>
-      <c r="O16" s="18" t="e">
+      <c r="O16" s="18">
         <f>ROUND(IMDIV(G16,J16),2)</f>
-        <v>#NUM!</v>
+        <v>2.96</v>
       </c>
       <c r="P16" s="18">
         <f>ROUND(IMDIV(H16,J16),2)</f>
@@ -2335,51 +2332,51 @@
         <v>33</v>
       </c>
       <c r="B20" s="15">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C20" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15">
         <v>4</v>
       </c>
       <c r="F20" s="15">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G20" s="15">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H20" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>5734</v>
+        <v>6460</v>
       </c>
       <c r="J20" s="15">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K20" s="15">
         <f>ROUND(IMDIV(B20,J20),2)</f>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L20" s="17">
         <f>E20/J20</f>
-        <v>4.9382716049382713E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="M20" s="17">
         <f>D20/J20</f>
-        <v>0.13580246913580246</v>
+        <v>0.13043478260869565</v>
       </c>
       <c r="N20" s="15">
         <f>ROUND(IMDIV(F20,J20),2)</f>
-        <v>0.69</v>
+        <v>0.67</v>
       </c>
       <c r="O20" s="15">
         <f>ROUND(IMDIV(G20,J20),2)</f>
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P20" s="15">
         <f>ROUND(IMDIV(H20,J20),2)</f>
@@ -2387,15 +2384,15 @@
       </c>
       <c r="Q20" s="15">
         <f>ROUND(IMDIV(B20,F20),2)</f>
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="R20" s="15">
         <f>ROUND(IMDIV(C20,B20),4)*100</f>
-        <v>77.55</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="S20" s="15">
         <f>ROUND(IMDIV(I20,J20),2)</f>
-        <v>70.790000000000006</v>
+        <v>70.22</v>
       </c>
       <c r="T20" s="16" t="s">
         <v>42</v>
@@ -2405,7 +2402,7 @@
       </c>
       <c r="V20" s="45">
         <f>((K20/2.5)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
-        <v>0.93458297444731553</v>
+        <v>0.95340899898887754</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B18C827-23B8-4728-B7BE-51A8E4BD5797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6815AA8A-76B1-4445-9EE4-8FDF37CD5F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="5235" windowWidth="28800" windowHeight="15285" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -928,19 +928,19 @@
         <v>28</v>
       </c>
       <c r="B2" s="6">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C2" s="6">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D2" s="6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E2" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" s="6">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G2" s="6">
         <v>618</v>
@@ -949,46 +949,46 @@
         <v>28</v>
       </c>
       <c r="I2" s="6">
-        <v>8756</v>
+        <v>10813</v>
       </c>
       <c r="J2" s="6">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="K2" s="6">
         <f>ROUND(IMDIV(B2,J2),2)</f>
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="L2" s="7">
         <f>E2/J2</f>
-        <v>6.0240963855421686E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="M2" s="7">
         <f>D2/J2</f>
-        <v>0.28915662650602408</v>
+        <v>0.27619047619047621</v>
       </c>
       <c r="N2" s="6">
         <f>ROUND(IMDIV(F2,J2),2)</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O2" s="6">
         <f>ROUND(IMDIV(G2,J2),2)</f>
-        <v>7.45</v>
+        <v>5.89</v>
       </c>
       <c r="P2" s="6">
         <f>ROUND(IMDIV(H2,J2),2)</f>
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="Q2" s="6">
         <f>ROUND(IMDIV(B2,F2),2)</f>
-        <v>2.5499999999999998</v>
+        <v>2.17</v>
       </c>
       <c r="R2" s="6">
         <f>ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>66.67</v>
+        <v>65.69</v>
       </c>
       <c r="S2" s="6">
         <f>ROUND(IMDIV(I2,J2),2)</f>
-        <v>105.49</v>
+        <v>102.98</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>47</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="V2" s="45">
         <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>1.595988512188288</v>
+        <v>1.5128576965669989</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1006,19 +1006,19 @@
         <v>27</v>
       </c>
       <c r="B3" s="6">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C3" s="6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G3" s="6">
         <v>41</v>
@@ -1027,46 +1027,46 @@
         <v>13</v>
       </c>
       <c r="I3" s="6">
-        <v>4432</v>
+        <v>5818</v>
       </c>
       <c r="J3" s="6">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="K3" s="6">
         <f>ROUND(IMDIV(B3,J3),2)</f>
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="7">
         <f>E3/J3</f>
-        <v>1.2048192771084338E-2</v>
+        <v>1.9047619047619049E-2</v>
       </c>
       <c r="M3" s="7">
         <f>D3/J3</f>
-        <v>7.2289156626506021E-2</v>
+        <v>8.5714285714285715E-2</v>
       </c>
       <c r="N3" s="6">
         <f>ROUND(IMDIV(F3,J3),2)</f>
-        <v>0.55000000000000004</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="O3" s="6">
         <f>ROUND(IMDIV(G3,J3),2)</f>
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="P3" s="6">
         <f>ROUND(IMDIV(H3,J3),2)</f>
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="Q3" s="6">
         <f>ROUND(IMDIV(B3,F3),2)</f>
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="R3" s="6">
         <f>ROUND(IMDIV(C3,B3),4)*100</f>
-        <v>58.540000000000006</v>
+        <v>50.94</v>
       </c>
       <c r="S3" s="6">
         <f>ROUND(IMDIV(I3,J3),2)</f>
-        <v>53.4</v>
+        <v>55.41</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>47</v>
@@ -1076,631 +1076,631 @@
       </c>
       <c r="V3" s="45">
         <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
-        <v>0.92285402073409917</v>
+        <v>0.90895902547065344</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="9">
-        <v>86</v>
-      </c>
-      <c r="C4" s="9">
-        <v>44</v>
-      </c>
-      <c r="D4" s="9">
-        <v>22</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="A4" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="29">
+        <v>97</v>
+      </c>
+      <c r="C4" s="29">
+        <v>55</v>
+      </c>
+      <c r="D4" s="29">
+        <v>32</v>
+      </c>
+      <c r="E4" s="29">
         <v>10</v>
       </c>
-      <c r="F4" s="9">
-        <v>58</v>
-      </c>
-      <c r="G4" s="9">
-        <v>167</v>
-      </c>
-      <c r="H4" s="9">
-        <v>31</v>
-      </c>
-      <c r="I4" s="9">
-        <v>9617</v>
-      </c>
-      <c r="J4" s="9">
-        <v>110</v>
-      </c>
-      <c r="K4" s="9">
+      <c r="F4" s="29">
+        <v>51</v>
+      </c>
+      <c r="G4" s="29">
+        <v>674</v>
+      </c>
+      <c r="H4" s="29">
+        <v>15</v>
+      </c>
+      <c r="I4" s="29">
+        <v>11154</v>
+      </c>
+      <c r="J4" s="29">
+        <v>109</v>
+      </c>
+      <c r="K4" s="30">
         <f>ROUND(IMDIV(B4,J4),2)</f>
-        <v>0.78</v>
-      </c>
-      <c r="L4" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="L4" s="31">
         <f>E4/J4</f>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="M4" s="11">
+        <v>9.1743119266055051E-2</v>
+      </c>
+      <c r="M4" s="31">
         <f>D4/J4</f>
-        <v>0.2</v>
-      </c>
-      <c r="N4" s="9">
+        <v>0.29357798165137616</v>
+      </c>
+      <c r="N4" s="30">
         <f>ROUND(IMDIV(F4,J4),2)</f>
-        <v>0.53</v>
-      </c>
-      <c r="O4" s="9">
+        <v>0.47</v>
+      </c>
+      <c r="O4" s="30">
         <f>ROUND(IMDIV(G4,J4),2)</f>
-        <v>1.52</v>
-      </c>
-      <c r="P4" s="9">
+        <v>6.18</v>
+      </c>
+      <c r="P4" s="30">
         <f>ROUND(IMDIV(H4,J4),2)</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q4" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q4" s="30">
         <f>ROUND(IMDIV(B4,F4),2)</f>
-        <v>1.48</v>
-      </c>
-      <c r="R4" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="R4" s="30">
         <f>ROUND(IMDIV(C4,B4),4)*100</f>
-        <v>51.160000000000004</v>
-      </c>
-      <c r="S4" s="9">
+        <v>56.699999999999996</v>
+      </c>
+      <c r="S4" s="30">
         <f>ROUND(IMDIV(I4,J4),2)</f>
-        <v>87.43</v>
-      </c>
-      <c r="T4" s="9" t="s">
+        <v>102.33</v>
+      </c>
+      <c r="T4" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="10" t="s">
+      <c r="U4" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V4" s="45">
         <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
-        <v>1.2708329809725158</v>
+        <v>1.460696607638148</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="9">
-        <v>60</v>
-      </c>
-      <c r="C5" s="9">
-        <v>28</v>
-      </c>
-      <c r="D5" s="9">
-        <v>10</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="A5" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="29">
+        <v>42</v>
+      </c>
+      <c r="C5" s="29">
+        <v>15</v>
+      </c>
+      <c r="D5" s="29">
         <v>4</v>
       </c>
-      <c r="F5" s="9">
-        <v>66</v>
-      </c>
-      <c r="G5" s="9">
-        <v>527</v>
-      </c>
-      <c r="H5" s="9">
-        <v>18</v>
-      </c>
-      <c r="I5" s="9">
-        <v>6419</v>
-      </c>
-      <c r="J5" s="9">
-        <v>110</v>
-      </c>
-      <c r="K5" s="9">
+      <c r="E5" s="29">
+        <v>1</v>
+      </c>
+      <c r="F5" s="29">
+        <v>62</v>
+      </c>
+      <c r="G5" s="29">
+        <v>229</v>
+      </c>
+      <c r="H5" s="29">
+        <v>23</v>
+      </c>
+      <c r="I5" s="29">
+        <v>4816</v>
+      </c>
+      <c r="J5" s="29">
+        <v>109</v>
+      </c>
+      <c r="K5" s="30">
         <f>ROUND(IMDIV(B5,J5),2)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="L5" s="11">
+        <v>0.39</v>
+      </c>
+      <c r="L5" s="31">
         <f>E5/J5</f>
-        <v>3.6363636363636362E-2</v>
-      </c>
-      <c r="M5" s="11">
+        <v>9.1743119266055051E-3</v>
+      </c>
+      <c r="M5" s="31">
         <f>D5/J5</f>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="N5" s="9">
+        <v>3.669724770642202E-2</v>
+      </c>
+      <c r="N5" s="30">
         <f>ROUND(IMDIV(F5,J5),2)</f>
-        <v>0.6</v>
-      </c>
-      <c r="O5" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O5" s="30">
         <f>ROUND(IMDIV(G5,J5),2)</f>
-        <v>4.79</v>
-      </c>
-      <c r="P5" s="9">
+        <v>2.1</v>
+      </c>
+      <c r="P5" s="30">
         <f>ROUND(IMDIV(H5,J5),2)</f>
-        <v>0.16</v>
-      </c>
-      <c r="Q5" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="Q5" s="30">
         <f>ROUND(IMDIV(B5,F5),2)</f>
-        <v>0.91</v>
-      </c>
-      <c r="R5" s="9">
+        <v>0.68</v>
+      </c>
+      <c r="R5" s="30">
         <f>ROUND(IMDIV(C5,B5),4)*100</f>
-        <v>46.67</v>
-      </c>
-      <c r="S5" s="9">
+        <v>35.709999999999994</v>
+      </c>
+      <c r="S5" s="30">
         <f>ROUND(IMDIV(I5,J5),2)</f>
-        <v>58.35</v>
-      </c>
-      <c r="T5" s="9" t="s">
+        <v>44.18</v>
+      </c>
+      <c r="T5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="U5" s="10" t="s">
+      <c r="U5" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V5" s="45">
         <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
-        <v>0.92939534883720931</v>
+        <v>0.81299754640494992</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="12">
-        <v>75</v>
-      </c>
-      <c r="C6" s="12">
-        <v>33</v>
-      </c>
-      <c r="D6" s="12">
-        <v>19</v>
-      </c>
-      <c r="E6" s="12">
-        <v>5</v>
-      </c>
-      <c r="F6" s="12">
-        <v>48</v>
-      </c>
-      <c r="G6" s="12">
-        <v>302</v>
-      </c>
-      <c r="H6" s="12">
+      <c r="A6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="9">
+        <v>96</v>
+      </c>
+      <c r="C6" s="9">
+        <v>49</v>
+      </c>
+      <c r="D6" s="9">
+        <v>24</v>
+      </c>
+      <c r="E6" s="9">
         <v>10</v>
       </c>
-      <c r="I6" s="12">
-        <v>9181</v>
-      </c>
-      <c r="J6" s="12">
-        <v>92</v>
-      </c>
-      <c r="K6" s="12">
+      <c r="F6" s="9">
+        <v>67</v>
+      </c>
+      <c r="G6" s="9">
+        <v>293</v>
+      </c>
+      <c r="H6" s="9">
+        <v>35</v>
+      </c>
+      <c r="I6" s="9">
+        <v>11002</v>
+      </c>
+      <c r="J6" s="9">
+        <v>126</v>
+      </c>
+      <c r="K6" s="9">
         <f>ROUND(IMDIV(B6,J6),2)</f>
-        <v>0.82</v>
-      </c>
-      <c r="L6" s="13">
+        <v>0.76</v>
+      </c>
+      <c r="L6" s="11">
         <f>E6/J6</f>
-        <v>5.434782608695652E-2</v>
-      </c>
-      <c r="M6" s="13">
+        <v>7.9365079365079361E-2</v>
+      </c>
+      <c r="M6" s="11">
         <f>D6/J6</f>
-        <v>0.20652173913043478</v>
-      </c>
-      <c r="N6" s="12">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="N6" s="9">
         <f>ROUND(IMDIV(F6,J6),2)</f>
-        <v>0.52</v>
-      </c>
-      <c r="O6" s="12">
+        <v>0.53</v>
+      </c>
+      <c r="O6" s="9">
         <f>ROUND(IMDIV(G6,J6),2)</f>
-        <v>3.28</v>
-      </c>
-      <c r="P6" s="12">
+        <v>2.33</v>
+      </c>
+      <c r="P6" s="9">
         <f>ROUND(IMDIV(H6,J6),2)</f>
-        <v>0.11</v>
-      </c>
-      <c r="Q6" s="12">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q6" s="9">
         <f>ROUND(IMDIV(B6,F6),2)</f>
-        <v>1.56</v>
-      </c>
-      <c r="R6" s="12">
+        <v>1.43</v>
+      </c>
+      <c r="R6" s="9">
         <f>ROUND(IMDIV(C6,B6),4)*100</f>
-        <v>44</v>
-      </c>
-      <c r="S6" s="12">
+        <v>51.04</v>
+      </c>
+      <c r="S6" s="9">
         <f>ROUND(IMDIV(I6,J6),2)</f>
-        <v>99.79</v>
-      </c>
-      <c r="T6" s="51" t="s">
+        <v>87.32</v>
+      </c>
+      <c r="T6" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="14" t="s">
+      <c r="U6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V6" s="45">
         <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>1.3401395348837208</v>
+        <v>1.2576315983757844</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="12">
-        <v>45</v>
-      </c>
-      <c r="C7" s="12">
-        <v>22</v>
-      </c>
-      <c r="D7" s="12">
-        <v>6</v>
-      </c>
-      <c r="E7" s="12">
-        <v>2</v>
-      </c>
-      <c r="F7" s="12">
-        <v>51</v>
-      </c>
-      <c r="G7" s="12">
-        <v>115</v>
-      </c>
-      <c r="H7" s="12">
+      <c r="A7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9">
+        <v>70</v>
+      </c>
+      <c r="C7" s="9">
+        <v>31</v>
+      </c>
+      <c r="D7" s="9">
         <v>12</v>
       </c>
-      <c r="I7" s="12">
-        <v>4641</v>
-      </c>
-      <c r="J7" s="12">
-        <v>92</v>
-      </c>
-      <c r="K7" s="12">
+      <c r="E7" s="9">
+        <v>4</v>
+      </c>
+      <c r="F7" s="9">
+        <v>76</v>
+      </c>
+      <c r="G7" s="9">
+        <v>618</v>
+      </c>
+      <c r="H7" s="9">
+        <v>18</v>
+      </c>
+      <c r="I7" s="9">
+        <v>7491</v>
+      </c>
+      <c r="J7" s="9">
+        <v>126</v>
+      </c>
+      <c r="K7" s="9">
         <f>ROUND(IMDIV(B7,J7),2)</f>
-        <v>0.49</v>
-      </c>
-      <c r="L7" s="13">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L7" s="11">
         <f>E7/J7</f>
-        <v>2.1739130434782608E-2</v>
-      </c>
-      <c r="M7" s="13">
+        <v>3.1746031746031744E-2</v>
+      </c>
+      <c r="M7" s="11">
         <f>D7/J7</f>
-        <v>6.5217391304347824E-2</v>
-      </c>
-      <c r="N7" s="12">
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="N7" s="9">
         <f>ROUND(IMDIV(F7,J7),2)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O7" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="O7" s="9">
         <f>ROUND(IMDIV(G7,J7),2)</f>
-        <v>1.25</v>
-      </c>
-      <c r="P7" s="12">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P7" s="9">
         <f>ROUND(IMDIV(H7,J7),2)</f>
-        <v>0.13</v>
-      </c>
-      <c r="Q7" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q7" s="9">
         <f>ROUND(IMDIV(B7,F7),2)</f>
-        <v>0.88</v>
-      </c>
-      <c r="R7" s="12">
+        <v>0.92</v>
+      </c>
+      <c r="R7" s="9">
         <f>ROUND(IMDIV(C7,B7),4)*100</f>
-        <v>48.89</v>
-      </c>
-      <c r="S7" s="12">
+        <v>44.29</v>
+      </c>
+      <c r="S7" s="9">
         <f>ROUND(IMDIV(I7,J7),2)</f>
-        <v>50.45</v>
-      </c>
-      <c r="T7" s="51" t="s">
+        <v>59.45</v>
+      </c>
+      <c r="T7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="U7" s="14" t="s">
+      <c r="U7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V7" s="45">
         <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
-        <v>0.90780333670374114</v>
+        <v>0.93767035806570698</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="29">
-        <v>86</v>
-      </c>
-      <c r="C8" s="29">
+      <c r="A8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="26">
+        <v>92</v>
+      </c>
+      <c r="C8" s="26">
         <v>50</v>
       </c>
-      <c r="D8" s="29">
-        <v>29</v>
-      </c>
-      <c r="E8" s="29">
-        <v>9</v>
-      </c>
-      <c r="F8" s="29">
-        <v>42</v>
-      </c>
-      <c r="G8" s="29">
-        <v>586</v>
-      </c>
-      <c r="H8" s="29">
-        <v>15</v>
-      </c>
-      <c r="I8" s="29">
-        <v>9874</v>
-      </c>
-      <c r="J8" s="29">
-        <v>93</v>
-      </c>
-      <c r="K8" s="30">
+      <c r="D8" s="26">
+        <v>17</v>
+      </c>
+      <c r="E8" s="26">
+        <v>14</v>
+      </c>
+      <c r="F8" s="26">
+        <v>66</v>
+      </c>
+      <c r="G8" s="26">
+        <v>252</v>
+      </c>
+      <c r="H8" s="26">
+        <v>34</v>
+      </c>
+      <c r="I8" s="26">
+        <v>10439</v>
+      </c>
+      <c r="J8" s="26">
+        <v>123</v>
+      </c>
+      <c r="K8" s="27">
         <f>ROUND(IMDIV(B8,J8),2)</f>
-        <v>0.92</v>
-      </c>
-      <c r="L8" s="31">
+        <v>0.75</v>
+      </c>
+      <c r="L8" s="28">
         <f>E8/J8</f>
-        <v>9.6774193548387094E-2</v>
-      </c>
-      <c r="M8" s="31">
+        <v>0.11382113821138211</v>
+      </c>
+      <c r="M8" s="28">
         <f>D8/J8</f>
-        <v>0.31182795698924731</v>
-      </c>
-      <c r="N8" s="30">
+        <v>0.13821138211382114</v>
+      </c>
+      <c r="N8" s="27">
         <f>ROUND(IMDIV(F8,J8),2)</f>
-        <v>0.45</v>
-      </c>
-      <c r="O8" s="30">
+        <v>0.54</v>
+      </c>
+      <c r="O8" s="27">
         <f>ROUND(IMDIV(G8,J8),2)</f>
-        <v>6.3</v>
-      </c>
-      <c r="P8" s="30">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P8" s="27">
         <f>ROUND(IMDIV(H8,J8),2)</f>
-        <v>0.16</v>
-      </c>
-      <c r="Q8" s="30">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q8" s="27">
         <f>ROUND(IMDIV(B8,F8),2)</f>
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="R8" s="30">
+        <v>1.39</v>
+      </c>
+      <c r="R8" s="27">
         <f>ROUND(IMDIV(C8,B8),4)*100</f>
-        <v>58.14</v>
-      </c>
-      <c r="S8" s="30">
+        <v>54.35</v>
+      </c>
+      <c r="S8" s="27">
         <f>ROUND(IMDIV(I8,J8),2)</f>
-        <v>106.17</v>
-      </c>
-      <c r="T8" s="29" t="s">
+        <v>84.87</v>
+      </c>
+      <c r="T8" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="U8" s="29" t="s">
+      <c r="U8" s="26" t="s">
         <v>24</v>
       </c>
       <c r="V8" s="45">
         <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
-        <v>1.5171257814453614</v>
+        <v>1.2260612592172433</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="26">
+        <v>65</v>
+      </c>
+      <c r="C9" s="26">
+        <v>26</v>
+      </c>
+      <c r="D9" s="26">
+        <v>10</v>
+      </c>
+      <c r="E9" s="26">
+        <v>2</v>
+      </c>
+      <c r="F9" s="26">
+        <v>72</v>
+      </c>
+      <c r="G9" s="26">
+        <v>304</v>
+      </c>
+      <c r="H9" s="26">
+        <v>25</v>
+      </c>
+      <c r="I9" s="26">
+        <v>7274</v>
+      </c>
+      <c r="J9" s="26">
+        <v>112</v>
+      </c>
+      <c r="K9" s="27">
+        <f>ROUND(IMDIV(B9,J9),2)</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L9" s="28">
+        <f>E9/J9</f>
+        <v>1.7857142857142856E-2</v>
+      </c>
+      <c r="M9" s="28">
+        <f>D9/J9</f>
+        <v>8.9285714285714288E-2</v>
+      </c>
+      <c r="N9" s="27">
+        <f>ROUND(IMDIV(F9,J9),2)</f>
+        <v>0.64</v>
+      </c>
+      <c r="O9" s="27">
+        <f>ROUND(IMDIV(G9,J9),2)</f>
+        <v>2.71</v>
+      </c>
+      <c r="P9" s="27">
+        <f>ROUND(IMDIV(H9,J9),2)</f>
+        <v>0.22</v>
+      </c>
+      <c r="Q9" s="27">
+        <f>ROUND(IMDIV(B9,F9),2)</f>
+        <v>0.9</v>
+      </c>
+      <c r="R9" s="27">
+        <f>ROUND(IMDIV(C9,B9),4)*100</f>
         <v>40</v>
       </c>
-      <c r="B9" s="29">
-        <v>34</v>
-      </c>
-      <c r="C9" s="29">
-        <v>12</v>
-      </c>
-      <c r="D9" s="29">
-        <v>3</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
-        <v>51</v>
-      </c>
-      <c r="G9" s="29">
-        <v>165</v>
-      </c>
-      <c r="H9" s="29">
-        <v>19</v>
-      </c>
-      <c r="I9" s="29">
-        <v>3824</v>
-      </c>
-      <c r="J9" s="29">
-        <v>93</v>
-      </c>
-      <c r="K9" s="30">
-        <f>ROUND(IMDIV(B9,J9),2)</f>
-        <v>0.37</v>
-      </c>
-      <c r="L9" s="31">
-        <f>E9/J9</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="31">
-        <f>D9/J9</f>
-        <v>3.2258064516129031E-2</v>
-      </c>
-      <c r="N9" s="30">
-        <f>ROUND(IMDIV(F9,J9),2)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O9" s="30">
-        <f>ROUND(IMDIV(G9,J9),2)</f>
-        <v>1.77</v>
-      </c>
-      <c r="P9" s="30">
-        <f>ROUND(IMDIV(H9,J9),2)</f>
-        <v>0.2</v>
-      </c>
-      <c r="Q9" s="30">
-        <f>ROUND(IMDIV(B9,F9),2)</f>
-        <v>0.67</v>
-      </c>
-      <c r="R9" s="30">
-        <f>ROUND(IMDIV(C9,B9),4)*100</f>
-        <v>35.29</v>
-      </c>
-      <c r="S9" s="30">
+      <c r="S9" s="27">
         <f>ROUND(IMDIV(I9,J9),2)</f>
-        <v>41.12</v>
-      </c>
-      <c r="T9" s="29" t="s">
+        <v>64.95</v>
+      </c>
+      <c r="T9" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="U9" s="29" t="s">
+      <c r="U9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="V9" s="45">
         <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
-        <v>0.80732033008252058</v>
+        <v>0.93098588039867103</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="12">
+        <v>85</v>
+      </c>
+      <c r="C10" s="12">
         <v>37</v>
       </c>
-      <c r="B10" s="26">
-        <v>73</v>
-      </c>
-      <c r="C10" s="26">
-        <v>37</v>
-      </c>
-      <c r="D10" s="26">
-        <v>14</v>
-      </c>
-      <c r="E10" s="26">
-        <v>11</v>
-      </c>
-      <c r="F10" s="26">
-        <v>53</v>
-      </c>
-      <c r="G10" s="26">
-        <v>252</v>
-      </c>
-      <c r="H10" s="26">
-        <v>34</v>
-      </c>
-      <c r="I10" s="26">
-        <v>8657</v>
-      </c>
-      <c r="J10" s="26">
-        <v>101</v>
-      </c>
-      <c r="K10" s="27">
+      <c r="D10" s="12">
+        <v>23</v>
+      </c>
+      <c r="E10" s="12">
+        <v>6</v>
+      </c>
+      <c r="F10" s="12">
+        <v>51</v>
+      </c>
+      <c r="G10" s="12">
+        <v>302</v>
+      </c>
+      <c r="H10" s="12">
+        <v>13</v>
+      </c>
+      <c r="I10" s="12">
+        <v>10270</v>
+      </c>
+      <c r="J10" s="12">
+        <v>103</v>
+      </c>
+      <c r="K10" s="12">
         <f>ROUND(IMDIV(B10,J10),2)</f>
-        <v>0.72</v>
-      </c>
-      <c r="L10" s="28">
+        <v>0.83</v>
+      </c>
+      <c r="L10" s="13">
         <f>E10/J10</f>
-        <v>0.10891089108910891</v>
-      </c>
-      <c r="M10" s="28">
+        <v>5.8252427184466021E-2</v>
+      </c>
+      <c r="M10" s="13">
         <f>D10/J10</f>
-        <v>0.13861386138613863</v>
-      </c>
-      <c r="N10" s="27">
+        <v>0.22330097087378642</v>
+      </c>
+      <c r="N10" s="12">
         <f>ROUND(IMDIV(F10,J10),2)</f>
-        <v>0.52</v>
-      </c>
-      <c r="O10" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="O10" s="12">
         <f>ROUND(IMDIV(G10,J10),2)</f>
-        <v>2.5</v>
-      </c>
-      <c r="P10" s="27">
+        <v>2.93</v>
+      </c>
+      <c r="P10" s="12">
         <f>ROUND(IMDIV(H10,J10),2)</f>
-        <v>0.34</v>
-      </c>
-      <c r="Q10" s="27">
+        <v>0.13</v>
+      </c>
+      <c r="Q10" s="12">
         <f>ROUND(IMDIV(B10,F10),2)</f>
-        <v>1.38</v>
-      </c>
-      <c r="R10" s="27">
+        <v>1.67</v>
+      </c>
+      <c r="R10" s="12">
         <f>ROUND(IMDIV(C10,B10),4)*100</f>
-        <v>50.68</v>
-      </c>
-      <c r="S10" s="27">
+        <v>43.53</v>
+      </c>
+      <c r="S10" s="12">
         <f>ROUND(IMDIV(I10,J10),2)</f>
-        <v>85.71</v>
-      </c>
-      <c r="T10" s="26" t="s">
+        <v>99.71</v>
+      </c>
+      <c r="T10" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="U10" s="26" t="s">
+      <c r="U10" s="14" t="s">
         <v>24</v>
       </c>
       <c r="V10" s="45">
         <f>((K10/2.5)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
-        <v>1.2400868063550541</v>
+        <v>1.3697431700158047</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="A11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12">
         <v>55</v>
       </c>
-      <c r="C11" s="26">
-        <v>20</v>
-      </c>
-      <c r="D11" s="26">
+      <c r="C11" s="12">
+        <v>29</v>
+      </c>
+      <c r="D11" s="12">
         <v>9</v>
       </c>
-      <c r="E11" s="26">
-        <v>2</v>
-      </c>
-      <c r="F11" s="26">
-        <v>55</v>
-      </c>
-      <c r="G11" s="26">
-        <v>304</v>
-      </c>
-      <c r="H11" s="26">
-        <v>25</v>
-      </c>
-      <c r="I11" s="26">
-        <v>5800</v>
-      </c>
-      <c r="J11" s="26">
-        <v>90</v>
-      </c>
-      <c r="K11" s="27">
+      <c r="E11" s="12">
+        <v>3</v>
+      </c>
+      <c r="F11" s="12">
+        <v>56</v>
+      </c>
+      <c r="G11" s="12">
+        <v>144</v>
+      </c>
+      <c r="H11" s="12">
+        <v>15</v>
+      </c>
+      <c r="I11" s="12">
+        <v>5653</v>
+      </c>
+      <c r="J11" s="12">
+        <v>103</v>
+      </c>
+      <c r="K11" s="12">
         <f>ROUND(IMDIV(B11,J11),2)</f>
-        <v>0.61</v>
-      </c>
-      <c r="L11" s="28">
+        <v>0.53</v>
+      </c>
+      <c r="L11" s="13">
         <f>E11/J11</f>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="M11" s="28">
+        <v>2.9126213592233011E-2</v>
+      </c>
+      <c r="M11" s="13">
         <f>D11/J11</f>
-        <v>0.1</v>
-      </c>
-      <c r="N11" s="27">
+        <v>8.7378640776699032E-2</v>
+      </c>
+      <c r="N11" s="12">
         <f>ROUND(IMDIV(F11,J11),2)</f>
-        <v>0.61</v>
-      </c>
-      <c r="O11" s="27">
+        <v>0.54</v>
+      </c>
+      <c r="O11" s="12">
         <f>ROUND(IMDIV(G11,J11),2)</f>
-        <v>3.38</v>
-      </c>
-      <c r="P11" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="P11" s="12">
         <f>ROUND(IMDIV(H11,J11),2)</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q11" s="27">
+        <v>0.15</v>
+      </c>
+      <c r="Q11" s="12">
         <f>ROUND(IMDIV(B11,F11),2)</f>
-        <v>1</v>
-      </c>
-      <c r="R11" s="27">
+        <v>0.98</v>
+      </c>
+      <c r="R11" s="12">
         <f>ROUND(IMDIV(C11,B11),4)*100</f>
-        <v>36.36</v>
-      </c>
-      <c r="S11" s="27">
+        <v>52.73</v>
+      </c>
+      <c r="S11" s="12">
         <f>ROUND(IMDIV(I11,J11),2)</f>
-        <v>64.44</v>
-      </c>
-      <c r="T11" s="26" t="s">
+        <v>54.88</v>
+      </c>
+      <c r="T11" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="U11" s="26" t="s">
+      <c r="U11" s="14" t="s">
         <v>24</v>
       </c>
       <c r="V11" s="45">
         <f>((K11/2.5)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
-        <v>0.9771653746770026</v>
+        <v>0.96242571686610967</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1708,67 +1708,67 @@
         <v>34</v>
       </c>
       <c r="B12" s="50">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C12" s="50">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D12" s="50">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E12" s="50">
         <v>8</v>
       </c>
       <c r="F12" s="50">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G12" s="50">
-        <v>473</v>
+        <v>568</v>
       </c>
       <c r="H12" s="50">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" s="50">
-        <v>7629</v>
+        <v>8757</v>
       </c>
       <c r="J12" s="50">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="K12" s="20">
         <f>ROUND(IMDIV(B12,J12),2)</f>
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="L12" s="21">
         <f>E12/J12</f>
-        <v>7.7669902912621352E-2</v>
+        <v>6.9565217391304349E-2</v>
       </c>
       <c r="M12" s="21">
         <f>D12/J12</f>
-        <v>0.20388349514563106</v>
+        <v>0.20869565217391303</v>
       </c>
       <c r="N12" s="20">
         <f>ROUND(IMDIV(F12,J12),2)</f>
-        <v>0.59</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="O12" s="20">
         <f>ROUND(IMDIV(G12,J12),2)</f>
-        <v>4.59</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="P12" s="20">
         <f>ROUND(IMDIV(H12,J12),2)</f>
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="Q12" s="20">
         <f>ROUND(IMDIV(B12,F12),2)</f>
-        <v>1.1000000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="R12" s="20">
         <f>ROUND(IMDIV(C12,B12),4)*100</f>
-        <v>70.150000000000006</v>
+        <v>68.83</v>
       </c>
       <c r="S12" s="20">
         <f>ROUND(IMDIV(I12,J12),2)</f>
-        <v>74.069999999999993</v>
+        <v>76.150000000000006</v>
       </c>
       <c r="T12" s="20" t="s">
         <v>46</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="V12" s="45">
         <f>((K12/2.5)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
-        <v>1.0905164822759088</v>
+        <v>1.1272730030333671</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1786,67 +1786,67 @@
         <v>35</v>
       </c>
       <c r="B13" s="50">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C13" s="50">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13" s="50">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E13" s="50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="50">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G13" s="50">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="H13" s="50">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I13" s="50">
-        <v>6610</v>
+        <v>7414</v>
       </c>
       <c r="J13" s="50">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="K13" s="20">
         <f>ROUND(IMDIV(B13,J13),2)</f>
-        <v>0.54</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="L13" s="21">
         <f>E13/J13</f>
-        <v>4.8543689320388349E-2</v>
+        <v>5.2173913043478258E-2</v>
       </c>
       <c r="M13" s="21">
         <f>D13/J13</f>
-        <v>0.1553398058252427</v>
+        <v>0.16521739130434782</v>
       </c>
       <c r="N13" s="20">
         <f>ROUND(IMDIV(F13,J13),2)</f>
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="O13" s="20">
         <f>ROUND(IMDIV(G13,J13),2)</f>
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="P13" s="20">
         <f>ROUND(IMDIV(H13,J13),2)</f>
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="Q13" s="20">
         <f>ROUND(IMDIV(B13,F13),2)</f>
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="R13" s="20">
         <f>ROUND(IMDIV(C13,B13),4)*100</f>
-        <v>50</v>
+        <v>49.230000000000004</v>
       </c>
       <c r="S13" s="20">
         <f>ROUND(IMDIV(I13,J13),2)</f>
-        <v>64.17</v>
+        <v>64.47</v>
       </c>
       <c r="T13" s="20" t="s">
         <v>46</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="V13" s="45">
         <f>((K13/2.5)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
-        <v>0.93500880559945809</v>
+        <v>0.98109959555106163</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1864,67 +1864,67 @@
         <v>41</v>
       </c>
       <c r="B14" s="32">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C14" s="32">
         <v>16</v>
       </c>
       <c r="D14" s="32">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="32">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G14" s="32">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="H14" s="32">
         <v>17</v>
       </c>
       <c r="I14" s="32">
-        <v>5224</v>
+        <v>6196</v>
       </c>
       <c r="J14" s="32">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="K14" s="33">
         <f>ROUND(IMDIV(B14,J14),2)</f>
-        <v>0.55000000000000004</v>
+        <v>0.53</v>
       </c>
       <c r="L14" s="34">
         <f>E14/J14</f>
-        <v>1.3698630136986301E-2</v>
+        <v>2.3529411764705882E-2</v>
       </c>
       <c r="M14" s="34">
         <f>D14/J14</f>
-        <v>0.16438356164383561</v>
+        <v>0.15294117647058825</v>
       </c>
       <c r="N14" s="33">
         <f>ROUND(IMDIV(F14,J14),2)</f>
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="O14" s="33">
         <f>ROUND(IMDIV(G14,J14),2)</f>
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="P14" s="33">
         <f>ROUND(IMDIV(H14,J14),2)</f>
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" s="33">
         <f>ROUND(IMDIV(B14,F14),2)</f>
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="R14" s="33">
         <f>ROUND(IMDIV(C14,B14),4)*100</f>
-        <v>40</v>
+        <v>35.56</v>
       </c>
       <c r="S14" s="33">
         <f>ROUND(IMDIV(I14,J14),2)</f>
-        <v>71.56</v>
+        <v>72.89</v>
       </c>
       <c r="T14" s="32" t="s">
         <v>46</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="V14" s="45">
         <f>((K14/2.5)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
-        <v>0.93817282574068173</v>
+        <v>0.92396443228454173</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1942,10 +1942,10 @@
         <v>26</v>
       </c>
       <c r="B15" s="32">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" s="32">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="32">
         <v>8</v>
@@ -1954,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="32">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G15" s="32">
         <v>253</v>
@@ -1963,46 +1963,46 @@
         <v>6</v>
       </c>
       <c r="I15" s="32">
-        <v>3677</v>
+        <v>4025</v>
       </c>
       <c r="J15" s="32">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="K15" s="33">
         <f>ROUND(IMDIV(B15,J15),2)</f>
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="L15" s="34">
         <f>E15/J15</f>
-        <v>4.1095890410958902E-2</v>
+        <v>3.5294117647058823E-2</v>
       </c>
       <c r="M15" s="34">
         <f>D15/J15</f>
-        <v>0.1095890410958904</v>
+        <v>9.4117647058823528E-2</v>
       </c>
       <c r="N15" s="33">
         <f>ROUND(IMDIV(F15,J15),2)</f>
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="O15" s="33">
         <f>ROUND(IMDIV(G15,J15),2)</f>
-        <v>3.47</v>
+        <v>2.98</v>
       </c>
       <c r="P15" s="33">
         <f>ROUND(IMDIV(H15,J15),2)</f>
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q15" s="33">
         <f>ROUND(IMDIV(B15,F15),2)</f>
-        <v>0.69</v>
+        <v>0.63</v>
       </c>
       <c r="R15" s="33">
         <f>ROUND(IMDIV(C15,B15),4)*100</f>
-        <v>47.06</v>
+        <v>45.95</v>
       </c>
       <c r="S15" s="33">
         <f>ROUND(IMDIV(I15,J15),2)</f>
-        <v>50.37</v>
+        <v>47.35</v>
       </c>
       <c r="T15" s="32" t="s">
         <v>46</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="V15" s="45">
         <f>((K15/2.5)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
-        <v>0.79189550812360621</v>
+        <v>0.74032079343365265</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -2020,43 +2020,43 @@
         <v>22</v>
       </c>
       <c r="B16" s="18">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C16" s="18">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D16" s="18">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="18">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G16" s="18">
-        <v>293</v>
+        <v>367</v>
       </c>
       <c r="H16" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="18">
-        <v>6973</v>
+        <v>8413</v>
       </c>
       <c r="J16" s="18">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="K16" s="18">
         <f>ROUND(IMDIV(B16,J16),2)</f>
-        <v>0.55000000000000004</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="L16" s="19">
         <f>E16/J16</f>
-        <v>2.0202020202020204E-2</v>
+        <v>2.5210084033613446E-2</v>
       </c>
       <c r="M16" s="19">
         <f>D16/J16</f>
-        <v>0.1111111111111111</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="N16" s="18">
         <f>ROUND(IMDIV(F16,J16),2)</f>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="O16" s="18">
         <f>ROUND(IMDIV(G16,J16),2)</f>
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="P16" s="18">
         <f>ROUND(IMDIV(H16,J16),2)</f>
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Q16" s="18">
         <f>ROUND(IMDIV(B16,F16),2)</f>
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="R16" s="18">
         <f>ROUND(IMDIV(C16,B16),4)*100</f>
-        <v>51.849999999999994</v>
+        <v>52.239999999999995</v>
       </c>
       <c r="S16" s="18">
         <f>ROUND(IMDIV(I16,J16),2)</f>
-        <v>70.430000000000007</v>
+        <v>70.7</v>
       </c>
       <c r="T16" s="18" t="s">
         <v>46</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="V16" s="45">
         <f>((K16/2.5)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
-        <v>0.93539957716701916</v>
+        <v>0.94279099081493056</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -2098,31 +2098,31 @@
         <v>23</v>
       </c>
       <c r="B17" s="18">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C17" s="18">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D17" s="18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="18">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G17" s="18">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="H17" s="18">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I17" s="18">
-        <v>5547</v>
+        <v>6687</v>
       </c>
       <c r="J17" s="18">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="K17" s="18">
         <f>ROUND(IMDIV(B17,J17),2)</f>
@@ -2130,35 +2130,35 @@
       </c>
       <c r="L17" s="19">
         <f>E17/J17</f>
-        <v>1.0101010101010102E-2</v>
+        <v>1.680672268907563E-2</v>
       </c>
       <c r="M17" s="19">
         <f>D17/J17</f>
-        <v>8.0808080808080815E-2</v>
+        <v>8.4033613445378158E-2</v>
       </c>
       <c r="N17" s="18">
         <f>ROUND(IMDIV(F17,J17),2)</f>
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="O17" s="18">
         <f>ROUND(IMDIV(G17,J17),2)</f>
-        <v>0.67</v>
+        <v>1.49</v>
       </c>
       <c r="P17" s="18">
         <f>ROUND(IMDIV(H17,J17),2)</f>
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="Q17" s="18">
         <f>ROUND(IMDIV(B17,F17),2)</f>
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="R17" s="18">
         <f>ROUND(IMDIV(C17,B17),4)*100</f>
-        <v>39.129999999999995</v>
+        <v>38.18</v>
       </c>
       <c r="S17" s="18">
         <f>ROUND(IMDIV(I17,J17),2)</f>
-        <v>56.03</v>
+        <v>56.19</v>
       </c>
       <c r="T17" s="18" t="s">
         <v>46</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" s="45">
         <f>((K17/2.5)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
-        <v>0.83282687338501282</v>
+        <v>0.8162185851084619</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -2176,10 +2176,10 @@
         <v>36</v>
       </c>
       <c r="B18" s="23">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C18" s="23">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D18" s="23">
         <v>18</v>
@@ -2188,55 +2188,55 @@
         <v>2</v>
       </c>
       <c r="F18" s="23">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G18" s="23">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="H18" s="23">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I18" s="23">
-        <v>7200</v>
+        <v>7926</v>
       </c>
       <c r="J18" s="23">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K18" s="24">
         <f>ROUND(IMDIV(B18,J18),2)</f>
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="L18" s="25">
         <f>E18/J18</f>
-        <v>2.2988505747126436E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="M18" s="25">
         <f>D18/J18</f>
-        <v>0.20689655172413793</v>
+        <v>0.18367346938775511</v>
       </c>
       <c r="N18" s="24">
         <f>ROUND(IMDIV(F18,J18),2)</f>
-        <v>0.69</v>
+        <v>0.72</v>
       </c>
       <c r="O18" s="24">
         <f>ROUND(IMDIV(G18,J18),2)</f>
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
       <c r="P18" s="24">
         <f>ROUND(IMDIV(H18,J18),2)</f>
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q18" s="24">
         <f>ROUND(IMDIV(B18,F18),2)</f>
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="R18" s="24">
         <f>ROUND(IMDIV(C18,B18),4)*100</f>
-        <v>60</v>
+        <v>61.019999999999996</v>
       </c>
       <c r="S18" s="24">
         <f>ROUND(IMDIV(I18,J18),2)</f>
-        <v>82.76</v>
+        <v>80.88</v>
       </c>
       <c r="T18" s="24" t="s">
         <v>46</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="V18" s="45">
         <f>((K18/2.5)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
-        <v>1.0097520716385993</v>
+        <v>0.95318604651162786</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -2254,19 +2254,19 @@
         <v>25</v>
       </c>
       <c r="B19" s="23">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C19" s="23">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="23">
         <v>2</v>
       </c>
       <c r="F19" s="23">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G19" s="24">
         <v>113</v>
@@ -2275,10 +2275,10 @@
         <v>9</v>
       </c>
       <c r="I19" s="23">
-        <v>3045</v>
+        <v>3573</v>
       </c>
       <c r="J19" s="23">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K19" s="24">
         <f>ROUND(IMDIV(B19,J19),2)</f>
@@ -2286,35 +2286,35 @@
       </c>
       <c r="L19" s="25">
         <f>E19/J19</f>
-        <v>2.8169014084507043E-2</v>
+        <v>2.4390243902439025E-2</v>
       </c>
       <c r="M19" s="25">
         <f>D19/J19</f>
-        <v>7.0422535211267609E-2</v>
+        <v>7.3170731707317069E-2</v>
       </c>
       <c r="N19" s="24">
         <f>ROUND(IMDIV(F19,J19),2)</f>
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="O19" s="24">
         <f>ROUND(IMDIV(G19,J19),2)</f>
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="P19" s="24">
         <f>ROUND(IMDIV(H19,J19),2)</f>
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="Q19" s="24">
         <f>ROUND(IMDIV(B19,F19),2)</f>
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="R19" s="24">
         <f>ROUND(IMDIV(C19,B19),4)*100</f>
-        <v>52</v>
+        <v>48.28</v>
       </c>
       <c r="S19" s="24">
         <f>ROUND(IMDIV(I19,J19),2)</f>
-        <v>42.89</v>
+        <v>43.57</v>
       </c>
       <c r="T19" s="24" t="s">
         <v>46</v>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="V19" s="45">
         <f>((K19/2.5)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
-        <v>0.67922780871274169</v>
+        <v>0.66132189449801471</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -2332,67 +2332,67 @@
         <v>33</v>
       </c>
       <c r="B20" s="15">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C20" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D20" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
         <v>4</v>
       </c>
       <c r="F20" s="15">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G20" s="15">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H20" s="15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I20" s="15">
-        <v>6460</v>
+        <v>7920</v>
       </c>
       <c r="J20" s="15">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="K20" s="15">
         <f>ROUND(IMDIV(B20,J20),2)</f>
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="L20" s="17">
         <f>E20/J20</f>
-        <v>4.3478260869565216E-2</v>
+        <v>3.5714285714285712E-2</v>
       </c>
       <c r="M20" s="17">
         <f>D20/J20</f>
-        <v>0.13043478260869565</v>
+        <v>0.11607142857142858</v>
       </c>
       <c r="N20" s="15">
         <f>ROUND(IMDIV(F20,J20),2)</f>
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="O20" s="15">
         <f>ROUND(IMDIV(G20,J20),2)</f>
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="P20" s="15">
         <f>ROUND(IMDIV(H20,J20),2)</f>
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="Q20" s="15">
         <f>ROUND(IMDIV(B20,F20),2)</f>
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="R20" s="15">
         <f>ROUND(IMDIV(C20,B20),4)*100</f>
-        <v>71.430000000000007</v>
+        <v>66.67</v>
       </c>
       <c r="S20" s="15">
         <f>ROUND(IMDIV(I20,J20),2)</f>
-        <v>70.22</v>
+        <v>70.709999999999994</v>
       </c>
       <c r="T20" s="16" t="s">
         <v>42</v>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="V20" s="45">
         <f>((K20/2.5)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
-        <v>0.95340899898887754</v>
+        <v>0.9755444352159468</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -2410,67 +2410,67 @@
         <v>21</v>
       </c>
       <c r="B21" s="15">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C21" s="15">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D21" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="15">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G21" s="15">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="H21" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I21" s="15">
-        <v>3560</v>
+        <v>5180</v>
       </c>
       <c r="J21" s="15">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="K21" s="15">
         <f>ROUND(IMDIV(B21,J21),2)</f>
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="L21" s="17">
         <f>E21/J21</f>
-        <v>0</v>
+        <v>9.9009900990099011E-3</v>
       </c>
       <c r="M21" s="17">
         <f>D21/J21</f>
-        <v>4.9382716049382713E-2</v>
+        <v>6.9306930693069313E-2</v>
       </c>
       <c r="N21" s="15">
         <f>ROUND(IMDIV(F21,J21),2)</f>
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="O21" s="15">
         <f>ROUND(IMDIV(G21,J21),2)</f>
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="P21" s="15">
         <f>ROUND(IMDIV(H21,J21),2)</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="Q21" s="15">
         <f>ROUND(IMDIV(B21,F21),2)</f>
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="R21" s="15">
         <f>ROUND(IMDIV(C21,B21),4)*100</f>
-        <v>41.94</v>
+        <v>47.83</v>
       </c>
       <c r="S21" s="15">
         <f>ROUND(IMDIV(I21,J21),2)</f>
-        <v>43.95</v>
+        <v>51.29</v>
       </c>
       <c r="T21" s="16" t="s">
         <v>42</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="V21" s="45">
         <f>((K21/2.5)+(M21/4)+(L21/5)-(N21)+(S21/215)+(P21/20))+1</f>
-        <v>0.62476428366350845</v>
+        <v>0.73936507022795306</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6815AA8A-76B1-4445-9EE4-8FDF37CD5F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6869C109-053B-4327-8584-F035651B4560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="2205" yWindow="2235" windowWidth="25815" windowHeight="12810" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -164,9 +164,6 @@
     <t>dverad74</t>
   </si>
   <si>
-    <t>10th</t>
-  </si>
-  <si>
     <t>PadRating1.2</t>
   </si>
   <si>
@@ -176,10 +173,13 @@
     <t>nth</t>
   </si>
   <si>
-    <t>9th</t>
-  </si>
-  <si>
-    <t>5th</t>
+    <t>3rd-4th</t>
+  </si>
+  <si>
+    <t>5th-6th</t>
+  </si>
+  <si>
+    <t>7th-10th</t>
   </si>
 </sst>
 </file>
@@ -920,7 +920,7 @@
         <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -928,77 +928,77 @@
         <v>28</v>
       </c>
       <c r="B2" s="6">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C2" s="6">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D2" s="6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="6">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G2" s="6">
-        <v>618</v>
+        <v>668</v>
       </c>
       <c r="H2" s="6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I2" s="6">
-        <v>10813</v>
+        <v>12100</v>
       </c>
       <c r="J2" s="6">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="K2" s="6">
         <f>ROUND(IMDIV(B2,J2),2)</f>
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="L2" s="7">
         <f>E2/J2</f>
-        <v>6.6666666666666666E-2</v>
+        <v>6.7796610169491525E-2</v>
       </c>
       <c r="M2" s="7">
         <f>D2/J2</f>
-        <v>0.27619047619047621</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="N2" s="6">
         <f>ROUND(IMDIV(F2,J2),2)</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="O2" s="6">
         <f>ROUND(IMDIV(G2,J2),2)</f>
-        <v>5.89</v>
+        <v>5.66</v>
       </c>
       <c r="P2" s="6">
         <f>ROUND(IMDIV(H2,J2),2)</f>
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="Q2" s="6">
         <f>ROUND(IMDIV(B2,F2),2)</f>
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="R2" s="6">
         <f>ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>65.69</v>
+        <v>65.180000000000007</v>
       </c>
       <c r="S2" s="6">
         <f>ROUND(IMDIV(I2,J2),2)</f>
-        <v>102.98</v>
+        <v>102.54</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="U2" s="8" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="45">
         <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>1.5128576965669989</v>
+        <v>1.4812861647615294</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1006,51 +1006,51 @@
         <v>27</v>
       </c>
       <c r="B3" s="6">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C3" s="6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6">
         <v>2</v>
       </c>
       <c r="F3" s="6">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G3" s="6">
         <v>41</v>
       </c>
       <c r="H3" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="6">
-        <v>5818</v>
+        <v>6117</v>
       </c>
       <c r="J3" s="6">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="K3" s="6">
         <f>ROUND(IMDIV(B3,J3),2)</f>
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="L3" s="7">
         <f>E3/J3</f>
-        <v>1.9047619047619049E-2</v>
+        <v>1.6949152542372881E-2</v>
       </c>
       <c r="M3" s="7">
         <f>D3/J3</f>
-        <v>8.5714285714285715E-2</v>
+        <v>8.4745762711864403E-2</v>
       </c>
       <c r="N3" s="6">
         <f>ROUND(IMDIV(F3,J3),2)</f>
-        <v>0.57999999999999996</v>
+        <v>0.61</v>
       </c>
       <c r="O3" s="6">
         <f>ROUND(IMDIV(G3,J3),2)</f>
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="P3" s="6">
         <f>ROUND(IMDIV(H3,J3),2)</f>
@@ -1058,25 +1058,25 @@
       </c>
       <c r="Q3" s="6">
         <f>ROUND(IMDIV(B3,F3),2)</f>
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="R3" s="6">
         <f>ROUND(IMDIV(C3,B3),4)*100</f>
-        <v>50.94</v>
+        <v>50.88</v>
       </c>
       <c r="S3" s="6">
         <f>ROUND(IMDIV(I3,J3),2)</f>
-        <v>55.41</v>
+        <v>51.84</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="V3" s="45">
         <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
-        <v>0.90895902547065344</v>
+        <v>0.85369255025620816</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1084,31 +1084,31 @@
         <v>39</v>
       </c>
       <c r="B4" s="29">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C4" s="29">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D4" s="29">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4" s="29">
         <v>10</v>
       </c>
       <c r="F4" s="29">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G4" s="29">
-        <v>674</v>
+        <v>794</v>
       </c>
       <c r="H4" s="29">
         <v>15</v>
       </c>
       <c r="I4" s="29">
-        <v>11154</v>
+        <v>12350</v>
       </c>
       <c r="J4" s="29">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K4" s="30">
         <f>ROUND(IMDIV(B4,J4),2)</f>
@@ -1116,45 +1116,45 @@
       </c>
       <c r="L4" s="31">
         <f>E4/J4</f>
-        <v>9.1743119266055051E-2</v>
+        <v>8.1967213114754092E-2</v>
       </c>
       <c r="M4" s="31">
         <f>D4/J4</f>
-        <v>0.29357798165137616</v>
+        <v>0.28688524590163933</v>
       </c>
       <c r="N4" s="30">
         <f>ROUND(IMDIV(F4,J4),2)</f>
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="O4" s="30">
         <f>ROUND(IMDIV(G4,J4),2)</f>
-        <v>6.18</v>
+        <v>6.51</v>
       </c>
       <c r="P4" s="30">
         <f>ROUND(IMDIV(H4,J4),2)</f>
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="Q4" s="30">
         <f>ROUND(IMDIV(B4,F4),2)</f>
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R4" s="30">
         <f>ROUND(IMDIV(C4,B4),4)*100</f>
-        <v>56.699999999999996</v>
+        <v>57.410000000000004</v>
       </c>
       <c r="S4" s="30">
         <f>ROUND(IMDIV(I4,J4),2)</f>
-        <v>102.33</v>
+        <v>101.23</v>
       </c>
       <c r="T4" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U4" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V4" s="45">
         <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
-        <v>1.460696607638148</v>
+        <v>1.4309519634006862</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1162,77 +1162,77 @@
         <v>40</v>
       </c>
       <c r="B5" s="29">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C5" s="29">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="29">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G5" s="29">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H5" s="29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I5" s="29">
-        <v>4816</v>
+        <v>5570</v>
       </c>
       <c r="J5" s="29">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K5" s="30">
         <f>ROUND(IMDIV(B5,J5),2)</f>
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="L5" s="31">
         <f>E5/J5</f>
-        <v>9.1743119266055051E-3</v>
+        <v>2.4590163934426229E-2</v>
       </c>
       <c r="M5" s="31">
         <f>D5/J5</f>
-        <v>3.669724770642202E-2</v>
+        <v>4.9180327868852458E-2</v>
       </c>
       <c r="N5" s="30">
         <f>ROUND(IMDIV(F5,J5),2)</f>
-        <v>0.56999999999999995</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O5" s="30">
         <f>ROUND(IMDIV(G5,J5),2)</f>
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P5" s="30">
         <f>ROUND(IMDIV(H5,J5),2)</f>
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="30">
         <f>ROUND(IMDIV(B5,F5),2)</f>
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="R5" s="30">
         <f>ROUND(IMDIV(C5,B5),4)*100</f>
-        <v>35.709999999999994</v>
+        <v>36</v>
       </c>
       <c r="S5" s="30">
         <f>ROUND(IMDIV(I5,J5),2)</f>
-        <v>44.18</v>
+        <v>45.66</v>
       </c>
       <c r="T5" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U5" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V5" s="45">
         <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
-        <v>0.81299754640494992</v>
+        <v>0.85358520777735414</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1240,67 +1240,67 @@
         <v>31</v>
       </c>
       <c r="B6" s="9">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C6" s="9">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D6" s="9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E6" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="9">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G6" s="9">
-        <v>293</v>
+        <v>446</v>
       </c>
       <c r="H6" s="9">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" s="9">
-        <v>11002</v>
+        <v>13070</v>
       </c>
       <c r="J6" s="9">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="K6" s="9">
         <f>ROUND(IMDIV(B6,J6),2)</f>
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="L6" s="11">
         <f>E6/J6</f>
-        <v>7.9365079365079361E-2</v>
+        <v>7.4324324324324328E-2</v>
       </c>
       <c r="M6" s="11">
         <f>D6/J6</f>
-        <v>0.19047619047619047</v>
+        <v>0.19594594594594594</v>
       </c>
       <c r="N6" s="9">
         <f>ROUND(IMDIV(F6,J6),2)</f>
-        <v>0.53</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O6" s="9">
         <f>ROUND(IMDIV(G6,J6),2)</f>
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="P6" s="9">
         <f>ROUND(IMDIV(H6,J6),2)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="Q6" s="9">
         <f>ROUND(IMDIV(B6,F6),2)</f>
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="R6" s="9">
         <f>ROUND(IMDIV(C6,B6),4)*100</f>
-        <v>51.04</v>
+        <v>49.55</v>
       </c>
       <c r="S6" s="9">
         <f>ROUND(IMDIV(I6,J6),2)</f>
-        <v>87.32</v>
+        <v>88.31</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>46</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="V6" s="45">
         <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>1.2576315983757844</v>
+        <v>1.2370955373978629</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1318,51 +1318,51 @@
         <v>32</v>
       </c>
       <c r="B7" s="9">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C7" s="9">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" s="9">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E7" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" s="9">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G7" s="9">
-        <v>618</v>
+        <v>748</v>
       </c>
       <c r="H7" s="9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I7" s="9">
-        <v>7491</v>
+        <v>8723</v>
       </c>
       <c r="J7" s="9">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="K7" s="9">
         <f>ROUND(IMDIV(B7,J7),2)</f>
-        <v>0.56000000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L7" s="11">
         <f>E7/J7</f>
-        <v>3.1746031746031744E-2</v>
+        <v>5.4054054054054057E-2</v>
       </c>
       <c r="M7" s="11">
         <f>D7/J7</f>
-        <v>9.5238095238095233E-2</v>
+        <v>0.10810810810810811</v>
       </c>
       <c r="N7" s="9">
         <f>ROUND(IMDIV(F7,J7),2)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="O7" s="9">
         <f>ROUND(IMDIV(G7,J7),2)</f>
-        <v>4.9000000000000004</v>
+        <v>5.05</v>
       </c>
       <c r="P7" s="9">
         <f>ROUND(IMDIV(H7,J7),2)</f>
@@ -1370,15 +1370,15 @@
       </c>
       <c r="Q7" s="9">
         <f>ROUND(IMDIV(B7,F7),2)</f>
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="R7" s="9">
         <f>ROUND(IMDIV(C7,B7),4)*100</f>
-        <v>44.29</v>
+        <v>41.46</v>
       </c>
       <c r="S7" s="9">
         <f>ROUND(IMDIV(I7,J7),2)</f>
-        <v>59.45</v>
+        <v>58.94</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>46</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="V7" s="45">
         <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
-        <v>0.93767035806570698</v>
+        <v>0.9489773727215588</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1396,51 +1396,51 @@
         <v>37</v>
       </c>
       <c r="B8" s="26">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C8" s="26">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D8" s="26">
+        <v>21</v>
+      </c>
+      <c r="E8" s="26">
         <v>17</v>
       </c>
-      <c r="E8" s="26">
-        <v>14</v>
-      </c>
       <c r="F8" s="26">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G8" s="26">
-        <v>252</v>
+        <v>300</v>
       </c>
       <c r="H8" s="26">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I8" s="26">
-        <v>10439</v>
+        <v>11765</v>
       </c>
       <c r="J8" s="26">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="K8" s="27">
         <f>ROUND(IMDIV(B8,J8),2)</f>
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="L8" s="28">
         <f>E8/J8</f>
-        <v>0.11382113821138211</v>
+        <v>0.125</v>
       </c>
       <c r="M8" s="28">
         <f>D8/J8</f>
-        <v>0.13821138211382114</v>
+        <v>0.15441176470588236</v>
       </c>
       <c r="N8" s="27">
         <f>ROUND(IMDIV(F8,J8),2)</f>
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="O8" s="27">
         <f>ROUND(IMDIV(G8,J8),2)</f>
-        <v>2.0499999999999998</v>
+        <v>2.21</v>
       </c>
       <c r="P8" s="27">
         <f>ROUND(IMDIV(H8,J8),2)</f>
@@ -1448,15 +1448,15 @@
       </c>
       <c r="Q8" s="27">
         <f>ROUND(IMDIV(B8,F8),2)</f>
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="R8" s="27">
         <f>ROUND(IMDIV(C8,B8),4)*100</f>
-        <v>54.35</v>
+        <v>53.769999999999996</v>
       </c>
       <c r="S8" s="27">
         <f>ROUND(IMDIV(I8,J8),2)</f>
-        <v>84.87</v>
+        <v>86.51</v>
       </c>
       <c r="T8" s="26" t="s">
         <v>46</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="V8" s="45">
         <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
-        <v>1.2260612592172433</v>
+        <v>1.2719750341997265</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1474,10 +1474,10 @@
         <v>38</v>
       </c>
       <c r="B9" s="26">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" s="26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="26">
         <v>10</v>
@@ -1486,31 +1486,31 @@
         <v>2</v>
       </c>
       <c r="F9" s="26">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G9" s="26">
-        <v>304</v>
+        <v>347</v>
       </c>
       <c r="H9" s="26">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I9" s="26">
-        <v>7274</v>
+        <v>7963</v>
       </c>
       <c r="J9" s="26">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="K9" s="27">
         <f>ROUND(IMDIV(B9,J9),2)</f>
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="L9" s="28">
         <f>E9/J9</f>
-        <v>1.7857142857142856E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="M9" s="28">
         <f>D9/J9</f>
-        <v>8.9285714285714288E-2</v>
+        <v>0.08</v>
       </c>
       <c r="N9" s="27">
         <f>ROUND(IMDIV(F9,J9),2)</f>
@@ -1518,15 +1518,15 @@
       </c>
       <c r="O9" s="27">
         <f>ROUND(IMDIV(G9,J9),2)</f>
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="P9" s="27">
         <f>ROUND(IMDIV(H9,J9),2)</f>
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Q9" s="27">
         <f>ROUND(IMDIV(B9,F9),2)</f>
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="R9" s="27">
         <f>ROUND(IMDIV(C9,B9),4)*100</f>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="S9" s="27">
         <f>ROUND(IMDIV(I9,J9),2)</f>
-        <v>64.95</v>
+        <v>63.7</v>
       </c>
       <c r="T9" s="26" t="s">
         <v>46</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="V9" s="45">
         <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
-        <v>0.93098588039867103</v>
+        <v>0.91847906976744187</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1552,10 +1552,10 @@
         <v>29</v>
       </c>
       <c r="B10" s="12">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C10" s="12">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D10" s="12">
         <v>23</v>
@@ -1564,55 +1564,55 @@
         <v>6</v>
       </c>
       <c r="F10" s="12">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G10" s="12">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="H10" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="12">
-        <v>10270</v>
+        <v>11401</v>
       </c>
       <c r="J10" s="12">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="K10" s="12">
         <f>ROUND(IMDIV(B10,J10),2)</f>
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="L10" s="13">
         <f>E10/J10</f>
-        <v>5.8252427184466021E-2</v>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="M10" s="13">
         <f>D10/J10</f>
-        <v>0.22330097087378642</v>
+        <v>0.19827586206896552</v>
       </c>
       <c r="N10" s="12">
         <f>ROUND(IMDIV(F10,J10),2)</f>
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="O10" s="12">
         <f>ROUND(IMDIV(G10,J10),2)</f>
-        <v>2.93</v>
+        <v>3.29</v>
       </c>
       <c r="P10" s="12">
         <f>ROUND(IMDIV(H10,J10),2)</f>
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Q10" s="12">
         <f>ROUND(IMDIV(B10,F10),2)</f>
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="R10" s="12">
         <f>ROUND(IMDIV(C10,B10),4)*100</f>
-        <v>43.53</v>
+        <v>45.16</v>
       </c>
       <c r="S10" s="12">
         <f>ROUND(IMDIV(I10,J10),2)</f>
-        <v>99.71</v>
+        <v>98.28</v>
       </c>
       <c r="T10" s="51" t="s">
         <v>46</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="V10" s="45">
         <f>((K10/2.5)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
-        <v>1.3697431700158047</v>
+        <v>1.3230300721732158</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1630,10 +1630,10 @@
         <v>30</v>
       </c>
       <c r="B11" s="12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C11" s="12">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11" s="12">
         <v>9</v>
@@ -1642,55 +1642,55 @@
         <v>3</v>
       </c>
       <c r="F11" s="12">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G11" s="12">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H11" s="12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I11" s="12">
-        <v>5653</v>
+        <v>6173</v>
       </c>
       <c r="J11" s="12">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="K11" s="12">
         <f>ROUND(IMDIV(B11,J11),2)</f>
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="L11" s="13">
         <f>E11/J11</f>
-        <v>2.9126213592233011E-2</v>
+        <v>2.5862068965517241E-2</v>
       </c>
       <c r="M11" s="13">
         <f>D11/J11</f>
-        <v>8.7378640776699032E-2</v>
+        <v>7.7586206896551727E-2</v>
       </c>
       <c r="N11" s="12">
         <f>ROUND(IMDIV(F11,J11),2)</f>
-        <v>0.54</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="O11" s="12">
         <f>ROUND(IMDIV(G11,J11),2)</f>
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="P11" s="12">
         <f>ROUND(IMDIV(H11,J11),2)</f>
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q11" s="12">
         <f>ROUND(IMDIV(B11,F11),2)</f>
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="R11" s="12">
         <f>ROUND(IMDIV(C11,B11),4)*100</f>
-        <v>52.73</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="S11" s="12">
         <f>ROUND(IMDIV(I11,J11),2)</f>
-        <v>54.88</v>
+        <v>53.22</v>
       </c>
       <c r="T11" s="51" t="s">
         <v>46</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="V11" s="45">
         <f>((K11/2.5)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
-        <v>0.96242571686610967</v>
+        <v>0.91810384923817168</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1708,31 +1708,31 @@
         <v>34</v>
       </c>
       <c r="B12" s="50">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C12" s="50">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D12" s="50">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E12" s="50">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="50">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="G12" s="50">
-        <v>568</v>
+        <v>717</v>
       </c>
       <c r="H12" s="50">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I12" s="50">
-        <v>8757</v>
+        <v>10649</v>
       </c>
       <c r="J12" s="50">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="K12" s="20">
         <f>ROUND(IMDIV(B12,J12),2)</f>
@@ -1740,35 +1740,35 @@
       </c>
       <c r="L12" s="21">
         <f>E12/J12</f>
-        <v>6.9565217391304349E-2</v>
+        <v>6.569343065693431E-2</v>
       </c>
       <c r="M12" s="21">
         <f>D12/J12</f>
-        <v>0.20869565217391303</v>
+        <v>0.19708029197080293</v>
       </c>
       <c r="N12" s="20">
         <f>ROUND(IMDIV(F12,J12),2)</f>
-        <v>0.56999999999999995</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="O12" s="20">
         <f>ROUND(IMDIV(G12,J12),2)</f>
-        <v>4.9400000000000004</v>
+        <v>5.23</v>
       </c>
       <c r="P12" s="20">
         <f>ROUND(IMDIV(H12,J12),2)</f>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="Q12" s="20">
         <f>ROUND(IMDIV(B12,F12),2)</f>
-        <v>1.18</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="R12" s="20">
         <f>ROUND(IMDIV(C12,B12),4)*100</f>
-        <v>68.83</v>
+        <v>65.22</v>
       </c>
       <c r="S12" s="20">
         <f>ROUND(IMDIV(I12,J12),2)</f>
-        <v>76.150000000000006</v>
+        <v>77.73</v>
       </c>
       <c r="T12" s="20" t="s">
         <v>46</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="V12" s="45">
         <f>((K12/2.5)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
-        <v>1.1272730030333671</v>
+        <v>1.1229436428450179</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1786,43 +1786,43 @@
         <v>35</v>
       </c>
       <c r="B13" s="50">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C13" s="50">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D13" s="50">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E13" s="50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="50">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G13" s="50">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="H13" s="50">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I13" s="50">
-        <v>7414</v>
+        <v>8448</v>
       </c>
       <c r="J13" s="50">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="K13" s="20">
         <f>ROUND(IMDIV(B13,J13),2)</f>
-        <v>0.56999999999999995</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L13" s="21">
         <f>E13/J13</f>
-        <v>5.2173913043478258E-2</v>
+        <v>5.1094890510948905E-2</v>
       </c>
       <c r="M13" s="21">
         <f>D13/J13</f>
-        <v>0.16521739130434782</v>
+        <v>0.16058394160583941</v>
       </c>
       <c r="N13" s="20">
         <f>ROUND(IMDIV(F13,J13),2)</f>
@@ -1830,23 +1830,23 @@
       </c>
       <c r="O13" s="20">
         <f>ROUND(IMDIV(G13,J13),2)</f>
-        <v>1.98</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="P13" s="20">
         <f>ROUND(IMDIV(H13,J13),2)</f>
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="Q13" s="20">
         <f>ROUND(IMDIV(B13,F13),2)</f>
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="R13" s="20">
         <f>ROUND(IMDIV(C13,B13),4)*100</f>
-        <v>49.230000000000004</v>
+        <v>46.050000000000004</v>
       </c>
       <c r="S13" s="20">
         <f>ROUND(IMDIV(I13,J13),2)</f>
-        <v>64.47</v>
+        <v>61.66</v>
       </c>
       <c r="T13" s="20" t="s">
         <v>46</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="V13" s="45">
         <f>((K13/2.5)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
-        <v>0.98109959555106163</v>
+        <v>0.96065566117806833</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1927,7 +1927,7 @@
         <v>72.89</v>
       </c>
       <c r="T14" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U14" s="32" t="s">
         <v>24</v>
@@ -2005,7 +2005,7 @@
         <v>47.35</v>
       </c>
       <c r="T15" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U15" s="32" t="s">
         <v>24</v>
@@ -2083,7 +2083,7 @@
         <v>70.7</v>
       </c>
       <c r="T16" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U16" s="18" t="s">
         <v>24</v>
@@ -2161,7 +2161,7 @@
         <v>56.19</v>
       </c>
       <c r="T17" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U17" s="18" t="s">
         <v>24</v>
@@ -2239,7 +2239,7 @@
         <v>80.88</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U18" s="24" t="s">
         <v>24</v>
@@ -2317,7 +2317,7 @@
         <v>43.57</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U19" s="24" t="s">
         <v>24</v>
@@ -2395,7 +2395,7 @@
         <v>70.709999999999994</v>
       </c>
       <c r="T20" s="16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U20" s="16" t="s">
         <v>24</v>
@@ -2473,7 +2473,7 @@
         <v>51.29</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U21" s="16" t="s">
         <v>24</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="47">
         <v>3</v>
@@ -2551,7 +2551,7 @@
         <v>27</v>
       </c>
       <c r="T22" s="47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U22" s="47" t="s">
         <v>24</v>

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6869C109-053B-4327-8584-F035651B4560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE51AD4-825C-4F1A-9ED4-337B9AA0C021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2235" windowWidth="25815" windowHeight="12810" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tourney" sheetId="1" r:id="rId1"/>
+    <sheet name="Regular Season" sheetId="4" r:id="rId2"/>
+    <sheet name="Playoffs" sheetId="3" r:id="rId3"/>
+    <sheet name="QuarterFinals" sheetId="5" r:id="rId4"/>
+    <sheet name="SemiFinals" sheetId="6" r:id="rId5"/>
+    <sheet name="Finals" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="63">
   <si>
     <t>player</t>
   </si>
@@ -181,12 +186,57 @@
   <si>
     <t>7th-10th</t>
   </si>
+  <si>
+    <t>34-25</t>
+  </si>
+  <si>
+    <t>25-27</t>
+  </si>
+  <si>
+    <t>37-29</t>
+  </si>
+  <si>
+    <t>15-30</t>
+  </si>
+  <si>
+    <t>K-D</t>
+  </si>
+  <si>
+    <t>+/-</t>
+  </si>
+  <si>
+    <t>+9</t>
+  </si>
+  <si>
+    <t>+8</t>
+  </si>
+  <si>
+    <t>Mooks</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>Match 1:</t>
+  </si>
+  <si>
+    <t>1v2s</t>
+  </si>
+  <si>
+    <t>MultiKills</t>
+  </si>
+  <si>
+    <t>Match 2:</t>
+  </si>
+  <si>
+    <t>JewSpace</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,8 +288,50 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFEF3E88"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0038B8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -324,6 +416,22 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -334,10 +442,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -490,11 +600,96 @@
     <xf numFmtId="16" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="1" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4EA72E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -507,16 +702,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0038B8"/>
+      <color rgb="FFEF3E88"/>
       <color rgb="FFF87D18"/>
       <color rgb="FFDF060A"/>
       <color rgb="FF56260B"/>
       <color rgb="FF7D86E0"/>
       <color rgb="FF501C75"/>
-      <color rgb="FF0038B8"/>
       <color rgb="FF1A3C8E"/>
       <color rgb="FFCF5B1B"/>
       <color rgb="FF8C3E12"/>
-      <color rgb="FFEF3E88"/>
     </mruColors>
   </colors>
   <extLst>
@@ -955,39 +1150,39 @@
         <v>118</v>
       </c>
       <c r="K2" s="6">
-        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
         <v>0.95</v>
       </c>
       <c r="L2" s="7">
-        <f>E2/J2</f>
+        <f t="shared" ref="L2:L22" si="1">E2/J2</f>
         <v>6.7796610169491525E-2</v>
       </c>
       <c r="M2" s="7">
-        <f>D2/J2</f>
+        <f t="shared" ref="M2:M22" si="2">D2/J2</f>
         <v>0.2711864406779661</v>
       </c>
       <c r="N2" s="6">
-        <f>ROUND(IMDIV(F2,J2),2)</f>
+        <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
         <v>0.47</v>
       </c>
       <c r="O2" s="6">
-        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
         <v>5.66</v>
       </c>
       <c r="P2" s="6">
-        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
         <v>0.26</v>
       </c>
       <c r="Q2" s="6">
-        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
         <v>2.04</v>
       </c>
       <c r="R2" s="6">
-        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
         <v>65.180000000000007</v>
       </c>
       <c r="S2" s="6">
-        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
         <v>102.54</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -997,7 +1192,7 @@
         <v>24</v>
       </c>
       <c r="V2" s="45">
-        <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
         <v>1.4812861647615294</v>
       </c>
     </row>
@@ -1033,39 +1228,39 @@
         <v>118</v>
       </c>
       <c r="K3" s="6">
-        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <f t="shared" si="0"/>
         <v>0.48</v>
       </c>
       <c r="L3" s="7">
-        <f>E3/J3</f>
+        <f t="shared" si="1"/>
         <v>1.6949152542372881E-2</v>
       </c>
       <c r="M3" s="7">
-        <f>D3/J3</f>
+        <f t="shared" si="2"/>
         <v>8.4745762711864403E-2</v>
       </c>
       <c r="N3" s="6">
-        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <f t="shared" si="3"/>
         <v>0.61</v>
       </c>
       <c r="O3" s="6">
-        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <f t="shared" si="4"/>
         <v>0.35</v>
       </c>
       <c r="P3" s="6">
-        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
       <c r="Q3" s="6">
-        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <f t="shared" si="6"/>
         <v>0.79</v>
       </c>
       <c r="R3" s="6">
-        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <f t="shared" si="7"/>
         <v>50.88</v>
       </c>
       <c r="S3" s="6">
-        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <f t="shared" si="8"/>
         <v>51.84</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1075,7 +1270,7 @@
         <v>24</v>
       </c>
       <c r="V3" s="45">
-        <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.85369255025620816</v>
       </c>
     </row>
@@ -1111,39 +1306,39 @@
         <v>122</v>
       </c>
       <c r="K4" s="30">
-        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <f t="shared" si="0"/>
         <v>0.89</v>
       </c>
       <c r="L4" s="31">
-        <f>E4/J4</f>
+        <f t="shared" si="1"/>
         <v>8.1967213114754092E-2</v>
       </c>
       <c r="M4" s="31">
-        <f>D4/J4</f>
+        <f t="shared" si="2"/>
         <v>0.28688524590163933</v>
       </c>
       <c r="N4" s="30">
-        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <f t="shared" si="3"/>
         <v>0.49</v>
       </c>
       <c r="O4" s="30">
-        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <f t="shared" si="4"/>
         <v>6.51</v>
       </c>
       <c r="P4" s="30">
-        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
       <c r="Q4" s="30">
-        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <f t="shared" si="6"/>
         <v>1.8</v>
       </c>
       <c r="R4" s="30">
-        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <f t="shared" si="7"/>
         <v>57.410000000000004</v>
       </c>
       <c r="S4" s="30">
-        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <f t="shared" si="8"/>
         <v>101.23</v>
       </c>
       <c r="T4" s="29" t="s">
@@ -1153,7 +1348,7 @@
         <v>24</v>
       </c>
       <c r="V4" s="45">
-        <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.4309519634006862</v>
       </c>
     </row>
@@ -1189,39 +1384,39 @@
         <v>122</v>
       </c>
       <c r="K5" s="30">
-        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <f t="shared" si="0"/>
         <v>0.41</v>
       </c>
       <c r="L5" s="31">
-        <f>E5/J5</f>
+        <f t="shared" si="1"/>
         <v>2.4590163934426229E-2</v>
       </c>
       <c r="M5" s="31">
-        <f>D5/J5</f>
+        <f t="shared" si="2"/>
         <v>4.9180327868852458E-2</v>
       </c>
       <c r="N5" s="30">
-        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <f t="shared" si="3"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="O5" s="30">
-        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <f t="shared" si="4"/>
         <v>1.91</v>
       </c>
       <c r="P5" s="30">
-        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="Q5" s="30">
-        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="R5" s="30">
-        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="S5" s="30">
-        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <f t="shared" si="8"/>
         <v>45.66</v>
       </c>
       <c r="T5" s="29" t="s">
@@ -1231,7 +1426,7 @@
         <v>24</v>
       </c>
       <c r="V5" s="45">
-        <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.85358520777735414</v>
       </c>
     </row>
@@ -1240,77 +1435,77 @@
         <v>31</v>
       </c>
       <c r="B6" s="9">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="C6" s="9">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D6" s="9">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E6" s="9">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6" s="9">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="G6" s="9">
-        <v>446</v>
+        <v>789</v>
       </c>
       <c r="H6" s="9">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="I6" s="9">
-        <v>13070</v>
+        <v>16449</v>
       </c>
       <c r="J6" s="9">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="K6" s="9">
-        <f>ROUND(IMDIV(B6,J6),2)</f>
-        <v>0.75</v>
+        <f t="shared" si="0"/>
+        <v>0.76</v>
       </c>
       <c r="L6" s="11">
-        <f>E6/J6</f>
-        <v>7.4324324324324328E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.2916666666666671E-2</v>
       </c>
       <c r="M6" s="11">
-        <f>D6/J6</f>
-        <v>0.19594594594594594</v>
+        <f t="shared" si="2"/>
+        <v>0.20833333333333334</v>
       </c>
       <c r="N6" s="9">
-        <f>ROUND(IMDIV(F6,J6),2)</f>
+        <f t="shared" si="3"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="O6" s="9">
-        <f>ROUND(IMDIV(G6,J6),2)</f>
-        <v>3.01</v>
+        <f t="shared" si="4"/>
+        <v>4.1100000000000003</v>
       </c>
       <c r="P6" s="9">
-        <f>ROUND(IMDIV(H6,J6),2)</f>
-        <v>0.25</v>
+        <f t="shared" si="5"/>
+        <v>0.26</v>
       </c>
       <c r="Q6" s="9">
-        <f>ROUND(IMDIV(B6,F6),2)</f>
+        <f t="shared" si="6"/>
         <v>1.37</v>
       </c>
       <c r="R6" s="9">
-        <f>ROUND(IMDIV(C6,B6),4)*100</f>
-        <v>49.55</v>
+        <f t="shared" si="7"/>
+        <v>47.589999999999996</v>
       </c>
       <c r="S6" s="9">
-        <f>ROUND(IMDIV(I6,J6),2)</f>
-        <v>88.31</v>
+        <f t="shared" si="8"/>
+        <v>85.67</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V6" s="45">
-        <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>1.2370955373978629</v>
+        <f t="shared" si="9"/>
+        <v>1.2321317829457363</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1318,77 +1513,77 @@
         <v>32</v>
       </c>
       <c r="B7" s="9">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C7" s="9">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D7" s="9">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E7" s="9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="9">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="G7" s="9">
-        <v>748</v>
+        <v>1068</v>
       </c>
       <c r="H7" s="9">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I7" s="9">
-        <v>8723</v>
+        <v>12196</v>
       </c>
       <c r="J7" s="9">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="K7" s="9">
-        <f>ROUND(IMDIV(B7,J7),2)</f>
-        <v>0.55000000000000004</v>
+        <f t="shared" si="0"/>
+        <v>0.56000000000000005</v>
       </c>
       <c r="L7" s="11">
-        <f>E7/J7</f>
-        <v>5.4054054054054057E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2083333333333336E-2</v>
       </c>
       <c r="M7" s="11">
-        <f>D7/J7</f>
-        <v>0.10810810810810811</v>
+        <f t="shared" si="2"/>
+        <v>0.11979166666666667</v>
       </c>
       <c r="N7" s="9">
-        <f>ROUND(IMDIV(F7,J7),2)</f>
-        <v>0.59</v>
+        <f t="shared" si="3"/>
+        <v>0.6</v>
       </c>
       <c r="O7" s="9">
-        <f>ROUND(IMDIV(G7,J7),2)</f>
-        <v>5.05</v>
+        <f t="shared" si="4"/>
+        <v>5.56</v>
       </c>
       <c r="P7" s="9">
-        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <f t="shared" si="5"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="Q7" s="9">
-        <f>ROUND(IMDIV(B7,F7),2)</f>
+        <f t="shared" si="6"/>
         <v>0.93</v>
       </c>
       <c r="R7" s="9">
-        <f>ROUND(IMDIV(C7,B7),4)*100</f>
-        <v>41.46</v>
+        <f t="shared" si="7"/>
+        <v>40.19</v>
       </c>
       <c r="S7" s="9">
-        <f>ROUND(IMDIV(I7,J7),2)</f>
-        <v>58.94</v>
+        <f t="shared" si="8"/>
+        <v>63.52</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V7" s="45">
-        <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
-        <v>0.9489773727215588</v>
+        <f t="shared" si="9"/>
+        <v>0.96680644379844971</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1423,39 +1618,39 @@
         <v>136</v>
       </c>
       <c r="K8" s="27">
-        <f>ROUND(IMDIV(B8,J8),2)</f>
+        <f t="shared" si="0"/>
         <v>0.78</v>
       </c>
       <c r="L8" s="28">
-        <f>E8/J8</f>
+        <f t="shared" si="1"/>
         <v>0.125</v>
       </c>
       <c r="M8" s="28">
-        <f>D8/J8</f>
+        <f t="shared" si="2"/>
         <v>0.15441176470588236</v>
       </c>
       <c r="N8" s="27">
-        <f>ROUND(IMDIV(F8,J8),2)</f>
+        <f t="shared" si="3"/>
         <v>0.52</v>
       </c>
       <c r="O8" s="27">
-        <f>ROUND(IMDIV(G8,J8),2)</f>
+        <f t="shared" si="4"/>
         <v>2.21</v>
       </c>
       <c r="P8" s="27">
-        <f>ROUND(IMDIV(H8,J8),2)</f>
+        <f t="shared" si="5"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="Q8" s="27">
-        <f>ROUND(IMDIV(B8,F8),2)</f>
+        <f t="shared" si="6"/>
         <v>1.49</v>
       </c>
       <c r="R8" s="27">
-        <f>ROUND(IMDIV(C8,B8),4)*100</f>
+        <f t="shared" si="7"/>
         <v>53.769999999999996</v>
       </c>
       <c r="S8" s="27">
-        <f>ROUND(IMDIV(I8,J8),2)</f>
+        <f t="shared" si="8"/>
         <v>86.51</v>
       </c>
       <c r="T8" s="26" t="s">
@@ -1465,7 +1660,7 @@
         <v>24</v>
       </c>
       <c r="V8" s="45">
-        <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.2719750341997265</v>
       </c>
     </row>
@@ -1501,39 +1696,39 @@
         <v>125</v>
       </c>
       <c r="K9" s="27">
-        <f>ROUND(IMDIV(B9,J9),2)</f>
+        <f t="shared" si="0"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="L9" s="28">
-        <f>E9/J9</f>
+        <f t="shared" si="1"/>
         <v>1.6E-2</v>
       </c>
       <c r="M9" s="28">
-        <f>D9/J9</f>
+        <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="N9" s="27">
-        <f>ROUND(IMDIV(F9,J9),2)</f>
+        <f t="shared" si="3"/>
         <v>0.64</v>
       </c>
       <c r="O9" s="27">
-        <f>ROUND(IMDIV(G9,J9),2)</f>
+        <f t="shared" si="4"/>
         <v>2.78</v>
       </c>
       <c r="P9" s="27">
-        <f>ROUND(IMDIV(H9,J9),2)</f>
+        <f t="shared" si="5"/>
         <v>0.3</v>
       </c>
       <c r="Q9" s="27">
-        <f>ROUND(IMDIV(B9,F9),2)</f>
+        <f t="shared" si="6"/>
         <v>0.88</v>
       </c>
       <c r="R9" s="27">
-        <f>ROUND(IMDIV(C9,B9),4)*100</f>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="S9" s="27">
-        <f>ROUND(IMDIV(I9,J9),2)</f>
+        <f t="shared" si="8"/>
         <v>63.7</v>
       </c>
       <c r="T9" s="26" t="s">
@@ -1543,7 +1738,7 @@
         <v>24</v>
       </c>
       <c r="V9" s="45">
-        <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.91847906976744187</v>
       </c>
     </row>
@@ -1579,39 +1774,39 @@
         <v>116</v>
       </c>
       <c r="K10" s="12">
-        <f>ROUND(IMDIV(B10,J10),2)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="L10" s="13">
-        <f>E10/J10</f>
+        <f t="shared" si="1"/>
         <v>5.1724137931034482E-2</v>
       </c>
       <c r="M10" s="13">
-        <f>D10/J10</f>
+        <f t="shared" si="2"/>
         <v>0.19827586206896552</v>
       </c>
       <c r="N10" s="12">
-        <f>ROUND(IMDIV(F10,J10),2)</f>
+        <f t="shared" si="3"/>
         <v>0.52</v>
       </c>
       <c r="O10" s="12">
-        <f>ROUND(IMDIV(G10,J10),2)</f>
+        <f t="shared" si="4"/>
         <v>3.29</v>
       </c>
       <c r="P10" s="12">
-        <f>ROUND(IMDIV(H10,J10),2)</f>
+        <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
       <c r="Q10" s="12">
-        <f>ROUND(IMDIV(B10,F10),2)</f>
+        <f t="shared" si="6"/>
         <v>1.55</v>
       </c>
       <c r="R10" s="12">
-        <f>ROUND(IMDIV(C10,B10),4)*100</f>
+        <f t="shared" si="7"/>
         <v>45.16</v>
       </c>
       <c r="S10" s="12">
-        <f>ROUND(IMDIV(I10,J10),2)</f>
+        <f t="shared" si="8"/>
         <v>98.28</v>
       </c>
       <c r="T10" s="51" t="s">
@@ -1621,7 +1816,7 @@
         <v>24</v>
       </c>
       <c r="V10" s="45">
-        <f>((K10/2.5)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.3230300721732158</v>
       </c>
     </row>
@@ -1657,39 +1852,39 @@
         <v>116</v>
       </c>
       <c r="K11" s="12">
-        <f>ROUND(IMDIV(B11,J11),2)</f>
+        <f t="shared" si="0"/>
         <v>0.52</v>
       </c>
       <c r="L11" s="13">
-        <f>E11/J11</f>
+        <f t="shared" si="1"/>
         <v>2.5862068965517241E-2</v>
       </c>
       <c r="M11" s="13">
-        <f>D11/J11</f>
+        <f t="shared" si="2"/>
         <v>7.7586206896551727E-2</v>
       </c>
       <c r="N11" s="12">
-        <f>ROUND(IMDIV(F11,J11),2)</f>
+        <f t="shared" si="3"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="O11" s="12">
-        <f>ROUND(IMDIV(G11,J11),2)</f>
+        <f t="shared" si="4"/>
         <v>1.25</v>
       </c>
       <c r="P11" s="12">
-        <f>ROUND(IMDIV(H11,J11),2)</f>
+        <f t="shared" si="5"/>
         <v>0.16</v>
       </c>
       <c r="Q11" s="12">
-        <f>ROUND(IMDIV(B11,F11),2)</f>
+        <f t="shared" si="6"/>
         <v>0.91</v>
       </c>
       <c r="R11" s="12">
-        <f>ROUND(IMDIV(C11,B11),4)*100</f>
+        <f t="shared" si="7"/>
         <v>55.000000000000007</v>
       </c>
       <c r="S11" s="12">
-        <f>ROUND(IMDIV(I11,J11),2)</f>
+        <f t="shared" si="8"/>
         <v>53.22</v>
       </c>
       <c r="T11" s="51" t="s">
@@ -1699,7 +1894,7 @@
         <v>24</v>
       </c>
       <c r="V11" s="45">
-        <f>((K11/2.5)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.91810384923817168</v>
       </c>
     </row>
@@ -1708,67 +1903,67 @@
         <v>34</v>
       </c>
       <c r="B12" s="50">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="C12" s="50">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D12" s="50">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E12" s="50">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F12" s="50">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="G12" s="50">
-        <v>717</v>
+        <v>895</v>
       </c>
       <c r="H12" s="50">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I12" s="50">
-        <v>10649</v>
+        <v>14207</v>
       </c>
       <c r="J12" s="50">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="K12" s="20">
-        <f>ROUND(IMDIV(B12,J12),2)</f>
-        <v>0.67</v>
+        <f t="shared" si="0"/>
+        <v>0.71</v>
       </c>
       <c r="L12" s="21">
-        <f>E12/J12</f>
-        <v>6.569343065693431E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.6298342541436461E-2</v>
       </c>
       <c r="M12" s="21">
-        <f>D12/J12</f>
-        <v>0.19708029197080293</v>
+        <f t="shared" si="2"/>
+        <v>0.19889502762430938</v>
       </c>
       <c r="N12" s="20">
-        <f>ROUND(IMDIV(F12,J12),2)</f>
-        <v>0.57999999999999996</v>
+        <f t="shared" si="3"/>
+        <v>0.6</v>
       </c>
       <c r="O12" s="20">
-        <f>ROUND(IMDIV(G12,J12),2)</f>
-        <v>5.23</v>
+        <f t="shared" si="4"/>
+        <v>4.9400000000000004</v>
       </c>
       <c r="P12" s="20">
-        <f>ROUND(IMDIV(H12,J12),2)</f>
-        <v>0.22</v>
+        <f t="shared" si="5"/>
+        <v>0.23</v>
       </c>
       <c r="Q12" s="20">
-        <f>ROUND(IMDIV(B12,F12),2)</f>
-        <v>1.1599999999999999</v>
+        <f t="shared" si="6"/>
+        <v>1.19</v>
       </c>
       <c r="R12" s="20">
-        <f>ROUND(IMDIV(C12,B12),4)*100</f>
-        <v>65.22</v>
+        <f t="shared" si="7"/>
+        <v>66.67</v>
       </c>
       <c r="S12" s="20">
-        <f>ROUND(IMDIV(I12,J12),2)</f>
-        <v>77.73</v>
+        <f t="shared" si="8"/>
+        <v>78.489999999999995</v>
       </c>
       <c r="T12" s="20" t="s">
         <v>46</v>
@@ -1777,8 +1972,8 @@
         <v>24</v>
       </c>
       <c r="V12" s="45">
-        <f>((K12/2.5)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
-        <v>1.1229436428450179</v>
+        <f t="shared" si="9"/>
+        <v>1.123553192856225</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1786,67 +1981,67 @@
         <v>35</v>
       </c>
       <c r="B13" s="50">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C13" s="50">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D13" s="50">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="50">
         <v>7</v>
       </c>
       <c r="F13" s="50">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="G13" s="50">
-        <v>275</v>
+        <v>454</v>
       </c>
       <c r="H13" s="50">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I13" s="50">
-        <v>8448</v>
+        <v>10965</v>
       </c>
       <c r="J13" s="50">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="K13" s="20">
-        <f>ROUND(IMDIV(B13,J13),2)</f>
-        <v>0.55000000000000004</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="L13" s="21">
-        <f>E13/J13</f>
-        <v>5.1094890510948905E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.8674033149171269E-2</v>
       </c>
       <c r="M13" s="21">
-        <f>D13/J13</f>
-        <v>0.16058394160583941</v>
+        <f t="shared" si="2"/>
+        <v>0.1270718232044199</v>
       </c>
       <c r="N13" s="20">
-        <f>ROUND(IMDIV(F13,J13),2)</f>
-        <v>0.61</v>
+        <f t="shared" si="3"/>
+        <v>0.62</v>
       </c>
       <c r="O13" s="20">
-        <f>ROUND(IMDIV(G13,J13),2)</f>
-        <v>2.0099999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.5099999999999998</v>
       </c>
       <c r="P13" s="20">
-        <f>ROUND(IMDIV(H13,J13),2)</f>
-        <v>0.27</v>
+        <f t="shared" si="5"/>
+        <v>0.25</v>
       </c>
       <c r="Q13" s="20">
-        <f>ROUND(IMDIV(B13,F13),2)</f>
-        <v>0.92</v>
+        <f t="shared" si="6"/>
+        <v>0.81</v>
       </c>
       <c r="R13" s="20">
-        <f>ROUND(IMDIV(C13,B13),4)*100</f>
-        <v>46.050000000000004</v>
+        <f t="shared" si="7"/>
+        <v>46.150000000000006</v>
       </c>
       <c r="S13" s="20">
-        <f>ROUND(IMDIV(I13,J13),2)</f>
-        <v>61.66</v>
+        <f t="shared" si="8"/>
+        <v>60.58</v>
       </c>
       <c r="T13" s="20" t="s">
         <v>46</v>
@@ -1855,8 +2050,8 @@
         <v>24</v>
       </c>
       <c r="V13" s="45">
-        <f>((K13/2.5)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
-        <v>0.96065566117806833</v>
+        <f t="shared" si="9"/>
+        <v>0.91377020429140432</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1891,39 +2086,39 @@
         <v>85</v>
       </c>
       <c r="K14" s="33">
-        <f>ROUND(IMDIV(B14,J14),2)</f>
+        <f t="shared" si="0"/>
         <v>0.53</v>
       </c>
       <c r="L14" s="34">
-        <f>E14/J14</f>
+        <f t="shared" si="1"/>
         <v>2.3529411764705882E-2</v>
       </c>
       <c r="M14" s="34">
-        <f>D14/J14</f>
+        <f t="shared" si="2"/>
         <v>0.15294117647058825</v>
       </c>
       <c r="N14" s="33">
-        <f>ROUND(IMDIV(F14,J14),2)</f>
+        <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
       <c r="O14" s="33">
-        <f>ROUND(IMDIV(G14,J14),2)</f>
+        <f t="shared" si="4"/>
         <v>3.04</v>
       </c>
       <c r="P14" s="33">
-        <f>ROUND(IMDIV(H14,J14),2)</f>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="Q14" s="33">
-        <f>ROUND(IMDIV(B14,F14),2)</f>
+        <f t="shared" si="6"/>
         <v>0.78</v>
       </c>
       <c r="R14" s="33">
-        <f>ROUND(IMDIV(C14,B14),4)*100</f>
+        <f t="shared" si="7"/>
         <v>35.56</v>
       </c>
       <c r="S14" s="33">
-        <f>ROUND(IMDIV(I14,J14),2)</f>
+        <f t="shared" si="8"/>
         <v>72.89</v>
       </c>
       <c r="T14" s="32" t="s">
@@ -1933,7 +2128,7 @@
         <v>24</v>
       </c>
       <c r="V14" s="45">
-        <f>((K14/2.5)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.92396443228454173</v>
       </c>
     </row>
@@ -1969,39 +2164,39 @@
         <v>85</v>
       </c>
       <c r="K15" s="33">
-        <f>ROUND(IMDIV(B15,J15),2)</f>
+        <f t="shared" si="0"/>
         <v>0.44</v>
       </c>
       <c r="L15" s="34">
-        <f>E15/J15</f>
+        <f t="shared" si="1"/>
         <v>3.5294117647058823E-2</v>
       </c>
       <c r="M15" s="34">
-        <f>D15/J15</f>
+        <f t="shared" si="2"/>
         <v>9.4117647058823528E-2</v>
       </c>
       <c r="N15" s="33">
-        <f>ROUND(IMDIV(F15,J15),2)</f>
+        <f t="shared" si="3"/>
         <v>0.69</v>
       </c>
       <c r="O15" s="33">
-        <f>ROUND(IMDIV(G15,J15),2)</f>
+        <f t="shared" si="4"/>
         <v>2.98</v>
       </c>
       <c r="P15" s="33">
-        <f>ROUND(IMDIV(H15,J15),2)</f>
+        <f t="shared" si="5"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q15" s="33">
-        <f>ROUND(IMDIV(B15,F15),2)</f>
+        <f t="shared" si="6"/>
         <v>0.63</v>
       </c>
       <c r="R15" s="33">
-        <f>ROUND(IMDIV(C15,B15),4)*100</f>
+        <f t="shared" si="7"/>
         <v>45.95</v>
       </c>
       <c r="S15" s="33">
-        <f>ROUND(IMDIV(I15,J15),2)</f>
+        <f t="shared" si="8"/>
         <v>47.35</v>
       </c>
       <c r="T15" s="32" t="s">
@@ -2011,7 +2206,7 @@
         <v>24</v>
       </c>
       <c r="V15" s="45">
-        <f>((K15/2.5)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.74032079343365265</v>
       </c>
     </row>
@@ -2047,39 +2242,39 @@
         <v>119</v>
       </c>
       <c r="K16" s="18">
-        <f>ROUND(IMDIV(B16,J16),2)</f>
+        <f t="shared" si="0"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="L16" s="19">
-        <f>E16/J16</f>
+        <f t="shared" si="1"/>
         <v>2.5210084033613446E-2</v>
       </c>
       <c r="M16" s="19">
-        <f>D16/J16</f>
+        <f t="shared" si="2"/>
         <v>0.11764705882352941</v>
       </c>
       <c r="N16" s="18">
-        <f>ROUND(IMDIV(F16,J16),2)</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="O16" s="18">
-        <f>ROUND(IMDIV(G16,J16),2)</f>
+        <f t="shared" si="4"/>
         <v>3.08</v>
       </c>
       <c r="P16" s="18">
-        <f>ROUND(IMDIV(H16,J16),2)</f>
+        <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
       <c r="Q16" s="18">
-        <f>ROUND(IMDIV(B16,F16),2)</f>
+        <f t="shared" si="6"/>
         <v>0.87</v>
       </c>
       <c r="R16" s="18">
-        <f>ROUND(IMDIV(C16,B16),4)*100</f>
+        <f t="shared" si="7"/>
         <v>52.239999999999995</v>
       </c>
       <c r="S16" s="18">
-        <f>ROUND(IMDIV(I16,J16),2)</f>
+        <f t="shared" si="8"/>
         <v>70.7</v>
       </c>
       <c r="T16" s="18" t="s">
@@ -2089,7 +2284,7 @@
         <v>24</v>
       </c>
       <c r="V16" s="45">
-        <f>((K16/2.5)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.94279099081493056</v>
       </c>
     </row>
@@ -2125,39 +2320,39 @@
         <v>119</v>
       </c>
       <c r="K17" s="18">
-        <f>ROUND(IMDIV(B17,J17),2)</f>
+        <f t="shared" si="0"/>
         <v>0.46</v>
       </c>
       <c r="L17" s="19">
-        <f>E17/J17</f>
+        <f t="shared" si="1"/>
         <v>1.680672268907563E-2</v>
       </c>
       <c r="M17" s="19">
-        <f>D17/J17</f>
+        <f t="shared" si="2"/>
         <v>8.4033613445378158E-2</v>
       </c>
       <c r="N17" s="18">
-        <f>ROUND(IMDIV(F17,J17),2)</f>
+        <f t="shared" si="3"/>
         <v>0.66</v>
       </c>
       <c r="O17" s="18">
-        <f>ROUND(IMDIV(G17,J17),2)</f>
+        <f t="shared" si="4"/>
         <v>1.49</v>
       </c>
       <c r="P17" s="18">
-        <f>ROUND(IMDIV(H17,J17),2)</f>
+        <f t="shared" si="5"/>
         <v>0.13</v>
       </c>
       <c r="Q17" s="18">
-        <f>ROUND(IMDIV(B17,F17),2)</f>
+        <f t="shared" si="6"/>
         <v>0.71</v>
       </c>
       <c r="R17" s="18">
-        <f>ROUND(IMDIV(C17,B17),4)*100</f>
+        <f t="shared" si="7"/>
         <v>38.18</v>
       </c>
       <c r="S17" s="18">
-        <f>ROUND(IMDIV(I17,J17),2)</f>
+        <f t="shared" si="8"/>
         <v>56.19</v>
       </c>
       <c r="T17" s="18" t="s">
@@ -2167,7 +2362,7 @@
         <v>24</v>
       </c>
       <c r="V17" s="45">
-        <f>((K17/2.5)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.8162185851084619</v>
       </c>
     </row>
@@ -2203,39 +2398,39 @@
         <v>98</v>
       </c>
       <c r="K18" s="24">
-        <f>ROUND(IMDIV(B18,J18),2)</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="L18" s="25">
-        <f>E18/J18</f>
+        <f t="shared" si="1"/>
         <v>2.0408163265306121E-2</v>
       </c>
       <c r="M18" s="25">
-        <f>D18/J18</f>
+        <f t="shared" si="2"/>
         <v>0.18367346938775511</v>
       </c>
       <c r="N18" s="24">
-        <f>ROUND(IMDIV(F18,J18),2)</f>
+        <f t="shared" si="3"/>
         <v>0.72</v>
       </c>
       <c r="O18" s="24">
-        <f>ROUND(IMDIV(G18,J18),2)</f>
+        <f t="shared" si="4"/>
         <v>3.39</v>
       </c>
       <c r="P18" s="24">
-        <f>ROUND(IMDIV(H18,J18),2)</f>
+        <f t="shared" si="5"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="Q18" s="24">
-        <f>ROUND(IMDIV(B18,F18),2)</f>
+        <f t="shared" si="6"/>
         <v>0.83</v>
       </c>
       <c r="R18" s="24">
-        <f>ROUND(IMDIV(C18,B18),4)*100</f>
+        <f t="shared" si="7"/>
         <v>61.019999999999996</v>
       </c>
       <c r="S18" s="24">
-        <f>ROUND(IMDIV(I18,J18),2)</f>
+        <f t="shared" si="8"/>
         <v>80.88</v>
       </c>
       <c r="T18" s="24" t="s">
@@ -2245,7 +2440,7 @@
         <v>24</v>
       </c>
       <c r="V18" s="45">
-        <f>((K18/2.5)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.95318604651162786</v>
       </c>
     </row>
@@ -2281,39 +2476,39 @@
         <v>82</v>
       </c>
       <c r="K19" s="24">
-        <f>ROUND(IMDIV(B19,J19),2)</f>
+        <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
       <c r="L19" s="25">
-        <f>E19/J19</f>
+        <f t="shared" si="1"/>
         <v>2.4390243902439025E-2</v>
       </c>
       <c r="M19" s="25">
-        <f>D19/J19</f>
+        <f t="shared" si="2"/>
         <v>7.3170731707317069E-2</v>
       </c>
       <c r="N19" s="24">
-        <f>ROUND(IMDIV(F19,J19),2)</f>
+        <f t="shared" si="3"/>
         <v>0.71</v>
       </c>
       <c r="O19" s="24">
-        <f>ROUND(IMDIV(G19,J19),2)</f>
+        <f t="shared" si="4"/>
         <v>1.38</v>
       </c>
       <c r="P19" s="24">
-        <f>ROUND(IMDIV(H19,J19),2)</f>
+        <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
       <c r="Q19" s="24">
-        <f>ROUND(IMDIV(B19,F19),2)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="R19" s="24">
-        <f>ROUND(IMDIV(C19,B19),4)*100</f>
+        <f t="shared" si="7"/>
         <v>48.28</v>
       </c>
       <c r="S19" s="24">
-        <f>ROUND(IMDIV(I19,J19),2)</f>
+        <f t="shared" si="8"/>
         <v>43.57</v>
       </c>
       <c r="T19" s="24" t="s">
@@ -2323,7 +2518,7 @@
         <v>24</v>
       </c>
       <c r="V19" s="45">
-        <f>((K19/2.5)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.66132189449801471</v>
       </c>
     </row>
@@ -2359,39 +2554,39 @@
         <v>112</v>
       </c>
       <c r="K20" s="15">
-        <f>ROUND(IMDIV(B20,J20),2)</f>
+        <f t="shared" si="0"/>
         <v>0.62</v>
       </c>
       <c r="L20" s="17">
-        <f>E20/J20</f>
+        <f t="shared" si="1"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="M20" s="17">
-        <f>D20/J20</f>
+        <f t="shared" si="2"/>
         <v>0.11607142857142858</v>
       </c>
       <c r="N20" s="15">
-        <f>ROUND(IMDIV(F20,J20),2)</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="O20" s="15">
-        <f>ROUND(IMDIV(G20,J20),2)</f>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="P20" s="15">
-        <f>ROUND(IMDIV(H20,J20),2)</f>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="Q20" s="15">
-        <f>ROUND(IMDIV(B20,F20),2)</f>
+        <f t="shared" si="6"/>
         <v>0.95</v>
       </c>
       <c r="R20" s="15">
-        <f>ROUND(IMDIV(C20,B20),4)*100</f>
+        <f t="shared" si="7"/>
         <v>66.67</v>
       </c>
       <c r="S20" s="15">
-        <f>ROUND(IMDIV(I20,J20),2)</f>
+        <f t="shared" si="8"/>
         <v>70.709999999999994</v>
       </c>
       <c r="T20" s="16" t="s">
@@ -2401,7 +2596,7 @@
         <v>24</v>
       </c>
       <c r="V20" s="45">
-        <f>((K20/2.5)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.9755444352159468</v>
       </c>
     </row>
@@ -2437,39 +2632,39 @@
         <v>101</v>
       </c>
       <c r="K21" s="15">
-        <f>ROUND(IMDIV(B21,J21),2)</f>
+        <f t="shared" si="0"/>
         <v>0.46</v>
       </c>
       <c r="L21" s="17">
-        <f>E21/J21</f>
+        <f t="shared" si="1"/>
         <v>9.9009900990099011E-3</v>
       </c>
       <c r="M21" s="17">
-        <f>D21/J21</f>
+        <f t="shared" si="2"/>
         <v>6.9306930693069313E-2</v>
       </c>
       <c r="N21" s="15">
-        <f>ROUND(IMDIV(F21,J21),2)</f>
+        <f t="shared" si="3"/>
         <v>0.71</v>
       </c>
       <c r="O21" s="15">
-        <f>ROUND(IMDIV(G21,J21),2)</f>
+        <f t="shared" si="4"/>
         <v>1.58</v>
       </c>
       <c r="P21" s="15">
-        <f>ROUND(IMDIV(H21,J21),2)</f>
+        <f t="shared" si="5"/>
         <v>0.15</v>
       </c>
       <c r="Q21" s="15">
-        <f>ROUND(IMDIV(B21,F21),2)</f>
+        <f t="shared" si="6"/>
         <v>0.64</v>
       </c>
       <c r="R21" s="15">
-        <f>ROUND(IMDIV(C21,B21),4)*100</f>
+        <f t="shared" si="7"/>
         <v>47.83</v>
       </c>
       <c r="S21" s="15">
-        <f>ROUND(IMDIV(I21,J21),2)</f>
+        <f t="shared" si="8"/>
         <v>51.29</v>
       </c>
       <c r="T21" s="16" t="s">
@@ -2479,7 +2674,7 @@
         <v>24</v>
       </c>
       <c r="V21" s="45">
-        <f>((K21/2.5)+(M21/4)+(L21/5)-(N21)+(S21/215)+(P21/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.73936507022795306</v>
       </c>
     </row>
@@ -2515,39 +2710,39 @@
         <v>16</v>
       </c>
       <c r="K22" s="48">
-        <f>ROUND(IMDIV(B22,J22),2)</f>
+        <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
       <c r="L22" s="49">
-        <f>E22/J22</f>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="M22" s="49">
-        <f>D22/J22</f>
+        <f t="shared" si="2"/>
         <v>6.25E-2</v>
       </c>
       <c r="N22" s="48">
-        <f>ROUND(IMDIV(F22,J22),2)</f>
+        <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
       <c r="O22" s="48">
-        <f>ROUND(IMDIV(G22,J22),2)</f>
+        <f t="shared" si="4"/>
         <v>2.69</v>
       </c>
       <c r="P22" s="48">
-        <f>ROUND(IMDIV(H22,J22),2)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q22" s="48">
-        <f>ROUND(IMDIV(B22,F22),2)</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="R22" s="48">
-        <f>ROUND(IMDIV(C22,B22),4)*100</f>
+        <f t="shared" si="7"/>
         <v>66.67</v>
       </c>
       <c r="S22" s="48">
-        <f>ROUND(IMDIV(I22,J22),2)</f>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="T22" s="47" t="s">
@@ -2557,14 +2752,5840 @@
         <v>24</v>
       </c>
       <c r="V22" s="45">
-        <f>((K22/2.5)+(M22/4)+(L22/5)-(N22)+(S22/215)+(P22/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.47970639534883719</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
-    <sortCondition sortBy="cellColor" ref="A22" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="A22" dxfId="1"/>
   </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82623B68-2CCB-468D-B947-83DB7F94C282}">
+  <dimension ref="A1:V22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6">
+        <v>112</v>
+      </c>
+      <c r="C2" s="6">
+        <v>73</v>
+      </c>
+      <c r="D2" s="6">
+        <v>32</v>
+      </c>
+      <c r="E2" s="6">
+        <v>8</v>
+      </c>
+      <c r="F2" s="6">
+        <v>55</v>
+      </c>
+      <c r="G2" s="6">
+        <v>668</v>
+      </c>
+      <c r="H2" s="6">
+        <v>31</v>
+      </c>
+      <c r="I2" s="6">
+        <v>12100</v>
+      </c>
+      <c r="J2" s="6">
+        <v>118</v>
+      </c>
+      <c r="K2" s="6">
+        <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <v>0.95</v>
+      </c>
+      <c r="L2" s="7">
+        <f t="shared" ref="L2:L22" si="1">E2/J2</f>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="M2" s="7">
+        <f t="shared" ref="M2:M22" si="2">D2/J2</f>
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="N2" s="6">
+        <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="O2" s="6">
+        <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <v>5.66</v>
+      </c>
+      <c r="P2" s="6">
+        <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <v>0.26</v>
+      </c>
+      <c r="Q2" s="6">
+        <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <v>2.04</v>
+      </c>
+      <c r="R2" s="6">
+        <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>65.180000000000007</v>
+      </c>
+      <c r="S2" s="6">
+        <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <v>102.54</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45">
+        <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.4812861647615294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6">
+        <v>57</v>
+      </c>
+      <c r="C3" s="6">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6">
+        <v>72</v>
+      </c>
+      <c r="G3" s="6">
+        <v>41</v>
+      </c>
+      <c r="H3" s="6">
+        <v>14</v>
+      </c>
+      <c r="I3" s="6">
+        <v>6117</v>
+      </c>
+      <c r="J3" s="6">
+        <v>118</v>
+      </c>
+      <c r="K3" s="6">
+        <f t="shared" si="0"/>
+        <v>0.48</v>
+      </c>
+      <c r="L3" s="7">
+        <f t="shared" si="1"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" si="2"/>
+        <v>8.4745762711864403E-2</v>
+      </c>
+      <c r="N3" s="6">
+        <f t="shared" si="3"/>
+        <v>0.61</v>
+      </c>
+      <c r="O3" s="6">
+        <f t="shared" si="4"/>
+        <v>0.35</v>
+      </c>
+      <c r="P3" s="6">
+        <f t="shared" si="5"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q3" s="6">
+        <f t="shared" si="6"/>
+        <v>0.79</v>
+      </c>
+      <c r="R3" s="6">
+        <f t="shared" si="7"/>
+        <v>50.88</v>
+      </c>
+      <c r="S3" s="6">
+        <f t="shared" si="8"/>
+        <v>51.84</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45">
+        <f t="shared" si="9"/>
+        <v>0.85369255025620816</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="29">
+        <v>108</v>
+      </c>
+      <c r="C4" s="29">
+        <v>62</v>
+      </c>
+      <c r="D4" s="29">
+        <v>35</v>
+      </c>
+      <c r="E4" s="29">
+        <v>10</v>
+      </c>
+      <c r="F4" s="29">
+        <v>60</v>
+      </c>
+      <c r="G4" s="29">
+        <v>794</v>
+      </c>
+      <c r="H4" s="29">
+        <v>15</v>
+      </c>
+      <c r="I4" s="29">
+        <v>12350</v>
+      </c>
+      <c r="J4" s="29">
+        <v>122</v>
+      </c>
+      <c r="K4" s="30">
+        <f t="shared" si="0"/>
+        <v>0.89</v>
+      </c>
+      <c r="L4" s="31">
+        <f t="shared" si="1"/>
+        <v>8.1967213114754092E-2</v>
+      </c>
+      <c r="M4" s="31">
+        <f t="shared" si="2"/>
+        <v>0.28688524590163933</v>
+      </c>
+      <c r="N4" s="30">
+        <f t="shared" si="3"/>
+        <v>0.49</v>
+      </c>
+      <c r="O4" s="30">
+        <f t="shared" si="4"/>
+        <v>6.51</v>
+      </c>
+      <c r="P4" s="30">
+        <f t="shared" si="5"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q4" s="30">
+        <f t="shared" si="6"/>
+        <v>1.8</v>
+      </c>
+      <c r="R4" s="30">
+        <f t="shared" si="7"/>
+        <v>57.410000000000004</v>
+      </c>
+      <c r="S4" s="30">
+        <f t="shared" si="8"/>
+        <v>101.23</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45">
+        <f t="shared" si="9"/>
+        <v>1.4309519634006862</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="29">
+        <v>50</v>
+      </c>
+      <c r="C5" s="29">
+        <v>18</v>
+      </c>
+      <c r="D5" s="29">
+        <v>6</v>
+      </c>
+      <c r="E5" s="29">
+        <v>3</v>
+      </c>
+      <c r="F5" s="29">
+        <v>67</v>
+      </c>
+      <c r="G5" s="29">
+        <v>233</v>
+      </c>
+      <c r="H5" s="29">
+        <v>24</v>
+      </c>
+      <c r="I5" s="29">
+        <v>5570</v>
+      </c>
+      <c r="J5" s="29">
+        <v>122</v>
+      </c>
+      <c r="K5" s="30">
+        <f t="shared" si="0"/>
+        <v>0.41</v>
+      </c>
+      <c r="L5" s="31">
+        <f t="shared" si="1"/>
+        <v>2.4590163934426229E-2</v>
+      </c>
+      <c r="M5" s="31">
+        <f t="shared" si="2"/>
+        <v>4.9180327868852458E-2</v>
+      </c>
+      <c r="N5" s="30">
+        <f t="shared" si="3"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O5" s="30">
+        <f t="shared" si="4"/>
+        <v>1.91</v>
+      </c>
+      <c r="P5" s="30">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q5" s="30">
+        <f t="shared" si="6"/>
+        <v>0.75</v>
+      </c>
+      <c r="R5" s="30">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="S5" s="30">
+        <f t="shared" si="8"/>
+        <v>45.66</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45">
+        <f t="shared" si="9"/>
+        <v>0.85358520777735414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="9">
+        <v>111</v>
+      </c>
+      <c r="C6" s="9">
+        <v>55</v>
+      </c>
+      <c r="D6" s="9">
+        <v>29</v>
+      </c>
+      <c r="E6" s="9">
+        <v>11</v>
+      </c>
+      <c r="F6" s="9">
+        <v>81</v>
+      </c>
+      <c r="G6" s="9">
+        <v>446</v>
+      </c>
+      <c r="H6" s="9">
+        <v>37</v>
+      </c>
+      <c r="I6" s="9">
+        <v>13070</v>
+      </c>
+      <c r="J6" s="9">
+        <v>148</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="L6" s="11">
+        <f t="shared" si="1"/>
+        <v>7.4324324324324328E-2</v>
+      </c>
+      <c r="M6" s="11">
+        <f t="shared" si="2"/>
+        <v>0.19594594594594594</v>
+      </c>
+      <c r="N6" s="9">
+        <f t="shared" si="3"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O6" s="9">
+        <f t="shared" si="4"/>
+        <v>3.01</v>
+      </c>
+      <c r="P6" s="9">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="Q6" s="9">
+        <f t="shared" si="6"/>
+        <v>1.37</v>
+      </c>
+      <c r="R6" s="9">
+        <f t="shared" si="7"/>
+        <v>49.55</v>
+      </c>
+      <c r="S6" s="9">
+        <f t="shared" si="8"/>
+        <v>88.31</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45">
+        <f t="shared" si="9"/>
+        <v>1.2370955373978629</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9">
+        <v>82</v>
+      </c>
+      <c r="C7" s="9">
+        <v>34</v>
+      </c>
+      <c r="D7" s="9">
+        <v>16</v>
+      </c>
+      <c r="E7" s="9">
+        <v>8</v>
+      </c>
+      <c r="F7" s="9">
+        <v>88</v>
+      </c>
+      <c r="G7" s="9">
+        <v>748</v>
+      </c>
+      <c r="H7" s="9">
+        <v>21</v>
+      </c>
+      <c r="I7" s="9">
+        <v>8723</v>
+      </c>
+      <c r="J7" s="9">
+        <v>148</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L7" s="11">
+        <f t="shared" si="1"/>
+        <v>5.4054054054054057E-2</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" si="2"/>
+        <v>0.10810810810810811</v>
+      </c>
+      <c r="N7" s="9">
+        <f t="shared" si="3"/>
+        <v>0.59</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" si="4"/>
+        <v>5.05</v>
+      </c>
+      <c r="P7" s="9">
+        <f t="shared" si="5"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q7" s="9">
+        <f t="shared" si="6"/>
+        <v>0.93</v>
+      </c>
+      <c r="R7" s="9">
+        <f t="shared" si="7"/>
+        <v>41.46</v>
+      </c>
+      <c r="S7" s="9">
+        <f t="shared" si="8"/>
+        <v>58.94</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45">
+        <f t="shared" si="9"/>
+        <v>0.9489773727215588</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="26">
+        <v>106</v>
+      </c>
+      <c r="C8" s="26">
+        <v>57</v>
+      </c>
+      <c r="D8" s="26">
+        <v>21</v>
+      </c>
+      <c r="E8" s="26">
+        <v>17</v>
+      </c>
+      <c r="F8" s="26">
+        <v>71</v>
+      </c>
+      <c r="G8" s="26">
+        <v>300</v>
+      </c>
+      <c r="H8" s="26">
+        <v>38</v>
+      </c>
+      <c r="I8" s="26">
+        <v>11765</v>
+      </c>
+      <c r="J8" s="26">
+        <v>136</v>
+      </c>
+      <c r="K8" s="27">
+        <f t="shared" si="0"/>
+        <v>0.78</v>
+      </c>
+      <c r="L8" s="28">
+        <f t="shared" si="1"/>
+        <v>0.125</v>
+      </c>
+      <c r="M8" s="28">
+        <f t="shared" si="2"/>
+        <v>0.15441176470588236</v>
+      </c>
+      <c r="N8" s="27">
+        <f t="shared" si="3"/>
+        <v>0.52</v>
+      </c>
+      <c r="O8" s="27">
+        <f t="shared" si="4"/>
+        <v>2.21</v>
+      </c>
+      <c r="P8" s="27">
+        <f t="shared" si="5"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q8" s="27">
+        <f t="shared" si="6"/>
+        <v>1.49</v>
+      </c>
+      <c r="R8" s="27">
+        <f t="shared" si="7"/>
+        <v>53.769999999999996</v>
+      </c>
+      <c r="S8" s="27">
+        <f t="shared" si="8"/>
+        <v>86.51</v>
+      </c>
+      <c r="T8" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="45">
+        <f t="shared" si="9"/>
+        <v>1.2719750341997265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="26">
+        <v>70</v>
+      </c>
+      <c r="C9" s="26">
+        <v>28</v>
+      </c>
+      <c r="D9" s="26">
+        <v>10</v>
+      </c>
+      <c r="E9" s="26">
+        <v>2</v>
+      </c>
+      <c r="F9" s="26">
+        <v>80</v>
+      </c>
+      <c r="G9" s="26">
+        <v>347</v>
+      </c>
+      <c r="H9" s="26">
+        <v>38</v>
+      </c>
+      <c r="I9" s="26">
+        <v>7963</v>
+      </c>
+      <c r="J9" s="26">
+        <v>125</v>
+      </c>
+      <c r="K9" s="27">
+        <f t="shared" si="0"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L9" s="28">
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="M9" s="28">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+      <c r="N9" s="27">
+        <f t="shared" si="3"/>
+        <v>0.64</v>
+      </c>
+      <c r="O9" s="27">
+        <f t="shared" si="4"/>
+        <v>2.78</v>
+      </c>
+      <c r="P9" s="27">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q9" s="27">
+        <f t="shared" si="6"/>
+        <v>0.88</v>
+      </c>
+      <c r="R9" s="27">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="S9" s="27">
+        <f t="shared" si="8"/>
+        <v>63.7</v>
+      </c>
+      <c r="T9" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V9" s="45">
+        <f t="shared" si="9"/>
+        <v>0.91847906976744187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="12">
+        <v>93</v>
+      </c>
+      <c r="C10" s="12">
+        <v>42</v>
+      </c>
+      <c r="D10" s="12">
+        <v>23</v>
+      </c>
+      <c r="E10" s="12">
+        <v>6</v>
+      </c>
+      <c r="F10" s="12">
+        <v>60</v>
+      </c>
+      <c r="G10" s="12">
+        <v>382</v>
+      </c>
+      <c r="H10" s="12">
+        <v>14</v>
+      </c>
+      <c r="I10" s="12">
+        <v>11401</v>
+      </c>
+      <c r="J10" s="12">
+        <v>116</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="L10" s="13">
+        <f t="shared" si="1"/>
+        <v>5.1724137931034482E-2</v>
+      </c>
+      <c r="M10" s="13">
+        <f t="shared" si="2"/>
+        <v>0.19827586206896552</v>
+      </c>
+      <c r="N10" s="12">
+        <f t="shared" si="3"/>
+        <v>0.52</v>
+      </c>
+      <c r="O10" s="12">
+        <f t="shared" si="4"/>
+        <v>3.29</v>
+      </c>
+      <c r="P10" s="12">
+        <f t="shared" si="5"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q10" s="12">
+        <f t="shared" si="6"/>
+        <v>1.55</v>
+      </c>
+      <c r="R10" s="12">
+        <f t="shared" si="7"/>
+        <v>45.16</v>
+      </c>
+      <c r="S10" s="12">
+        <f t="shared" si="8"/>
+        <v>98.28</v>
+      </c>
+      <c r="T10" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="45">
+        <f t="shared" si="9"/>
+        <v>1.3230300721732158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12">
+        <v>60</v>
+      </c>
+      <c r="C11" s="12">
+        <v>33</v>
+      </c>
+      <c r="D11" s="12">
+        <v>9</v>
+      </c>
+      <c r="E11" s="12">
+        <v>3</v>
+      </c>
+      <c r="F11" s="12">
+        <v>66</v>
+      </c>
+      <c r="G11" s="12">
+        <v>145</v>
+      </c>
+      <c r="H11" s="12">
+        <v>18</v>
+      </c>
+      <c r="I11" s="12">
+        <v>6173</v>
+      </c>
+      <c r="J11" s="12">
+        <v>116</v>
+      </c>
+      <c r="K11" s="12">
+        <f t="shared" si="0"/>
+        <v>0.52</v>
+      </c>
+      <c r="L11" s="13">
+        <f t="shared" si="1"/>
+        <v>2.5862068965517241E-2</v>
+      </c>
+      <c r="M11" s="13">
+        <f t="shared" si="2"/>
+        <v>7.7586206896551727E-2</v>
+      </c>
+      <c r="N11" s="12">
+        <f t="shared" si="3"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O11" s="12">
+        <f t="shared" si="4"/>
+        <v>1.25</v>
+      </c>
+      <c r="P11" s="12">
+        <f t="shared" si="5"/>
+        <v>0.16</v>
+      </c>
+      <c r="Q11" s="12">
+        <f t="shared" si="6"/>
+        <v>0.91</v>
+      </c>
+      <c r="R11" s="12">
+        <f t="shared" si="7"/>
+        <v>55.000000000000007</v>
+      </c>
+      <c r="S11" s="12">
+        <f t="shared" si="8"/>
+        <v>53.22</v>
+      </c>
+      <c r="T11" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V11" s="45">
+        <f t="shared" si="9"/>
+        <v>0.91810384923817168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="50">
+        <v>92</v>
+      </c>
+      <c r="C12" s="50">
+        <v>60</v>
+      </c>
+      <c r="D12" s="50">
+        <v>27</v>
+      </c>
+      <c r="E12" s="50">
+        <v>9</v>
+      </c>
+      <c r="F12" s="50">
+        <v>79</v>
+      </c>
+      <c r="G12" s="50">
+        <v>717</v>
+      </c>
+      <c r="H12" s="50">
+        <v>30</v>
+      </c>
+      <c r="I12" s="50">
+        <v>10649</v>
+      </c>
+      <c r="J12" s="50">
+        <v>137</v>
+      </c>
+      <c r="K12" s="20">
+        <f t="shared" si="0"/>
+        <v>0.67</v>
+      </c>
+      <c r="L12" s="21">
+        <f t="shared" si="1"/>
+        <v>6.569343065693431E-2</v>
+      </c>
+      <c r="M12" s="21">
+        <f t="shared" si="2"/>
+        <v>0.19708029197080293</v>
+      </c>
+      <c r="N12" s="20">
+        <f t="shared" si="3"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O12" s="20">
+        <f t="shared" si="4"/>
+        <v>5.23</v>
+      </c>
+      <c r="P12" s="20">
+        <f t="shared" si="5"/>
+        <v>0.22</v>
+      </c>
+      <c r="Q12" s="20">
+        <f t="shared" si="6"/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="R12" s="20">
+        <f t="shared" si="7"/>
+        <v>65.22</v>
+      </c>
+      <c r="S12" s="20">
+        <f t="shared" si="8"/>
+        <v>77.73</v>
+      </c>
+      <c r="T12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="U12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="V12" s="45">
+        <f t="shared" si="9"/>
+        <v>1.1229436428450179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="50">
+        <v>76</v>
+      </c>
+      <c r="C13" s="50">
+        <v>35</v>
+      </c>
+      <c r="D13" s="50">
+        <v>22</v>
+      </c>
+      <c r="E13" s="50">
+        <v>7</v>
+      </c>
+      <c r="F13" s="50">
+        <v>83</v>
+      </c>
+      <c r="G13" s="50">
+        <v>275</v>
+      </c>
+      <c r="H13" s="50">
+        <v>37</v>
+      </c>
+      <c r="I13" s="50">
+        <v>8448</v>
+      </c>
+      <c r="J13" s="50">
+        <v>137</v>
+      </c>
+      <c r="K13" s="20">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L13" s="21">
+        <f t="shared" si="1"/>
+        <v>5.1094890510948905E-2</v>
+      </c>
+      <c r="M13" s="21">
+        <f t="shared" si="2"/>
+        <v>0.16058394160583941</v>
+      </c>
+      <c r="N13" s="20">
+        <f t="shared" si="3"/>
+        <v>0.61</v>
+      </c>
+      <c r="O13" s="20">
+        <f t="shared" si="4"/>
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="P13" s="20">
+        <f t="shared" si="5"/>
+        <v>0.27</v>
+      </c>
+      <c r="Q13" s="20">
+        <f t="shared" si="6"/>
+        <v>0.92</v>
+      </c>
+      <c r="R13" s="20">
+        <f t="shared" si="7"/>
+        <v>46.050000000000004</v>
+      </c>
+      <c r="S13" s="20">
+        <f t="shared" si="8"/>
+        <v>61.66</v>
+      </c>
+      <c r="T13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="U13" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="V13" s="45">
+        <f t="shared" si="9"/>
+        <v>0.96065566117806833</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="32">
+        <v>45</v>
+      </c>
+      <c r="C14" s="32">
+        <v>16</v>
+      </c>
+      <c r="D14" s="32">
+        <v>13</v>
+      </c>
+      <c r="E14" s="32">
+        <v>2</v>
+      </c>
+      <c r="F14" s="32">
+        <v>58</v>
+      </c>
+      <c r="G14" s="32">
+        <v>258</v>
+      </c>
+      <c r="H14" s="32">
+        <v>17</v>
+      </c>
+      <c r="I14" s="32">
+        <v>6196</v>
+      </c>
+      <c r="J14" s="32">
+        <v>85</v>
+      </c>
+      <c r="K14" s="33">
+        <f t="shared" si="0"/>
+        <v>0.53</v>
+      </c>
+      <c r="L14" s="34">
+        <f t="shared" si="1"/>
+        <v>2.3529411764705882E-2</v>
+      </c>
+      <c r="M14" s="34">
+        <f t="shared" si="2"/>
+        <v>0.15294117647058825</v>
+      </c>
+      <c r="N14" s="33">
+        <f t="shared" si="3"/>
+        <v>0.68</v>
+      </c>
+      <c r="O14" s="33">
+        <f t="shared" si="4"/>
+        <v>3.04</v>
+      </c>
+      <c r="P14" s="33">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q14" s="33">
+        <f t="shared" si="6"/>
+        <v>0.78</v>
+      </c>
+      <c r="R14" s="33">
+        <f t="shared" si="7"/>
+        <v>35.56</v>
+      </c>
+      <c r="S14" s="33">
+        <f t="shared" si="8"/>
+        <v>72.89</v>
+      </c>
+      <c r="T14" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="U14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="45">
+        <f t="shared" si="9"/>
+        <v>0.92396443228454173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="32">
+        <v>37</v>
+      </c>
+      <c r="C15" s="32">
+        <v>17</v>
+      </c>
+      <c r="D15" s="32">
+        <v>8</v>
+      </c>
+      <c r="E15" s="32">
+        <v>3</v>
+      </c>
+      <c r="F15" s="32">
+        <v>59</v>
+      </c>
+      <c r="G15" s="32">
+        <v>253</v>
+      </c>
+      <c r="H15" s="32">
+        <v>6</v>
+      </c>
+      <c r="I15" s="32">
+        <v>4025</v>
+      </c>
+      <c r="J15" s="32">
+        <v>85</v>
+      </c>
+      <c r="K15" s="33">
+        <f t="shared" si="0"/>
+        <v>0.44</v>
+      </c>
+      <c r="L15" s="34">
+        <f t="shared" si="1"/>
+        <v>3.5294117647058823E-2</v>
+      </c>
+      <c r="M15" s="34">
+        <f t="shared" si="2"/>
+        <v>9.4117647058823528E-2</v>
+      </c>
+      <c r="N15" s="33">
+        <f t="shared" si="3"/>
+        <v>0.69</v>
+      </c>
+      <c r="O15" s="33">
+        <f t="shared" si="4"/>
+        <v>2.98</v>
+      </c>
+      <c r="P15" s="33">
+        <f t="shared" si="5"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="Q15" s="33">
+        <f t="shared" si="6"/>
+        <v>0.63</v>
+      </c>
+      <c r="R15" s="33">
+        <f t="shared" si="7"/>
+        <v>45.95</v>
+      </c>
+      <c r="S15" s="33">
+        <f t="shared" si="8"/>
+        <v>47.35</v>
+      </c>
+      <c r="T15" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="U15" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="V15" s="45">
+        <f t="shared" si="9"/>
+        <v>0.74032079343365265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="18">
+        <v>67</v>
+      </c>
+      <c r="C16" s="18">
+        <v>35</v>
+      </c>
+      <c r="D16" s="18">
+        <v>14</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3</v>
+      </c>
+      <c r="F16" s="18">
+        <v>77</v>
+      </c>
+      <c r="G16" s="18">
+        <v>367</v>
+      </c>
+      <c r="H16" s="18">
+        <v>13</v>
+      </c>
+      <c r="I16" s="18">
+        <v>8413</v>
+      </c>
+      <c r="J16" s="18">
+        <v>119</v>
+      </c>
+      <c r="K16" s="18">
+        <f t="shared" si="0"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L16" s="19">
+        <f t="shared" si="1"/>
+        <v>2.5210084033613446E-2</v>
+      </c>
+      <c r="M16" s="19">
+        <f t="shared" si="2"/>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="N16" s="18">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+      <c r="O16" s="18">
+        <f t="shared" si="4"/>
+        <v>3.08</v>
+      </c>
+      <c r="P16" s="18">
+        <f t="shared" si="5"/>
+        <v>0.11</v>
+      </c>
+      <c r="Q16" s="18">
+        <f t="shared" si="6"/>
+        <v>0.87</v>
+      </c>
+      <c r="R16" s="18">
+        <f t="shared" si="7"/>
+        <v>52.239999999999995</v>
+      </c>
+      <c r="S16" s="18">
+        <f t="shared" si="8"/>
+        <v>70.7</v>
+      </c>
+      <c r="T16" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="U16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="V16" s="45">
+        <f t="shared" si="9"/>
+        <v>0.94279099081493056</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="18">
+        <v>55</v>
+      </c>
+      <c r="C17" s="18">
+        <v>21</v>
+      </c>
+      <c r="D17" s="18">
+        <v>10</v>
+      </c>
+      <c r="E17" s="18">
+        <v>2</v>
+      </c>
+      <c r="F17" s="18">
+        <v>78</v>
+      </c>
+      <c r="G17" s="18">
+        <v>177</v>
+      </c>
+      <c r="H17" s="18">
+        <v>15</v>
+      </c>
+      <c r="I17" s="18">
+        <v>6687</v>
+      </c>
+      <c r="J17" s="18">
+        <v>119</v>
+      </c>
+      <c r="K17" s="18">
+        <f t="shared" si="0"/>
+        <v>0.46</v>
+      </c>
+      <c r="L17" s="19">
+        <f t="shared" si="1"/>
+        <v>1.680672268907563E-2</v>
+      </c>
+      <c r="M17" s="19">
+        <f t="shared" si="2"/>
+        <v>8.4033613445378158E-2</v>
+      </c>
+      <c r="N17" s="18">
+        <f t="shared" si="3"/>
+        <v>0.66</v>
+      </c>
+      <c r="O17" s="18">
+        <f t="shared" si="4"/>
+        <v>1.49</v>
+      </c>
+      <c r="P17" s="18">
+        <f t="shared" si="5"/>
+        <v>0.13</v>
+      </c>
+      <c r="Q17" s="18">
+        <f t="shared" si="6"/>
+        <v>0.71</v>
+      </c>
+      <c r="R17" s="18">
+        <f t="shared" si="7"/>
+        <v>38.18</v>
+      </c>
+      <c r="S17" s="18">
+        <f t="shared" si="8"/>
+        <v>56.19</v>
+      </c>
+      <c r="T17" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="U17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="V17" s="45">
+        <f t="shared" si="9"/>
+        <v>0.8162185851084619</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="23">
+        <v>59</v>
+      </c>
+      <c r="C18" s="23">
+        <v>36</v>
+      </c>
+      <c r="D18" s="23">
+        <v>18</v>
+      </c>
+      <c r="E18" s="23">
+        <v>2</v>
+      </c>
+      <c r="F18" s="23">
+        <v>71</v>
+      </c>
+      <c r="G18" s="23">
+        <v>332</v>
+      </c>
+      <c r="H18" s="23">
+        <v>14</v>
+      </c>
+      <c r="I18" s="23">
+        <v>7926</v>
+      </c>
+      <c r="J18" s="23">
+        <v>98</v>
+      </c>
+      <c r="K18" s="24">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="L18" s="25">
+        <f t="shared" si="1"/>
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="M18" s="25">
+        <f t="shared" si="2"/>
+        <v>0.18367346938775511</v>
+      </c>
+      <c r="N18" s="24">
+        <f t="shared" si="3"/>
+        <v>0.72</v>
+      </c>
+      <c r="O18" s="24">
+        <f t="shared" si="4"/>
+        <v>3.39</v>
+      </c>
+      <c r="P18" s="24">
+        <f t="shared" si="5"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q18" s="24">
+        <f t="shared" si="6"/>
+        <v>0.83</v>
+      </c>
+      <c r="R18" s="24">
+        <f t="shared" si="7"/>
+        <v>61.019999999999996</v>
+      </c>
+      <c r="S18" s="24">
+        <f t="shared" si="8"/>
+        <v>80.88</v>
+      </c>
+      <c r="T18" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="V18" s="45">
+        <f t="shared" si="9"/>
+        <v>0.95318604651162786</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="23">
+        <v>29</v>
+      </c>
+      <c r="C19" s="23">
+        <v>14</v>
+      </c>
+      <c r="D19" s="23">
+        <v>6</v>
+      </c>
+      <c r="E19" s="23">
+        <v>2</v>
+      </c>
+      <c r="F19" s="23">
+        <v>58</v>
+      </c>
+      <c r="G19" s="24">
+        <v>113</v>
+      </c>
+      <c r="H19" s="23">
+        <v>9</v>
+      </c>
+      <c r="I19" s="23">
+        <v>3573</v>
+      </c>
+      <c r="J19" s="23">
+        <v>82</v>
+      </c>
+      <c r="K19" s="24">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="L19" s="25">
+        <f t="shared" si="1"/>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="M19" s="25">
+        <f t="shared" si="2"/>
+        <v>7.3170731707317069E-2</v>
+      </c>
+      <c r="N19" s="24">
+        <f t="shared" si="3"/>
+        <v>0.71</v>
+      </c>
+      <c r="O19" s="24">
+        <f t="shared" si="4"/>
+        <v>1.38</v>
+      </c>
+      <c r="P19" s="24">
+        <f t="shared" si="5"/>
+        <v>0.11</v>
+      </c>
+      <c r="Q19" s="24">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="R19" s="24">
+        <f t="shared" si="7"/>
+        <v>48.28</v>
+      </c>
+      <c r="S19" s="24">
+        <f t="shared" si="8"/>
+        <v>43.57</v>
+      </c>
+      <c r="T19" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="U19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="V19" s="45">
+        <f t="shared" si="9"/>
+        <v>0.66132189449801471</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="15">
+        <v>69</v>
+      </c>
+      <c r="C20" s="15">
+        <v>46</v>
+      </c>
+      <c r="D20" s="15">
+        <v>13</v>
+      </c>
+      <c r="E20" s="15">
+        <v>4</v>
+      </c>
+      <c r="F20" s="15">
+        <v>73</v>
+      </c>
+      <c r="G20" s="15">
+        <v>168</v>
+      </c>
+      <c r="H20" s="15">
+        <v>28</v>
+      </c>
+      <c r="I20" s="15">
+        <v>7920</v>
+      </c>
+      <c r="J20" s="15">
+        <v>112</v>
+      </c>
+      <c r="K20" s="15">
+        <f t="shared" si="0"/>
+        <v>0.62</v>
+      </c>
+      <c r="L20" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="M20" s="17">
+        <f t="shared" si="2"/>
+        <v>0.11607142857142858</v>
+      </c>
+      <c r="N20" s="15">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+      <c r="O20" s="15">
+        <f t="shared" si="4"/>
+        <v>1.5</v>
+      </c>
+      <c r="P20" s="15">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="Q20" s="15">
+        <f t="shared" si="6"/>
+        <v>0.95</v>
+      </c>
+      <c r="R20" s="15">
+        <f t="shared" si="7"/>
+        <v>66.67</v>
+      </c>
+      <c r="S20" s="15">
+        <f t="shared" si="8"/>
+        <v>70.709999999999994</v>
+      </c>
+      <c r="T20" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="V20" s="45">
+        <f t="shared" si="9"/>
+        <v>0.9755444352159468</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="15">
+        <v>46</v>
+      </c>
+      <c r="C21" s="15">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15">
+        <v>7</v>
+      </c>
+      <c r="E21" s="15">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15">
+        <v>72</v>
+      </c>
+      <c r="G21" s="15">
+        <v>160</v>
+      </c>
+      <c r="H21" s="15">
+        <v>15</v>
+      </c>
+      <c r="I21" s="15">
+        <v>5180</v>
+      </c>
+      <c r="J21" s="15">
+        <v>101</v>
+      </c>
+      <c r="K21" s="15">
+        <f t="shared" si="0"/>
+        <v>0.46</v>
+      </c>
+      <c r="L21" s="17">
+        <f t="shared" si="1"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="M21" s="17">
+        <f t="shared" si="2"/>
+        <v>6.9306930693069313E-2</v>
+      </c>
+      <c r="N21" s="15">
+        <f t="shared" si="3"/>
+        <v>0.71</v>
+      </c>
+      <c r="O21" s="15">
+        <f t="shared" si="4"/>
+        <v>1.58</v>
+      </c>
+      <c r="P21" s="15">
+        <f t="shared" si="5"/>
+        <v>0.15</v>
+      </c>
+      <c r="Q21" s="15">
+        <f t="shared" si="6"/>
+        <v>0.64</v>
+      </c>
+      <c r="R21" s="15">
+        <f t="shared" si="7"/>
+        <v>47.83</v>
+      </c>
+      <c r="S21" s="15">
+        <f t="shared" si="8"/>
+        <v>51.29</v>
+      </c>
+      <c r="T21" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="U21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="V21" s="45">
+        <f t="shared" si="9"/>
+        <v>0.73936507022795306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="47">
+        <v>3</v>
+      </c>
+      <c r="C22" s="47">
+        <v>2</v>
+      </c>
+      <c r="D22" s="47">
+        <v>1</v>
+      </c>
+      <c r="E22" s="47">
+        <v>1</v>
+      </c>
+      <c r="F22" s="47">
+        <v>12</v>
+      </c>
+      <c r="G22" s="47">
+        <v>43</v>
+      </c>
+      <c r="H22" s="47">
+        <v>0</v>
+      </c>
+      <c r="I22" s="47">
+        <v>432</v>
+      </c>
+      <c r="J22" s="47">
+        <v>16</v>
+      </c>
+      <c r="K22" s="48">
+        <f t="shared" si="0"/>
+        <v>0.19</v>
+      </c>
+      <c r="L22" s="49">
+        <f t="shared" si="1"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="M22" s="49">
+        <f t="shared" si="2"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="N22" s="48">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="O22" s="48">
+        <f t="shared" si="4"/>
+        <v>2.69</v>
+      </c>
+      <c r="P22" s="48">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="48">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="R22" s="48">
+        <f t="shared" si="7"/>
+        <v>66.67</v>
+      </c>
+      <c r="S22" s="48">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="T22" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="U22" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="V22" s="45">
+        <f t="shared" si="9"/>
+        <v>0.47970639534883719</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF723AF-29F9-4B27-9BD4-7CDF4E72CFCA}">
+  <dimension ref="A1:V22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6" t="e">
+        <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" s="7" t="e">
+        <f t="shared" ref="L2:L22" si="1">E2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M2" s="7" t="e">
+        <f t="shared" ref="M2:M22" si="2">D2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N2" s="6" t="e">
+        <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O2" s="6" t="e">
+        <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P2" s="6" t="e">
+        <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q2" s="6" t="e">
+        <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R2" s="6" t="e">
+        <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S2" s="6" t="e">
+        <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45" t="e">
+        <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M3" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N3" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O3" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P3" s="6" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q3" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R3" s="6" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S3" s="6" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L4" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M4" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O4" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P4" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q4" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R4" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S4" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L5" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M5" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O5" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P5" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q5" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R5" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S5" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="9">
+        <v>34</v>
+      </c>
+      <c r="C6" s="9">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9">
+        <v>11</v>
+      </c>
+      <c r="E6" s="9">
+        <v>3</v>
+      </c>
+      <c r="F6" s="9">
+        <v>25</v>
+      </c>
+      <c r="G6" s="9">
+        <v>343</v>
+      </c>
+      <c r="H6" s="9">
+        <v>12</v>
+      </c>
+      <c r="I6" s="9">
+        <v>3379</v>
+      </c>
+      <c r="J6" s="9">
+        <v>44</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="0"/>
+        <v>0.77</v>
+      </c>
+      <c r="L6" s="11">
+        <f t="shared" si="1"/>
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="M6" s="11">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="N6" s="9">
+        <f t="shared" si="3"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O6" s="9">
+        <f t="shared" si="4"/>
+        <v>7.8</v>
+      </c>
+      <c r="P6" s="9">
+        <f t="shared" si="5"/>
+        <v>0.27</v>
+      </c>
+      <c r="Q6" s="9">
+        <f t="shared" si="6"/>
+        <v>1.36</v>
+      </c>
+      <c r="R6" s="9">
+        <f t="shared" si="7"/>
+        <v>41.18</v>
+      </c>
+      <c r="S6" s="9">
+        <f t="shared" si="8"/>
+        <v>76.8</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45">
+        <f t="shared" si="9"/>
+        <v>1.1848456659619451</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9">
+        <v>25</v>
+      </c>
+      <c r="C7" s="9">
+        <v>9</v>
+      </c>
+      <c r="D7" s="9">
+        <v>7</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9">
+        <v>27</v>
+      </c>
+      <c r="G7" s="9">
+        <v>320</v>
+      </c>
+      <c r="H7" s="9">
+        <v>5</v>
+      </c>
+      <c r="I7" s="9">
+        <v>3473</v>
+      </c>
+      <c r="J7" s="9">
+        <v>44</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L7" s="11">
+        <f t="shared" si="1"/>
+        <v>4.5454545454545456E-2</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" si="2"/>
+        <v>0.15909090909090909</v>
+      </c>
+      <c r="N7" s="9">
+        <f t="shared" si="3"/>
+        <v>0.61</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" si="4"/>
+        <v>7.27</v>
+      </c>
+      <c r="P7" s="9">
+        <f t="shared" si="5"/>
+        <v>0.11</v>
+      </c>
+      <c r="Q7" s="9">
+        <f t="shared" si="6"/>
+        <v>0.93</v>
+      </c>
+      <c r="R7" s="9">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="S7" s="9">
+        <f t="shared" si="8"/>
+        <v>78.930000000000007</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45">
+        <f t="shared" si="9"/>
+        <v>1.0394799154334038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L8" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="27" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O8" s="27" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P8" s="27" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q8" s="27" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R8" s="27" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S8" s="27" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T8" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="27" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L9" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M9" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="27" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O9" s="27" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P9" s="27" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q9" s="27" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R9" s="27" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S9" s="27" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T9" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V9" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L10" s="13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="12" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O10" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P10" s="12" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q10" s="12" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R10" s="12" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S10" s="12" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T10" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L11" s="13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M11" s="13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="12" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O11" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P11" s="12" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q11" s="12" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R11" s="12" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S11" s="12" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T11" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V11" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="50">
+        <v>37</v>
+      </c>
+      <c r="C12" s="50">
+        <v>26</v>
+      </c>
+      <c r="D12" s="50">
+        <v>9</v>
+      </c>
+      <c r="E12" s="50">
+        <v>3</v>
+      </c>
+      <c r="F12" s="50">
+        <v>29</v>
+      </c>
+      <c r="G12" s="50">
+        <v>178</v>
+      </c>
+      <c r="H12" s="50">
+        <v>11</v>
+      </c>
+      <c r="I12" s="50">
+        <v>3558</v>
+      </c>
+      <c r="J12" s="50">
+        <v>44</v>
+      </c>
+      <c r="K12" s="20">
+        <f t="shared" si="0"/>
+        <v>0.84</v>
+      </c>
+      <c r="L12" s="21">
+        <f t="shared" si="1"/>
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="M12" s="21">
+        <f t="shared" si="2"/>
+        <v>0.20454545454545456</v>
+      </c>
+      <c r="N12" s="20">
+        <f t="shared" si="3"/>
+        <v>0.66</v>
+      </c>
+      <c r="O12" s="20">
+        <f t="shared" si="4"/>
+        <v>4.05</v>
+      </c>
+      <c r="P12" s="20">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="Q12" s="20">
+        <f t="shared" si="6"/>
+        <v>1.28</v>
+      </c>
+      <c r="R12" s="20">
+        <f t="shared" si="7"/>
+        <v>70.27</v>
+      </c>
+      <c r="S12" s="20">
+        <f t="shared" si="8"/>
+        <v>80.86</v>
+      </c>
+      <c r="T12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="U12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="V12" s="45">
+        <f t="shared" si="9"/>
+        <v>1.129365750528541</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="50">
+        <v>15</v>
+      </c>
+      <c r="C13" s="50">
+        <v>7</v>
+      </c>
+      <c r="D13" s="50">
+        <v>1</v>
+      </c>
+      <c r="E13" s="50">
+        <v>0</v>
+      </c>
+      <c r="F13" s="50">
+        <v>30</v>
+      </c>
+      <c r="G13" s="50">
+        <v>179</v>
+      </c>
+      <c r="H13" s="50">
+        <v>9</v>
+      </c>
+      <c r="I13" s="50">
+        <v>2517</v>
+      </c>
+      <c r="J13" s="50">
+        <v>44</v>
+      </c>
+      <c r="K13" s="20">
+        <f t="shared" si="0"/>
+        <v>0.34</v>
+      </c>
+      <c r="L13" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="21">
+        <f t="shared" si="2"/>
+        <v>2.2727272727272728E-2</v>
+      </c>
+      <c r="N13" s="20">
+        <f t="shared" si="3"/>
+        <v>0.68</v>
+      </c>
+      <c r="O13" s="20">
+        <f t="shared" si="4"/>
+        <v>4.07</v>
+      </c>
+      <c r="P13" s="20">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q13" s="20">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="R13" s="20">
+        <f t="shared" si="7"/>
+        <v>46.67</v>
+      </c>
+      <c r="S13" s="20">
+        <f t="shared" si="8"/>
+        <v>57.2</v>
+      </c>
+      <c r="T13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="U13" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="V13" s="45">
+        <f t="shared" si="9"/>
+        <v>0.73772832980972503</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="56"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="53"/>
+      <c r="U15" s="53"/>
+      <c r="V15" s="56"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="57"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="58"/>
+      <c r="T16" s="58"/>
+      <c r="U16" s="58"/>
+      <c r="V16" s="56"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="57"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="58"/>
+      <c r="V17" s="56"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="57"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="58"/>
+      <c r="V18" s="56"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="57"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="58"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="58"/>
+      <c r="V19" s="56"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="61"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="56"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="61"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="56"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="63"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="53"/>
+      <c r="V22" s="56"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C7BC6-1079-408F-93C8-005DF99ABE1B}">
+  <dimension ref="A1:AA24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="9">
+        <v>34</v>
+      </c>
+      <c r="C2" s="9">
+        <v>14</v>
+      </c>
+      <c r="D2" s="9">
+        <v>11</v>
+      </c>
+      <c r="E2" s="9">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9">
+        <v>25</v>
+      </c>
+      <c r="G2" s="9">
+        <v>343</v>
+      </c>
+      <c r="H2" s="9">
+        <v>12</v>
+      </c>
+      <c r="I2" s="9">
+        <v>3379</v>
+      </c>
+      <c r="J2" s="9">
+        <v>44</v>
+      </c>
+      <c r="K2" s="9">
+        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <v>0.77</v>
+      </c>
+      <c r="L2" s="11">
+        <f>E2/J2</f>
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="M2" s="11">
+        <f>D2/J2</f>
+        <v>0.25</v>
+      </c>
+      <c r="N2" s="9">
+        <f>ROUND(IMDIV(F2,J2),2)</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O2" s="9">
+        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <v>7.8</v>
+      </c>
+      <c r="P2" s="9">
+        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <v>0.27</v>
+      </c>
+      <c r="Q2" s="9">
+        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <v>1.36</v>
+      </c>
+      <c r="R2" s="9">
+        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>41.18</v>
+      </c>
+      <c r="S2" s="9">
+        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <v>76.8</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45">
+        <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.1848456659619451</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9">
+        <v>25</v>
+      </c>
+      <c r="C3" s="9">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9">
+        <v>7</v>
+      </c>
+      <c r="E3" s="9">
+        <v>2</v>
+      </c>
+      <c r="F3" s="9">
+        <v>27</v>
+      </c>
+      <c r="G3" s="9">
+        <v>320</v>
+      </c>
+      <c r="H3" s="9">
+        <v>5</v>
+      </c>
+      <c r="I3" s="9">
+        <v>3473</v>
+      </c>
+      <c r="J3" s="9">
+        <v>44</v>
+      </c>
+      <c r="K3" s="9">
+        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L3" s="11">
+        <f>E3/J3</f>
+        <v>4.5454545454545456E-2</v>
+      </c>
+      <c r="M3" s="11">
+        <f>D3/J3</f>
+        <v>0.15909090909090909</v>
+      </c>
+      <c r="N3" s="9">
+        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <v>0.61</v>
+      </c>
+      <c r="O3" s="9">
+        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <v>7.27</v>
+      </c>
+      <c r="P3" s="9">
+        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <v>0.11</v>
+      </c>
+      <c r="Q3" s="9">
+        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <v>0.93</v>
+      </c>
+      <c r="R3" s="9">
+        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <v>36</v>
+      </c>
+      <c r="S3" s="9">
+        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <v>78.930000000000007</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45">
+        <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <v>1.0394799154334038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="50">
+        <v>37</v>
+      </c>
+      <c r="C4" s="50">
+        <v>26</v>
+      </c>
+      <c r="D4" s="50">
+        <v>9</v>
+      </c>
+      <c r="E4" s="50">
+        <v>3</v>
+      </c>
+      <c r="F4" s="50">
+        <v>29</v>
+      </c>
+      <c r="G4" s="50">
+        <v>178</v>
+      </c>
+      <c r="H4" s="50">
+        <v>11</v>
+      </c>
+      <c r="I4" s="50">
+        <v>3558</v>
+      </c>
+      <c r="J4" s="50">
+        <v>44</v>
+      </c>
+      <c r="K4" s="20">
+        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <v>0.84</v>
+      </c>
+      <c r="L4" s="21">
+        <f>E4/J4</f>
+        <v>6.8181818181818177E-2</v>
+      </c>
+      <c r="M4" s="21">
+        <f>D4/J4</f>
+        <v>0.20454545454545456</v>
+      </c>
+      <c r="N4" s="20">
+        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <v>0.66</v>
+      </c>
+      <c r="O4" s="20">
+        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <v>4.05</v>
+      </c>
+      <c r="P4" s="20">
+        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="Q4" s="20">
+        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <v>1.28</v>
+      </c>
+      <c r="R4" s="20">
+        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <v>70.27</v>
+      </c>
+      <c r="S4" s="20">
+        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <v>80.86</v>
+      </c>
+      <c r="T4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45">
+        <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <v>1.129365750528541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="50">
+        <v>15</v>
+      </c>
+      <c r="C5" s="50">
+        <v>7</v>
+      </c>
+      <c r="D5" s="50">
+        <v>1</v>
+      </c>
+      <c r="E5" s="50">
+        <v>0</v>
+      </c>
+      <c r="F5" s="50">
+        <v>30</v>
+      </c>
+      <c r="G5" s="50">
+        <v>179</v>
+      </c>
+      <c r="H5" s="50">
+        <v>9</v>
+      </c>
+      <c r="I5" s="50">
+        <v>2517</v>
+      </c>
+      <c r="J5" s="50">
+        <v>44</v>
+      </c>
+      <c r="K5" s="20">
+        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <v>0.34</v>
+      </c>
+      <c r="L5" s="21">
+        <f>E5/J5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="21">
+        <f>D5/J5</f>
+        <v>2.2727272727272728E-2</v>
+      </c>
+      <c r="N5" s="20">
+        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <v>0.68</v>
+      </c>
+      <c r="O5" s="20">
+        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <v>4.07</v>
+      </c>
+      <c r="P5" s="20">
+        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <v>0.2</v>
+      </c>
+      <c r="Q5" s="20">
+        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="R5" s="20">
+        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <v>46.67</v>
+      </c>
+      <c r="S5" s="20">
+        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <v>57.2</v>
+      </c>
+      <c r="T5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45">
+        <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <v>0.73772832980972503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27" t="e">
+        <f>ROUND(IMDIV(B6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L6" s="28" t="e">
+        <f>E6/J6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M6" s="28" t="e">
+        <f>D6/J6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="27" t="e">
+        <f>ROUND(IMDIV(F6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O6" s="27" t="e">
+        <f>ROUND(IMDIV(G6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P6" s="27" t="e">
+        <f>ROUND(IMDIV(H6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q6" s="27" t="e">
+        <f>ROUND(IMDIV(B6,F6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R6" s="27" t="e">
+        <f>ROUND(IMDIV(C6,B6),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S6" s="27" t="e">
+        <f>ROUND(IMDIV(I6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45" t="e">
+        <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="27" t="e">
+        <f>ROUND(IMDIV(B7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L7" s="28" t="e">
+        <f>E7/J7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M7" s="28" t="e">
+        <f>D7/J7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="27" t="e">
+        <f>ROUND(IMDIV(F7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O7" s="27" t="e">
+        <f>ROUND(IMDIV(G7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P7" s="27" t="e">
+        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q7" s="27" t="e">
+        <f>ROUND(IMDIV(B7,F7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R7" s="27" t="e">
+        <f>ROUND(IMDIV(C7,B7),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S7" s="27" t="e">
+        <f>ROUND(IMDIV(I7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T7" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45" t="e">
+        <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12" t="e">
+        <f>ROUND(IMDIV(B8,J8),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L8" s="13" t="e">
+        <f>E8/J8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="13" t="e">
+        <f>D8/J8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="12" t="e">
+        <f>ROUND(IMDIV(F8,J8),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O8" s="12" t="e">
+        <f>ROUND(IMDIV(G8,J8),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P8" s="12" t="e">
+        <f>ROUND(IMDIV(H8,J8),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q8" s="12" t="e">
+        <f>ROUND(IMDIV(B8,F8),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R8" s="12" t="e">
+        <f>ROUND(IMDIV(C8,B8),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S8" s="12" t="e">
+        <f>ROUND(IMDIV(I8,J8),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T8" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="45" t="e">
+        <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA8" s="63"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12" t="e">
+        <f>ROUND(IMDIV(B9,J9),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L9" s="13" t="e">
+        <f>E9/J9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M9" s="13" t="e">
+        <f>D9/J9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="12" t="e">
+        <f>ROUND(IMDIV(F9,J9),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O9" s="12" t="e">
+        <f>ROUND(IMDIV(G9,J9),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P9" s="12" t="e">
+        <f>ROUND(IMDIV(H9,J9),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q9" s="12" t="e">
+        <f>ROUND(IMDIV(B9,F9),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R9" s="12" t="e">
+        <f>ROUND(IMDIV(C9,B9),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S9" s="12" t="e">
+        <f>ROUND(IMDIV(I9,J9),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T9" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V9" s="45" t="e">
+        <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="56"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="66" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="53"/>
+      <c r="U11" s="53"/>
+      <c r="V11" s="56"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="70">
+        <v>76.8</v>
+      </c>
+      <c r="E12" s="71">
+        <v>1.1848456659619451</v>
+      </c>
+      <c r="F12" s="70">
+        <v>0.77</v>
+      </c>
+      <c r="G12" s="70">
+        <v>3</v>
+      </c>
+      <c r="H12" s="70">
+        <v>11</v>
+      </c>
+      <c r="I12" s="70">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J12" s="70">
+        <v>343</v>
+      </c>
+      <c r="K12" s="70">
+        <v>0.27</v>
+      </c>
+      <c r="L12" s="70">
+        <v>1.36</v>
+      </c>
+      <c r="M12" s="70">
+        <v>41.18</v>
+      </c>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="58"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="58"/>
+      <c r="V12" s="56"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="72">
+        <v>-2</v>
+      </c>
+      <c r="D13" s="70">
+        <v>78.930000000000007</v>
+      </c>
+      <c r="E13" s="71">
+        <v>1.0394799154334038</v>
+      </c>
+      <c r="F13" s="70">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G13" s="70">
+        <v>2</v>
+      </c>
+      <c r="H13" s="70">
+        <v>7</v>
+      </c>
+      <c r="I13" s="70">
+        <v>0.61</v>
+      </c>
+      <c r="J13" s="70">
+        <v>320</v>
+      </c>
+      <c r="K13" s="70">
+        <v>0.11</v>
+      </c>
+      <c r="L13" s="70">
+        <v>0.93</v>
+      </c>
+      <c r="M13" s="70">
+        <v>36</v>
+      </c>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="58"/>
+      <c r="Q13" s="58"/>
+      <c r="R13" s="58"/>
+      <c r="S13" s="58"/>
+      <c r="T13" s="58"/>
+      <c r="U13" s="58"/>
+      <c r="V13" s="56"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="76"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="58"/>
+      <c r="Q14" s="58"/>
+      <c r="R14" s="58"/>
+      <c r="S14" s="58"/>
+      <c r="T14" s="58"/>
+      <c r="U14" s="58"/>
+      <c r="V14" s="56"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="70">
+        <v>80.86</v>
+      </c>
+      <c r="E15" s="71">
+        <v>1.129365750528541</v>
+      </c>
+      <c r="F15" s="70">
+        <v>0.84</v>
+      </c>
+      <c r="G15" s="75">
+        <v>3</v>
+      </c>
+      <c r="H15" s="75">
+        <v>9</v>
+      </c>
+      <c r="I15" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="J15" s="75">
+        <v>178</v>
+      </c>
+      <c r="K15" s="70">
+        <v>0.25</v>
+      </c>
+      <c r="L15" s="70">
+        <v>1.28</v>
+      </c>
+      <c r="M15" s="70">
+        <v>70.27</v>
+      </c>
+      <c r="N15" s="58"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="58"/>
+      <c r="S15" s="58"/>
+      <c r="T15" s="58"/>
+      <c r="U15" s="58"/>
+      <c r="V15" s="56"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="72">
+        <v>-15</v>
+      </c>
+      <c r="D16" s="70">
+        <v>57.2</v>
+      </c>
+      <c r="E16" s="71">
+        <v>0.73772832980972503</v>
+      </c>
+      <c r="F16" s="70">
+        <v>0.34</v>
+      </c>
+      <c r="G16" s="75">
+        <v>0</v>
+      </c>
+      <c r="H16" s="75">
+        <v>1</v>
+      </c>
+      <c r="I16" s="70">
+        <v>0.68</v>
+      </c>
+      <c r="J16" s="75">
+        <v>179</v>
+      </c>
+      <c r="K16" s="70">
+        <v>0.2</v>
+      </c>
+      <c r="L16" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="70">
+        <v>46.67</v>
+      </c>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="56"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="61"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="56"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="53"/>
+      <c r="U18" s="53"/>
+      <c r="V18" s="56"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="65"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="65"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="76"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="65"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="65"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V9">
+    <sortCondition sortBy="cellColor" ref="A5:A9" dxfId="0"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40897AC2-0114-4A6D-BFFC-5EDF88F8CE8F}">
+  <dimension ref="A1:V22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6" t="e">
+        <f t="shared" ref="K2:K5" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" s="7" t="e">
+        <f t="shared" ref="L2:L5" si="1">E2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M2" s="7" t="e">
+        <f t="shared" ref="M2:M5" si="2">D2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N2" s="6" t="e">
+        <f t="shared" ref="N2:N5" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O2" s="6" t="e">
+        <f t="shared" ref="O2:O5" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P2" s="6" t="e">
+        <f t="shared" ref="P2:P5" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q2" s="6" t="e">
+        <f t="shared" ref="Q2:Q5" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R2" s="6" t="e">
+        <f t="shared" ref="R2:R5" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S2" s="6" t="e">
+        <f t="shared" ref="S2:S5" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45" t="e">
+        <f t="shared" ref="V2:V5" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M3" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N3" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O3" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P3" s="6" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q3" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R3" s="6" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S3" s="6" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L4" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M4" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O4" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P4" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q4" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R4" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S4" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L5" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M5" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O5" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P5" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q5" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R5" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S5" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="e">
+        <f t="shared" ref="K6:K13" si="10">ROUND(IMDIV(B6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L6" s="11" t="e">
+        <f t="shared" ref="L6:L13" si="11">E6/J6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M6" s="11" t="e">
+        <f t="shared" ref="M6:M13" si="12">D6/J6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="9" t="e">
+        <f t="shared" ref="N6:N13" si="13">ROUND(IMDIV(F6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O6" s="9" t="e">
+        <f t="shared" ref="O6:O13" si="14">ROUND(IMDIV(G6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P6" s="9" t="e">
+        <f t="shared" ref="P6:P13" si="15">ROUND(IMDIV(H6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q6" s="9" t="e">
+        <f t="shared" ref="Q6:Q13" si="16">ROUND(IMDIV(B6,F6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R6" s="9" t="e">
+        <f t="shared" ref="R6:R13" si="17">ROUND(IMDIV(C6,B6),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S6" s="9" t="e">
+        <f t="shared" ref="S6:S13" si="18">ROUND(IMDIV(I6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45" t="e">
+        <f t="shared" ref="V6:V13" si="19">((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L7" s="11" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M7" s="11" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="9" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O7" s="9" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P7" s="9" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q7" s="9" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R7" s="9" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S7" s="9" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L8" s="28" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="28" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="27" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O8" s="27" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P8" s="27" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q8" s="27" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R8" s="27" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S8" s="27" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T8" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="27" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L9" s="28" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M9" s="28" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="27" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O9" s="27" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P9" s="27" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q9" s="27" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R9" s="27" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S9" s="27" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T9" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V9" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L10" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="13" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="12" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O10" s="12" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P10" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q10" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R10" s="12" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S10" s="12" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T10" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L11" s="13" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M11" s="13" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="12" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O11" s="12" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P11" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q11" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R11" s="12" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S11" s="12" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T11" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V11" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="61"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="62"/>
+      <c r="V12" s="56"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="61"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="54"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="62"/>
+      <c r="V13" s="56"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="56"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="53"/>
+      <c r="U15" s="53"/>
+      <c r="V15" s="56"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="57"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="58"/>
+      <c r="T16" s="58"/>
+      <c r="U16" s="58"/>
+      <c r="V16" s="56"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="57"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="58"/>
+      <c r="V17" s="56"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="57"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="58"/>
+      <c r="V18" s="56"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="57"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="58"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="58"/>
+      <c r="V19" s="56"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="61"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="56"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="61"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="56"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="63"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="53"/>
+      <c r="V22" s="56"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D112C103-7A2C-4701-8F60-5B846BF871DD}">
+  <dimension ref="A1:V22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6" t="e">
+        <f t="shared" ref="K2:K11" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" s="7" t="e">
+        <f t="shared" ref="L2:L11" si="1">E2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M2" s="7" t="e">
+        <f t="shared" ref="M2:M11" si="2">D2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N2" s="6" t="e">
+        <f t="shared" ref="N2:N11" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O2" s="6" t="e">
+        <f t="shared" ref="O2:O11" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P2" s="6" t="e">
+        <f t="shared" ref="P2:P11" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q2" s="6" t="e">
+        <f t="shared" ref="Q2:Q11" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R2" s="6" t="e">
+        <f t="shared" ref="R2:R11" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S2" s="6" t="e">
+        <f t="shared" ref="S2:S11" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45" t="e">
+        <f t="shared" ref="V2:V11" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M3" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N3" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O3" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P3" s="6" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q3" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R3" s="6" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S3" s="6" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L4" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M4" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O4" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P4" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q4" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R4" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S4" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L5" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M5" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O5" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P5" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q5" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R5" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S5" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L6" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M6" s="11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="9" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O6" s="9" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P6" s="9" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q6" s="9" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R6" s="9" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S6" s="9" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L7" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M7" s="11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="9" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O7" s="9" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P7" s="9" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q7" s="9" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R7" s="9" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S7" s="9" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L8" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="27" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O8" s="27" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P8" s="27" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q8" s="27" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R8" s="27" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S8" s="27" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T8" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="27" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L9" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M9" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="27" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O9" s="27" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P9" s="27" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q9" s="27" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R9" s="27" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S9" s="27" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T9" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V9" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L10" s="13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="12" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O10" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P10" s="12" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q10" s="12" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R10" s="12" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S10" s="12" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T10" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L11" s="13" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M11" s="13" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="12" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O11" s="12" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P11" s="12" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q11" s="12" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R11" s="12" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S11" s="12" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T11" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="V11" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="61"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="62"/>
+      <c r="V12" s="56"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="61"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="54"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="62"/>
+      <c r="V13" s="56"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="56"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="53"/>
+      <c r="U15" s="53"/>
+      <c r="V15" s="56"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="57"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="58"/>
+      <c r="T16" s="58"/>
+      <c r="U16" s="58"/>
+      <c r="V16" s="56"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="57"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="58"/>
+      <c r="V17" s="56"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="57"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="58"/>
+      <c r="T18" s="58"/>
+      <c r="U18" s="58"/>
+      <c r="V18" s="56"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="57"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="58"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="58"/>
+      <c r="V19" s="56"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="61"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="56"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="61"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="56"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="63"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="53"/>
+      <c r="V22" s="56"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE51AD4-825C-4F1A-9ED4-337B9AA0C021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2BF150-050C-4390-B7C6-4ACAFFA45930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tourney" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="69">
   <si>
     <t>player</t>
   </si>
@@ -231,12 +231,30 @@
   <si>
     <t>JewSpace</t>
   </si>
+  <si>
+    <t>CHUDS</t>
+  </si>
+  <si>
+    <t>JS/SP</t>
+  </si>
+  <si>
+    <t>Burger</t>
+  </si>
+  <si>
+    <t>Team A</t>
+  </si>
+  <si>
+    <t>Team B</t>
+  </si>
+  <si>
+    <t>EVP</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +344,26 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0038B8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF501C75"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF3A602"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -600,41 +638,34 @@
     <xf numFmtId="16" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -675,6 +706,15 @@
     <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -685,7 +725,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF4EA72E"/>
+          <fgColor rgb="FFF3A602"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -693,7 +733,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
+          <fgColor rgb="FF4EA72E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -702,16 +742,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF3A602"/>
+      <color rgb="FF501C75"/>
       <color rgb="FF0038B8"/>
       <color rgb="FFEF3E88"/>
       <color rgb="FFF87D18"/>
       <color rgb="FFDF060A"/>
       <color rgb="FF56260B"/>
       <color rgb="FF7D86E0"/>
-      <color rgb="FF501C75"/>
       <color rgb="FF1A3C8E"/>
       <color rgb="FFCF5B1B"/>
-      <color rgb="FF8C3E12"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1150,39 +1190,39 @@
         <v>118</v>
       </c>
       <c r="K2" s="6">
-        <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <f>ROUND(IMDIV(B2,J2),2)</f>
         <v>0.95</v>
       </c>
       <c r="L2" s="7">
-        <f t="shared" ref="L2:L22" si="1">E2/J2</f>
+        <f>E2/J2</f>
         <v>6.7796610169491525E-2</v>
       </c>
       <c r="M2" s="7">
-        <f t="shared" ref="M2:M22" si="2">D2/J2</f>
+        <f>D2/J2</f>
         <v>0.2711864406779661</v>
       </c>
       <c r="N2" s="6">
-        <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <f>ROUND(IMDIV(F2,J2),2)</f>
         <v>0.47</v>
       </c>
       <c r="O2" s="6">
-        <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <f>ROUND(IMDIV(G2,J2),2)</f>
         <v>5.66</v>
       </c>
       <c r="P2" s="6">
-        <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <f>ROUND(IMDIV(H2,J2),2)</f>
         <v>0.26</v>
       </c>
       <c r="Q2" s="6">
-        <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <f>ROUND(IMDIV(B2,F2),2)</f>
         <v>2.04</v>
       </c>
       <c r="R2" s="6">
-        <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <f>ROUND(IMDIV(C2,B2),4)*100</f>
         <v>65.180000000000007</v>
       </c>
       <c r="S2" s="6">
-        <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <f>ROUND(IMDIV(I2,J2),2)</f>
         <v>102.54</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1192,7 +1232,7 @@
         <v>24</v>
       </c>
       <c r="V2" s="45">
-        <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
         <v>1.4812861647615294</v>
       </c>
     </row>
@@ -1228,39 +1268,39 @@
         <v>118</v>
       </c>
       <c r="K3" s="6">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B3,J3),2)</f>
         <v>0.48</v>
       </c>
       <c r="L3" s="7">
-        <f t="shared" si="1"/>
+        <f>E3/J3</f>
         <v>1.6949152542372881E-2</v>
       </c>
       <c r="M3" s="7">
-        <f t="shared" si="2"/>
+        <f>D3/J3</f>
         <v>8.4745762711864403E-2</v>
       </c>
       <c r="N3" s="6">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F3,J3),2)</f>
         <v>0.61</v>
       </c>
       <c r="O3" s="6">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G3,J3),2)</f>
         <v>0.35</v>
       </c>
       <c r="P3" s="6">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H3,J3),2)</f>
         <v>0.12</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B3,F3),2)</f>
         <v>0.79</v>
       </c>
       <c r="R3" s="6">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C3,B3),4)*100</f>
         <v>50.88</v>
       </c>
       <c r="S3" s="6">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I3,J3),2)</f>
         <v>51.84</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1270,7 +1310,7 @@
         <v>24</v>
       </c>
       <c r="V3" s="45">
-        <f t="shared" si="9"/>
+        <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
         <v>0.85369255025620816</v>
       </c>
     </row>
@@ -1306,39 +1346,39 @@
         <v>122</v>
       </c>
       <c r="K4" s="30">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B4,J4),2)</f>
         <v>0.89</v>
       </c>
       <c r="L4" s="31">
-        <f t="shared" si="1"/>
+        <f>E4/J4</f>
         <v>8.1967213114754092E-2</v>
       </c>
       <c r="M4" s="31">
-        <f t="shared" si="2"/>
+        <f>D4/J4</f>
         <v>0.28688524590163933</v>
       </c>
       <c r="N4" s="30">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F4,J4),2)</f>
         <v>0.49</v>
       </c>
       <c r="O4" s="30">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G4,J4),2)</f>
         <v>6.51</v>
       </c>
       <c r="P4" s="30">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H4,J4),2)</f>
         <v>0.12</v>
       </c>
       <c r="Q4" s="30">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B4,F4),2)</f>
         <v>1.8</v>
       </c>
       <c r="R4" s="30">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C4,B4),4)*100</f>
         <v>57.410000000000004</v>
       </c>
       <c r="S4" s="30">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I4,J4),2)</f>
         <v>101.23</v>
       </c>
       <c r="T4" s="29" t="s">
@@ -1348,7 +1388,7 @@
         <v>24</v>
       </c>
       <c r="V4" s="45">
-        <f t="shared" si="9"/>
+        <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
         <v>1.4309519634006862</v>
       </c>
     </row>
@@ -1384,39 +1424,39 @@
         <v>122</v>
       </c>
       <c r="K5" s="30">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B5,J5),2)</f>
         <v>0.41</v>
       </c>
       <c r="L5" s="31">
-        <f t="shared" si="1"/>
+        <f>E5/J5</f>
         <v>2.4590163934426229E-2</v>
       </c>
       <c r="M5" s="31">
-        <f t="shared" si="2"/>
+        <f>D5/J5</f>
         <v>4.9180327868852458E-2</v>
       </c>
       <c r="N5" s="30">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F5,J5),2)</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O5" s="30">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G5,J5),2)</f>
         <v>1.91</v>
       </c>
       <c r="P5" s="30">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H5,J5),2)</f>
         <v>0.2</v>
       </c>
       <c r="Q5" s="30">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B5,F5),2)</f>
         <v>0.75</v>
       </c>
       <c r="R5" s="30">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C5,B5),4)*100</f>
         <v>36</v>
       </c>
       <c r="S5" s="30">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I5,J5),2)</f>
         <v>45.66</v>
       </c>
       <c r="T5" s="29" t="s">
@@ -1426,7 +1466,7 @@
         <v>24</v>
       </c>
       <c r="V5" s="45">
-        <f t="shared" si="9"/>
+        <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
         <v>0.85358520777735414</v>
       </c>
     </row>
@@ -1462,39 +1502,39 @@
         <v>192</v>
       </c>
       <c r="K6" s="9">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B6,J6),2)</f>
         <v>0.76</v>
       </c>
       <c r="L6" s="11">
-        <f t="shared" si="1"/>
+        <f>E6/J6</f>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="M6" s="11">
-        <f t="shared" si="2"/>
+        <f>D6/J6</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="N6" s="9">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F6,J6),2)</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="O6" s="9">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G6,J6),2)</f>
         <v>4.1100000000000003</v>
       </c>
       <c r="P6" s="9">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H6,J6),2)</f>
         <v>0.26</v>
       </c>
       <c r="Q6" s="9">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B6,F6),2)</f>
         <v>1.37</v>
       </c>
       <c r="R6" s="9">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C6,B6),4)*100</f>
         <v>47.589999999999996</v>
       </c>
       <c r="S6" s="9">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I6,J6),2)</f>
         <v>85.67</v>
       </c>
       <c r="T6" s="9" t="s">
@@ -1504,7 +1544,7 @@
         <v>24</v>
       </c>
       <c r="V6" s="45">
-        <f t="shared" si="9"/>
+        <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
         <v>1.2321317829457363</v>
       </c>
     </row>
@@ -1540,39 +1580,39 @@
         <v>192</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B7,J7),2)</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="L7" s="11">
-        <f t="shared" si="1"/>
+        <f>E7/J7</f>
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" si="2"/>
+        <f>D7/J7</f>
         <v>0.11979166666666667</v>
       </c>
       <c r="N7" s="9">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F7,J7),2)</f>
         <v>0.6</v>
       </c>
       <c r="O7" s="9">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G7,J7),2)</f>
         <v>5.56</v>
       </c>
       <c r="P7" s="9">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H7,J7),2)</f>
         <v>0.14000000000000001</v>
       </c>
       <c r="Q7" s="9">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B7,F7),2)</f>
         <v>0.93</v>
       </c>
       <c r="R7" s="9">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C7,B7),4)*100</f>
         <v>40.19</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I7,J7),2)</f>
         <v>63.52</v>
       </c>
       <c r="T7" s="9" t="s">
@@ -1582,7 +1622,7 @@
         <v>24</v>
       </c>
       <c r="V7" s="45">
-        <f t="shared" si="9"/>
+        <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
         <v>0.96680644379844971</v>
       </c>
     </row>
@@ -1618,39 +1658,39 @@
         <v>136</v>
       </c>
       <c r="K8" s="27">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B8,J8),2)</f>
         <v>0.78</v>
       </c>
       <c r="L8" s="28">
-        <f t="shared" si="1"/>
+        <f>E8/J8</f>
         <v>0.125</v>
       </c>
       <c r="M8" s="28">
-        <f t="shared" si="2"/>
+        <f>D8/J8</f>
         <v>0.15441176470588236</v>
       </c>
       <c r="N8" s="27">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F8,J8),2)</f>
         <v>0.52</v>
       </c>
       <c r="O8" s="27">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G8,J8),2)</f>
         <v>2.21</v>
       </c>
       <c r="P8" s="27">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H8,J8),2)</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="Q8" s="27">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B8,F8),2)</f>
         <v>1.49</v>
       </c>
       <c r="R8" s="27">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C8,B8),4)*100</f>
         <v>53.769999999999996</v>
       </c>
       <c r="S8" s="27">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I8,J8),2)</f>
         <v>86.51</v>
       </c>
       <c r="T8" s="26" t="s">
@@ -1660,7 +1700,7 @@
         <v>24</v>
       </c>
       <c r="V8" s="45">
-        <f t="shared" si="9"/>
+        <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
         <v>1.2719750341997265</v>
       </c>
     </row>
@@ -1696,39 +1736,39 @@
         <v>125</v>
       </c>
       <c r="K9" s="27">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B9,J9),2)</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="L9" s="28">
-        <f t="shared" si="1"/>
+        <f>E9/J9</f>
         <v>1.6E-2</v>
       </c>
       <c r="M9" s="28">
-        <f t="shared" si="2"/>
+        <f>D9/J9</f>
         <v>0.08</v>
       </c>
       <c r="N9" s="27">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F9,J9),2)</f>
         <v>0.64</v>
       </c>
       <c r="O9" s="27">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G9,J9),2)</f>
         <v>2.78</v>
       </c>
       <c r="P9" s="27">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H9,J9),2)</f>
         <v>0.3</v>
       </c>
       <c r="Q9" s="27">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B9,F9),2)</f>
         <v>0.88</v>
       </c>
       <c r="R9" s="27">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C9,B9),4)*100</f>
         <v>40</v>
       </c>
       <c r="S9" s="27">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I9,J9),2)</f>
         <v>63.7</v>
       </c>
       <c r="T9" s="26" t="s">
@@ -1738,7 +1778,7 @@
         <v>24</v>
       </c>
       <c r="V9" s="45">
-        <f t="shared" si="9"/>
+        <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
         <v>0.91847906976744187</v>
       </c>
     </row>
@@ -1774,39 +1814,39 @@
         <v>116</v>
       </c>
       <c r="K10" s="12">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B10,J10),2)</f>
         <v>0.8</v>
       </c>
       <c r="L10" s="13">
-        <f t="shared" si="1"/>
+        <f>E10/J10</f>
         <v>5.1724137931034482E-2</v>
       </c>
       <c r="M10" s="13">
-        <f t="shared" si="2"/>
+        <f>D10/J10</f>
         <v>0.19827586206896552</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F10,J10),2)</f>
         <v>0.52</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G10,J10),2)</f>
         <v>3.29</v>
       </c>
       <c r="P10" s="12">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H10,J10),2)</f>
         <v>0.12</v>
       </c>
       <c r="Q10" s="12">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B10,F10),2)</f>
         <v>1.55</v>
       </c>
       <c r="R10" s="12">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C10,B10),4)*100</f>
         <v>45.16</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I10,J10),2)</f>
         <v>98.28</v>
       </c>
       <c r="T10" s="51" t="s">
@@ -1816,7 +1856,7 @@
         <v>24</v>
       </c>
       <c r="V10" s="45">
-        <f t="shared" si="9"/>
+        <f>((K10/2.5)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
         <v>1.3230300721732158</v>
       </c>
     </row>
@@ -1852,39 +1892,39 @@
         <v>116</v>
       </c>
       <c r="K11" s="12">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B11,J11),2)</f>
         <v>0.52</v>
       </c>
       <c r="L11" s="13">
-        <f t="shared" si="1"/>
+        <f>E11/J11</f>
         <v>2.5862068965517241E-2</v>
       </c>
       <c r="M11" s="13">
-        <f t="shared" si="2"/>
+        <f>D11/J11</f>
         <v>7.7586206896551727E-2</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F11,J11),2)</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="O11" s="12">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G11,J11),2)</f>
         <v>1.25</v>
       </c>
       <c r="P11" s="12">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H11,J11),2)</f>
         <v>0.16</v>
       </c>
       <c r="Q11" s="12">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B11,F11),2)</f>
         <v>0.91</v>
       </c>
       <c r="R11" s="12">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C11,B11),4)*100</f>
         <v>55.000000000000007</v>
       </c>
       <c r="S11" s="12">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I11,J11),2)</f>
         <v>53.22</v>
       </c>
       <c r="T11" s="51" t="s">
@@ -1894,7 +1934,7 @@
         <v>24</v>
       </c>
       <c r="V11" s="45">
-        <f t="shared" si="9"/>
+        <f>((K11/2.5)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
         <v>0.91810384923817168</v>
       </c>
     </row>
@@ -1930,49 +1970,49 @@
         <v>181</v>
       </c>
       <c r="K12" s="20">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B12,J12),2)</f>
         <v>0.71</v>
       </c>
       <c r="L12" s="21">
-        <f t="shared" si="1"/>
+        <f>E12/J12</f>
         <v>6.6298342541436461E-2</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="2"/>
+        <f>D12/J12</f>
         <v>0.19889502762430938</v>
       </c>
       <c r="N12" s="20">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F12,J12),2)</f>
         <v>0.6</v>
       </c>
       <c r="O12" s="20">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G12,J12),2)</f>
         <v>4.9400000000000004</v>
       </c>
       <c r="P12" s="20">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H12,J12),2)</f>
         <v>0.23</v>
       </c>
       <c r="Q12" s="20">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B12,F12),2)</f>
         <v>1.19</v>
       </c>
       <c r="R12" s="20">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C12,B12),4)*100</f>
         <v>66.67</v>
       </c>
       <c r="S12" s="20">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I12,J12),2)</f>
         <v>78.489999999999995</v>
       </c>
       <c r="T12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="22" t="s">
-        <v>24</v>
+      <c r="U12" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="V12" s="45">
-        <f t="shared" si="9"/>
+        <f>((K12/2.5)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
         <v>1.123553192856225</v>
       </c>
     </row>
@@ -2008,39 +2048,39 @@
         <v>181</v>
       </c>
       <c r="K13" s="20">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B13,J13),2)</f>
         <v>0.5</v>
       </c>
       <c r="L13" s="21">
-        <f t="shared" si="1"/>
+        <f>E13/J13</f>
         <v>3.8674033149171269E-2</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="2"/>
+        <f>D13/J13</f>
         <v>0.1270718232044199</v>
       </c>
       <c r="N13" s="20">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F13,J13),2)</f>
         <v>0.62</v>
       </c>
       <c r="O13" s="20">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G13,J13),2)</f>
         <v>2.5099999999999998</v>
       </c>
       <c r="P13" s="20">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H13,J13),2)</f>
         <v>0.25</v>
       </c>
       <c r="Q13" s="20">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B13,F13),2)</f>
         <v>0.81</v>
       </c>
       <c r="R13" s="20">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C13,B13),4)*100</f>
         <v>46.150000000000006</v>
       </c>
       <c r="S13" s="20">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I13,J13),2)</f>
         <v>60.58</v>
       </c>
       <c r="T13" s="20" t="s">
@@ -2050,7 +2090,7 @@
         <v>24</v>
       </c>
       <c r="V13" s="45">
-        <f t="shared" si="9"/>
+        <f>((K13/2.5)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
         <v>0.91377020429140432</v>
       </c>
     </row>
@@ -2086,39 +2126,39 @@
         <v>85</v>
       </c>
       <c r="K14" s="33">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B14,J14),2)</f>
         <v>0.53</v>
       </c>
       <c r="L14" s="34">
-        <f t="shared" si="1"/>
+        <f>E14/J14</f>
         <v>2.3529411764705882E-2</v>
       </c>
       <c r="M14" s="34">
-        <f t="shared" si="2"/>
+        <f>D14/J14</f>
         <v>0.15294117647058825</v>
       </c>
       <c r="N14" s="33">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F14,J14),2)</f>
         <v>0.68</v>
       </c>
       <c r="O14" s="33">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G14,J14),2)</f>
         <v>3.04</v>
       </c>
       <c r="P14" s="33">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H14,J14),2)</f>
         <v>0.2</v>
       </c>
       <c r="Q14" s="33">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B14,F14),2)</f>
         <v>0.78</v>
       </c>
       <c r="R14" s="33">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C14,B14),4)*100</f>
         <v>35.56</v>
       </c>
       <c r="S14" s="33">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I14,J14),2)</f>
         <v>72.89</v>
       </c>
       <c r="T14" s="32" t="s">
@@ -2128,7 +2168,7 @@
         <v>24</v>
       </c>
       <c r="V14" s="45">
-        <f t="shared" si="9"/>
+        <f>((K14/2.5)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
         <v>0.92396443228454173</v>
       </c>
     </row>
@@ -2164,39 +2204,39 @@
         <v>85</v>
       </c>
       <c r="K15" s="33">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B15,J15),2)</f>
         <v>0.44</v>
       </c>
       <c r="L15" s="34">
-        <f t="shared" si="1"/>
+        <f>E15/J15</f>
         <v>3.5294117647058823E-2</v>
       </c>
       <c r="M15" s="34">
-        <f t="shared" si="2"/>
+        <f>D15/J15</f>
         <v>9.4117647058823528E-2</v>
       </c>
       <c r="N15" s="33">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F15,J15),2)</f>
         <v>0.69</v>
       </c>
       <c r="O15" s="33">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G15,J15),2)</f>
         <v>2.98</v>
       </c>
       <c r="P15" s="33">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H15,J15),2)</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q15" s="33">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B15,F15),2)</f>
         <v>0.63</v>
       </c>
       <c r="R15" s="33">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C15,B15),4)*100</f>
         <v>45.95</v>
       </c>
       <c r="S15" s="33">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I15,J15),2)</f>
         <v>47.35</v>
       </c>
       <c r="T15" s="32" t="s">
@@ -2206,7 +2246,7 @@
         <v>24</v>
       </c>
       <c r="V15" s="45">
-        <f t="shared" si="9"/>
+        <f>((K15/2.5)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
         <v>0.74032079343365265</v>
       </c>
     </row>
@@ -2242,39 +2282,39 @@
         <v>119</v>
       </c>
       <c r="K16" s="18">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B16,J16),2)</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="L16" s="19">
-        <f t="shared" si="1"/>
+        <f>E16/J16</f>
         <v>2.5210084033613446E-2</v>
       </c>
       <c r="M16" s="19">
-        <f t="shared" si="2"/>
+        <f>D16/J16</f>
         <v>0.11764705882352941</v>
       </c>
       <c r="N16" s="18">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F16,J16),2)</f>
         <v>0.65</v>
       </c>
       <c r="O16" s="18">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G16,J16),2)</f>
         <v>3.08</v>
       </c>
       <c r="P16" s="18">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H16,J16),2)</f>
         <v>0.11</v>
       </c>
       <c r="Q16" s="18">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B16,F16),2)</f>
         <v>0.87</v>
       </c>
       <c r="R16" s="18">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C16,B16),4)*100</f>
         <v>52.239999999999995</v>
       </c>
       <c r="S16" s="18">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I16,J16),2)</f>
         <v>70.7</v>
       </c>
       <c r="T16" s="18" t="s">
@@ -2284,7 +2324,7 @@
         <v>24</v>
       </c>
       <c r="V16" s="45">
-        <f t="shared" si="9"/>
+        <f>((K16/2.5)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
         <v>0.94279099081493056</v>
       </c>
     </row>
@@ -2320,39 +2360,39 @@
         <v>119</v>
       </c>
       <c r="K17" s="18">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B17,J17),2)</f>
         <v>0.46</v>
       </c>
       <c r="L17" s="19">
-        <f t="shared" si="1"/>
+        <f>E17/J17</f>
         <v>1.680672268907563E-2</v>
       </c>
       <c r="M17" s="19">
-        <f t="shared" si="2"/>
+        <f>D17/J17</f>
         <v>8.4033613445378158E-2</v>
       </c>
       <c r="N17" s="18">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F17,J17),2)</f>
         <v>0.66</v>
       </c>
       <c r="O17" s="18">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G17,J17),2)</f>
         <v>1.49</v>
       </c>
       <c r="P17" s="18">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H17,J17),2)</f>
         <v>0.13</v>
       </c>
       <c r="Q17" s="18">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B17,F17),2)</f>
         <v>0.71</v>
       </c>
       <c r="R17" s="18">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C17,B17),4)*100</f>
         <v>38.18</v>
       </c>
       <c r="S17" s="18">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I17,J17),2)</f>
         <v>56.19</v>
       </c>
       <c r="T17" s="18" t="s">
@@ -2362,7 +2402,7 @@
         <v>24</v>
       </c>
       <c r="V17" s="45">
-        <f t="shared" si="9"/>
+        <f>((K17/2.5)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
         <v>0.8162185851084619</v>
       </c>
     </row>
@@ -2398,39 +2438,39 @@
         <v>98</v>
       </c>
       <c r="K18" s="24">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B18,J18),2)</f>
         <v>0.6</v>
       </c>
       <c r="L18" s="25">
-        <f t="shared" si="1"/>
+        <f>E18/J18</f>
         <v>2.0408163265306121E-2</v>
       </c>
       <c r="M18" s="25">
-        <f t="shared" si="2"/>
+        <f>D18/J18</f>
         <v>0.18367346938775511</v>
       </c>
       <c r="N18" s="24">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F18,J18),2)</f>
         <v>0.72</v>
       </c>
       <c r="O18" s="24">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G18,J18),2)</f>
         <v>3.39</v>
       </c>
       <c r="P18" s="24">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H18,J18),2)</f>
         <v>0.14000000000000001</v>
       </c>
       <c r="Q18" s="24">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B18,F18),2)</f>
         <v>0.83</v>
       </c>
       <c r="R18" s="24">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C18,B18),4)*100</f>
         <v>61.019999999999996</v>
       </c>
       <c r="S18" s="24">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I18,J18),2)</f>
         <v>80.88</v>
       </c>
       <c r="T18" s="24" t="s">
@@ -2440,7 +2480,7 @@
         <v>24</v>
       </c>
       <c r="V18" s="45">
-        <f t="shared" si="9"/>
+        <f>((K18/2.5)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
         <v>0.95318604651162786</v>
       </c>
     </row>
@@ -2476,39 +2516,39 @@
         <v>82</v>
       </c>
       <c r="K19" s="24">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B19,J19),2)</f>
         <v>0.35</v>
       </c>
       <c r="L19" s="25">
-        <f t="shared" si="1"/>
+        <f>E19/J19</f>
         <v>2.4390243902439025E-2</v>
       </c>
       <c r="M19" s="25">
-        <f t="shared" si="2"/>
+        <f>D19/J19</f>
         <v>7.3170731707317069E-2</v>
       </c>
       <c r="N19" s="24">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F19,J19),2)</f>
         <v>0.71</v>
       </c>
       <c r="O19" s="24">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G19,J19),2)</f>
         <v>1.38</v>
       </c>
       <c r="P19" s="24">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H19,J19),2)</f>
         <v>0.11</v>
       </c>
       <c r="Q19" s="24">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B19,F19),2)</f>
         <v>0.5</v>
       </c>
       <c r="R19" s="24">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C19,B19),4)*100</f>
         <v>48.28</v>
       </c>
       <c r="S19" s="24">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I19,J19),2)</f>
         <v>43.57</v>
       </c>
       <c r="T19" s="24" t="s">
@@ -2518,7 +2558,7 @@
         <v>24</v>
       </c>
       <c r="V19" s="45">
-        <f t="shared" si="9"/>
+        <f>((K19/2.5)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
         <v>0.66132189449801471</v>
       </c>
     </row>
@@ -2554,39 +2594,39 @@
         <v>112</v>
       </c>
       <c r="K20" s="15">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B20,J20),2)</f>
         <v>0.62</v>
       </c>
       <c r="L20" s="17">
-        <f t="shared" si="1"/>
+        <f>E20/J20</f>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="M20" s="17">
-        <f t="shared" si="2"/>
+        <f>D20/J20</f>
         <v>0.11607142857142858</v>
       </c>
       <c r="N20" s="15">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F20,J20),2)</f>
         <v>0.65</v>
       </c>
       <c r="O20" s="15">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G20,J20),2)</f>
         <v>1.5</v>
       </c>
       <c r="P20" s="15">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H20,J20),2)</f>
         <v>0.25</v>
       </c>
       <c r="Q20" s="15">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B20,F20),2)</f>
         <v>0.95</v>
       </c>
       <c r="R20" s="15">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C20,B20),4)*100</f>
         <v>66.67</v>
       </c>
       <c r="S20" s="15">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I20,J20),2)</f>
         <v>70.709999999999994</v>
       </c>
       <c r="T20" s="16" t="s">
@@ -2596,7 +2636,7 @@
         <v>24</v>
       </c>
       <c r="V20" s="45">
-        <f t="shared" si="9"/>
+        <f>((K20/2.5)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
         <v>0.9755444352159468</v>
       </c>
     </row>
@@ -2632,39 +2672,39 @@
         <v>101</v>
       </c>
       <c r="K21" s="15">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B21,J21),2)</f>
         <v>0.46</v>
       </c>
       <c r="L21" s="17">
-        <f t="shared" si="1"/>
+        <f>E21/J21</f>
         <v>9.9009900990099011E-3</v>
       </c>
       <c r="M21" s="17">
-        <f t="shared" si="2"/>
+        <f>D21/J21</f>
         <v>6.9306930693069313E-2</v>
       </c>
       <c r="N21" s="15">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F21,J21),2)</f>
         <v>0.71</v>
       </c>
       <c r="O21" s="15">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G21,J21),2)</f>
         <v>1.58</v>
       </c>
       <c r="P21" s="15">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H21,J21),2)</f>
         <v>0.15</v>
       </c>
       <c r="Q21" s="15">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B21,F21),2)</f>
         <v>0.64</v>
       </c>
       <c r="R21" s="15">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C21,B21),4)*100</f>
         <v>47.83</v>
       </c>
       <c r="S21" s="15">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I21,J21),2)</f>
         <v>51.29</v>
       </c>
       <c r="T21" s="16" t="s">
@@ -2674,7 +2714,7 @@
         <v>24</v>
       </c>
       <c r="V21" s="45">
-        <f t="shared" si="9"/>
+        <f>((K21/2.5)+(M21/4)+(L21/5)-(N21)+(S21/215)+(P21/20))+1</f>
         <v>0.73936507022795306</v>
       </c>
     </row>
@@ -2710,39 +2750,39 @@
         <v>16</v>
       </c>
       <c r="K22" s="48">
-        <f t="shared" si="0"/>
+        <f>ROUND(IMDIV(B22,J22),2)</f>
         <v>0.19</v>
       </c>
       <c r="L22" s="49">
-        <f t="shared" si="1"/>
+        <f>E22/J22</f>
         <v>6.25E-2</v>
       </c>
       <c r="M22" s="49">
-        <f t="shared" si="2"/>
+        <f>D22/J22</f>
         <v>6.25E-2</v>
       </c>
       <c r="N22" s="48">
-        <f t="shared" si="3"/>
+        <f>ROUND(IMDIV(F22,J22),2)</f>
         <v>0.75</v>
       </c>
       <c r="O22" s="48">
-        <f t="shared" si="4"/>
+        <f>ROUND(IMDIV(G22,J22),2)</f>
         <v>2.69</v>
       </c>
       <c r="P22" s="48">
-        <f t="shared" si="5"/>
+        <f>ROUND(IMDIV(H22,J22),2)</f>
         <v>0</v>
       </c>
       <c r="Q22" s="48">
-        <f t="shared" si="6"/>
+        <f>ROUND(IMDIV(B22,F22),2)</f>
         <v>0.25</v>
       </c>
       <c r="R22" s="48">
-        <f t="shared" si="7"/>
+        <f>ROUND(IMDIV(C22,B22),4)*100</f>
         <v>66.67</v>
       </c>
       <c r="S22" s="48">
-        <f t="shared" si="8"/>
+        <f>ROUND(IMDIV(I22,J22),2)</f>
         <v>27</v>
       </c>
       <c r="T22" s="47" t="s">
@@ -2752,13 +2792,13 @@
         <v>24</v>
       </c>
       <c r="V22" s="45">
-        <f t="shared" si="9"/>
+        <f>((K22/2.5)+(M22/4)+(L22/5)-(N22)+(S22/215)+(P22/20))+1</f>
         <v>0.47970639534883719</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
-    <sortCondition sortBy="cellColor" ref="A22" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="A22" dxfId="0"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3692,8 +3732,8 @@
       <c r="T12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="22" t="s">
-        <v>24</v>
+      <c r="U12" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="V12" s="45">
         <f t="shared" si="9"/>
@@ -4577,39 +4617,39 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6" t="e">
-        <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <f t="shared" ref="K2:K13" si="0">ROUND(IMDIV(B2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="L2" s="7" t="e">
-        <f t="shared" ref="L2:L22" si="1">E2/J2</f>
+        <f t="shared" ref="L2:L13" si="1">E2/J2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M2" s="7" t="e">
-        <f t="shared" ref="M2:M22" si="2">D2/J2</f>
+        <f t="shared" ref="M2:M13" si="2">D2/J2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N2" s="6" t="e">
-        <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <f t="shared" ref="N2:N13" si="3">ROUND(IMDIV(F2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="O2" s="6" t="e">
-        <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <f t="shared" ref="O2:O13" si="4">ROUND(IMDIV(G2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="P2" s="6" t="e">
-        <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <f t="shared" ref="P2:P13" si="5">ROUND(IMDIV(H2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="Q2" s="6" t="e">
-        <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <f t="shared" ref="Q2:Q13" si="6">ROUND(IMDIV(B2,F2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="R2" s="6" t="e">
-        <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <f t="shared" ref="R2:R13" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
         <v>#NUM!</v>
       </c>
       <c r="S2" s="6" t="e">
-        <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <f t="shared" ref="S2:S13" si="8">ROUND(IMDIV(I2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -4619,7 +4659,7 @@
         <v>24</v>
       </c>
       <c r="V2" s="45" t="e">
-        <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <f t="shared" ref="V2:V13" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
         <v>#NUM!</v>
       </c>
     </row>
@@ -5269,8 +5309,8 @@
       <c r="T12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="22" t="s">
-        <v>24</v>
+      <c r="U12" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="V12" s="45">
         <f t="shared" si="9"/>
@@ -5357,219 +5397,218 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="52"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="56"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="55"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="52"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="53"/>
-      <c r="U15" s="53"/>
-      <c r="V15" s="56"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="55"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="59"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="56"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="55"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="56"/>
+      <c r="A17" s="56"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="55"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="56"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="55"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="56"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="55"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="56"/>
+      <c r="A20" s="60"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="55"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="56"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="55"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="63"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="56"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5578,7 +5617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C7BC6-1079-408F-93C8-005DF99ABE1B}">
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -5589,7 +5628,7 @@
     <col min="26" max="27" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5657,7 +5696,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
         <v>31</v>
       </c>
@@ -5689,39 +5728,39 @@
         <v>44</v>
       </c>
       <c r="K2" s="9">
-        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <f t="shared" ref="K2:K9" si="0">ROUND(IMDIV(B2,J2),2)</f>
         <v>0.77</v>
       </c>
       <c r="L2" s="11">
-        <f>E2/J2</f>
+        <f t="shared" ref="L2:L9" si="1">E2/J2</f>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="M2" s="11">
-        <f>D2/J2</f>
+        <f t="shared" ref="M2:M9" si="2">D2/J2</f>
         <v>0.25</v>
       </c>
       <c r="N2" s="9">
-        <f>ROUND(IMDIV(F2,J2),2)</f>
+        <f t="shared" ref="N2:N9" si="3">ROUND(IMDIV(F2,J2),2)</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="O2" s="9">
-        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <f t="shared" ref="O2:O9" si="4">ROUND(IMDIV(G2,J2),2)</f>
         <v>7.8</v>
       </c>
       <c r="P2" s="9">
-        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <f t="shared" ref="P2:P9" si="5">ROUND(IMDIV(H2,J2),2)</f>
         <v>0.27</v>
       </c>
       <c r="Q2" s="9">
-        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <f t="shared" ref="Q2:Q9" si="6">ROUND(IMDIV(B2,F2),2)</f>
         <v>1.36</v>
       </c>
       <c r="R2" s="9">
-        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <f t="shared" ref="R2:R9" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
         <v>41.18</v>
       </c>
       <c r="S2" s="9">
-        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <f t="shared" ref="S2:S9" si="8">ROUND(IMDIV(I2,J2),2)</f>
         <v>76.8</v>
       </c>
       <c r="T2" s="9" t="s">
@@ -5731,11 +5770,11 @@
         <v>24</v>
       </c>
       <c r="V2" s="45">
-        <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <f t="shared" ref="V2:V9" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
         <v>1.1848456659619451</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
         <v>32</v>
       </c>
@@ -5767,39 +5806,39 @@
         <v>44</v>
       </c>
       <c r="K3" s="9">
-        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <f t="shared" si="0"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="L3" s="11">
-        <f>E3/J3</f>
+        <f t="shared" si="1"/>
         <v>4.5454545454545456E-2</v>
       </c>
       <c r="M3" s="11">
-        <f>D3/J3</f>
+        <f t="shared" si="2"/>
         <v>0.15909090909090909</v>
       </c>
       <c r="N3" s="9">
-        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <f t="shared" si="3"/>
         <v>0.61</v>
       </c>
       <c r="O3" s="9">
-        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <f t="shared" si="4"/>
         <v>7.27</v>
       </c>
       <c r="P3" s="9">
-        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
       <c r="Q3" s="9">
-        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <f t="shared" si="6"/>
         <v>0.93</v>
       </c>
       <c r="R3" s="9">
-        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="S3" s="9">
-        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <f t="shared" si="8"/>
         <v>78.930000000000007</v>
       </c>
       <c r="T3" s="9" t="s">
@@ -5809,11 +5848,11 @@
         <v>24</v>
       </c>
       <c r="V3" s="45">
-        <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.0394799154334038</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>34</v>
       </c>
@@ -5845,53 +5884,53 @@
         <v>44</v>
       </c>
       <c r="K4" s="20">
-        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <f t="shared" si="0"/>
         <v>0.84</v>
       </c>
       <c r="L4" s="21">
-        <f>E4/J4</f>
+        <f t="shared" si="1"/>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="M4" s="21">
-        <f>D4/J4</f>
+        <f t="shared" si="2"/>
         <v>0.20454545454545456</v>
       </c>
       <c r="N4" s="20">
-        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <f t="shared" si="3"/>
         <v>0.66</v>
       </c>
       <c r="O4" s="20">
-        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <f t="shared" si="4"/>
         <v>4.05</v>
       </c>
       <c r="P4" s="20">
-        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="Q4" s="20">
-        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <f t="shared" si="6"/>
         <v>1.28</v>
       </c>
       <c r="R4" s="20">
-        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <f t="shared" si="7"/>
         <v>70.27</v>
       </c>
       <c r="S4" s="20">
-        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <f t="shared" si="8"/>
         <v>80.86</v>
       </c>
       <c r="T4" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="22" t="s">
-        <v>24</v>
+      <c r="U4" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="V4" s="45">
-        <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.129365750528541</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
         <v>35</v>
       </c>
@@ -5923,39 +5962,39 @@
         <v>44</v>
       </c>
       <c r="K5" s="20">
-        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="L5" s="21">
-        <f>E5/J5</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M5" s="21">
-        <f>D5/J5</f>
+        <f t="shared" si="2"/>
         <v>2.2727272727272728E-2</v>
       </c>
       <c r="N5" s="20">
-        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
       <c r="O5" s="20">
-        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <f t="shared" si="4"/>
         <v>4.07</v>
       </c>
       <c r="P5" s="20">
-        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="Q5" s="20">
-        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="R5" s="20">
-        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <f t="shared" si="7"/>
         <v>46.67</v>
       </c>
       <c r="S5" s="20">
-        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <f t="shared" si="8"/>
         <v>57.2</v>
       </c>
       <c r="T5" s="20" t="s">
@@ -5965,11 +6004,11 @@
         <v>24</v>
       </c>
       <c r="V5" s="45">
-        <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.73772832980972503</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
         <v>37</v>
       </c>
@@ -5983,39 +6022,39 @@
       <c r="I6" s="26"/>
       <c r="J6" s="26"/>
       <c r="K6" s="27" t="e">
-        <f>ROUND(IMDIV(B6,J6),2)</f>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L6" s="28" t="e">
-        <f>E6/J6</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M6" s="28" t="e">
-        <f>D6/J6</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N6" s="27" t="e">
-        <f>ROUND(IMDIV(F6,J6),2)</f>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O6" s="27" t="e">
-        <f>ROUND(IMDIV(G6,J6),2)</f>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P6" s="27" t="e">
-        <f>ROUND(IMDIV(H6,J6),2)</f>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q6" s="27" t="e">
-        <f>ROUND(IMDIV(B6,F6),2)</f>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R6" s="27" t="e">
-        <f>ROUND(IMDIV(C6,B6),4)*100</f>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S6" s="27" t="e">
-        <f>ROUND(IMDIV(I6,J6),2)</f>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T6" s="26" t="s">
@@ -6025,11 +6064,11 @@
         <v>24</v>
       </c>
       <c r="V6" s="45" t="e">
-        <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>38</v>
       </c>
@@ -6043,39 +6082,39 @@
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
       <c r="K7" s="27" t="e">
-        <f>ROUND(IMDIV(B7,J7),2)</f>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L7" s="28" t="e">
-        <f>E7/J7</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M7" s="28" t="e">
-        <f>D7/J7</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N7" s="27" t="e">
-        <f>ROUND(IMDIV(F7,J7),2)</f>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O7" s="27" t="e">
-        <f>ROUND(IMDIV(G7,J7),2)</f>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P7" s="27" t="e">
-        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q7" s="27" t="e">
-        <f>ROUND(IMDIV(B7,F7),2)</f>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R7" s="27" t="e">
-        <f>ROUND(IMDIV(C7,B7),4)*100</f>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S7" s="27" t="e">
-        <f>ROUND(IMDIV(I7,J7),2)</f>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T7" s="26" t="s">
@@ -6085,11 +6124,11 @@
         <v>24</v>
       </c>
       <c r="V7" s="45" t="e">
-        <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>29</v>
       </c>
@@ -6103,39 +6142,39 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="12" t="e">
-        <f>ROUND(IMDIV(B8,J8),2)</f>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L8" s="13" t="e">
-        <f>E8/J8</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M8" s="13" t="e">
-        <f>D8/J8</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N8" s="12" t="e">
-        <f>ROUND(IMDIV(F8,J8),2)</f>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O8" s="12" t="e">
-        <f>ROUND(IMDIV(G8,J8),2)</f>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P8" s="12" t="e">
-        <f>ROUND(IMDIV(H8,J8),2)</f>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q8" s="12" t="e">
-        <f>ROUND(IMDIV(B8,F8),2)</f>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R8" s="12" t="e">
-        <f>ROUND(IMDIV(C8,B8),4)*100</f>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S8" s="12" t="e">
-        <f>ROUND(IMDIV(I8,J8),2)</f>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T8" s="51" t="s">
@@ -6145,12 +6184,11 @@
         <v>24</v>
       </c>
       <c r="V8" s="45" t="e">
-        <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA8" s="63"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
         <v>30</v>
       </c>
@@ -6164,39 +6202,39 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12" t="e">
-        <f>ROUND(IMDIV(B9,J9),2)</f>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L9" s="13" t="e">
-        <f>E9/J9</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M9" s="13" t="e">
-        <f>D9/J9</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N9" s="12" t="e">
-        <f>ROUND(IMDIV(F9,J9),2)</f>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O9" s="12" t="e">
-        <f>ROUND(IMDIV(G9,J9),2)</f>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P9" s="12" t="e">
-        <f>ROUND(IMDIV(H9,J9),2)</f>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q9" s="12" t="e">
-        <f>ROUND(IMDIV(B9,F9),2)</f>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R9" s="12" t="e">
-        <f>ROUND(IMDIV(C9,B9),4)*100</f>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S9" s="12" t="e">
-        <f>ROUND(IMDIV(I9,J9),2)</f>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T9" s="51" t="s">
@@ -6206,491 +6244,491 @@
         <v>24</v>
       </c>
       <c r="V9" s="45" t="e">
-        <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="56"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="55"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="65" t="s">
+      <c r="F11" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="65" t="s">
+      <c r="G11" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="65" t="s">
+      <c r="H11" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="65" t="s">
+      <c r="I11" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="67" t="s">
+      <c r="J11" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="67" t="s">
+      <c r="K11" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="L11" s="67" t="s">
+      <c r="L11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="67" t="s">
+      <c r="M11" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="53"/>
-      <c r="U11" s="53"/>
-      <c r="V11" s="56"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="68" t="s">
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="53"/>
+      <c r="Q11" s="53"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="55"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="67">
         <v>76.8</v>
       </c>
-      <c r="E12" s="71">
+      <c r="E12" s="68">
         <v>1.1848456659619451</v>
       </c>
-      <c r="F12" s="70">
+      <c r="F12" s="67">
         <v>0.77</v>
       </c>
-      <c r="G12" s="70">
+      <c r="G12" s="67">
         <v>3</v>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="67">
         <v>11</v>
       </c>
-      <c r="I12" s="70">
+      <c r="I12" s="67">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J12" s="70">
+      <c r="J12" s="67">
         <v>343</v>
       </c>
-      <c r="K12" s="70">
+      <c r="K12" s="67">
         <v>0.27</v>
       </c>
-      <c r="L12" s="70">
+      <c r="L12" s="67">
         <v>1.36</v>
       </c>
-      <c r="M12" s="70">
+      <c r="M12" s="67">
         <v>41.18</v>
       </c>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="56"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="68" t="s">
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="57"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="57"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="57"/>
+      <c r="V12" s="55"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="72">
+      <c r="C13" s="69">
         <v>-2</v>
       </c>
-      <c r="D13" s="70">
+      <c r="D13" s="67">
         <v>78.930000000000007</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="68">
         <v>1.0394799154334038</v>
       </c>
-      <c r="F13" s="70">
+      <c r="F13" s="67">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G13" s="70">
+      <c r="G13" s="67">
         <v>2</v>
       </c>
-      <c r="H13" s="70">
+      <c r="H13" s="67">
         <v>7</v>
       </c>
-      <c r="I13" s="70">
+      <c r="I13" s="67">
         <v>0.61</v>
       </c>
-      <c r="J13" s="70">
+      <c r="J13" s="67">
         <v>320</v>
       </c>
-      <c r="K13" s="70">
+      <c r="K13" s="67">
         <v>0.11</v>
       </c>
-      <c r="L13" s="70">
+      <c r="L13" s="67">
         <v>0.93</v>
       </c>
-      <c r="M13" s="70">
+      <c r="M13" s="67">
         <v>36</v>
       </c>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="56"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="74" t="s">
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
+      <c r="V13" s="55"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="58"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="58"/>
-      <c r="V14" s="56"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="68" t="s">
+      <c r="B14" s="73"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="55"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="70">
+      <c r="D15" s="67">
         <v>80.86</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="68">
         <v>1.129365750528541</v>
       </c>
-      <c r="F15" s="70">
+      <c r="F15" s="67">
         <v>0.84</v>
       </c>
-      <c r="G15" s="75">
+      <c r="G15" s="72">
         <v>3</v>
       </c>
-      <c r="H15" s="75">
+      <c r="H15" s="72">
         <v>9</v>
       </c>
-      <c r="I15" s="70">
+      <c r="I15" s="67">
         <v>0.66</v>
       </c>
-      <c r="J15" s="75">
+      <c r="J15" s="72">
         <v>178</v>
       </c>
-      <c r="K15" s="70">
+      <c r="K15" s="67">
         <v>0.25</v>
       </c>
-      <c r="L15" s="70">
+      <c r="L15" s="67">
         <v>1.28</v>
       </c>
-      <c r="M15" s="70">
+      <c r="M15" s="67">
         <v>70.27</v>
       </c>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="58"/>
-      <c r="V15" s="56"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="57"/>
+      <c r="V15" s="55"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="65" t="s">
+      <c r="B16" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="69">
         <v>-15</v>
       </c>
-      <c r="D16" s="70">
+      <c r="D16" s="67">
         <v>57.2</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="68">
         <v>0.73772832980972503</v>
       </c>
-      <c r="F16" s="70">
+      <c r="F16" s="67">
         <v>0.34</v>
       </c>
-      <c r="G16" s="75">
+      <c r="G16" s="72">
         <v>0</v>
       </c>
-      <c r="H16" s="75">
+      <c r="H16" s="72">
         <v>1</v>
       </c>
-      <c r="I16" s="70">
+      <c r="I16" s="67">
         <v>0.68</v>
       </c>
-      <c r="J16" s="75">
+      <c r="J16" s="72">
         <v>179</v>
       </c>
-      <c r="K16" s="70">
+      <c r="K16" s="67">
         <v>0.2</v>
       </c>
-      <c r="L16" s="70">
+      <c r="L16" s="67">
         <v>0.5</v>
       </c>
-      <c r="M16" s="70">
+      <c r="M16" s="67">
         <v>46.67</v>
       </c>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="62"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="56"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="61"/>
+      <c r="U16" s="61"/>
+      <c r="V16" s="55"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="62"/>
-      <c r="U17" s="62"/>
-      <c r="V17" s="56"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="61"/>
+      <c r="V17" s="55"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="54"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="54"/>
-      <c r="R18" s="54"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="53"/>
-      <c r="U18" s="53"/>
-      <c r="V18" s="56"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="55"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="65" t="s">
+      <c r="B19" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="65" t="s">
+      <c r="E19" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="65" t="s">
+      <c r="F19" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="65" t="s">
+      <c r="G19" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="65" t="s">
+      <c r="H19" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="65" t="s">
+      <c r="I19" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="67" t="s">
+      <c r="J19" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="K19" s="67" t="s">
+      <c r="K19" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="L19" s="67" t="s">
+      <c r="L19" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="M19" s="67" t="s">
+      <c r="M19" s="64" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="65"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="70"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="65"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="70"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="68"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="70"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="68" t="s">
+      <c r="A24" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="65"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="70"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V9">
-    <sortCondition sortBy="cellColor" ref="A5:A9" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="A5:A9" dxfId="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6698,7 +6736,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40897AC2-0114-4A6D-BFFC-5EDF88F8CE8F}">
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -7028,39 +7066,39 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9" t="e">
-        <f t="shared" ref="K6:K13" si="10">ROUND(IMDIV(B6,J6),2)</f>
+        <f t="shared" ref="K6:K11" si="10">ROUND(IMDIV(B6,J6),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="L6" s="11" t="e">
-        <f t="shared" ref="L6:L13" si="11">E6/J6</f>
+        <f t="shared" ref="L6:L11" si="11">E6/J6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M6" s="11" t="e">
-        <f t="shared" ref="M6:M13" si="12">D6/J6</f>
+        <f t="shared" ref="M6:M11" si="12">D6/J6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N6" s="9" t="e">
-        <f t="shared" ref="N6:N13" si="13">ROUND(IMDIV(F6,J6),2)</f>
+        <f t="shared" ref="N6:N11" si="13">ROUND(IMDIV(F6,J6),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="O6" s="9" t="e">
-        <f t="shared" ref="O6:O13" si="14">ROUND(IMDIV(G6,J6),2)</f>
+        <f t="shared" ref="O6:O11" si="14">ROUND(IMDIV(G6,J6),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="P6" s="9" t="e">
-        <f t="shared" ref="P6:P13" si="15">ROUND(IMDIV(H6,J6),2)</f>
+        <f t="shared" ref="P6:P11" si="15">ROUND(IMDIV(H6,J6),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="Q6" s="9" t="e">
-        <f t="shared" ref="Q6:Q13" si="16">ROUND(IMDIV(B6,F6),2)</f>
+        <f t="shared" ref="Q6:Q11" si="16">ROUND(IMDIV(B6,F6),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="R6" s="9" t="e">
-        <f t="shared" ref="R6:R13" si="17">ROUND(IMDIV(C6,B6),4)*100</f>
+        <f t="shared" ref="R6:R11" si="17">ROUND(IMDIV(C6,B6),4)*100</f>
         <v>#NUM!</v>
       </c>
       <c r="S6" s="9" t="e">
-        <f t="shared" ref="S6:S13" si="18">ROUND(IMDIV(I6,J6),2)</f>
+        <f t="shared" ref="S6:S11" si="18">ROUND(IMDIV(I6,J6),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="T6" s="9" t="s">
@@ -7070,7 +7108,7 @@
         <v>24</v>
       </c>
       <c r="V6" s="45" t="e">
-        <f t="shared" ref="V6:V13" si="19">((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
+        <f t="shared" ref="V6:V11" si="19">((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
         <v>#NUM!</v>
       </c>
     </row>
@@ -7375,268 +7413,416 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="62"/>
-      <c r="V12" s="56"/>
+      <c r="A12" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
+      <c r="U12" s="61"/>
+      <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="56"/>
+      <c r="A13" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="61"/>
+      <c r="V13" s="55"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="56"/>
+      <c r="A14" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="62"/>
+      <c r="C14" s="66">
+        <v>0</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="55"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="53"/>
-      <c r="U15" s="53"/>
-      <c r="V15" s="56"/>
+      <c r="A15" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="69">
+        <v>0</v>
+      </c>
+      <c r="D15" s="67"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="55"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="59"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="56"/>
+      <c r="A16" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="73"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="55"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="56"/>
+      <c r="A17" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="66">
+        <v>0</v>
+      </c>
+      <c r="D17" s="67"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="55"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="56"/>
+      <c r="A18" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="62"/>
+      <c r="C18" s="69">
+        <v>0</v>
+      </c>
+      <c r="D18" s="67"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="55"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="56"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="55"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="56"/>
+      <c r="A20" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="55"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="56"/>
+      <c r="A21" s="78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="55"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="63"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="56"/>
+      <c r="A22" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="62"/>
+      <c r="C22" s="66">
+        <v>0</v>
+      </c>
+      <c r="D22" s="67"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="55"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="62"/>
+      <c r="C23" s="69">
+        <v>0</v>
+      </c>
+      <c r="D23" s="67"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="73"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="65"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="66">
+        <v>0</v>
+      </c>
+      <c r="D25" s="67"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="65"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="69">
+        <v>0</v>
+      </c>
+      <c r="D26" s="67"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8322,268 +8508,305 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="62"/>
-      <c r="V12" s="56"/>
+      <c r="A12" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
+      <c r="U12" s="61"/>
+      <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="56"/>
+      <c r="A13" s="77" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="61"/>
+      <c r="V13" s="55"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="56"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="66">
+        <v>0</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="55"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="53"/>
-      <c r="U15" s="53"/>
-      <c r="V15" s="56"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="69">
+        <v>0</v>
+      </c>
+      <c r="D15" s="67"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="55"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="59"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="56"/>
+      <c r="A16" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="73"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="55"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="56"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="66">
+        <v>0</v>
+      </c>
+      <c r="D17" s="67"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="55"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="56"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="69">
+        <v>0</v>
+      </c>
+      <c r="D18" s="67"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="55"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="56"/>
+      <c r="A19" s="56"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="55"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="54"/>
-      <c r="R20" s="54"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="56"/>
+      <c r="A20" s="60"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="55"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="56"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="55"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="63"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="56"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2BF150-050C-4390-B7C6-4ACAFFA45930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0AC5F5-0CB7-4D6C-9496-A8F81398CEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tourney" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="72">
   <si>
     <t>player</t>
   </si>
@@ -235,9 +235,6 @@
     <t>CHUDS</t>
   </si>
   <si>
-    <t>JS/SP</t>
-  </si>
-  <si>
     <t>Burger</t>
   </si>
   <si>
@@ -248,6 +245,18 @@
   </si>
   <si>
     <t>EVP</t>
+  </si>
+  <si>
+    <t>30-13</t>
+  </si>
+  <si>
+    <t>17-18</t>
+  </si>
+  <si>
+    <t>21-22</t>
+  </si>
+  <si>
+    <t>10-25</t>
   </si>
 </sst>
 </file>
@@ -485,7 +494,7 @@
     <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -715,6 +724,12 @@
     <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -725,7 +740,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
+          <fgColor rgb="FF4EA72E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -733,7 +748,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF4EA72E"/>
+          <fgColor rgb="FFF3A602"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1083,14 +1098,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C412513A-E0D1-405F-B780-5234AC262E79}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1158,7 +1173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>28</v>
       </c>
@@ -1190,39 +1205,39 @@
         <v>118</v>
       </c>
       <c r="K2" s="6">
-        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
         <v>0.95</v>
       </c>
       <c r="L2" s="7">
-        <f>E2/J2</f>
+        <f t="shared" ref="L2:L22" si="1">E2/J2</f>
         <v>6.7796610169491525E-2</v>
       </c>
       <c r="M2" s="7">
-        <f>D2/J2</f>
+        <f t="shared" ref="M2:M22" si="2">D2/J2</f>
         <v>0.2711864406779661</v>
       </c>
       <c r="N2" s="6">
-        <f>ROUND(IMDIV(F2,J2),2)</f>
+        <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
         <v>0.47</v>
       </c>
       <c r="O2" s="6">
-        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
         <v>5.66</v>
       </c>
       <c r="P2" s="6">
-        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
         <v>0.26</v>
       </c>
       <c r="Q2" s="6">
-        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
         <v>2.04</v>
       </c>
       <c r="R2" s="6">
-        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
         <v>65.180000000000007</v>
       </c>
       <c r="S2" s="6">
-        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
         <v>102.54</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -1232,11 +1247,11 @@
         <v>24</v>
       </c>
       <c r="V2" s="45">
-        <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
         <v>1.4812861647615294</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
         <v>27</v>
       </c>
@@ -1268,39 +1283,39 @@
         <v>118</v>
       </c>
       <c r="K3" s="6">
-        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <f t="shared" si="0"/>
         <v>0.48</v>
       </c>
       <c r="L3" s="7">
-        <f>E3/J3</f>
+        <f t="shared" si="1"/>
         <v>1.6949152542372881E-2</v>
       </c>
       <c r="M3" s="7">
-        <f>D3/J3</f>
+        <f t="shared" si="2"/>
         <v>8.4745762711864403E-2</v>
       </c>
       <c r="N3" s="6">
-        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <f t="shared" si="3"/>
         <v>0.61</v>
       </c>
       <c r="O3" s="6">
-        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <f t="shared" si="4"/>
         <v>0.35</v>
       </c>
       <c r="P3" s="6">
-        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
       <c r="Q3" s="6">
-        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <f t="shared" si="6"/>
         <v>0.79</v>
       </c>
       <c r="R3" s="6">
-        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <f t="shared" si="7"/>
         <v>50.88</v>
       </c>
       <c r="S3" s="6">
-        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <f t="shared" si="8"/>
         <v>51.84</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -1310,11 +1325,11 @@
         <v>24</v>
       </c>
       <c r="V3" s="45">
-        <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.85369255025620816</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="43" t="s">
         <v>39</v>
       </c>
@@ -1346,39 +1361,39 @@
         <v>122</v>
       </c>
       <c r="K4" s="30">
-        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <f t="shared" si="0"/>
         <v>0.89</v>
       </c>
       <c r="L4" s="31">
-        <f>E4/J4</f>
+        <f t="shared" si="1"/>
         <v>8.1967213114754092E-2</v>
       </c>
       <c r="M4" s="31">
-        <f>D4/J4</f>
+        <f t="shared" si="2"/>
         <v>0.28688524590163933</v>
       </c>
       <c r="N4" s="30">
-        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <f t="shared" si="3"/>
         <v>0.49</v>
       </c>
       <c r="O4" s="30">
-        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <f t="shared" si="4"/>
         <v>6.51</v>
       </c>
       <c r="P4" s="30">
-        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
       <c r="Q4" s="30">
-        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <f t="shared" si="6"/>
         <v>1.8</v>
       </c>
       <c r="R4" s="30">
-        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <f t="shared" si="7"/>
         <v>57.410000000000004</v>
       </c>
       <c r="S4" s="30">
-        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <f t="shared" si="8"/>
         <v>101.23</v>
       </c>
       <c r="T4" s="29" t="s">
@@ -1388,11 +1403,11 @@
         <v>24</v>
       </c>
       <c r="V4" s="45">
-        <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.4309519634006862</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="43" t="s">
         <v>40</v>
       </c>
@@ -1424,39 +1439,39 @@
         <v>122</v>
       </c>
       <c r="K5" s="30">
-        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <f t="shared" si="0"/>
         <v>0.41</v>
       </c>
       <c r="L5" s="31">
-        <f>E5/J5</f>
+        <f t="shared" si="1"/>
         <v>2.4590163934426229E-2</v>
       </c>
       <c r="M5" s="31">
-        <f>D5/J5</f>
+        <f t="shared" si="2"/>
         <v>4.9180327868852458E-2</v>
       </c>
       <c r="N5" s="30">
-        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <f t="shared" si="3"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="O5" s="30">
-        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <f t="shared" si="4"/>
         <v>1.91</v>
       </c>
       <c r="P5" s="30">
-        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="Q5" s="30">
-        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="R5" s="30">
-        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="S5" s="30">
-        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <f t="shared" si="8"/>
         <v>45.66</v>
       </c>
       <c r="T5" s="29" t="s">
@@ -1466,11 +1481,11 @@
         <v>24</v>
       </c>
       <c r="V5" s="45">
-        <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.85358520777735414</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="36" t="s">
         <v>31</v>
       </c>
@@ -1502,39 +1517,39 @@
         <v>192</v>
       </c>
       <c r="K6" s="9">
-        <f>ROUND(IMDIV(B6,J6),2)</f>
+        <f t="shared" si="0"/>
         <v>0.76</v>
       </c>
       <c r="L6" s="11">
-        <f>E6/J6</f>
+        <f t="shared" si="1"/>
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="M6" s="11">
-        <f>D6/J6</f>
+        <f t="shared" si="2"/>
         <v>0.20833333333333334</v>
       </c>
       <c r="N6" s="9">
-        <f>ROUND(IMDIV(F6,J6),2)</f>
+        <f t="shared" si="3"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="O6" s="9">
-        <f>ROUND(IMDIV(G6,J6),2)</f>
+        <f t="shared" si="4"/>
         <v>4.1100000000000003</v>
       </c>
       <c r="P6" s="9">
-        <f>ROUND(IMDIV(H6,J6),2)</f>
+        <f t="shared" si="5"/>
         <v>0.26</v>
       </c>
       <c r="Q6" s="9">
-        <f>ROUND(IMDIV(B6,F6),2)</f>
+        <f t="shared" si="6"/>
         <v>1.37</v>
       </c>
       <c r="R6" s="9">
-        <f>ROUND(IMDIV(C6,B6),4)*100</f>
+        <f t="shared" si="7"/>
         <v>47.589999999999996</v>
       </c>
       <c r="S6" s="9">
-        <f>ROUND(IMDIV(I6,J6),2)</f>
+        <f t="shared" si="8"/>
         <v>85.67</v>
       </c>
       <c r="T6" s="9" t="s">
@@ -1544,11 +1559,11 @@
         <v>24</v>
       </c>
       <c r="V6" s="45">
-        <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.2321317829457363</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="36" t="s">
         <v>32</v>
       </c>
@@ -1580,39 +1595,39 @@
         <v>192</v>
       </c>
       <c r="K7" s="9">
-        <f>ROUND(IMDIV(B7,J7),2)</f>
+        <f t="shared" si="0"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="L7" s="11">
-        <f>E7/J7</f>
+        <f t="shared" si="1"/>
         <v>5.2083333333333336E-2</v>
       </c>
       <c r="M7" s="11">
-        <f>D7/J7</f>
+        <f t="shared" si="2"/>
         <v>0.11979166666666667</v>
       </c>
       <c r="N7" s="9">
-        <f>ROUND(IMDIV(F7,J7),2)</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="O7" s="9">
-        <f>ROUND(IMDIV(G7,J7),2)</f>
+        <f t="shared" si="4"/>
         <v>5.56</v>
       </c>
       <c r="P7" s="9">
-        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <f t="shared" si="5"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="Q7" s="9">
-        <f>ROUND(IMDIV(B7,F7),2)</f>
+        <f t="shared" si="6"/>
         <v>0.93</v>
       </c>
       <c r="R7" s="9">
-        <f>ROUND(IMDIV(C7,B7),4)*100</f>
+        <f t="shared" si="7"/>
         <v>40.19</v>
       </c>
       <c r="S7" s="9">
-        <f>ROUND(IMDIV(I7,J7),2)</f>
+        <f t="shared" si="8"/>
         <v>63.52</v>
       </c>
       <c r="T7" s="9" t="s">
@@ -1622,232 +1637,232 @@
         <v>24</v>
       </c>
       <c r="V7" s="45">
-        <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.96680644379844971</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="42" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="26">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="C8" s="26">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D8" s="26">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E8" s="26">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F8" s="26">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G8" s="26">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="H8" s="26">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I8" s="26">
-        <v>11765</v>
+        <v>14847</v>
       </c>
       <c r="J8" s="26">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="K8" s="27">
-        <f>ROUND(IMDIV(B8,J8),2)</f>
-        <v>0.78</v>
+        <f t="shared" si="0"/>
+        <v>0.81</v>
       </c>
       <c r="L8" s="28">
-        <f>E8/J8</f>
-        <v>0.125</v>
+        <f t="shared" si="1"/>
+        <v>0.11904761904761904</v>
       </c>
       <c r="M8" s="28">
-        <f>D8/J8</f>
-        <v>0.15441176470588236</v>
+        <f t="shared" si="2"/>
+        <v>0.17261904761904762</v>
       </c>
       <c r="N8" s="27">
-        <f>ROUND(IMDIV(F8,J8),2)</f>
-        <v>0.52</v>
+        <f t="shared" si="3"/>
+        <v>0.5</v>
       </c>
       <c r="O8" s="27">
-        <f>ROUND(IMDIV(G8,J8),2)</f>
-        <v>2.21</v>
+        <f t="shared" si="4"/>
+        <v>1.98</v>
       </c>
       <c r="P8" s="27">
-        <f>ROUND(IMDIV(H8,J8),2)</f>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="5"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Q8" s="27">
-        <f>ROUND(IMDIV(B8,F8),2)</f>
-        <v>1.49</v>
+        <f t="shared" si="6"/>
+        <v>1.62</v>
       </c>
       <c r="R8" s="27">
-        <f>ROUND(IMDIV(C8,B8),4)*100</f>
-        <v>53.769999999999996</v>
+        <f t="shared" si="7"/>
+        <v>50</v>
       </c>
       <c r="S8" s="27">
-        <f>ROUND(IMDIV(I8,J8),2)</f>
-        <v>86.51</v>
+        <f t="shared" si="8"/>
+        <v>88.38</v>
       </c>
       <c r="T8" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U8" s="26" t="s">
         <v>24</v>
       </c>
       <c r="V8" s="45">
-        <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
-        <v>1.2719750341997265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>1.3165340531561462</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="42" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="26">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C9" s="26">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D9" s="26">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" s="26">
         <v>2</v>
       </c>
       <c r="F9" s="26">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G9" s="26">
-        <v>347</v>
+        <v>436</v>
       </c>
       <c r="H9" s="26">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="I9" s="26">
-        <v>7963</v>
+        <v>9979</v>
       </c>
       <c r="J9" s="26">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="K9" s="27">
-        <f>ROUND(IMDIV(B9,J9),2)</f>
-        <v>0.56000000000000005</v>
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L9" s="28">
-        <f>E9/J9</f>
-        <v>1.6E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.2738853503184714E-2</v>
       </c>
       <c r="M9" s="28">
-        <f>D9/J9</f>
-        <v>0.08</v>
+        <f t="shared" si="2"/>
+        <v>8.2802547770700632E-2</v>
       </c>
       <c r="N9" s="27">
-        <f>ROUND(IMDIV(F9,J9),2)</f>
-        <v>0.64</v>
+        <f t="shared" si="3"/>
+        <v>0.62</v>
       </c>
       <c r="O9" s="27">
-        <f>ROUND(IMDIV(G9,J9),2)</f>
+        <f t="shared" si="4"/>
         <v>2.78</v>
       </c>
       <c r="P9" s="27">
-        <f>ROUND(IMDIV(H9,J9),2)</f>
-        <v>0.3</v>
+        <f t="shared" si="5"/>
+        <v>0.34</v>
       </c>
       <c r="Q9" s="27">
-        <f>ROUND(IMDIV(B9,F9),2)</f>
-        <v>0.88</v>
+        <f t="shared" si="6"/>
+        <v>0.89</v>
       </c>
       <c r="R9" s="27">
-        <f>ROUND(IMDIV(C9,B9),4)*100</f>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>42.53</v>
       </c>
       <c r="S9" s="27">
-        <f>ROUND(IMDIV(I9,J9),2)</f>
-        <v>63.7</v>
+        <f t="shared" si="8"/>
+        <v>63.56</v>
       </c>
       <c r="T9" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="V9" s="45">
-        <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
-        <v>0.91847906976744187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0.93587631462005627</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="37" t="s">
         <v>29</v>
       </c>
       <c r="B10" s="12">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C10" s="12">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D10" s="12">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E10" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="12">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G10" s="12">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="H10" s="12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I10" s="12">
-        <v>11401</v>
+        <v>14021</v>
       </c>
       <c r="J10" s="12">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="K10" s="12">
-        <f>ROUND(IMDIV(B10,J10),2)</f>
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>0.77</v>
       </c>
       <c r="L10" s="13">
-        <f>E10/J10</f>
-        <v>5.1724137931034482E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.72972972972973E-2</v>
       </c>
       <c r="M10" s="13">
-        <f>D10/J10</f>
-        <v>0.19827586206896552</v>
+        <f t="shared" si="2"/>
+        <v>0.19594594594594594</v>
       </c>
       <c r="N10" s="12">
-        <f>ROUND(IMDIV(F10,J10),2)</f>
-        <v>0.52</v>
+        <f t="shared" si="3"/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O10" s="12">
-        <f>ROUND(IMDIV(G10,J10),2)</f>
-        <v>3.29</v>
+        <f t="shared" si="4"/>
+        <v>2.86</v>
       </c>
       <c r="P10" s="12">
-        <f>ROUND(IMDIV(H10,J10),2)</f>
+        <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
       <c r="Q10" s="12">
-        <f>ROUND(IMDIV(B10,F10),2)</f>
-        <v>1.55</v>
+        <f t="shared" si="6"/>
+        <v>1.39</v>
       </c>
       <c r="R10" s="12">
-        <f>ROUND(IMDIV(C10,B10),4)*100</f>
-        <v>45.16</v>
+        <f t="shared" si="7"/>
+        <v>45.61</v>
       </c>
       <c r="S10" s="12">
-        <f>ROUND(IMDIV(I10,J10),2)</f>
-        <v>98.28</v>
+        <f t="shared" si="8"/>
+        <v>94.74</v>
       </c>
       <c r="T10" s="51" t="s">
         <v>46</v>
@@ -1856,76 +1871,76 @@
         <v>24</v>
       </c>
       <c r="V10" s="45">
-        <f>((K10/2.5)+(M10/4)+(L10/5)-(N10)+(S10/215)+(P10/20))+1</f>
-        <v>1.3230300721732158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>1.2630971087366436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="37" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C11" s="12">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D11" s="12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="12">
         <v>3</v>
       </c>
       <c r="F11" s="12">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="G11" s="12">
         <v>145</v>
       </c>
       <c r="H11" s="12">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I11" s="12">
-        <v>6173</v>
+        <v>7557</v>
       </c>
       <c r="J11" s="12">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="K11" s="12">
-        <f>ROUND(IMDIV(B11,J11),2)</f>
-        <v>0.52</v>
+        <f t="shared" si="0"/>
+        <v>0.47</v>
       </c>
       <c r="L11" s="13">
-        <f>E11/J11</f>
-        <v>2.5862068965517241E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.0270270270270271E-2</v>
       </c>
       <c r="M11" s="13">
-        <f>D11/J11</f>
-        <v>7.7586206896551727E-2</v>
+        <f t="shared" si="2"/>
+        <v>7.4324324324324328E-2</v>
       </c>
       <c r="N11" s="12">
-        <f>ROUND(IMDIV(F11,J11),2)</f>
-        <v>0.56999999999999995</v>
+        <f t="shared" si="3"/>
+        <v>0.61</v>
       </c>
       <c r="O11" s="12">
-        <f>ROUND(IMDIV(G11,J11),2)</f>
-        <v>1.25</v>
+        <f t="shared" si="4"/>
+        <v>0.98</v>
       </c>
       <c r="P11" s="12">
-        <f>ROUND(IMDIV(H11,J11),2)</f>
+        <f t="shared" si="5"/>
         <v>0.16</v>
       </c>
       <c r="Q11" s="12">
-        <f>ROUND(IMDIV(B11,F11),2)</f>
-        <v>0.91</v>
+        <f t="shared" si="6"/>
+        <v>0.77</v>
       </c>
       <c r="R11" s="12">
-        <f>ROUND(IMDIV(C11,B11),4)*100</f>
-        <v>55.000000000000007</v>
+        <f t="shared" si="7"/>
+        <v>55.71</v>
       </c>
       <c r="S11" s="12">
-        <f>ROUND(IMDIV(I11,J11),2)</f>
-        <v>53.22</v>
+        <f t="shared" si="8"/>
+        <v>51.06</v>
       </c>
       <c r="T11" s="51" t="s">
         <v>46</v>
@@ -1934,11 +1949,11 @@
         <v>24</v>
       </c>
       <c r="V11" s="45">
-        <f>((K11/2.5)+(M11/4)+(L11/5)-(N11)+(S11/215)+(P11/20))+1</f>
-        <v>0.91810384923817168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0.84612350722815843</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="40" t="s">
         <v>34</v>
       </c>
@@ -1970,53 +1985,53 @@
         <v>181</v>
       </c>
       <c r="K12" s="20">
-        <f>ROUND(IMDIV(B12,J12),2)</f>
+        <f t="shared" si="0"/>
         <v>0.71</v>
       </c>
       <c r="L12" s="21">
-        <f>E12/J12</f>
+        <f t="shared" si="1"/>
         <v>6.6298342541436461E-2</v>
       </c>
       <c r="M12" s="21">
-        <f>D12/J12</f>
+        <f t="shared" si="2"/>
         <v>0.19889502762430938</v>
       </c>
       <c r="N12" s="20">
-        <f>ROUND(IMDIV(F12,J12),2)</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="O12" s="20">
-        <f>ROUND(IMDIV(G12,J12),2)</f>
+        <f t="shared" si="4"/>
         <v>4.9400000000000004</v>
       </c>
       <c r="P12" s="20">
-        <f>ROUND(IMDIV(H12,J12),2)</f>
+        <f t="shared" si="5"/>
         <v>0.23</v>
       </c>
       <c r="Q12" s="20">
-        <f>ROUND(IMDIV(B12,F12),2)</f>
+        <f t="shared" si="6"/>
         <v>1.19</v>
       </c>
       <c r="R12" s="20">
-        <f>ROUND(IMDIV(C12,B12),4)*100</f>
+        <f t="shared" si="7"/>
         <v>66.67</v>
       </c>
       <c r="S12" s="20">
-        <f>ROUND(IMDIV(I12,J12),2)</f>
+        <f t="shared" si="8"/>
         <v>78.489999999999995</v>
       </c>
       <c r="T12" s="20" t="s">
         <v>46</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V12" s="45">
-        <f>((K12/2.5)+(M12/4)+(L12/5)-(N12)+(S12/215)+(P12/20))+1</f>
+        <f t="shared" si="9"/>
         <v>1.123553192856225</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="40" t="s">
         <v>35</v>
       </c>
@@ -2048,39 +2063,39 @@
         <v>181</v>
       </c>
       <c r="K13" s="20">
-        <f>ROUND(IMDIV(B13,J13),2)</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="L13" s="21">
-        <f>E13/J13</f>
+        <f t="shared" si="1"/>
         <v>3.8674033149171269E-2</v>
       </c>
       <c r="M13" s="21">
-        <f>D13/J13</f>
+        <f t="shared" si="2"/>
         <v>0.1270718232044199</v>
       </c>
       <c r="N13" s="20">
-        <f>ROUND(IMDIV(F13,J13),2)</f>
+        <f t="shared" si="3"/>
         <v>0.62</v>
       </c>
       <c r="O13" s="20">
-        <f>ROUND(IMDIV(G13,J13),2)</f>
+        <f t="shared" si="4"/>
         <v>2.5099999999999998</v>
       </c>
       <c r="P13" s="20">
-        <f>ROUND(IMDIV(H13,J13),2)</f>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="Q13" s="20">
-        <f>ROUND(IMDIV(B13,F13),2)</f>
+        <f t="shared" si="6"/>
         <v>0.81</v>
       </c>
       <c r="R13" s="20">
-        <f>ROUND(IMDIV(C13,B13),4)*100</f>
+        <f t="shared" si="7"/>
         <v>46.150000000000006</v>
       </c>
       <c r="S13" s="20">
-        <f>ROUND(IMDIV(I13,J13),2)</f>
+        <f t="shared" si="8"/>
         <v>60.58</v>
       </c>
       <c r="T13" s="20" t="s">
@@ -2090,11 +2105,11 @@
         <v>24</v>
       </c>
       <c r="V13" s="45">
-        <f>((K13/2.5)+(M13/4)+(L13/5)-(N13)+(S13/215)+(P13/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.91377020429140432</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="44" t="s">
         <v>41</v>
       </c>
@@ -2126,39 +2141,39 @@
         <v>85</v>
       </c>
       <c r="K14" s="33">
-        <f>ROUND(IMDIV(B14,J14),2)</f>
+        <f t="shared" si="0"/>
         <v>0.53</v>
       </c>
       <c r="L14" s="34">
-        <f>E14/J14</f>
+        <f t="shared" si="1"/>
         <v>2.3529411764705882E-2</v>
       </c>
       <c r="M14" s="34">
-        <f>D14/J14</f>
+        <f t="shared" si="2"/>
         <v>0.15294117647058825</v>
       </c>
       <c r="N14" s="33">
-        <f>ROUND(IMDIV(F14,J14),2)</f>
+        <f t="shared" si="3"/>
         <v>0.68</v>
       </c>
       <c r="O14" s="33">
-        <f>ROUND(IMDIV(G14,J14),2)</f>
+        <f t="shared" si="4"/>
         <v>3.04</v>
       </c>
       <c r="P14" s="33">
-        <f>ROUND(IMDIV(H14,J14),2)</f>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="Q14" s="33">
-        <f>ROUND(IMDIV(B14,F14),2)</f>
+        <f t="shared" si="6"/>
         <v>0.78</v>
       </c>
       <c r="R14" s="33">
-        <f>ROUND(IMDIV(C14,B14),4)*100</f>
+        <f t="shared" si="7"/>
         <v>35.56</v>
       </c>
       <c r="S14" s="33">
-        <f>ROUND(IMDIV(I14,J14),2)</f>
+        <f t="shared" si="8"/>
         <v>72.89</v>
       </c>
       <c r="T14" s="32" t="s">
@@ -2168,11 +2183,11 @@
         <v>24</v>
       </c>
       <c r="V14" s="45">
-        <f>((K14/2.5)+(M14/4)+(L14/5)-(N14)+(S14/215)+(P14/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.92396443228454173</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="44" t="s">
         <v>26</v>
       </c>
@@ -2204,39 +2219,39 @@
         <v>85</v>
       </c>
       <c r="K15" s="33">
-        <f>ROUND(IMDIV(B15,J15),2)</f>
+        <f t="shared" si="0"/>
         <v>0.44</v>
       </c>
       <c r="L15" s="34">
-        <f>E15/J15</f>
+        <f t="shared" si="1"/>
         <v>3.5294117647058823E-2</v>
       </c>
       <c r="M15" s="34">
-        <f>D15/J15</f>
+        <f t="shared" si="2"/>
         <v>9.4117647058823528E-2</v>
       </c>
       <c r="N15" s="33">
-        <f>ROUND(IMDIV(F15,J15),2)</f>
+        <f t="shared" si="3"/>
         <v>0.69</v>
       </c>
       <c r="O15" s="33">
-        <f>ROUND(IMDIV(G15,J15),2)</f>
+        <f t="shared" si="4"/>
         <v>2.98</v>
       </c>
       <c r="P15" s="33">
-        <f>ROUND(IMDIV(H15,J15),2)</f>
+        <f t="shared" si="5"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q15" s="33">
-        <f>ROUND(IMDIV(B15,F15),2)</f>
+        <f t="shared" si="6"/>
         <v>0.63</v>
       </c>
       <c r="R15" s="33">
-        <f>ROUND(IMDIV(C15,B15),4)*100</f>
+        <f t="shared" si="7"/>
         <v>45.95</v>
       </c>
       <c r="S15" s="33">
-        <f>ROUND(IMDIV(I15,J15),2)</f>
+        <f t="shared" si="8"/>
         <v>47.35</v>
       </c>
       <c r="T15" s="32" t="s">
@@ -2246,11 +2261,11 @@
         <v>24</v>
       </c>
       <c r="V15" s="45">
-        <f>((K15/2.5)+(M15/4)+(L15/5)-(N15)+(S15/215)+(P15/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.74032079343365265</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="39" t="s">
         <v>22</v>
       </c>
@@ -2282,39 +2297,39 @@
         <v>119</v>
       </c>
       <c r="K16" s="18">
-        <f>ROUND(IMDIV(B16,J16),2)</f>
+        <f t="shared" si="0"/>
         <v>0.56000000000000005</v>
       </c>
       <c r="L16" s="19">
-        <f>E16/J16</f>
+        <f t="shared" si="1"/>
         <v>2.5210084033613446E-2</v>
       </c>
       <c r="M16" s="19">
-        <f>D16/J16</f>
+        <f t="shared" si="2"/>
         <v>0.11764705882352941</v>
       </c>
       <c r="N16" s="18">
-        <f>ROUND(IMDIV(F16,J16),2)</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="O16" s="18">
-        <f>ROUND(IMDIV(G16,J16),2)</f>
+        <f t="shared" si="4"/>
         <v>3.08</v>
       </c>
       <c r="P16" s="18">
-        <f>ROUND(IMDIV(H16,J16),2)</f>
+        <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
       <c r="Q16" s="18">
-        <f>ROUND(IMDIV(B16,F16),2)</f>
+        <f t="shared" si="6"/>
         <v>0.87</v>
       </c>
       <c r="R16" s="18">
-        <f>ROUND(IMDIV(C16,B16),4)*100</f>
+        <f t="shared" si="7"/>
         <v>52.239999999999995</v>
       </c>
       <c r="S16" s="18">
-        <f>ROUND(IMDIV(I16,J16),2)</f>
+        <f t="shared" si="8"/>
         <v>70.7</v>
       </c>
       <c r="T16" s="18" t="s">
@@ -2324,11 +2339,11 @@
         <v>24</v>
       </c>
       <c r="V16" s="45">
-        <f>((K16/2.5)+(M16/4)+(L16/5)-(N16)+(S16/215)+(P16/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.94279099081493056</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="39" t="s">
         <v>23</v>
       </c>
@@ -2360,39 +2375,39 @@
         <v>119</v>
       </c>
       <c r="K17" s="18">
-        <f>ROUND(IMDIV(B17,J17),2)</f>
+        <f t="shared" si="0"/>
         <v>0.46</v>
       </c>
       <c r="L17" s="19">
-        <f>E17/J17</f>
+        <f t="shared" si="1"/>
         <v>1.680672268907563E-2</v>
       </c>
       <c r="M17" s="19">
-        <f>D17/J17</f>
+        <f t="shared" si="2"/>
         <v>8.4033613445378158E-2</v>
       </c>
       <c r="N17" s="18">
-        <f>ROUND(IMDIV(F17,J17),2)</f>
+        <f t="shared" si="3"/>
         <v>0.66</v>
       </c>
       <c r="O17" s="18">
-        <f>ROUND(IMDIV(G17,J17),2)</f>
+        <f t="shared" si="4"/>
         <v>1.49</v>
       </c>
       <c r="P17" s="18">
-        <f>ROUND(IMDIV(H17,J17),2)</f>
+        <f t="shared" si="5"/>
         <v>0.13</v>
       </c>
       <c r="Q17" s="18">
-        <f>ROUND(IMDIV(B17,F17),2)</f>
+        <f t="shared" si="6"/>
         <v>0.71</v>
       </c>
       <c r="R17" s="18">
-        <f>ROUND(IMDIV(C17,B17),4)*100</f>
+        <f t="shared" si="7"/>
         <v>38.18</v>
       </c>
       <c r="S17" s="18">
-        <f>ROUND(IMDIV(I17,J17),2)</f>
+        <f t="shared" si="8"/>
         <v>56.19</v>
       </c>
       <c r="T17" s="18" t="s">
@@ -2402,11 +2417,11 @@
         <v>24</v>
       </c>
       <c r="V17" s="45">
-        <f>((K17/2.5)+(M17/4)+(L17/5)-(N17)+(S17/215)+(P17/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.8162185851084619</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" s="41" t="s">
         <v>36</v>
       </c>
@@ -2438,39 +2453,39 @@
         <v>98</v>
       </c>
       <c r="K18" s="24">
-        <f>ROUND(IMDIV(B18,J18),2)</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="L18" s="25">
-        <f>E18/J18</f>
+        <f t="shared" si="1"/>
         <v>2.0408163265306121E-2</v>
       </c>
       <c r="M18" s="25">
-        <f>D18/J18</f>
+        <f t="shared" si="2"/>
         <v>0.18367346938775511</v>
       </c>
       <c r="N18" s="24">
-        <f>ROUND(IMDIV(F18,J18),2)</f>
+        <f t="shared" si="3"/>
         <v>0.72</v>
       </c>
       <c r="O18" s="24">
-        <f>ROUND(IMDIV(G18,J18),2)</f>
+        <f t="shared" si="4"/>
         <v>3.39</v>
       </c>
       <c r="P18" s="24">
-        <f>ROUND(IMDIV(H18,J18),2)</f>
+        <f t="shared" si="5"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="Q18" s="24">
-        <f>ROUND(IMDIV(B18,F18),2)</f>
+        <f t="shared" si="6"/>
         <v>0.83</v>
       </c>
       <c r="R18" s="24">
-        <f>ROUND(IMDIV(C18,B18),4)*100</f>
+        <f t="shared" si="7"/>
         <v>61.019999999999996</v>
       </c>
       <c r="S18" s="24">
-        <f>ROUND(IMDIV(I18,J18),2)</f>
+        <f t="shared" si="8"/>
         <v>80.88</v>
       </c>
       <c r="T18" s="24" t="s">
@@ -2480,11 +2495,11 @@
         <v>24</v>
       </c>
       <c r="V18" s="45">
-        <f>((K18/2.5)+(M18/4)+(L18/5)-(N18)+(S18/215)+(P18/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.95318604651162786</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="41" t="s">
         <v>25</v>
       </c>
@@ -2516,39 +2531,39 @@
         <v>82</v>
       </c>
       <c r="K19" s="24">
-        <f>ROUND(IMDIV(B19,J19),2)</f>
+        <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
       <c r="L19" s="25">
-        <f>E19/J19</f>
+        <f t="shared" si="1"/>
         <v>2.4390243902439025E-2</v>
       </c>
       <c r="M19" s="25">
-        <f>D19/J19</f>
+        <f t="shared" si="2"/>
         <v>7.3170731707317069E-2</v>
       </c>
       <c r="N19" s="24">
-        <f>ROUND(IMDIV(F19,J19),2)</f>
+        <f t="shared" si="3"/>
         <v>0.71</v>
       </c>
       <c r="O19" s="24">
-        <f>ROUND(IMDIV(G19,J19),2)</f>
+        <f t="shared" si="4"/>
         <v>1.38</v>
       </c>
       <c r="P19" s="24">
-        <f>ROUND(IMDIV(H19,J19),2)</f>
+        <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
       <c r="Q19" s="24">
-        <f>ROUND(IMDIV(B19,F19),2)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="R19" s="24">
-        <f>ROUND(IMDIV(C19,B19),4)*100</f>
+        <f t="shared" si="7"/>
         <v>48.28</v>
       </c>
       <c r="S19" s="24">
-        <f>ROUND(IMDIV(I19,J19),2)</f>
+        <f t="shared" si="8"/>
         <v>43.57</v>
       </c>
       <c r="T19" s="24" t="s">
@@ -2558,11 +2573,11 @@
         <v>24</v>
       </c>
       <c r="V19" s="45">
-        <f>((K19/2.5)+(M19/4)+(L19/5)-(N19)+(S19/215)+(P19/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.66132189449801471</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" s="38" t="s">
         <v>33</v>
       </c>
@@ -2594,39 +2609,39 @@
         <v>112</v>
       </c>
       <c r="K20" s="15">
-        <f>ROUND(IMDIV(B20,J20),2)</f>
+        <f t="shared" si="0"/>
         <v>0.62</v>
       </c>
       <c r="L20" s="17">
-        <f>E20/J20</f>
+        <f t="shared" si="1"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="M20" s="17">
-        <f>D20/J20</f>
+        <f t="shared" si="2"/>
         <v>0.11607142857142858</v>
       </c>
       <c r="N20" s="15">
-        <f>ROUND(IMDIV(F20,J20),2)</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="O20" s="15">
-        <f>ROUND(IMDIV(G20,J20),2)</f>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="P20" s="15">
-        <f>ROUND(IMDIV(H20,J20),2)</f>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="Q20" s="15">
-        <f>ROUND(IMDIV(B20,F20),2)</f>
+        <f t="shared" si="6"/>
         <v>0.95</v>
       </c>
       <c r="R20" s="15">
-        <f>ROUND(IMDIV(C20,B20),4)*100</f>
+        <f t="shared" si="7"/>
         <v>66.67</v>
       </c>
       <c r="S20" s="15">
-        <f>ROUND(IMDIV(I20,J20),2)</f>
+        <f t="shared" si="8"/>
         <v>70.709999999999994</v>
       </c>
       <c r="T20" s="16" t="s">
@@ -2636,11 +2651,11 @@
         <v>24</v>
       </c>
       <c r="V20" s="45">
-        <f>((K20/2.5)+(M20/4)+(L20/5)-(N20)+(S20/215)+(P20/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.9755444352159468</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>21</v>
       </c>
@@ -2672,39 +2687,39 @@
         <v>101</v>
       </c>
       <c r="K21" s="15">
-        <f>ROUND(IMDIV(B21,J21),2)</f>
+        <f t="shared" si="0"/>
         <v>0.46</v>
       </c>
       <c r="L21" s="17">
-        <f>E21/J21</f>
+        <f t="shared" si="1"/>
         <v>9.9009900990099011E-3</v>
       </c>
       <c r="M21" s="17">
-        <f>D21/J21</f>
+        <f t="shared" si="2"/>
         <v>6.9306930693069313E-2</v>
       </c>
       <c r="N21" s="15">
-        <f>ROUND(IMDIV(F21,J21),2)</f>
+        <f t="shared" si="3"/>
         <v>0.71</v>
       </c>
       <c r="O21" s="15">
-        <f>ROUND(IMDIV(G21,J21),2)</f>
+        <f t="shared" si="4"/>
         <v>1.58</v>
       </c>
       <c r="P21" s="15">
-        <f>ROUND(IMDIV(H21,J21),2)</f>
+        <f t="shared" si="5"/>
         <v>0.15</v>
       </c>
       <c r="Q21" s="15">
-        <f>ROUND(IMDIV(B21,F21),2)</f>
+        <f t="shared" si="6"/>
         <v>0.64</v>
       </c>
       <c r="R21" s="15">
-        <f>ROUND(IMDIV(C21,B21),4)*100</f>
+        <f t="shared" si="7"/>
         <v>47.83</v>
       </c>
       <c r="S21" s="15">
-        <f>ROUND(IMDIV(I21,J21),2)</f>
+        <f t="shared" si="8"/>
         <v>51.29</v>
       </c>
       <c r="T21" s="16" t="s">
@@ -2714,11 +2729,11 @@
         <v>24</v>
       </c>
       <c r="V21" s="45">
-        <f>((K21/2.5)+(M21/4)+(L21/5)-(N21)+(S21/215)+(P21/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.73936507022795306</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" s="46" t="s">
         <v>43</v>
       </c>
@@ -2750,39 +2765,39 @@
         <v>16</v>
       </c>
       <c r="K22" s="48">
-        <f>ROUND(IMDIV(B22,J22),2)</f>
+        <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
       <c r="L22" s="49">
-        <f>E22/J22</f>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="M22" s="49">
-        <f>D22/J22</f>
+        <f t="shared" si="2"/>
         <v>6.25E-2</v>
       </c>
       <c r="N22" s="48">
-        <f>ROUND(IMDIV(F22,J22),2)</f>
+        <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
       <c r="O22" s="48">
-        <f>ROUND(IMDIV(G22,J22),2)</f>
+        <f t="shared" si="4"/>
         <v>2.69</v>
       </c>
       <c r="P22" s="48">
-        <f>ROUND(IMDIV(H22,J22),2)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q22" s="48">
-        <f>ROUND(IMDIV(B22,F22),2)</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="R22" s="48">
-        <f>ROUND(IMDIV(C22,B22),4)*100</f>
+        <f t="shared" si="7"/>
         <v>66.67</v>
       </c>
       <c r="S22" s="48">
-        <f>ROUND(IMDIV(I22,J22),2)</f>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="T22" s="47" t="s">
@@ -2792,13 +2807,13 @@
         <v>24</v>
       </c>
       <c r="V22" s="45">
-        <f>((K22/2.5)+(M22/4)+(L22/5)-(N22)+(S22/215)+(P22/20))+1</f>
+        <f t="shared" si="9"/>
         <v>0.47970639534883719</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
-    <sortCondition sortBy="cellColor" ref="A22" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="A22" dxfId="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2807,14 +2822,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82623B68-2CCB-468D-B947-83DB7F94C282}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2882,7 +2897,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>28</v>
       </c>
@@ -2960,7 +2975,7 @@
         <v>1.4812861647615294</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
         <v>27</v>
       </c>
@@ -3038,7 +3053,7 @@
         <v>0.85369255025620816</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="43" t="s">
         <v>39</v>
       </c>
@@ -3116,7 +3131,7 @@
         <v>1.4309519634006862</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="43" t="s">
         <v>40</v>
       </c>
@@ -3194,7 +3209,7 @@
         <v>0.85358520777735414</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="36" t="s">
         <v>31</v>
       </c>
@@ -3272,7 +3287,7 @@
         <v>1.2370955373978629</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="36" t="s">
         <v>32</v>
       </c>
@@ -3350,7 +3365,7 @@
         <v>0.9489773727215588</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="42" t="s">
         <v>37</v>
       </c>
@@ -3418,7 +3433,7 @@
         <v>86.51</v>
       </c>
       <c r="T8" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U8" s="26" t="s">
         <v>24</v>
@@ -3428,7 +3443,7 @@
         <v>1.2719750341997265</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="42" t="s">
         <v>38</v>
       </c>
@@ -3496,7 +3511,7 @@
         <v>63.7</v>
       </c>
       <c r="T9" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U9" s="26" t="s">
         <v>24</v>
@@ -3506,7 +3521,7 @@
         <v>0.91847906976744187</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="37" t="s">
         <v>29</v>
       </c>
@@ -3584,7 +3599,7 @@
         <v>1.3230300721732158</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="37" t="s">
         <v>30</v>
       </c>
@@ -3662,7 +3677,7 @@
         <v>0.91810384923817168</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="40" t="s">
         <v>34</v>
       </c>
@@ -3733,14 +3748,14 @@
         <v>46</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V12" s="45">
         <f t="shared" si="9"/>
         <v>1.1229436428450179</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="40" t="s">
         <v>35</v>
       </c>
@@ -3818,7 +3833,7 @@
         <v>0.96065566117806833</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="44" t="s">
         <v>41</v>
       </c>
@@ -3896,7 +3911,7 @@
         <v>0.92396443228454173</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="44" t="s">
         <v>26</v>
       </c>
@@ -3974,7 +3989,7 @@
         <v>0.74032079343365265</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="39" t="s">
         <v>22</v>
       </c>
@@ -4052,7 +4067,7 @@
         <v>0.94279099081493056</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="39" t="s">
         <v>23</v>
       </c>
@@ -4130,7 +4145,7 @@
         <v>0.8162185851084619</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" s="41" t="s">
         <v>36</v>
       </c>
@@ -4208,7 +4223,7 @@
         <v>0.95318604651162786</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="41" t="s">
         <v>25</v>
       </c>
@@ -4286,7 +4301,7 @@
         <v>0.66132189449801471</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" s="38" t="s">
         <v>33</v>
       </c>
@@ -4364,7 +4379,7 @@
         <v>0.9755444352159468</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>21</v>
       </c>
@@ -4442,7 +4457,7 @@
         <v>0.73936507022795306</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" s="46" t="s">
         <v>43</v>
       </c>
@@ -4528,14 +4543,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF723AF-29F9-4B27-9BD4-7CDF4E72CFCA}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4603,7 +4618,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>28</v>
       </c>
@@ -4663,7 +4678,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
         <v>27</v>
       </c>
@@ -4723,7 +4738,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="43" t="s">
         <v>39</v>
       </c>
@@ -4783,7 +4798,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="43" t="s">
         <v>40</v>
       </c>
@@ -4843,7 +4858,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="36" t="s">
         <v>31</v>
       </c>
@@ -4921,7 +4936,7 @@
         <v>1.1848456659619451</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="36" t="s">
         <v>32</v>
       </c>
@@ -4999,234 +5014,306 @@
         <v>1.0394799154334038</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="27" t="e">
+      <c r="B8" s="26">
+        <v>30</v>
+      </c>
+      <c r="C8" s="26">
+        <v>11</v>
+      </c>
+      <c r="D8" s="26">
+        <v>8</v>
+      </c>
+      <c r="E8" s="26">
+        <v>3</v>
+      </c>
+      <c r="F8" s="26">
+        <v>13</v>
+      </c>
+      <c r="G8" s="26">
+        <v>33</v>
+      </c>
+      <c r="H8" s="26">
+        <v>10</v>
+      </c>
+      <c r="I8" s="26">
+        <v>3082</v>
+      </c>
+      <c r="J8" s="26">
+        <v>32</v>
+      </c>
+      <c r="K8" s="27">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L8" s="28" t="e">
+        <v>0.94</v>
+      </c>
+      <c r="L8" s="28">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="28" t="e">
+        <v>9.375E-2</v>
+      </c>
+      <c r="M8" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="27" t="e">
+        <v>0.25</v>
+      </c>
+      <c r="N8" s="27">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O8" s="27" t="e">
+        <v>0.41</v>
+      </c>
+      <c r="O8" s="27">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P8" s="27" t="e">
+        <v>1.03</v>
+      </c>
+      <c r="P8" s="27">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q8" s="27" t="e">
+        <v>0.31</v>
+      </c>
+      <c r="Q8" s="27">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R8" s="27" t="e">
+        <v>2.31</v>
+      </c>
+      <c r="R8" s="27">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S8" s="27" t="e">
+        <v>36.67</v>
+      </c>
+      <c r="S8" s="27">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>96.31</v>
       </c>
       <c r="T8" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U8" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="V8" s="45" t="e">
+      <c r="V8" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.5107034883720929</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="27" t="e">
+      <c r="B9" s="26">
+        <v>17</v>
+      </c>
+      <c r="C9" s="26">
+        <v>9</v>
+      </c>
+      <c r="D9" s="26">
+        <v>3</v>
+      </c>
+      <c r="E9" s="26">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26">
+        <v>18</v>
+      </c>
+      <c r="G9" s="26">
+        <v>89</v>
+      </c>
+      <c r="H9" s="26">
+        <v>15</v>
+      </c>
+      <c r="I9" s="26">
+        <v>2016</v>
+      </c>
+      <c r="J9" s="26">
+        <v>32</v>
+      </c>
+      <c r="K9" s="27">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L9" s="28" t="e">
+        <v>0.53</v>
+      </c>
+      <c r="L9" s="28">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M9" s="28" t="e">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N9" s="27" t="e">
+        <v>9.375E-2</v>
+      </c>
+      <c r="N9" s="27">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O9" s="27" t="e">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O9" s="27">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P9" s="27" t="e">
+        <v>2.78</v>
+      </c>
+      <c r="P9" s="27">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q9" s="27" t="e">
+        <v>0.47</v>
+      </c>
+      <c r="Q9" s="27">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R9" s="27" t="e">
+        <v>0.94</v>
+      </c>
+      <c r="R9" s="27">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S9" s="27" t="e">
+        <v>52.94</v>
+      </c>
+      <c r="S9" s="27">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>63</v>
       </c>
       <c r="T9" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="V9" s="45" t="e">
+      <c r="V9" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.99196075581395349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12" t="e">
+      <c r="B10" s="12">
+        <v>21</v>
+      </c>
+      <c r="C10" s="12">
+        <v>10</v>
+      </c>
+      <c r="D10" s="12">
+        <v>6</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12">
+        <v>22</v>
+      </c>
+      <c r="G10" s="12">
+        <v>41</v>
+      </c>
+      <c r="H10" s="12">
+        <v>4</v>
+      </c>
+      <c r="I10" s="12">
+        <v>2620</v>
+      </c>
+      <c r="J10" s="12">
+        <v>32</v>
+      </c>
+      <c r="K10" s="12">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L10" s="13" t="e">
+        <v>0.66</v>
+      </c>
+      <c r="L10" s="13">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M10" s="13" t="e">
+        <v>3.125E-2</v>
+      </c>
+      <c r="M10" s="13">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" s="12" t="e">
+        <v>0.1875</v>
+      </c>
+      <c r="N10" s="12">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O10" s="12" t="e">
+        <v>0.69</v>
+      </c>
+      <c r="O10" s="12">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P10" s="12" t="e">
+        <v>1.28</v>
+      </c>
+      <c r="P10" s="12">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q10" s="12" t="e">
+        <v>0.13</v>
+      </c>
+      <c r="Q10" s="12">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R10" s="12" t="e">
+        <v>0.95</v>
+      </c>
+      <c r="R10" s="12">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S10" s="12" t="e">
+        <v>47.620000000000005</v>
+      </c>
+      <c r="S10" s="12">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>81.88</v>
       </c>
       <c r="T10" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="U10" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="V10" s="45" t="e">
+      <c r="U10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="V10" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.0144622093023257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12" t="e">
+      <c r="B11" s="12">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12">
+        <v>6</v>
+      </c>
+      <c r="D11" s="12">
+        <v>2</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>25</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>5</v>
+      </c>
+      <c r="I11" s="12">
+        <v>1384</v>
+      </c>
+      <c r="J11" s="12">
+        <v>32</v>
+      </c>
+      <c r="K11" s="12">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L11" s="13" t="e">
+        <v>0.31</v>
+      </c>
+      <c r="L11" s="13">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M11" s="13" t="e">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="12" t="e">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N11" s="12">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O11" s="12" t="e">
+        <v>0.78</v>
+      </c>
+      <c r="O11" s="12">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P11" s="12" t="e">
+        <v>0</v>
+      </c>
+      <c r="P11" s="12">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q11" s="12" t="e">
+        <v>0.16</v>
+      </c>
+      <c r="Q11" s="12">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R11" s="12" t="e">
+        <v>0.4</v>
+      </c>
+      <c r="R11" s="12">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S11" s="12" t="e">
+        <v>60</v>
+      </c>
+      <c r="S11" s="12">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>43.25</v>
       </c>
       <c r="T11" s="51" t="s">
         <v>46</v>
@@ -5234,12 +5321,12 @@
       <c r="U11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="V11" s="45" t="e">
+      <c r="V11" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.56878779069767438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="40" t="s">
         <v>34</v>
       </c>
@@ -5310,14 +5397,14 @@
         <v>46</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V12" s="45">
         <f t="shared" si="9"/>
         <v>1.129365750528541</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="40" t="s">
         <v>35</v>
       </c>
@@ -5395,7 +5482,7 @@
         <v>0.73772832980972503</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="52"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -5419,7 +5506,7 @@
       <c r="U14" s="5"/>
       <c r="V14" s="55"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="52"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -5443,7 +5530,7 @@
       <c r="U15" s="5"/>
       <c r="V15" s="55"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="56"/>
       <c r="B16" s="57"/>
       <c r="C16" s="57"/>
@@ -5467,7 +5554,7 @@
       <c r="U16" s="57"/>
       <c r="V16" s="55"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="56"/>
       <c r="B17" s="57"/>
       <c r="C17" s="57"/>
@@ -5491,7 +5578,7 @@
       <c r="U17" s="57"/>
       <c r="V17" s="55"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" s="56"/>
       <c r="B18" s="59"/>
       <c r="C18" s="59"/>
@@ -5515,7 +5602,7 @@
       <c r="U18" s="57"/>
       <c r="V18" s="55"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="56"/>
       <c r="B19" s="59"/>
       <c r="C19" s="59"/>
@@ -5539,7 +5626,7 @@
       <c r="U19" s="57"/>
       <c r="V19" s="55"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" s="60"/>
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
@@ -5563,7 +5650,7 @@
       <c r="U20" s="61"/>
       <c r="V20" s="55"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="60"/>
       <c r="B21" s="53"/>
       <c r="C21" s="53"/>
@@ -5587,7 +5674,7 @@
       <c r="U21" s="61"/>
       <c r="V21" s="55"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -5618,17 +5705,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C7BC6-1079-408F-93C8-005DF99ABE1B}">
   <dimension ref="A1:V24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5696,7 +5783,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="36" t="s">
         <v>31</v>
       </c>
@@ -5774,7 +5861,7 @@
         <v>1.1848456659619451</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="36" t="s">
         <v>32</v>
       </c>
@@ -5852,7 +5939,7 @@
         <v>1.0394799154334038</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="40" t="s">
         <v>34</v>
       </c>
@@ -5923,14 +6010,14 @@
         <v>46</v>
       </c>
       <c r="U4" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V4" s="45">
         <f t="shared" si="9"/>
         <v>1.129365750528541</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>35</v>
       </c>
@@ -6008,234 +6095,306 @@
         <v>0.73772832980972503</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="27" t="e">
+      <c r="B6" s="26">
+        <v>30</v>
+      </c>
+      <c r="C6" s="26">
+        <v>11</v>
+      </c>
+      <c r="D6" s="26">
+        <v>8</v>
+      </c>
+      <c r="E6" s="26">
+        <v>3</v>
+      </c>
+      <c r="F6" s="26">
+        <v>13</v>
+      </c>
+      <c r="G6" s="26">
+        <v>33</v>
+      </c>
+      <c r="H6" s="26">
+        <v>10</v>
+      </c>
+      <c r="I6" s="26">
+        <v>3082</v>
+      </c>
+      <c r="J6" s="26">
+        <v>32</v>
+      </c>
+      <c r="K6" s="27">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L6" s="28" t="e">
+        <v>0.94</v>
+      </c>
+      <c r="L6" s="28">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M6" s="28" t="e">
+        <v>9.375E-2</v>
+      </c>
+      <c r="M6" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="27" t="e">
+        <v>0.25</v>
+      </c>
+      <c r="N6" s="27">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O6" s="27" t="e">
+        <v>0.41</v>
+      </c>
+      <c r="O6" s="27">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P6" s="27" t="e">
+        <v>1.03</v>
+      </c>
+      <c r="P6" s="27">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q6" s="27" t="e">
+        <v>0.31</v>
+      </c>
+      <c r="Q6" s="27">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R6" s="27" t="e">
+        <v>2.31</v>
+      </c>
+      <c r="R6" s="27">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S6" s="27" t="e">
+        <v>36.67</v>
+      </c>
+      <c r="S6" s="27">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>96.31</v>
       </c>
       <c r="T6" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U6" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="V6" s="45" t="e">
+      <c r="V6" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.5107034883720929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="27" t="e">
+      <c r="B7" s="26">
+        <v>17</v>
+      </c>
+      <c r="C7" s="26">
+        <v>9</v>
+      </c>
+      <c r="D7" s="26">
+        <v>3</v>
+      </c>
+      <c r="E7" s="26">
+        <v>0</v>
+      </c>
+      <c r="F7" s="26">
+        <v>18</v>
+      </c>
+      <c r="G7" s="26">
+        <v>89</v>
+      </c>
+      <c r="H7" s="26">
+        <v>15</v>
+      </c>
+      <c r="I7" s="26">
+        <v>2016</v>
+      </c>
+      <c r="J7" s="26">
+        <v>32</v>
+      </c>
+      <c r="K7" s="27">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L7" s="28" t="e">
+        <v>0.53</v>
+      </c>
+      <c r="L7" s="28">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M7" s="28" t="e">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="27" t="e">
+        <v>9.375E-2</v>
+      </c>
+      <c r="N7" s="27">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O7" s="27" t="e">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O7" s="27">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P7" s="27" t="e">
+        <v>2.78</v>
+      </c>
+      <c r="P7" s="27">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q7" s="27" t="e">
+        <v>0.47</v>
+      </c>
+      <c r="Q7" s="27">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R7" s="27" t="e">
+        <v>0.94</v>
+      </c>
+      <c r="R7" s="27">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S7" s="27" t="e">
+        <v>52.94</v>
+      </c>
+      <c r="S7" s="27">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>63</v>
       </c>
       <c r="T7" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="V7" s="45" t="e">
+      <c r="V7" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.99196075581395349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12" t="e">
+      <c r="B8" s="12">
+        <v>21</v>
+      </c>
+      <c r="C8" s="12">
+        <v>10</v>
+      </c>
+      <c r="D8" s="12">
+        <v>6</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12">
+        <v>22</v>
+      </c>
+      <c r="G8" s="12">
+        <v>41</v>
+      </c>
+      <c r="H8" s="12">
+        <v>4</v>
+      </c>
+      <c r="I8" s="12">
+        <v>2620</v>
+      </c>
+      <c r="J8" s="12">
+        <v>32</v>
+      </c>
+      <c r="K8" s="12">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L8" s="13" t="e">
+        <v>0.66</v>
+      </c>
+      <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="13" t="e">
+        <v>3.125E-2</v>
+      </c>
+      <c r="M8" s="13">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="12" t="e">
+        <v>0.1875</v>
+      </c>
+      <c r="N8" s="12">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O8" s="12" t="e">
+        <v>0.69</v>
+      </c>
+      <c r="O8" s="12">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P8" s="12" t="e">
+        <v>1.28</v>
+      </c>
+      <c r="P8" s="12">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q8" s="12" t="e">
+        <v>0.13</v>
+      </c>
+      <c r="Q8" s="12">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R8" s="12" t="e">
+        <v>0.95</v>
+      </c>
+      <c r="R8" s="12">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S8" s="12" t="e">
+        <v>47.620000000000005</v>
+      </c>
+      <c r="S8" s="12">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>81.88</v>
       </c>
       <c r="T8" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="U8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="V8" s="45" t="e">
+      <c r="U8" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="V8" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.0144622093023257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12" t="e">
+      <c r="B9" s="12">
+        <v>10</v>
+      </c>
+      <c r="C9" s="12">
+        <v>6</v>
+      </c>
+      <c r="D9" s="12">
+        <v>2</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
+        <v>25</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>5</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1384</v>
+      </c>
+      <c r="J9" s="12">
+        <v>32</v>
+      </c>
+      <c r="K9" s="12">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L9" s="13" t="e">
+        <v>0.31</v>
+      </c>
+      <c r="L9" s="13">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M9" s="13" t="e">
+        <v>0</v>
+      </c>
+      <c r="M9" s="13">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N9" s="12" t="e">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N9" s="12">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O9" s="12" t="e">
+        <v>0.78</v>
+      </c>
+      <c r="O9" s="12">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P9" s="12" t="e">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q9" s="12" t="e">
+        <v>0.16</v>
+      </c>
+      <c r="Q9" s="12">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R9" s="12" t="e">
+        <v>0.4</v>
+      </c>
+      <c r="R9" s="12">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S9" s="12" t="e">
+        <v>60</v>
+      </c>
+      <c r="S9" s="12">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
+        <v>43.25</v>
       </c>
       <c r="T9" s="51" t="s">
         <v>46</v>
@@ -6243,12 +6402,12 @@
       <c r="U9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="V9" s="45" t="e">
+      <c r="V9" s="45">
         <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.56878779069767438</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="52" t="s">
         <v>58</v>
       </c>
@@ -6274,7 +6433,7 @@
       <c r="U10" s="5"/>
       <c r="V10" s="55"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="70" t="s">
         <v>56</v>
       </c>
@@ -6324,7 +6483,7 @@
       <c r="U11" s="5"/>
       <c r="V11" s="55"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="65" t="s">
         <v>31</v>
       </c>
@@ -6374,7 +6533,7 @@
       <c r="U12" s="57"/>
       <c r="V12" s="55"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="65" t="s">
         <v>32</v>
       </c>
@@ -6424,7 +6583,7 @@
       <c r="U13" s="57"/>
       <c r="V13" s="55"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="71" t="s">
         <v>57</v>
       </c>
@@ -6450,7 +6609,7 @@
       <c r="U14" s="57"/>
       <c r="V14" s="55"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="65" t="s">
         <v>34</v>
       </c>
@@ -6500,7 +6659,7 @@
       <c r="U15" s="57"/>
       <c r="V15" s="55"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="65" t="s">
         <v>35</v>
       </c>
@@ -6550,7 +6709,7 @@
       <c r="U16" s="61"/>
       <c r="V16" s="55"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="60"/>
       <c r="B17" s="53"/>
       <c r="C17" s="53"/>
@@ -6574,7 +6733,7 @@
       <c r="U17" s="61"/>
       <c r="V17" s="55"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" s="52" t="s">
         <v>61</v>
       </c>
@@ -6600,7 +6759,7 @@
       <c r="U18" s="5"/>
       <c r="V18" s="55"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="75" t="s">
         <v>62</v>
       </c>
@@ -6641,12 +6800,1075 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" s="65" t="s">
         <v>37</v>
       </c>
+      <c r="B20" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="66">
+        <v>17</v>
+      </c>
+      <c r="D20" s="67">
+        <v>96.31</v>
+      </c>
+      <c r="E20" s="68">
+        <v>1.5107034883720929</v>
+      </c>
+      <c r="F20" s="67">
+        <v>0.94</v>
+      </c>
+      <c r="G20" s="67">
+        <v>3</v>
+      </c>
+      <c r="H20" s="67">
+        <v>8</v>
+      </c>
+      <c r="I20" s="67">
+        <v>0.41</v>
+      </c>
+      <c r="J20" s="67">
+        <v>33</v>
+      </c>
+      <c r="K20" s="67">
+        <v>0.31</v>
+      </c>
+      <c r="L20" s="67">
+        <v>2.31</v>
+      </c>
+      <c r="M20" s="67">
+        <v>36.67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A21" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="69">
+        <v>-1</v>
+      </c>
+      <c r="D21" s="67">
+        <v>63</v>
+      </c>
+      <c r="E21" s="68">
+        <v>0.99196075581395349</v>
+      </c>
+      <c r="F21" s="67">
+        <v>0.53</v>
+      </c>
+      <c r="G21" s="67">
+        <v>0</v>
+      </c>
+      <c r="H21" s="67">
+        <v>3</v>
+      </c>
+      <c r="I21" s="67">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J21" s="67">
+        <v>89</v>
+      </c>
+      <c r="K21" s="67">
+        <v>0.47</v>
+      </c>
+      <c r="L21" s="67">
+        <v>0.94</v>
+      </c>
+      <c r="M21" s="67">
+        <v>52.94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A22" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="63"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A23" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="66">
+        <v>-1</v>
+      </c>
+      <c r="D23" s="62">
+        <v>81.88</v>
+      </c>
+      <c r="E23" s="62">
+        <v>1.01</v>
+      </c>
+      <c r="F23" s="62">
+        <v>0.66</v>
+      </c>
+      <c r="G23" s="62">
+        <v>1</v>
+      </c>
+      <c r="H23" s="62">
+        <v>6</v>
+      </c>
+      <c r="I23" s="62">
+        <v>0.69</v>
+      </c>
+      <c r="J23" s="62">
+        <v>41</v>
+      </c>
+      <c r="K23" s="62">
+        <v>0.13</v>
+      </c>
+      <c r="L23" s="62">
+        <v>0.95</v>
+      </c>
+      <c r="M23" s="62">
+        <v>47.620000000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A24" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="69">
+        <v>-15</v>
+      </c>
+      <c r="D24" s="67">
+        <v>43.25</v>
+      </c>
+      <c r="E24" s="68">
+        <v>0.56878779069767438</v>
+      </c>
+      <c r="F24" s="67">
+        <v>0.31</v>
+      </c>
+      <c r="G24" s="72">
+        <v>0</v>
+      </c>
+      <c r="H24" s="72">
+        <v>2</v>
+      </c>
+      <c r="I24" s="67">
+        <v>0.78</v>
+      </c>
+      <c r="J24" s="72">
+        <v>0</v>
+      </c>
+      <c r="K24" s="67">
+        <v>0.16</v>
+      </c>
+      <c r="L24" s="67">
+        <v>0.4</v>
+      </c>
+      <c r="M24" s="67">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V9">
+    <sortCondition sortBy="cellColor" ref="A5:A9" dxfId="0"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40897AC2-0114-4A6D-BFFC-5EDF88F8CE8F}">
+  <dimension ref="A1:V24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A2" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6" t="e">
+        <f t="shared" ref="K2:K5" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" s="7" t="e">
+        <f t="shared" ref="L2:L5" si="1">E2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M2" s="7" t="e">
+        <f t="shared" ref="M2:M5" si="2">D2/J2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N2" s="6" t="e">
+        <f t="shared" ref="N2:N5" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O2" s="6" t="e">
+        <f t="shared" ref="O2:O5" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P2" s="6" t="e">
+        <f t="shared" ref="P2:P5" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q2" s="6" t="e">
+        <f t="shared" ref="Q2:Q5" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R2" s="6" t="e">
+        <f t="shared" ref="R2:R5" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S2" s="6" t="e">
+        <f t="shared" ref="S2:S5" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45" t="e">
+        <f t="shared" ref="V2:V5" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A3" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L3" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M3" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N3" s="6" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O3" s="6" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P3" s="6" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q3" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R3" s="6" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S3" s="6" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A4" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L4" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M4" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O4" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P4" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q4" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R4" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S4" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A5" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="30" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L5" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M5" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="30" t="e">
+        <f t="shared" si="3"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O5" s="30" t="e">
+        <f t="shared" si="4"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P5" s="30" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q5" s="30" t="e">
+        <f t="shared" si="6"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R5" s="30" t="e">
+        <f t="shared" si="7"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S5" s="30" t="e">
+        <f t="shared" si="8"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45" t="e">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="e">
+        <f t="shared" ref="K6:K9" si="10">ROUND(IMDIV(B6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L6" s="11" t="e">
+        <f t="shared" ref="L6:L9" si="11">E6/J6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M6" s="11" t="e">
+        <f t="shared" ref="M6:M9" si="12">D6/J6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="9" t="e">
+        <f t="shared" ref="N6:N9" si="13">ROUND(IMDIV(F6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O6" s="9" t="e">
+        <f t="shared" ref="O6:O9" si="14">ROUND(IMDIV(G6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P6" s="9" t="e">
+        <f t="shared" ref="P6:P9" si="15">ROUND(IMDIV(H6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q6" s="9" t="e">
+        <f t="shared" ref="Q6:Q9" si="16">ROUND(IMDIV(B6,F6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R6" s="9" t="e">
+        <f t="shared" ref="R6:R9" si="17">ROUND(IMDIV(C6,B6),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S6" s="9" t="e">
+        <f t="shared" ref="S6:S9" si="18">ROUND(IMDIV(I6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45" t="e">
+        <f t="shared" ref="V6:V9" si="19">((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L7" s="11" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M7" s="11" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="9" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O7" s="9" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P7" s="9" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q7" s="9" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R7" s="9" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S7" s="9" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A8" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L8" s="28" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="28" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="27" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O8" s="27" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P8" s="27" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q8" s="27" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R8" s="27" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S8" s="27" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T8" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A9" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="27" t="e">
+        <f t="shared" si="10"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="L9" s="28" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M9" s="28" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="27" t="e">
+        <f t="shared" si="13"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="O9" s="27" t="e">
+        <f t="shared" si="14"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="P9" s="27" t="e">
+        <f t="shared" si="15"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q9" s="27" t="e">
+        <f t="shared" si="16"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="R9" s="27" t="e">
+        <f t="shared" si="17"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="S9" s="27" t="e">
+        <f t="shared" si="18"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="T9" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U9" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V9" s="45" t="e">
+        <f t="shared" si="19"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A10" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="55"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A11" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="53"/>
+      <c r="Q11" s="53"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="61"/>
+      <c r="V11" s="55"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A12" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="66">
+        <v>0</v>
+      </c>
+      <c r="D12" s="67"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
+      <c r="U12" s="61"/>
+      <c r="V12" s="55"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A13" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="69">
+        <v>0</v>
+      </c>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="61"/>
+      <c r="V13" s="55"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A14" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="73"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="55"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A15" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="66">
+        <v>0</v>
+      </c>
+      <c r="D15" s="67"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="55"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A16" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="69">
+        <v>0</v>
+      </c>
+      <c r="D16" s="67"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="55"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="60"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="55"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A18" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="55"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A19" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="55"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A20" s="65" t="s">
+        <v>28</v>
+      </c>
       <c r="B20" s="62"/>
-      <c r="C20" s="66"/>
+      <c r="C20" s="66">
+        <v>0</v>
+      </c>
       <c r="D20" s="67"/>
       <c r="E20" s="68"/>
       <c r="F20" s="67"/>
@@ -6657,13 +7879,24 @@
       <c r="K20" s="67"/>
       <c r="L20" s="67"/>
       <c r="M20" s="67"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="55"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="65" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B21" s="62"/>
-      <c r="C21" s="69"/>
+      <c r="C21" s="69">
+        <v>0</v>
+      </c>
       <c r="D21" s="67"/>
       <c r="E21" s="68"/>
       <c r="F21" s="67"/>
@@ -6674,10 +7907,19 @@
       <c r="K21" s="67"/>
       <c r="L21" s="67"/>
       <c r="M21" s="67"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="74" t="s">
-        <v>57</v>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="55"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A22" s="75" t="s">
+        <v>62</v>
       </c>
       <c r="B22" s="73"/>
       <c r="C22" s="65"/>
@@ -6691,13 +7933,24 @@
       <c r="K22" s="65"/>
       <c r="L22" s="65"/>
       <c r="M22" s="65"/>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="55"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A23" s="65" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B23" s="62"/>
-      <c r="C23" s="66"/>
+      <c r="C23" s="66">
+        <v>0</v>
+      </c>
       <c r="D23" s="67"/>
       <c r="E23" s="68"/>
       <c r="F23" s="67"/>
@@ -6709,12 +7962,14 @@
       <c r="L23" s="67"/>
       <c r="M23" s="67"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A24" s="65" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B24" s="62"/>
-      <c r="C24" s="69"/>
+      <c r="C24" s="69">
+        <v>0</v>
+      </c>
       <c r="D24" s="67"/>
       <c r="E24" s="68"/>
       <c r="F24" s="67"/>
@@ -6727,24 +7982,21 @@
       <c r="M24" s="67"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V9">
-    <sortCondition sortBy="cellColor" ref="A5:A9" dxfId="1"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40897AC2-0114-4A6D-BFFC-5EDF88F8CE8F}">
-  <dimension ref="A1:V26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D112C103-7A2C-4701-8F60-5B846BF871DD}">
+  <dimension ref="A1:V22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6812,7 +8064,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>28</v>
       </c>
@@ -6826,39 +8078,39 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6" t="e">
-        <f t="shared" ref="K2:K5" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <f t="shared" ref="K2:K9" si="0">ROUND(IMDIV(B2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="L2" s="7" t="e">
-        <f t="shared" ref="L2:L5" si="1">E2/J2</f>
+        <f t="shared" ref="L2:L9" si="1">E2/J2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M2" s="7" t="e">
-        <f t="shared" ref="M2:M5" si="2">D2/J2</f>
+        <f t="shared" ref="M2:M9" si="2">D2/J2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N2" s="6" t="e">
-        <f t="shared" ref="N2:N5" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <f t="shared" ref="N2:N9" si="3">ROUND(IMDIV(F2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="O2" s="6" t="e">
-        <f t="shared" ref="O2:O5" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <f t="shared" ref="O2:O9" si="4">ROUND(IMDIV(G2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="P2" s="6" t="e">
-        <f t="shared" ref="P2:P5" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <f t="shared" ref="P2:P9" si="5">ROUND(IMDIV(H2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="Q2" s="6" t="e">
-        <f t="shared" ref="Q2:Q5" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <f t="shared" ref="Q2:Q9" si="6">ROUND(IMDIV(B2,F2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="R2" s="6" t="e">
-        <f t="shared" ref="R2:R5" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <f t="shared" ref="R2:R9" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
         <v>#NUM!</v>
       </c>
       <c r="S2" s="6" t="e">
-        <f t="shared" ref="S2:S5" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <f t="shared" ref="S2:S9" si="8">ROUND(IMDIV(I2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -6868,11 +8120,11 @@
         <v>24</v>
       </c>
       <c r="V2" s="45" t="e">
-        <f t="shared" ref="V2:V5" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" ref="V2:V9" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="35" t="s">
         <v>27</v>
       </c>
@@ -6932,7 +8184,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="43" t="s">
         <v>39</v>
       </c>
@@ -6992,7 +8244,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="43" t="s">
         <v>40</v>
       </c>
@@ -7052,7 +8304,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="36" t="s">
         <v>31</v>
       </c>
@@ -7066,39 +8318,39 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9" t="e">
-        <f t="shared" ref="K6:K11" si="10">ROUND(IMDIV(B6,J6),2)</f>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L6" s="11" t="e">
-        <f t="shared" ref="L6:L11" si="11">E6/J6</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M6" s="11" t="e">
-        <f t="shared" ref="M6:M11" si="12">D6/J6</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N6" s="9" t="e">
-        <f t="shared" ref="N6:N11" si="13">ROUND(IMDIV(F6,J6),2)</f>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O6" s="9" t="e">
-        <f t="shared" ref="O6:O11" si="14">ROUND(IMDIV(G6,J6),2)</f>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P6" s="9" t="e">
-        <f t="shared" ref="P6:P11" si="15">ROUND(IMDIV(H6,J6),2)</f>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q6" s="9" t="e">
-        <f t="shared" ref="Q6:Q11" si="16">ROUND(IMDIV(B6,F6),2)</f>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R6" s="9" t="e">
-        <f t="shared" ref="R6:R11" si="17">ROUND(IMDIV(C6,B6),4)*100</f>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S6" s="9" t="e">
-        <f t="shared" ref="S6:S11" si="18">ROUND(IMDIV(I6,J6),2)</f>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T6" s="9" t="s">
@@ -7108,11 +8360,11 @@
         <v>24</v>
       </c>
       <c r="V6" s="45" t="e">
-        <f t="shared" ref="V6:V11" si="19">((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="36" t="s">
         <v>32</v>
       </c>
@@ -7126,39 +8378,39 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L7" s="11" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M7" s="11" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N7" s="9" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O7" s="9" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P7" s="9" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q7" s="9" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R7" s="9" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S7" s="9" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T7" s="9" t="s">
@@ -7168,11 +8420,11 @@
         <v>24</v>
       </c>
       <c r="V7" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="42" t="s">
         <v>37</v>
       </c>
@@ -7186,39 +8438,39 @@
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
       <c r="K8" s="27" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L8" s="28" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M8" s="28" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N8" s="27" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O8" s="27" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P8" s="27" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q8" s="27" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R8" s="27" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S8" s="27" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T8" s="26" t="s">
@@ -7228,11 +8480,11 @@
         <v>24</v>
       </c>
       <c r="V8" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="42" t="s">
         <v>38</v>
       </c>
@@ -7246,39 +8498,39 @@
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
       <c r="K9" s="27" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
       <c r="L9" s="28" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M9" s="28" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N9" s="27" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
       <c r="O9" s="27" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
       <c r="P9" s="27" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
       <c r="Q9" s="27" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
       <c r="R9" s="27" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
       <c r="S9" s="27" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="T9" s="26" t="s">
@@ -7288,131 +8540,59 @@
         <v>24</v>
       </c>
       <c r="V9" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12" t="e">
-        <f t="shared" si="10"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L10" s="13" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M10" s="13" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" s="12" t="e">
-        <f t="shared" si="13"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O10" s="12" t="e">
-        <f t="shared" si="14"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P10" s="12" t="e">
-        <f t="shared" si="15"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q10" s="12" t="e">
-        <f t="shared" si="16"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R10" s="12" t="e">
-        <f t="shared" si="17"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S10" s="12" t="e">
-        <f t="shared" si="18"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T10" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="V10" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12" t="e">
-        <f t="shared" si="10"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L11" s="13" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M11" s="13" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="12" t="e">
-        <f t="shared" si="13"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O11" s="12" t="e">
-        <f t="shared" si="14"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P11" s="12" t="e">
-        <f t="shared" si="15"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q11" s="12" t="e">
-        <f t="shared" si="16"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R11" s="12" t="e">
-        <f t="shared" si="17"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S11" s="12" t="e">
-        <f t="shared" si="18"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T11" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="U11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="V11" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A10" s="60"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="55"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A11" s="60"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="53"/>
+      <c r="Q11" s="53"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="61"/>
+      <c r="V11" s="55"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="52" t="s">
         <v>58</v>
       </c>
@@ -7438,9 +8618,9 @@
       <c r="U12" s="61"/>
       <c r="V12" s="55"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="76" t="s">
-        <v>63</v>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A13" s="77" t="s">
+        <v>65</v>
       </c>
       <c r="B13" s="62" t="s">
         <v>52</v>
@@ -7488,10 +8668,8 @@
       <c r="U13" s="61"/>
       <c r="V13" s="55"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
-        <v>39</v>
-      </c>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A14" s="65"/>
       <c r="B14" s="62"/>
       <c r="C14" s="66">
         <v>0</v>
@@ -7516,10 +8694,8 @@
       <c r="U14" s="5"/>
       <c r="V14" s="55"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="65" t="s">
-        <v>40</v>
-      </c>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A15" s="65"/>
       <c r="B15" s="62"/>
       <c r="C15" s="69">
         <v>0</v>
@@ -7544,9 +8720,9 @@
       <c r="U15" s="5"/>
       <c r="V15" s="55"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="70" t="s">
-        <v>56</v>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A16" s="77" t="s">
+        <v>66</v>
       </c>
       <c r="B16" s="73"/>
       <c r="C16" s="65"/>
@@ -7570,10 +8746,8 @@
       <c r="U16" s="57"/>
       <c r="V16" s="55"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="65" t="s">
-        <v>31</v>
-      </c>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="65"/>
       <c r="B17" s="62"/>
       <c r="C17" s="66">
         <v>0</v>
@@ -7598,10 +8772,8 @@
       <c r="U17" s="57"/>
       <c r="V17" s="55"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="65" t="s">
-        <v>32</v>
-      </c>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A18" s="65"/>
       <c r="B18" s="62"/>
       <c r="C18" s="69">
         <v>0</v>
@@ -7626,1094 +8798,7 @@
       <c r="U18" s="57"/>
       <c r="V18" s="55"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="60"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="55"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="61"/>
-      <c r="U20" s="61"/>
-      <c r="V20" s="55"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="62" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="62" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="64" t="s">
-        <v>17</v>
-      </c>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="61"/>
-      <c r="V21" s="55"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="66">
-        <v>0</v>
-      </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="53"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="55"/>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="69">
-        <v>0</v>
-      </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="67"/>
-      <c r="M23" s="67"/>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="65"/>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="65"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="66">
-        <v>0</v>
-      </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="67"/>
-      <c r="M25" s="67"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="65"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="69">
-        <v>0</v>
-      </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="67"/>
-      <c r="L26" s="67"/>
-      <c r="M26" s="67"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D112C103-7A2C-4701-8F60-5B846BF871DD}">
-  <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6" t="e">
-        <f t="shared" ref="K2:K11" si="0">ROUND(IMDIV(B2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L2" s="7" t="e">
-        <f t="shared" ref="L2:L11" si="1">E2/J2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M2" s="7" t="e">
-        <f t="shared" ref="M2:M11" si="2">D2/J2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N2" s="6" t="e">
-        <f t="shared" ref="N2:N11" si="3">ROUND(IMDIV(F2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="O2" s="6" t="e">
-        <f t="shared" ref="O2:O11" si="4">ROUND(IMDIV(G2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="P2" s="6" t="e">
-        <f t="shared" ref="P2:P11" si="5">ROUND(IMDIV(H2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q2" s="6" t="e">
-        <f t="shared" ref="Q2:Q11" si="6">ROUND(IMDIV(B2,F2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R2" s="6" t="e">
-        <f t="shared" ref="R2:R11" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="S2" s="6" t="e">
-        <f t="shared" ref="S2:S11" si="8">ROUND(IMDIV(I2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" s="45" t="e">
-        <f t="shared" ref="V2:V11" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L3" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M3" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N3" s="6" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O3" s="6" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P3" s="6" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q3" s="6" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R3" s="6" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S3" s="6" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V3" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="30" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L4" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M4" s="31" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O4" s="30" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P4" s="30" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q4" s="30" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R4" s="30" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S4" s="30" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T4" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="V4" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="30" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L5" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M5" s="31" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O5" s="30" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P5" s="30" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q5" s="30" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R5" s="30" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S5" s="30" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T5" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="V5" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L6" s="11" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M6" s="11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="9" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O6" s="9" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P6" s="9" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q6" s="9" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R6" s="9" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S6" s="9" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V6" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L7" s="11" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M7" s="11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="9" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O7" s="9" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P7" s="9" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q7" s="9" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R7" s="9" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S7" s="9" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V7" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="27" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L8" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="28" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="27" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O8" s="27" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P8" s="27" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q8" s="27" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R8" s="27" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S8" s="27" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T8" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="V8" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="27" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L9" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M9" s="28" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N9" s="27" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O9" s="27" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P9" s="27" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q9" s="27" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R9" s="27" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S9" s="27" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T9" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="U9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="V9" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L10" s="13" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M10" s="13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" s="12" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O10" s="12" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P10" s="12" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q10" s="12" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R10" s="12" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S10" s="12" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T10" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="V10" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L11" s="13" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M11" s="13" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="12" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O11" s="12" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P11" s="12" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q11" s="12" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R11" s="12" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S11" s="12" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T11" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="U11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="V11" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="53"/>
-      <c r="U12" s="61"/>
-      <c r="V12" s="55"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="77" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="62" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="62" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="64" t="s">
-        <v>17</v>
-      </c>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="53"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="61"/>
-      <c r="V13" s="55"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="65"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="66">
-        <v>0</v>
-      </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="67"/>
-      <c r="M14" s="67"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="55"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="69">
-        <v>0</v>
-      </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="53"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="55"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="73"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="65"/>
-      <c r="K16" s="65"/>
-      <c r="L16" s="65"/>
-      <c r="M16" s="65"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="57"/>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="57"/>
-      <c r="R16" s="57"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="57"/>
-      <c r="U16" s="57"/>
-      <c r="V16" s="55"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="66">
-        <v>0</v>
-      </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="67"/>
-      <c r="M17" s="67"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57"/>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="57"/>
-      <c r="R17" s="57"/>
-      <c r="S17" s="57"/>
-      <c r="T17" s="57"/>
-      <c r="U17" s="57"/>
-      <c r="V17" s="55"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="65"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="69">
-        <v>0</v>
-      </c>
-      <c r="D18" s="67"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="57"/>
-      <c r="S18" s="57"/>
-      <c r="T18" s="57"/>
-      <c r="U18" s="57"/>
-      <c r="V18" s="55"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="56"/>
       <c r="B19" s="59"/>
       <c r="C19" s="59"/>
@@ -8737,7 +8822,7 @@
       <c r="U19" s="57"/>
       <c r="V19" s="55"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" s="60"/>
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
@@ -8761,7 +8846,7 @@
       <c r="U20" s="61"/>
       <c r="V20" s="55"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="60"/>
       <c r="B21" s="53"/>
       <c r="C21" s="53"/>
@@ -8785,7 +8870,7 @@
       <c r="U21" s="61"/>
       <c r="V21" s="55"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>

--- a/2026WinterLeagueXL.xlsx
+++ b/2026WinterLeagueXL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0AC5F5-0CB7-4D6C-9496-A8F81398CEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290F0006-CF56-4278-B456-3C1068F4CDA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="26505" windowHeight="13665" activeTab="4" xr2:uid="{44E8176A-B14F-4FEE-87B9-53CEBFA849EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tourney" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="77">
   <si>
     <t>player</t>
   </si>
@@ -238,9 +238,6 @@
     <t>Burger</t>
   </si>
   <si>
-    <t>Team A</t>
-  </si>
-  <si>
     <t>Team B</t>
   </si>
   <si>
@@ -257,6 +254,24 @@
   </si>
   <si>
     <t>10-25</t>
+  </si>
+  <si>
+    <t>33-33</t>
+  </si>
+  <si>
+    <t>25-33</t>
+  </si>
+  <si>
+    <t>31-32</t>
+  </si>
+  <si>
+    <t>35-26</t>
+  </si>
+  <si>
+    <t>4th</t>
+  </si>
+  <si>
+    <t>1st-2nd</t>
   </si>
 </sst>
 </file>
@@ -494,7 +509,7 @@
     <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -730,13 +745,32 @@
     <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF501C75"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF501C75"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -748,7 +782,55 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF3A602"/>
+          <fgColor rgb="FF4EA72E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF501C75"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF501C75"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4EA72E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4EA72E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4EA72E"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4EA72E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1098,14 +1180,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C412513A-E0D1-405F-B780-5234AC262E79}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,631 +1255,631 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="6">
-        <v>112</v>
-      </c>
-      <c r="C2" s="6">
-        <v>73</v>
-      </c>
-      <c r="D2" s="6">
-        <v>32</v>
-      </c>
-      <c r="E2" s="6">
-        <v>8</v>
-      </c>
-      <c r="F2" s="6">
-        <v>55</v>
-      </c>
-      <c r="G2" s="6">
-        <v>668</v>
-      </c>
-      <c r="H2" s="6">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="6">
-        <v>12100</v>
-      </c>
-      <c r="J2" s="6">
-        <v>118</v>
-      </c>
-      <c r="K2" s="6">
+      <c r="B2" s="9">
+        <v>176</v>
+      </c>
+      <c r="C2" s="9">
+        <v>87</v>
+      </c>
+      <c r="D2" s="9">
+        <v>48</v>
+      </c>
+      <c r="E2" s="9">
+        <v>16</v>
+      </c>
+      <c r="F2" s="9">
+        <v>138</v>
+      </c>
+      <c r="G2" s="9">
+        <v>901</v>
+      </c>
+      <c r="H2" s="9">
+        <v>59</v>
+      </c>
+      <c r="I2" s="9">
+        <v>20801</v>
+      </c>
+      <c r="J2" s="9">
+        <v>241</v>
+      </c>
+      <c r="K2" s="9">
         <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
-        <v>0.95</v>
-      </c>
-      <c r="L2" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="L2" s="11">
         <f t="shared" ref="L2:L22" si="1">E2/J2</f>
-        <v>6.7796610169491525E-2</v>
-      </c>
-      <c r="M2" s="7">
+        <v>6.6390041493775934E-2</v>
+      </c>
+      <c r="M2" s="11">
         <f t="shared" ref="M2:M22" si="2">D2/J2</f>
-        <v>0.2711864406779661</v>
-      </c>
-      <c r="N2" s="6">
+        <v>0.19917012448132779</v>
+      </c>
+      <c r="N2" s="9">
         <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
-        <v>0.47</v>
-      </c>
-      <c r="O2" s="6">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O2" s="9">
         <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
-        <v>5.66</v>
-      </c>
-      <c r="P2" s="6">
+        <v>3.74</v>
+      </c>
+      <c r="P2" s="9">
         <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
-        <v>0.26</v>
-      </c>
-      <c r="Q2" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="Q2" s="9">
         <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
-        <v>2.04</v>
-      </c>
-      <c r="R2" s="6">
+        <v>1.28</v>
+      </c>
+      <c r="R2" s="9">
         <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>65.180000000000007</v>
-      </c>
-      <c r="S2" s="6">
+        <v>49.43</v>
+      </c>
+      <c r="S2" s="9">
         <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
-        <v>102.54</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" s="8" t="s">
+        <v>86.31</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U2" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="45">
         <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.1985123998842035</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9">
+        <v>142</v>
+      </c>
+      <c r="C3" s="9">
+        <v>57</v>
+      </c>
+      <c r="D3" s="9">
+        <v>31</v>
+      </c>
+      <c r="E3" s="9">
+        <v>15</v>
+      </c>
+      <c r="F3" s="9">
+        <v>141</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1184</v>
+      </c>
+      <c r="H3" s="9">
+        <v>28</v>
+      </c>
+      <c r="I3" s="9">
+        <v>15017</v>
+      </c>
+      <c r="J3" s="9">
+        <v>241</v>
+      </c>
+      <c r="K3" s="9">
+        <f t="shared" si="0"/>
+        <v>0.59</v>
+      </c>
+      <c r="L3" s="11">
+        <f t="shared" si="1"/>
+        <v>6.2240663900414939E-2</v>
+      </c>
+      <c r="M3" s="11">
+        <f t="shared" si="2"/>
+        <v>0.12863070539419086</v>
+      </c>
+      <c r="N3" s="9">
+        <f t="shared" si="3"/>
+        <v>0.59</v>
+      </c>
+      <c r="O3" s="9">
+        <f t="shared" si="4"/>
+        <v>4.91</v>
+      </c>
+      <c r="P3" s="9">
+        <f t="shared" si="5"/>
+        <v>0.12</v>
+      </c>
+      <c r="Q3" s="9">
+        <f t="shared" si="6"/>
+        <v>1.01</v>
+      </c>
+      <c r="R3" s="9">
+        <f t="shared" si="7"/>
+        <v>40.14</v>
+      </c>
+      <c r="S3" s="9">
+        <f t="shared" si="8"/>
+        <v>62.31</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45">
+        <f t="shared" si="9"/>
+        <v>0.98641976261700282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6">
+        <v>112</v>
+      </c>
+      <c r="C4" s="6">
+        <v>73</v>
+      </c>
+      <c r="D4" s="6">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6">
+        <v>55</v>
+      </c>
+      <c r="G4" s="6">
+        <v>668</v>
+      </c>
+      <c r="H4" s="6">
+        <v>31</v>
+      </c>
+      <c r="I4" s="6">
+        <v>12100</v>
+      </c>
+      <c r="J4" s="6">
+        <v>118</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" si="0"/>
+        <v>0.95</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" si="1"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="2"/>
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" si="3"/>
+        <v>0.47</v>
+      </c>
+      <c r="O4" s="6">
+        <f t="shared" si="4"/>
+        <v>5.66</v>
+      </c>
+      <c r="P4" s="6">
+        <f t="shared" si="5"/>
+        <v>0.26</v>
+      </c>
+      <c r="Q4" s="6">
+        <f t="shared" si="6"/>
+        <v>2.04</v>
+      </c>
+      <c r="R4" s="6">
+        <f t="shared" si="7"/>
+        <v>65.180000000000007</v>
+      </c>
+      <c r="S4" s="6">
+        <f t="shared" si="8"/>
+        <v>102.54</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45">
+        <f t="shared" si="9"/>
         <v>1.4812861647615294</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B5" s="6">
         <v>57</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C5" s="6">
         <v>29</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D5" s="6">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E5" s="6">
         <v>2</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F5" s="6">
         <v>72</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G5" s="6">
         <v>41</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H5" s="6">
         <v>14</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I5" s="6">
         <v>6117</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J5" s="6">
         <v>118</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K5" s="6">
         <f t="shared" si="0"/>
         <v>0.48</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L5" s="7">
         <f t="shared" si="1"/>
         <v>1.6949152542372881E-2</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M5" s="7">
         <f t="shared" si="2"/>
         <v>8.4745762711864403E-2</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N5" s="6">
         <f t="shared" si="3"/>
         <v>0.61</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O5" s="6">
         <f t="shared" si="4"/>
         <v>0.35</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P5" s="6">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q5" s="6">
         <f t="shared" si="6"/>
         <v>0.79</v>
       </c>
-      <c r="R3" s="6">
+      <c r="R5" s="6">
         <f t="shared" si="7"/>
         <v>50.88</v>
       </c>
-      <c r="S3" s="6">
+      <c r="S5" s="6">
         <f t="shared" si="8"/>
         <v>51.84</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="45">
+      <c r="V5" s="45">
         <f t="shared" si="9"/>
         <v>0.85369255025620816</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="26">
+        <v>136</v>
+      </c>
+      <c r="C6" s="26">
+        <v>68</v>
+      </c>
+      <c r="D6" s="26">
+        <v>29</v>
+      </c>
+      <c r="E6" s="26">
+        <v>20</v>
+      </c>
+      <c r="F6" s="26">
+        <v>84</v>
+      </c>
+      <c r="G6" s="26">
+        <v>333</v>
+      </c>
+      <c r="H6" s="26">
+        <v>48</v>
+      </c>
+      <c r="I6" s="26">
+        <v>14847</v>
+      </c>
+      <c r="J6" s="26">
+        <v>168</v>
+      </c>
+      <c r="K6" s="27">
+        <f t="shared" si="0"/>
+        <v>0.81</v>
+      </c>
+      <c r="L6" s="28">
+        <f t="shared" si="1"/>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="M6" s="28">
+        <f t="shared" si="2"/>
+        <v>0.17261904761904762</v>
+      </c>
+      <c r="N6" s="27">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="O6" s="27">
+        <f t="shared" si="4"/>
+        <v>1.98</v>
+      </c>
+      <c r="P6" s="27">
+        <f t="shared" si="5"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Q6" s="27">
+        <f t="shared" si="6"/>
+        <v>1.62</v>
+      </c>
+      <c r="R6" s="27">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="S6" s="27">
+        <f t="shared" si="8"/>
+        <v>88.38</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45">
+        <f t="shared" si="9"/>
+        <v>1.3165340531561462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="26">
+        <v>87</v>
+      </c>
+      <c r="C7" s="26">
+        <v>37</v>
+      </c>
+      <c r="D7" s="26">
+        <v>13</v>
+      </c>
+      <c r="E7" s="26">
+        <v>2</v>
+      </c>
+      <c r="F7" s="26">
+        <v>98</v>
+      </c>
+      <c r="G7" s="26">
+        <v>436</v>
+      </c>
+      <c r="H7" s="26">
+        <v>53</v>
+      </c>
+      <c r="I7" s="26">
+        <v>9979</v>
+      </c>
+      <c r="J7" s="26">
+        <v>157</v>
+      </c>
+      <c r="K7" s="27">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L7" s="28">
+        <f t="shared" si="1"/>
+        <v>1.2738853503184714E-2</v>
+      </c>
+      <c r="M7" s="28">
+        <f t="shared" si="2"/>
+        <v>8.2802547770700632E-2</v>
+      </c>
+      <c r="N7" s="27">
+        <f t="shared" si="3"/>
+        <v>0.62</v>
+      </c>
+      <c r="O7" s="27">
+        <f t="shared" si="4"/>
+        <v>2.78</v>
+      </c>
+      <c r="P7" s="27">
+        <f t="shared" si="5"/>
+        <v>0.34</v>
+      </c>
+      <c r="Q7" s="27">
+        <f t="shared" si="6"/>
+        <v>0.89</v>
+      </c>
+      <c r="R7" s="27">
+        <f t="shared" si="7"/>
+        <v>42.53</v>
+      </c>
+      <c r="S7" s="27">
+        <f t="shared" si="8"/>
+        <v>63.56</v>
+      </c>
+      <c r="T7" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45">
+        <f t="shared" si="9"/>
+        <v>0.93587631462005627</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="29">
-        <v>108</v>
-      </c>
-      <c r="C4" s="29">
-        <v>62</v>
-      </c>
-      <c r="D4" s="29">
-        <v>35</v>
-      </c>
-      <c r="E4" s="29">
+      <c r="B8" s="29">
+        <v>141</v>
+      </c>
+      <c r="C8" s="29">
+        <v>79</v>
+      </c>
+      <c r="D8" s="29">
+        <v>42</v>
+      </c>
+      <c r="E8" s="29">
+        <v>13</v>
+      </c>
+      <c r="F8" s="29">
+        <v>93</v>
+      </c>
+      <c r="G8" s="29">
+        <v>844</v>
+      </c>
+      <c r="H8" s="29">
+        <v>17</v>
+      </c>
+      <c r="I8" s="29">
+        <v>16232</v>
+      </c>
+      <c r="J8" s="29">
+        <v>171</v>
+      </c>
+      <c r="K8" s="30">
+        <f t="shared" si="0"/>
+        <v>0.82</v>
+      </c>
+      <c r="L8" s="31">
+        <f t="shared" si="1"/>
+        <v>7.6023391812865493E-2</v>
+      </c>
+      <c r="M8" s="31">
+        <f t="shared" si="2"/>
+        <v>0.24561403508771928</v>
+      </c>
+      <c r="N8" s="30">
+        <f t="shared" si="3"/>
+        <v>0.54</v>
+      </c>
+      <c r="O8" s="30">
+        <f t="shared" si="4"/>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="P8" s="30">
+        <f t="shared" si="5"/>
+        <v>0.1</v>
+      </c>
+      <c r="Q8" s="30">
+        <f t="shared" si="6"/>
+        <v>1.52</v>
+      </c>
+      <c r="R8" s="30">
+        <f t="shared" si="7"/>
+        <v>56.03</v>
+      </c>
+      <c r="S8" s="30">
+        <f t="shared" si="8"/>
+        <v>94.92</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="U8" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="45">
+        <f t="shared" si="9"/>
+        <v>1.3110965592275261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="29">
+        <v>75</v>
+      </c>
+      <c r="C9" s="29">
+        <v>31</v>
+      </c>
+      <c r="D9" s="29">
         <v>10</v>
       </c>
-      <c r="F4" s="29">
-        <v>60</v>
-      </c>
-      <c r="G4" s="29">
-        <v>794</v>
-      </c>
-      <c r="H4" s="29">
-        <v>15</v>
-      </c>
-      <c r="I4" s="29">
-        <v>12350</v>
-      </c>
-      <c r="J4" s="29">
-        <v>122</v>
-      </c>
-      <c r="K4" s="30">
+      <c r="E9" s="29">
+        <v>4</v>
+      </c>
+      <c r="F9" s="29">
+        <v>100</v>
+      </c>
+      <c r="G9" s="29">
+        <v>339</v>
+      </c>
+      <c r="H9" s="29">
+        <v>34</v>
+      </c>
+      <c r="I9" s="29">
+        <v>8454</v>
+      </c>
+      <c r="J9" s="29">
+        <v>171</v>
+      </c>
+      <c r="K9" s="30">
         <f t="shared" si="0"/>
-        <v>0.89</v>
-      </c>
-      <c r="L4" s="31">
+        <v>0.44</v>
+      </c>
+      <c r="L9" s="31">
         <f t="shared" si="1"/>
-        <v>8.1967213114754092E-2</v>
-      </c>
-      <c r="M4" s="31">
+        <v>2.3391812865497075E-2</v>
+      </c>
+      <c r="M9" s="31">
         <f t="shared" si="2"/>
-        <v>0.28688524590163933</v>
-      </c>
-      <c r="N4" s="30">
+        <v>5.8479532163742687E-2</v>
+      </c>
+      <c r="N9" s="30">
         <f t="shared" si="3"/>
-        <v>0.49</v>
-      </c>
-      <c r="O4" s="30">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O9" s="30">
         <f t="shared" si="4"/>
-        <v>6.51</v>
-      </c>
-      <c r="P4" s="30">
-        <f t="shared" si="5"/>
-        <v>0.12</v>
-      </c>
-      <c r="Q4" s="30">
-        <f t="shared" si="6"/>
-        <v>1.8</v>
-      </c>
-      <c r="R4" s="30">
-        <f t="shared" si="7"/>
-        <v>57.410000000000004</v>
-      </c>
-      <c r="S4" s="30">
-        <f t="shared" si="8"/>
-        <v>101.23</v>
-      </c>
-      <c r="T4" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="V4" s="45">
-        <f t="shared" si="9"/>
-        <v>1.4309519634006862</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="29">
-        <v>50</v>
-      </c>
-      <c r="C5" s="29">
-        <v>18</v>
-      </c>
-      <c r="D5" s="29">
-        <v>6</v>
-      </c>
-      <c r="E5" s="29">
-        <v>3</v>
-      </c>
-      <c r="F5" s="29">
-        <v>67</v>
-      </c>
-      <c r="G5" s="29">
-        <v>233</v>
-      </c>
-      <c r="H5" s="29">
-        <v>24</v>
-      </c>
-      <c r="I5" s="29">
-        <v>5570</v>
-      </c>
-      <c r="J5" s="29">
-        <v>122</v>
-      </c>
-      <c r="K5" s="30">
-        <f t="shared" si="0"/>
-        <v>0.41</v>
-      </c>
-      <c r="L5" s="31">
-        <f t="shared" si="1"/>
-        <v>2.4590163934426229E-2</v>
-      </c>
-      <c r="M5" s="31">
-        <f t="shared" si="2"/>
-        <v>4.9180327868852458E-2</v>
-      </c>
-      <c r="N5" s="30">
-        <f t="shared" si="3"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O5" s="30">
-        <f t="shared" si="4"/>
-        <v>1.91</v>
-      </c>
-      <c r="P5" s="30">
+        <v>1.98</v>
+      </c>
+      <c r="P9" s="30">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-      <c r="Q5" s="30">
+      <c r="Q9" s="30">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
-      <c r="R5" s="30">
+      <c r="R9" s="30">
         <f t="shared" si="7"/>
-        <v>36</v>
-      </c>
-      <c r="S5" s="30">
+        <v>41.33</v>
+      </c>
+      <c r="S9" s="30">
         <f t="shared" si="8"/>
-        <v>45.66</v>
-      </c>
-      <c r="T5" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="V5" s="45">
-        <f t="shared" si="9"/>
-        <v>0.85358520777735414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="9">
-        <v>145</v>
-      </c>
-      <c r="C6" s="9">
-        <v>69</v>
-      </c>
-      <c r="D6" s="9">
-        <v>40</v>
-      </c>
-      <c r="E6" s="9">
-        <v>14</v>
-      </c>
-      <c r="F6" s="9">
-        <v>106</v>
-      </c>
-      <c r="G6" s="9">
-        <v>789</v>
-      </c>
-      <c r="H6" s="9">
-        <v>49</v>
-      </c>
-      <c r="I6" s="9">
-        <v>16449</v>
-      </c>
-      <c r="J6" s="9">
-        <v>192</v>
-      </c>
-      <c r="K6" s="9">
-        <f t="shared" si="0"/>
-        <v>0.76</v>
-      </c>
-      <c r="L6" s="11">
-        <f t="shared" si="1"/>
-        <v>7.2916666666666671E-2</v>
-      </c>
-      <c r="M6" s="11">
-        <f t="shared" si="2"/>
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="N6" s="9">
-        <f t="shared" si="3"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O6" s="9">
-        <f t="shared" si="4"/>
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="P6" s="9">
-        <f t="shared" si="5"/>
-        <v>0.26</v>
-      </c>
-      <c r="Q6" s="9">
-        <f t="shared" si="6"/>
-        <v>1.37</v>
-      </c>
-      <c r="R6" s="9">
-        <f t="shared" si="7"/>
-        <v>47.589999999999996</v>
-      </c>
-      <c r="S6" s="9">
-        <f t="shared" si="8"/>
-        <v>85.67</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V6" s="45">
-        <f t="shared" si="9"/>
-        <v>1.2321317829457363</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9">
-        <v>107</v>
-      </c>
-      <c r="C7" s="9">
-        <v>43</v>
-      </c>
-      <c r="D7" s="9">
-        <v>23</v>
-      </c>
-      <c r="E7" s="9">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9">
-        <v>115</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1068</v>
-      </c>
-      <c r="H7" s="9">
-        <v>26</v>
-      </c>
-      <c r="I7" s="9">
-        <v>12196</v>
-      </c>
-      <c r="J7" s="9">
-        <v>192</v>
-      </c>
-      <c r="K7" s="9">
-        <f t="shared" si="0"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L7" s="11">
-        <f t="shared" si="1"/>
-        <v>5.2083333333333336E-2</v>
-      </c>
-      <c r="M7" s="11">
-        <f t="shared" si="2"/>
-        <v>0.11979166666666667</v>
-      </c>
-      <c r="N7" s="9">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
-      </c>
-      <c r="O7" s="9">
-        <f t="shared" si="4"/>
-        <v>5.56</v>
-      </c>
-      <c r="P7" s="9">
-        <f t="shared" si="5"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q7" s="9">
-        <f t="shared" si="6"/>
-        <v>0.93</v>
-      </c>
-      <c r="R7" s="9">
-        <f t="shared" si="7"/>
-        <v>40.19</v>
-      </c>
-      <c r="S7" s="9">
-        <f t="shared" si="8"/>
-        <v>63.52</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V7" s="45">
-        <f t="shared" si="9"/>
-        <v>0.96680644379844971</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="26">
-        <v>136</v>
-      </c>
-      <c r="C8" s="26">
-        <v>68</v>
-      </c>
-      <c r="D8" s="26">
-        <v>29</v>
-      </c>
-      <c r="E8" s="26">
-        <v>20</v>
-      </c>
-      <c r="F8" s="26">
-        <v>84</v>
-      </c>
-      <c r="G8" s="26">
-        <v>333</v>
-      </c>
-      <c r="H8" s="26">
-        <v>48</v>
-      </c>
-      <c r="I8" s="26">
-        <v>14847</v>
-      </c>
-      <c r="J8" s="26">
-        <v>168</v>
-      </c>
-      <c r="K8" s="27">
-        <f t="shared" si="0"/>
-        <v>0.81</v>
-      </c>
-      <c r="L8" s="28">
-        <f t="shared" si="1"/>
-        <v>0.11904761904761904</v>
-      </c>
-      <c r="M8" s="28">
-        <f t="shared" si="2"/>
-        <v>0.17261904761904762</v>
-      </c>
-      <c r="N8" s="27">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="O8" s="27">
-        <f t="shared" si="4"/>
-        <v>1.98</v>
-      </c>
-      <c r="P8" s="27">
-        <f t="shared" si="5"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="Q8" s="27">
-        <f t="shared" si="6"/>
-        <v>1.62</v>
-      </c>
-      <c r="R8" s="27">
-        <f t="shared" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="S8" s="27">
-        <f t="shared" si="8"/>
-        <v>88.38</v>
-      </c>
-      <c r="T8" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="V8" s="45">
-        <f t="shared" si="9"/>
-        <v>1.3165340531561462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="26">
-        <v>87</v>
-      </c>
-      <c r="C9" s="26">
-        <v>37</v>
-      </c>
-      <c r="D9" s="26">
-        <v>13</v>
-      </c>
-      <c r="E9" s="26">
-        <v>2</v>
-      </c>
-      <c r="F9" s="26">
-        <v>98</v>
-      </c>
-      <c r="G9" s="26">
-        <v>436</v>
-      </c>
-      <c r="H9" s="26">
-        <v>53</v>
-      </c>
-      <c r="I9" s="26">
-        <v>9979</v>
-      </c>
-      <c r="J9" s="26">
-        <v>157</v>
-      </c>
-      <c r="K9" s="27">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="L9" s="28">
-        <f t="shared" si="1"/>
-        <v>1.2738853503184714E-2</v>
-      </c>
-      <c r="M9" s="28">
-        <f t="shared" si="2"/>
-        <v>8.2802547770700632E-2</v>
-      </c>
-      <c r="N9" s="27">
-        <f t="shared" si="3"/>
-        <v>0.62</v>
-      </c>
-      <c r="O9" s="27">
-        <f t="shared" si="4"/>
-        <v>2.78</v>
-      </c>
-      <c r="P9" s="27">
-        <f t="shared" si="5"/>
-        <v>0.34</v>
-      </c>
-      <c r="Q9" s="27">
-        <f t="shared" si="6"/>
-        <v>0.89</v>
-      </c>
-      <c r="R9" s="27">
-        <f t="shared" si="7"/>
-        <v>42.53</v>
-      </c>
-      <c r="S9" s="27">
-        <f t="shared" si="8"/>
-        <v>63.56</v>
-      </c>
-      <c r="T9" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="U9" s="26" t="s">
+        <v>49.44</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="U9" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V9" s="45">
         <f t="shared" si="9"/>
-        <v>0.93587631462005627</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+        <v>0.85525173398612808</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
         <v>29</v>
       </c>
@@ -1875,7 +1957,7 @@
         <v>1.2630971087366436</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
         <v>30</v>
       </c>
@@ -1953,7 +2035,7 @@
         <v>0.84612350722815843</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
         <v>34</v>
       </c>
@@ -2024,14 +2106,14 @@
         <v>46</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V12" s="45">
         <f t="shared" si="9"/>
         <v>1.123553192856225</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
         <v>35</v>
       </c>
@@ -2109,7 +2191,7 @@
         <v>0.91377020429140432</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
         <v>41</v>
       </c>
@@ -2187,7 +2269,7 @@
         <v>0.92396443228454173</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
         <v>26</v>
       </c>
@@ -2265,7 +2347,7 @@
         <v>0.74032079343365265</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
         <v>22</v>
       </c>
@@ -2343,7 +2425,7 @@
         <v>0.94279099081493056</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>23</v>
       </c>
@@ -2421,7 +2503,7 @@
         <v>0.8162185851084619</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>36</v>
       </c>
@@ -2499,7 +2581,7 @@
         <v>0.95318604651162786</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>25</v>
       </c>
@@ -2577,7 +2659,7 @@
         <v>0.66132189449801471</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
         <v>33</v>
       </c>
@@ -2655,7 +2737,7 @@
         <v>0.9755444352159468</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>21</v>
       </c>
@@ -2733,7 +2815,7 @@
         <v>0.73936507022795306</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="46" t="s">
         <v>43</v>
       </c>
@@ -2813,7 +2895,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
-    <sortCondition sortBy="cellColor" ref="A22" dxfId="1"/>
+    <sortCondition sortBy="cellColor" ref="R6:R22" dxfId="9"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2822,14 +2904,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82623B68-2CCB-468D-B947-83DB7F94C282}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2897,631 +2979,631 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="6">
-        <v>112</v>
-      </c>
-      <c r="C2" s="6">
-        <v>73</v>
-      </c>
-      <c r="D2" s="6">
-        <v>32</v>
-      </c>
-      <c r="E2" s="6">
-        <v>8</v>
-      </c>
-      <c r="F2" s="6">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="9">
+        <v>111</v>
+      </c>
+      <c r="C2" s="9">
         <v>55</v>
       </c>
-      <c r="G2" s="6">
-        <v>668</v>
-      </c>
-      <c r="H2" s="6">
-        <v>31</v>
-      </c>
-      <c r="I2" s="6">
-        <v>12100</v>
-      </c>
-      <c r="J2" s="6">
-        <v>118</v>
-      </c>
-      <c r="K2" s="6">
+      <c r="D2" s="9">
+        <v>29</v>
+      </c>
+      <c r="E2" s="9">
+        <v>11</v>
+      </c>
+      <c r="F2" s="9">
+        <v>81</v>
+      </c>
+      <c r="G2" s="9">
+        <v>446</v>
+      </c>
+      <c r="H2" s="9">
+        <v>37</v>
+      </c>
+      <c r="I2" s="9">
+        <v>13070</v>
+      </c>
+      <c r="J2" s="9">
+        <v>148</v>
+      </c>
+      <c r="K2" s="9">
         <f t="shared" ref="K2:K22" si="0">ROUND(IMDIV(B2,J2),2)</f>
-        <v>0.95</v>
-      </c>
-      <c r="L2" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="L2" s="11">
         <f t="shared" ref="L2:L22" si="1">E2/J2</f>
-        <v>6.7796610169491525E-2</v>
-      </c>
-      <c r="M2" s="7">
+        <v>7.4324324324324328E-2</v>
+      </c>
+      <c r="M2" s="11">
         <f t="shared" ref="M2:M22" si="2">D2/J2</f>
-        <v>0.2711864406779661</v>
-      </c>
-      <c r="N2" s="6">
+        <v>0.19594594594594594</v>
+      </c>
+      <c r="N2" s="9">
         <f t="shared" ref="N2:N22" si="3">ROUND(IMDIV(F2,J2),2)</f>
-        <v>0.47</v>
-      </c>
-      <c r="O2" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O2" s="9">
         <f t="shared" ref="O2:O22" si="4">ROUND(IMDIV(G2,J2),2)</f>
-        <v>5.66</v>
-      </c>
-      <c r="P2" s="6">
+        <v>3.01</v>
+      </c>
+      <c r="P2" s="9">
         <f t="shared" ref="P2:P22" si="5">ROUND(IMDIV(H2,J2),2)</f>
-        <v>0.26</v>
-      </c>
-      <c r="Q2" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Q2" s="9">
         <f t="shared" ref="Q2:Q22" si="6">ROUND(IMDIV(B2,F2),2)</f>
-        <v>2.04</v>
-      </c>
-      <c r="R2" s="6">
+        <v>1.37</v>
+      </c>
+      <c r="R2" s="9">
         <f t="shared" ref="R2:R22" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>65.180000000000007</v>
-      </c>
-      <c r="S2" s="6">
+        <v>49.55</v>
+      </c>
+      <c r="S2" s="9">
         <f t="shared" ref="S2:S22" si="8">ROUND(IMDIV(I2,J2),2)</f>
-        <v>102.54</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" s="8" t="s">
+        <v>88.31</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U2" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="45">
         <f t="shared" ref="V2:V22" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.2370955373978629</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9">
+        <v>82</v>
+      </c>
+      <c r="C3" s="9">
+        <v>34</v>
+      </c>
+      <c r="D3" s="9">
+        <v>16</v>
+      </c>
+      <c r="E3" s="9">
+        <v>8</v>
+      </c>
+      <c r="F3" s="9">
+        <v>88</v>
+      </c>
+      <c r="G3" s="9">
+        <v>748</v>
+      </c>
+      <c r="H3" s="9">
+        <v>21</v>
+      </c>
+      <c r="I3" s="9">
+        <v>8723</v>
+      </c>
+      <c r="J3" s="9">
+        <v>148</v>
+      </c>
+      <c r="K3" s="9">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L3" s="11">
+        <f t="shared" si="1"/>
+        <v>5.4054054054054057E-2</v>
+      </c>
+      <c r="M3" s="11">
+        <f t="shared" si="2"/>
+        <v>0.10810810810810811</v>
+      </c>
+      <c r="N3" s="9">
+        <f t="shared" si="3"/>
+        <v>0.59</v>
+      </c>
+      <c r="O3" s="9">
+        <f t="shared" si="4"/>
+        <v>5.05</v>
+      </c>
+      <c r="P3" s="9">
+        <f t="shared" si="5"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q3" s="9">
+        <f t="shared" si="6"/>
+        <v>0.93</v>
+      </c>
+      <c r="R3" s="9">
+        <f t="shared" si="7"/>
+        <v>41.46</v>
+      </c>
+      <c r="S3" s="9">
+        <f t="shared" si="8"/>
+        <v>58.94</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45">
+        <f t="shared" si="9"/>
+        <v>0.9489773727215588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6">
+        <v>112</v>
+      </c>
+      <c r="C4" s="6">
+        <v>73</v>
+      </c>
+      <c r="D4" s="6">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6">
+        <v>55</v>
+      </c>
+      <c r="G4" s="6">
+        <v>668</v>
+      </c>
+      <c r="H4" s="6">
+        <v>31</v>
+      </c>
+      <c r="I4" s="6">
+        <v>12100</v>
+      </c>
+      <c r="J4" s="6">
+        <v>118</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" si="0"/>
+        <v>0.95</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" si="1"/>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="2"/>
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" si="3"/>
+        <v>0.47</v>
+      </c>
+      <c r="O4" s="6">
+        <f t="shared" si="4"/>
+        <v>5.66</v>
+      </c>
+      <c r="P4" s="6">
+        <f t="shared" si="5"/>
+        <v>0.26</v>
+      </c>
+      <c r="Q4" s="6">
+        <f t="shared" si="6"/>
+        <v>2.04</v>
+      </c>
+      <c r="R4" s="6">
+        <f t="shared" si="7"/>
+        <v>65.180000000000007</v>
+      </c>
+      <c r="S4" s="6">
+        <f t="shared" si="8"/>
+        <v>102.54</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45">
+        <f t="shared" si="9"/>
         <v>1.4812861647615294</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B5" s="6">
         <v>57</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C5" s="6">
         <v>29</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D5" s="6">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E5" s="6">
         <v>2</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F5" s="6">
         <v>72</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G5" s="6">
         <v>41</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H5" s="6">
         <v>14</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I5" s="6">
         <v>6117</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J5" s="6">
         <v>118</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K5" s="6">
         <f t="shared" si="0"/>
         <v>0.48</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L5" s="7">
         <f t="shared" si="1"/>
         <v>1.6949152542372881E-2</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M5" s="7">
         <f t="shared" si="2"/>
         <v>8.4745762711864403E-2</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N5" s="6">
         <f t="shared" si="3"/>
         <v>0.61</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O5" s="6">
         <f t="shared" si="4"/>
         <v>0.35</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P5" s="6">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q5" s="6">
         <f t="shared" si="6"/>
         <v>0.79</v>
       </c>
-      <c r="R3" s="6">
+      <c r="R5" s="6">
         <f t="shared" si="7"/>
         <v>50.88</v>
       </c>
-      <c r="S3" s="6">
+      <c r="S5" s="6">
         <f t="shared" si="8"/>
         <v>51.84</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="45">
+      <c r="V5" s="45">
         <f t="shared" si="9"/>
         <v>0.85369255025620816</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="26">
+        <v>106</v>
+      </c>
+      <c r="C6" s="26">
+        <v>57</v>
+      </c>
+      <c r="D6" s="26">
+        <v>21</v>
+      </c>
+      <c r="E6" s="26">
+        <v>17</v>
+      </c>
+      <c r="F6" s="26">
+        <v>71</v>
+      </c>
+      <c r="G6" s="26">
+        <v>300</v>
+      </c>
+      <c r="H6" s="26">
+        <v>38</v>
+      </c>
+      <c r="I6" s="26">
+        <v>11765</v>
+      </c>
+      <c r="J6" s="26">
+        <v>136</v>
+      </c>
+      <c r="K6" s="27">
+        <f t="shared" si="0"/>
+        <v>0.78</v>
+      </c>
+      <c r="L6" s="28">
+        <f t="shared" si="1"/>
+        <v>0.125</v>
+      </c>
+      <c r="M6" s="28">
+        <f t="shared" si="2"/>
+        <v>0.15441176470588236</v>
+      </c>
+      <c r="N6" s="27">
+        <f t="shared" si="3"/>
+        <v>0.52</v>
+      </c>
+      <c r="O6" s="27">
+        <f t="shared" si="4"/>
+        <v>2.21</v>
+      </c>
+      <c r="P6" s="27">
+        <f t="shared" si="5"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q6" s="27">
+        <f t="shared" si="6"/>
+        <v>1.49</v>
+      </c>
+      <c r="R6" s="27">
+        <f t="shared" si="7"/>
+        <v>53.769999999999996</v>
+      </c>
+      <c r="S6" s="27">
+        <f t="shared" si="8"/>
+        <v>86.51</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="45">
+        <f t="shared" si="9"/>
+        <v>1.2719750341997265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="26">
+        <v>70</v>
+      </c>
+      <c r="C7" s="26">
+        <v>28</v>
+      </c>
+      <c r="D7" s="26">
+        <v>10</v>
+      </c>
+      <c r="E7" s="26">
+        <v>2</v>
+      </c>
+      <c r="F7" s="26">
+        <v>80</v>
+      </c>
+      <c r="G7" s="26">
+        <v>347</v>
+      </c>
+      <c r="H7" s="26">
+        <v>38</v>
+      </c>
+      <c r="I7" s="26">
+        <v>7963</v>
+      </c>
+      <c r="J7" s="26">
+        <v>125</v>
+      </c>
+      <c r="K7" s="27">
+        <f t="shared" si="0"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L7" s="28">
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="M7" s="28">
+        <f t="shared" si="2"/>
+        <v>0.08</v>
+      </c>
+      <c r="N7" s="27">
+        <f t="shared" si="3"/>
+        <v>0.64</v>
+      </c>
+      <c r="O7" s="27">
+        <f t="shared" si="4"/>
+        <v>2.78</v>
+      </c>
+      <c r="P7" s="27">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="Q7" s="27">
+        <f t="shared" si="6"/>
+        <v>0.88</v>
+      </c>
+      <c r="R7" s="27">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="S7" s="27">
+        <f t="shared" si="8"/>
+        <v>63.7</v>
+      </c>
+      <c r="T7" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="45">
+        <f t="shared" si="9"/>
+        <v>0.91847906976744187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B8" s="29">
         <v>108</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C8" s="29">
         <v>62</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D8" s="29">
         <v>35</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E8" s="29">
         <v>10</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F8" s="29">
         <v>60</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G8" s="29">
         <v>794</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H8" s="29">
         <v>15</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I8" s="29">
         <v>12350</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J8" s="29">
         <v>122</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K8" s="30">
         <f t="shared" si="0"/>
         <v>0.89</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L8" s="31">
         <f t="shared" si="1"/>
         <v>8.1967213114754092E-2</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M8" s="31">
         <f t="shared" si="2"/>
         <v>0.28688524590163933</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N8" s="30">
         <f t="shared" si="3"/>
         <v>0.49</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O8" s="30">
         <f t="shared" si="4"/>
         <v>6.51</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P8" s="30">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q8" s="30">
         <f t="shared" si="6"/>
         <v>1.8</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R8" s="30">
         <f t="shared" si="7"/>
         <v>57.410000000000004</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S8" s="30">
         <f t="shared" si="8"/>
         <v>101.23</v>
       </c>
-      <c r="T4" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="29" t="s">
+      <c r="T8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="U8" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="45">
+      <c r="V8" s="45">
         <f t="shared" si="9"/>
         <v>1.4309519634006862</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B9" s="29">
         <v>50</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C9" s="29">
         <v>18</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D9" s="29">
         <v>6</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E9" s="29">
         <v>3</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F9" s="29">
         <v>67</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G9" s="29">
         <v>233</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H9" s="29">
         <v>24</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I9" s="29">
         <v>5570</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J9" s="29">
         <v>122</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K9" s="30">
         <f t="shared" si="0"/>
         <v>0.41</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L9" s="31">
         <f t="shared" si="1"/>
         <v>2.4590163934426229E-2</v>
       </c>
-      <c r="M5" s="31">
+      <c r="M9" s="31">
         <f t="shared" si="2"/>
         <v>4.9180327868852458E-2</v>
       </c>
-      <c r="N5" s="30">
+      <c r="N9" s="30">
         <f t="shared" si="3"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="O5" s="30">
+      <c r="O9" s="30">
         <f t="shared" si="4"/>
         <v>1.91</v>
       </c>
-      <c r="P5" s="30">
+      <c r="P9" s="30">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-      <c r="Q5" s="30">
+      <c r="Q9" s="30">
         <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
-      <c r="R5" s="30">
+      <c r="R9" s="30">
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="S5" s="30">
+      <c r="S9" s="30">
         <f t="shared" si="8"/>
         <v>45.66</v>
       </c>
-      <c r="T5" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="29" t="s">
+      <c r="T9" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="U9" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="V5" s="45">
+      <c r="V9" s="45">
         <f t="shared" si="9"/>
         <v>0.85358520777735414</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="9">
-        <v>111</v>
-      </c>
-      <c r="C6" s="9">
-        <v>55</v>
-      </c>
-      <c r="D6" s="9">
-        <v>29</v>
-      </c>
-      <c r="E6" s="9">
-        <v>11</v>
-      </c>
-      <c r="F6" s="9">
-        <v>81</v>
-      </c>
-      <c r="G6" s="9">
-        <v>446</v>
-      </c>
-      <c r="H6" s="9">
-        <v>37</v>
-      </c>
-      <c r="I6" s="9">
-        <v>13070</v>
-      </c>
-      <c r="J6" s="9">
-        <v>148</v>
-      </c>
-      <c r="K6" s="9">
-        <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="L6" s="11">
-        <f t="shared" si="1"/>
-        <v>7.4324324324324328E-2</v>
-      </c>
-      <c r="M6" s="11">
-        <f t="shared" si="2"/>
-        <v>0.19594594594594594</v>
-      </c>
-      <c r="N6" s="9">
-        <f t="shared" si="3"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="O6" s="9">
-        <f t="shared" si="4"/>
-        <v>3.01</v>
-      </c>
-      <c r="P6" s="9">
-        <f t="shared" si="5"/>
-        <v>0.25</v>
-      </c>
-      <c r="Q6" s="9">
-        <f t="shared" si="6"/>
-        <v>1.37</v>
-      </c>
-      <c r="R6" s="9">
-        <f t="shared" si="7"/>
-        <v>49.55</v>
-      </c>
-      <c r="S6" s="9">
-        <f t="shared" si="8"/>
-        <v>88.31</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V6" s="45">
-        <f t="shared" si="9"/>
-        <v>1.2370955373978629</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9">
-        <v>82</v>
-      </c>
-      <c r="C7" s="9">
-        <v>34</v>
-      </c>
-      <c r="D7" s="9">
-        <v>16</v>
-      </c>
-      <c r="E7" s="9">
-        <v>8</v>
-      </c>
-      <c r="F7" s="9">
-        <v>88</v>
-      </c>
-      <c r="G7" s="9">
-        <v>748</v>
-      </c>
-      <c r="H7" s="9">
-        <v>21</v>
-      </c>
-      <c r="I7" s="9">
-        <v>8723</v>
-      </c>
-      <c r="J7" s="9">
-        <v>148</v>
-      </c>
-      <c r="K7" s="9">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="L7" s="11">
-        <f t="shared" si="1"/>
-        <v>5.4054054054054057E-2</v>
-      </c>
-      <c r="M7" s="11">
-        <f t="shared" si="2"/>
-        <v>0.10810810810810811</v>
-      </c>
-      <c r="N7" s="9">
-        <f t="shared" si="3"/>
-        <v>0.59</v>
-      </c>
-      <c r="O7" s="9">
-        <f t="shared" si="4"/>
-        <v>5.05</v>
-      </c>
-      <c r="P7" s="9">
-        <f t="shared" si="5"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q7" s="9">
-        <f t="shared" si="6"/>
-        <v>0.93</v>
-      </c>
-      <c r="R7" s="9">
-        <f t="shared" si="7"/>
-        <v>41.46</v>
-      </c>
-      <c r="S7" s="9">
-        <f t="shared" si="8"/>
-        <v>58.94</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V7" s="45">
-        <f t="shared" si="9"/>
-        <v>0.9489773727215588</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="26">
-        <v>106</v>
-      </c>
-      <c r="C8" s="26">
-        <v>57</v>
-      </c>
-      <c r="D8" s="26">
-        <v>21</v>
-      </c>
-      <c r="E8" s="26">
-        <v>17</v>
-      </c>
-      <c r="F8" s="26">
-        <v>71</v>
-      </c>
-      <c r="G8" s="26">
-        <v>300</v>
-      </c>
-      <c r="H8" s="26">
-        <v>38</v>
-      </c>
-      <c r="I8" s="26">
-        <v>11765</v>
-      </c>
-      <c r="J8" s="26">
-        <v>136</v>
-      </c>
-      <c r="K8" s="27">
-        <f t="shared" si="0"/>
-        <v>0.78</v>
-      </c>
-      <c r="L8" s="28">
-        <f t="shared" si="1"/>
-        <v>0.125</v>
-      </c>
-      <c r="M8" s="28">
-        <f t="shared" si="2"/>
-        <v>0.15441176470588236</v>
-      </c>
-      <c r="N8" s="27">
-        <f t="shared" si="3"/>
-        <v>0.52</v>
-      </c>
-      <c r="O8" s="27">
-        <f t="shared" si="4"/>
-        <v>2.21</v>
-      </c>
-      <c r="P8" s="27">
-        <f t="shared" si="5"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q8" s="27">
-        <f t="shared" si="6"/>
-        <v>1.49</v>
-      </c>
-      <c r="R8" s="27">
-        <f t="shared" si="7"/>
-        <v>53.769999999999996</v>
-      </c>
-      <c r="S8" s="27">
-        <f t="shared" si="8"/>
-        <v>86.51</v>
-      </c>
-      <c r="T8" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="V8" s="45">
-        <f t="shared" si="9"/>
-        <v>1.2719750341997265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="26">
-        <v>70</v>
-      </c>
-      <c r="C9" s="26">
-        <v>28</v>
-      </c>
-      <c r="D9" s="26">
-        <v>10</v>
-      </c>
-      <c r="E9" s="26">
-        <v>2</v>
-      </c>
-      <c r="F9" s="26">
-        <v>80</v>
-      </c>
-      <c r="G9" s="26">
-        <v>347</v>
-      </c>
-      <c r="H9" s="26">
-        <v>38</v>
-      </c>
-      <c r="I9" s="26">
-        <v>7963</v>
-      </c>
-      <c r="J9" s="26">
-        <v>125</v>
-      </c>
-      <c r="K9" s="27">
-        <f t="shared" si="0"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L9" s="28">
-        <f t="shared" si="1"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="M9" s="28">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
-      </c>
-      <c r="N9" s="27">
-        <f t="shared" si="3"/>
-        <v>0.64</v>
-      </c>
-      <c r="O9" s="27">
-        <f t="shared" si="4"/>
-        <v>2.78</v>
-      </c>
-      <c r="P9" s="27">
-        <f t="shared" si="5"/>
-        <v>0.3</v>
-      </c>
-      <c r="Q9" s="27">
-        <f t="shared" si="6"/>
-        <v>0.88</v>
-      </c>
-      <c r="R9" s="27">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="S9" s="27">
-        <f t="shared" si="8"/>
-        <v>63.7</v>
-      </c>
-      <c r="T9" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="U9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="V9" s="45">
-        <f t="shared" si="9"/>
-        <v>0.91847906976744187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
         <v>29</v>
       </c>
@@ -3599,7 +3681,7 @@
         <v>1.3230300721732158</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
         <v>30</v>
       </c>
@@ -3677,7 +3759,7 @@
         <v>0.91810384923817168</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
         <v>34</v>
       </c>
@@ -3748,14 +3830,14 @@
         <v>46</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V12" s="45">
         <f t="shared" si="9"/>
         <v>1.1229436428450179</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
         <v>35</v>
       </c>
@@ -3833,7 +3915,7 @@
         <v>0.96065566117806833</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
         <v>41</v>
       </c>
@@ -3911,7 +3993,7 @@
         <v>0.92396443228454173</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
         <v>26</v>
       </c>
@@ -3989,7 +4071,7 @@
         <v>0.74032079343365265</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
         <v>22</v>
       </c>
@@ -4067,7 +4149,7 @@
         <v>0.94279099081493056</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>23</v>
       </c>
@@ -4145,7 +4227,7 @@
         <v>0.8162185851084619</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
         <v>36</v>
       </c>
@@ -4223,7 +4305,7 @@
         <v>0.95318604651162786</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>25</v>
       </c>
@@ -4301,7 +4383,7 @@
         <v>0.66132189449801471</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
         <v>33</v>
       </c>
@@ -4379,7 +4461,7 @@
         <v>0.9755444352159468</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
         <v>21</v>
       </c>
@@ -4457,7 +4539,7 @@
         <v>0.73936507022795306</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="46" t="s">
         <v>43</v>
       </c>
@@ -4536,6 +4618,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
+    <sortCondition sortBy="cellColor" ref="S9:S22" dxfId="8"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4543,14 +4628,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF723AF-29F9-4B27-9BD4-7CDF4E72CFCA}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4618,559 +4703,595 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="9">
+        <v>65</v>
+      </c>
+      <c r="C2" s="9">
+        <v>32</v>
+      </c>
+      <c r="D2" s="9">
+        <v>19</v>
+      </c>
+      <c r="E2" s="9">
+        <v>5</v>
+      </c>
+      <c r="F2" s="9">
+        <v>57</v>
+      </c>
+      <c r="G2" s="9">
+        <v>455</v>
+      </c>
+      <c r="H2" s="9">
+        <v>22</v>
+      </c>
+      <c r="I2" s="9">
+        <v>7731</v>
+      </c>
+      <c r="J2" s="9">
+        <v>93</v>
+      </c>
+      <c r="K2" s="9">
+        <f t="shared" ref="K2:K13" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <v>0.7</v>
+      </c>
+      <c r="L2" s="11">
+        <f t="shared" ref="L2:L13" si="1">E2/J2</f>
+        <v>5.3763440860215055E-2</v>
+      </c>
+      <c r="M2" s="11">
+        <f t="shared" ref="M2:M13" si="2">D2/J2</f>
+        <v>0.20430107526881722</v>
+      </c>
+      <c r="N2" s="9">
+        <f t="shared" ref="N2:N13" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <v>0.61</v>
+      </c>
+      <c r="O2" s="9">
+        <f t="shared" ref="O2:O13" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="P2" s="9">
+        <f t="shared" ref="P2:P13" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <v>0.24</v>
+      </c>
+      <c r="Q2" s="9">
+        <f t="shared" ref="Q2:Q13" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R2" s="9">
+        <f t="shared" ref="R2:R13" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>49.230000000000004</v>
+      </c>
+      <c r="S2" s="9">
+        <f t="shared" ref="S2:S13" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <v>83.13</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45">
+        <f t="shared" ref="V2:V13" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.1304791197799449</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9">
+        <v>60</v>
+      </c>
+      <c r="C3" s="9">
+        <v>23</v>
+      </c>
+      <c r="D3" s="9">
+        <v>15</v>
+      </c>
+      <c r="E3" s="9">
+        <v>7</v>
+      </c>
+      <c r="F3" s="9">
+        <v>53</v>
+      </c>
+      <c r="G3" s="9">
+        <v>436</v>
+      </c>
+      <c r="H3" s="9">
+        <v>7</v>
+      </c>
+      <c r="I3" s="9">
+        <v>6294</v>
+      </c>
+      <c r="J3" s="9">
+        <v>93</v>
+      </c>
+      <c r="K3" s="9">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="L3" s="11">
+        <f t="shared" si="1"/>
+        <v>7.5268817204301078E-2</v>
+      </c>
+      <c r="M3" s="11">
+        <f t="shared" si="2"/>
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="N3" s="9">
+        <f t="shared" si="3"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O3" s="9">
+        <f t="shared" si="4"/>
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="P3" s="9">
+        <f t="shared" si="5"/>
+        <v>0.08</v>
+      </c>
+      <c r="Q3" s="9">
+        <f t="shared" si="6"/>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R3" s="9">
+        <f t="shared" si="7"/>
+        <v>38.33</v>
+      </c>
+      <c r="S3" s="9">
+        <f t="shared" si="8"/>
+        <v>67.680000000000007</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45">
+        <f t="shared" si="9"/>
+        <v>1.0641670417604403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="26">
+        <v>30</v>
+      </c>
+      <c r="C4" s="26">
+        <v>11</v>
+      </c>
+      <c r="D4" s="26">
+        <v>8</v>
+      </c>
+      <c r="E4" s="26">
+        <v>3</v>
+      </c>
+      <c r="F4" s="26">
+        <v>13</v>
+      </c>
+      <c r="G4" s="26">
+        <v>33</v>
+      </c>
+      <c r="H4" s="26">
+        <v>10</v>
+      </c>
+      <c r="I4" s="26">
+        <v>3082</v>
+      </c>
+      <c r="J4" s="26">
+        <v>32</v>
+      </c>
+      <c r="K4" s="27">
+        <f t="shared" si="0"/>
+        <v>0.94</v>
+      </c>
+      <c r="L4" s="28">
+        <f t="shared" si="1"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="M4" s="28">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="N4" s="27">
+        <f t="shared" si="3"/>
+        <v>0.41</v>
+      </c>
+      <c r="O4" s="27">
+        <f t="shared" si="4"/>
+        <v>1.03</v>
+      </c>
+      <c r="P4" s="27">
+        <f t="shared" si="5"/>
+        <v>0.31</v>
+      </c>
+      <c r="Q4" s="27">
+        <f t="shared" si="6"/>
+        <v>2.31</v>
+      </c>
+      <c r="R4" s="27">
+        <f t="shared" si="7"/>
+        <v>36.67</v>
+      </c>
+      <c r="S4" s="27">
+        <f t="shared" si="8"/>
+        <v>96.31</v>
+      </c>
+      <c r="T4" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45">
+        <f t="shared" si="9"/>
+        <v>1.5107034883720929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="26">
+        <v>17</v>
+      </c>
+      <c r="C5" s="26">
+        <v>9</v>
+      </c>
+      <c r="D5" s="26">
+        <v>3</v>
+      </c>
+      <c r="E5" s="26">
+        <v>0</v>
+      </c>
+      <c r="F5" s="26">
+        <v>18</v>
+      </c>
+      <c r="G5" s="26">
+        <v>89</v>
+      </c>
+      <c r="H5" s="26">
+        <v>15</v>
+      </c>
+      <c r="I5" s="26">
+        <v>2016</v>
+      </c>
+      <c r="J5" s="26">
+        <v>32</v>
+      </c>
+      <c r="K5" s="27">
+        <f t="shared" si="0"/>
+        <v>0.53</v>
+      </c>
+      <c r="L5" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="28">
+        <f t="shared" si="2"/>
+        <v>9.375E-2</v>
+      </c>
+      <c r="N5" s="27">
+        <f t="shared" si="3"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O5" s="27">
+        <f t="shared" si="4"/>
+        <v>2.78</v>
+      </c>
+      <c r="P5" s="27">
+        <f t="shared" si="5"/>
+        <v>0.47</v>
+      </c>
+      <c r="Q5" s="27">
+        <f t="shared" si="6"/>
+        <v>0.94</v>
+      </c>
+      <c r="R5" s="27">
+        <f t="shared" si="7"/>
+        <v>52.94</v>
+      </c>
+      <c r="S5" s="27">
+        <f t="shared" si="8"/>
+        <v>63</v>
+      </c>
+      <c r="T5" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45">
+        <f t="shared" si="9"/>
+        <v>0.99196075581395349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6" t="e">
-        <f t="shared" ref="K2:K13" si="0">ROUND(IMDIV(B2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L2" s="7" t="e">
-        <f t="shared" ref="L2:L13" si="1">E2/J2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M2" s="7" t="e">
-        <f t="shared" ref="M2:M13" si="2">D2/J2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N2" s="6" t="e">
-        <f t="shared" ref="N2:N13" si="3">ROUND(IMDIV(F2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="O2" s="6" t="e">
-        <f t="shared" ref="O2:O13" si="4">ROUND(IMDIV(G2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="P2" s="6" t="e">
-        <f t="shared" ref="P2:P13" si="5">ROUND(IMDIV(H2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q2" s="6" t="e">
-        <f t="shared" ref="Q2:Q13" si="6">ROUND(IMDIV(B2,F2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R2" s="6" t="e">
-        <f t="shared" ref="R2:R13" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="S2" s="6" t="e">
-        <f t="shared" ref="S2:S13" si="8">ROUND(IMDIV(I2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" s="45" t="e">
-        <f t="shared" ref="V2:V13" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="e">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="L3" s="7" t="e">
+      <c r="L6" s="7" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M3" s="7" t="e">
+      <c r="M6" s="7" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N3" s="6" t="e">
+      <c r="N6" s="6" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="O3" s="6" t="e">
+      <c r="O6" s="6" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="P3" s="6" t="e">
+      <c r="P6" s="6" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="Q3" s="6" t="e">
+      <c r="Q6" s="6" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="R3" s="6" t="e">
+      <c r="R6" s="6" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="S3" s="6" t="e">
+      <c r="S6" s="6" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="45" t="e">
+      <c r="V6" s="45" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="30" t="e">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="e">
         <f t="shared" si="0"/>
         <v>#NUM!</v>
       </c>
-      <c r="L4" s="31" t="e">
+      <c r="L7" s="7" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M4" s="31" t="e">
+      <c r="M7" s="7" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N4" s="30" t="e">
+      <c r="N7" s="6" t="e">
         <f t="shared" si="3"/>
         <v>#NUM!</v>
       </c>
-      <c r="O4" s="30" t="e">
+      <c r="O7" s="6" t="e">
         <f t="shared" si="4"/>
         <v>#NUM!</v>
       </c>
-      <c r="P4" s="30" t="e">
+      <c r="P7" s="6" t="e">
         <f t="shared" si="5"/>
         <v>#NUM!</v>
       </c>
-      <c r="Q4" s="30" t="e">
+      <c r="Q7" s="6" t="e">
         <f t="shared" si="6"/>
         <v>#NUM!</v>
       </c>
-      <c r="R4" s="30" t="e">
+      <c r="R7" s="6" t="e">
         <f t="shared" si="7"/>
         <v>#NUM!</v>
       </c>
-      <c r="S4" s="30" t="e">
+      <c r="S7" s="6" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="T4" s="29" t="s">
+      <c r="T7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="U7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="45" t="e">
+      <c r="V7" s="45" t="e">
         <f t="shared" si="9"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="30" t="e">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="29">
+        <v>33</v>
+      </c>
+      <c r="C8" s="29">
+        <v>17</v>
+      </c>
+      <c r="D8" s="29">
+        <v>7</v>
+      </c>
+      <c r="E8" s="29">
+        <v>3</v>
+      </c>
+      <c r="F8" s="29">
+        <v>33</v>
+      </c>
+      <c r="G8" s="29">
+        <v>50</v>
+      </c>
+      <c r="H8" s="29">
+        <v>2</v>
+      </c>
+      <c r="I8" s="29">
+        <v>3882</v>
+      </c>
+      <c r="J8" s="29">
+        <v>49</v>
+      </c>
+      <c r="K8" s="30">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L5" s="31" t="e">
+        <v>0.67</v>
+      </c>
+      <c r="L8" s="31">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M5" s="31" t="e">
+        <v>6.1224489795918366E-2</v>
+      </c>
+      <c r="M8" s="31">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="30" t="e">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="N8" s="30">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O5" s="30" t="e">
+        <v>0.67</v>
+      </c>
+      <c r="O8" s="30">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P5" s="30" t="e">
+        <v>1.02</v>
+      </c>
+      <c r="P8" s="30">
         <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q5" s="30" t="e">
+        <v>0.04</v>
+      </c>
+      <c r="Q8" s="30">
         <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R5" s="30" t="e">
+        <v>1</v>
+      </c>
+      <c r="R8" s="30">
         <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S5" s="30" t="e">
+        <v>51.519999999999996</v>
+      </c>
+      <c r="S8" s="30">
         <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T5" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="V5" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="9">
-        <v>34</v>
-      </c>
-      <c r="C6" s="9">
-        <v>14</v>
-      </c>
-      <c r="D6" s="9">
-        <v>11</v>
-      </c>
-      <c r="E6" s="9">
-        <v>3</v>
-      </c>
-      <c r="F6" s="9">
-        <v>25</v>
-      </c>
-      <c r="G6" s="9">
-        <v>343</v>
-      </c>
-      <c r="H6" s="9">
-        <v>12</v>
-      </c>
-      <c r="I6" s="9">
-        <v>3379</v>
-      </c>
-      <c r="J6" s="9">
-        <v>44</v>
-      </c>
-      <c r="K6" s="9">
-        <f t="shared" si="0"/>
-        <v>0.77</v>
-      </c>
-      <c r="L6" s="11">
-        <f t="shared" si="1"/>
-        <v>6.8181818181818177E-2</v>
-      </c>
-      <c r="M6" s="11">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-      <c r="N6" s="9">
-        <f t="shared" si="3"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O6" s="9">
-        <f t="shared" si="4"/>
-        <v>7.8</v>
-      </c>
-      <c r="P6" s="9">
-        <f t="shared" si="5"/>
-        <v>0.27</v>
-      </c>
-      <c r="Q6" s="9">
-        <f t="shared" si="6"/>
-        <v>1.36</v>
-      </c>
-      <c r="R6" s="9">
-        <f t="shared" si="7"/>
-        <v>41.18</v>
-      </c>
-      <c r="S6" s="9">
-        <f t="shared" si="8"/>
-        <v>76.8</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V6" s="45">
-        <f t="shared" si="9"/>
-        <v>1.1848456659619451</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9">
-        <v>25</v>
-      </c>
-      <c r="C7" s="9">
-        <v>9</v>
-      </c>
-      <c r="D7" s="9">
-        <v>7</v>
-      </c>
-      <c r="E7" s="9">
-        <v>2</v>
-      </c>
-      <c r="F7" s="9">
-        <v>27</v>
-      </c>
-      <c r="G7" s="9">
-        <v>320</v>
-      </c>
-      <c r="H7" s="9">
-        <v>5</v>
-      </c>
-      <c r="I7" s="9">
-        <v>3473</v>
-      </c>
-      <c r="J7" s="9">
-        <v>44</v>
-      </c>
-      <c r="K7" s="9">
-        <f t="shared" si="0"/>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L7" s="11">
-        <f t="shared" si="1"/>
-        <v>4.5454545454545456E-2</v>
-      </c>
-      <c r="M7" s="11">
-        <f t="shared" si="2"/>
-        <v>0.15909090909090909</v>
-      </c>
-      <c r="N7" s="9">
-        <f t="shared" si="3"/>
-        <v>0.61</v>
-      </c>
-      <c r="O7" s="9">
-        <f t="shared" si="4"/>
-        <v>7.27</v>
-      </c>
-      <c r="P7" s="9">
-        <f t="shared" si="5"/>
-        <v>0.11</v>
-      </c>
-      <c r="Q7" s="9">
-        <f t="shared" si="6"/>
-        <v>0.93</v>
-      </c>
-      <c r="R7" s="9">
-        <f t="shared" si="7"/>
-        <v>36</v>
-      </c>
-      <c r="S7" s="9">
-        <f t="shared" si="8"/>
-        <v>78.930000000000007</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V7" s="45">
-        <f t="shared" si="9"/>
-        <v>1.0394799154334038</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="26">
-        <v>30</v>
-      </c>
-      <c r="C8" s="26">
-        <v>11</v>
-      </c>
-      <c r="D8" s="26">
-        <v>8</v>
-      </c>
-      <c r="E8" s="26">
-        <v>3</v>
-      </c>
-      <c r="F8" s="26">
-        <v>13</v>
-      </c>
-      <c r="G8" s="26">
-        <v>33</v>
-      </c>
-      <c r="H8" s="26">
-        <v>10</v>
-      </c>
-      <c r="I8" s="26">
-        <v>3082</v>
-      </c>
-      <c r="J8" s="26">
-        <v>32</v>
-      </c>
-      <c r="K8" s="27">
-        <f t="shared" si="0"/>
-        <v>0.94</v>
-      </c>
-      <c r="L8" s="28">
-        <f t="shared" si="1"/>
-        <v>9.375E-2</v>
-      </c>
-      <c r="M8" s="28">
-        <f t="shared" si="2"/>
-        <v>0.25</v>
-      </c>
-      <c r="N8" s="27">
-        <f t="shared" si="3"/>
-        <v>0.41</v>
-      </c>
-      <c r="O8" s="27">
-        <f t="shared" si="4"/>
-        <v>1.03</v>
-      </c>
-      <c r="P8" s="27">
-        <f t="shared" si="5"/>
-        <v>0.31</v>
-      </c>
-      <c r="Q8" s="27">
-        <f t="shared" si="6"/>
-        <v>2.31</v>
-      </c>
-      <c r="R8" s="27">
-        <f t="shared" si="7"/>
-        <v>36.67</v>
-      </c>
-      <c r="S8" s="27">
-        <f t="shared" si="8"/>
-        <v>96.31</v>
-      </c>
-      <c r="T8" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" s="26" t="s">
+        <v>79.22</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="U8" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V8" s="45">
         <f t="shared" si="9"/>
-        <v>1.5107034883720929</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="26">
-        <v>17</v>
-      </c>
-      <c r="C9" s="26">
-        <v>9</v>
-      </c>
-      <c r="D9" s="26">
-        <v>3</v>
-      </c>
-      <c r="E9" s="26">
-        <v>0</v>
-      </c>
-      <c r="F9" s="26">
-        <v>18</v>
-      </c>
-      <c r="G9" s="26">
-        <v>89</v>
-      </c>
-      <c r="H9" s="26">
-        <v>15</v>
-      </c>
-      <c r="I9" s="26">
-        <v>2016</v>
-      </c>
-      <c r="J9" s="26">
-        <v>32</v>
-      </c>
-      <c r="K9" s="27">
+        <v>1.016424299952539</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="29">
+        <v>25</v>
+      </c>
+      <c r="C9" s="29">
+        <v>13</v>
+      </c>
+      <c r="D9" s="29">
+        <v>4</v>
+      </c>
+      <c r="E9" s="29">
+        <v>1</v>
+      </c>
+      <c r="F9" s="29">
+        <v>33</v>
+      </c>
+      <c r="G9" s="29">
+        <v>106</v>
+      </c>
+      <c r="H9" s="29">
+        <v>10</v>
+      </c>
+      <c r="I9" s="29">
+        <v>2884</v>
+      </c>
+      <c r="J9" s="29">
+        <v>49</v>
+      </c>
+      <c r="K9" s="30">
         <f t="shared" si="0"/>
-        <v>0.53</v>
-      </c>
-      <c r="L9" s="28">
+        <v>0.51</v>
+      </c>
+      <c r="L9" s="31">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="28">
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="M9" s="31">
         <f t="shared" si="2"/>
-        <v>9.375E-2</v>
-      </c>
-      <c r="N9" s="27">
+        <v>8.1632653061224483E-2</v>
+      </c>
+      <c r="N9" s="30">
         <f t="shared" si="3"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="O9" s="27">
+        <v>0.67</v>
+      </c>
+      <c r="O9" s="30">
         <f t="shared" si="4"/>
-        <v>2.78</v>
-      </c>
-      <c r="P9" s="27">
+        <v>2.16</v>
+      </c>
+      <c r="P9" s="30">
         <f t="shared" si="5"/>
-        <v>0.47</v>
-      </c>
-      <c r="Q9" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="Q9" s="30">
         <f t="shared" si="6"/>
-        <v>0.94</v>
-      </c>
-      <c r="R9" s="27">
+        <v>0.76</v>
+      </c>
+      <c r="R9" s="30">
         <f t="shared" si="7"/>
-        <v>52.94</v>
-      </c>
-      <c r="S9" s="27">
+        <v>52</v>
+      </c>
+      <c r="S9" s="30">
         <f t="shared" si="8"/>
-        <v>63</v>
-      </c>
-      <c r="T9" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="U9" s="26" t="s">
+        <v>58.86</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="U9" s="29" t="s">
         <v>24</v>
       </c>
       <c r="V9" s="45">
         <f t="shared" si="9"/>
-        <v>0.99196075581395349</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+        <v>0.84225723777883243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
         <v>29</v>
       </c>
@@ -5241,14 +5362,14 @@
         <v>46</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V10" s="45">
         <f t="shared" si="9"/>
         <v>1.0144622093023257</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
         <v>30</v>
       </c>
@@ -5326,7 +5447,7 @@
         <v>0.56878779069767438</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
         <v>34</v>
       </c>
@@ -5397,14 +5518,14 @@
         <v>46</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V12" s="45">
         <f t="shared" si="9"/>
         <v>1.129365750528541</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
         <v>35</v>
       </c>
@@ -5482,7 +5603,7 @@
         <v>0.73772832980972503</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="52"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -5506,7 +5627,7 @@
       <c r="U14" s="5"/>
       <c r="V14" s="55"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="52"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -5530,7 +5651,7 @@
       <c r="U15" s="5"/>
       <c r="V15" s="55"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="56"/>
       <c r="B16" s="57"/>
       <c r="C16" s="57"/>
@@ -5554,7 +5675,7 @@
       <c r="U16" s="57"/>
       <c r="V16" s="55"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="56"/>
       <c r="B17" s="57"/>
       <c r="C17" s="57"/>
@@ -5578,7 +5699,7 @@
       <c r="U17" s="57"/>
       <c r="V17" s="55"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="56"/>
       <c r="B18" s="59"/>
       <c r="C18" s="59"/>
@@ -5602,7 +5723,7 @@
       <c r="U18" s="57"/>
       <c r="V18" s="55"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="56"/>
       <c r="B19" s="59"/>
       <c r="C19" s="59"/>
@@ -5626,7 +5747,7 @@
       <c r="U19" s="57"/>
       <c r="V19" s="55"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="60"/>
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
@@ -5650,7 +5771,7 @@
       <c r="U20" s="61"/>
       <c r="V20" s="55"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="60"/>
       <c r="B21" s="53"/>
       <c r="C21" s="53"/>
@@ -5674,7 +5795,7 @@
       <c r="U21" s="61"/>
       <c r="V21" s="55"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -5698,6 +5819,9 @@
       <c r="V22" s="55"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V13">
+    <sortCondition sortBy="cellColor" ref="R8:R13" dxfId="7"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5705,17 +5829,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C7BC6-1079-408F-93C8-005DF99ABE1B}">
   <dimension ref="A1:V24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5783,7 +5907,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="36" t="s">
         <v>31</v>
       </c>
@@ -5861,7 +5985,7 @@
         <v>1.1848456659619451</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
         <v>32</v>
       </c>
@@ -5939,7 +6063,7 @@
         <v>1.0394799154334038</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>34</v>
       </c>
@@ -6010,14 +6134,14 @@
         <v>46</v>
       </c>
       <c r="U4" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V4" s="45">
         <f t="shared" si="9"/>
         <v>1.129365750528541</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
         <v>35</v>
       </c>
@@ -6095,7 +6219,7 @@
         <v>0.73772832980972503</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
         <v>37</v>
       </c>
@@ -6173,7 +6297,7 @@
         <v>1.5107034883720929</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>38</v>
       </c>
@@ -6251,7 +6375,7 @@
         <v>0.99196075581395349</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>29</v>
       </c>
@@ -6322,14 +6446,14 @@
         <v>46</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V8" s="45">
         <f t="shared" si="9"/>
         <v>1.0144622093023257</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
         <v>30</v>
       </c>
@@ -6407,7 +6531,7 @@
         <v>0.56878779069767438</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="52" t="s">
         <v>58</v>
       </c>
@@ -6433,7 +6557,7 @@
       <c r="U10" s="5"/>
       <c r="V10" s="55"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="70" t="s">
         <v>56</v>
       </c>
@@ -6483,7 +6607,7 @@
       <c r="U11" s="5"/>
       <c r="V11" s="55"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>31</v>
       </c>
@@ -6533,7 +6657,7 @@
       <c r="U12" s="57"/>
       <c r="V12" s="55"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="65" t="s">
         <v>32</v>
       </c>
@@ -6583,7 +6707,7 @@
       <c r="U13" s="57"/>
       <c r="V13" s="55"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="71" t="s">
         <v>57</v>
       </c>
@@ -6609,7 +6733,7 @@
       <c r="U14" s="57"/>
       <c r="V14" s="55"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="65" t="s">
         <v>34</v>
       </c>
@@ -6659,7 +6783,7 @@
       <c r="U15" s="57"/>
       <c r="V15" s="55"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>35</v>
       </c>
@@ -6709,7 +6833,7 @@
       <c r="U16" s="61"/>
       <c r="V16" s="55"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="60"/>
       <c r="B17" s="53"/>
       <c r="C17" s="53"/>
@@ -6733,7 +6857,7 @@
       <c r="U17" s="61"/>
       <c r="V17" s="55"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>61</v>
       </c>
@@ -6759,7 +6883,7 @@
       <c r="U18" s="5"/>
       <c r="V18" s="55"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>62</v>
       </c>
@@ -6800,12 +6924,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="66">
         <v>17</v>
@@ -6841,12 +6965,12 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="65" t="s">
         <v>38</v>
       </c>
       <c r="B21" s="62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="69">
         <v>-1</v>
@@ -6882,7 +7006,7 @@
         <v>52.94</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="74" t="s">
         <v>57</v>
       </c>
@@ -6899,12 +7023,12 @@
       <c r="L22" s="62"/>
       <c r="M22" s="62"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="65" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="66">
         <v>-1</v>
@@ -6940,12 +7064,12 @@
         <v>47.620000000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="69">
         <v>-15</v>
@@ -6983,7 +7107,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V9">
-    <sortCondition sortBy="cellColor" ref="A5:A9" dxfId="0"/>
+    <sortCondition sortBy="cellColor" ref="A5:A9" dxfId="6"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6992,14 +7116,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40897AC2-0114-4A6D-BFFC-5EDF88F8CE8F}">
   <dimension ref="A1:V24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7067,367 +7192,439 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="29">
+        <v>33</v>
+      </c>
+      <c r="C2" s="29">
+        <v>17</v>
+      </c>
+      <c r="D2" s="29">
+        <v>7</v>
+      </c>
+      <c r="E2" s="29">
+        <v>3</v>
+      </c>
+      <c r="F2" s="29">
+        <v>33</v>
+      </c>
+      <c r="G2" s="29">
+        <v>50</v>
+      </c>
+      <c r="H2" s="29">
+        <v>2</v>
+      </c>
+      <c r="I2" s="29">
+        <v>3882</v>
+      </c>
+      <c r="J2" s="29">
+        <v>49</v>
+      </c>
+      <c r="K2" s="30">
+        <f>ROUND(IMDIV(B2,J2),2)</f>
+        <v>0.67</v>
+      </c>
+      <c r="L2" s="31">
+        <f>E2/J2</f>
+        <v>6.1224489795918366E-2</v>
+      </c>
+      <c r="M2" s="31">
+        <f>D2/J2</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="N2" s="30">
+        <f>ROUND(IMDIV(F2,J2),2)</f>
+        <v>0.67</v>
+      </c>
+      <c r="O2" s="30">
+        <f>ROUND(IMDIV(G2,J2),2)</f>
+        <v>1.02</v>
+      </c>
+      <c r="P2" s="30">
+        <f>ROUND(IMDIV(H2,J2),2)</f>
+        <v>0.04</v>
+      </c>
+      <c r="Q2" s="30">
+        <f>ROUND(IMDIV(B2,F2),2)</f>
+        <v>1</v>
+      </c>
+      <c r="R2" s="30">
+        <f>ROUND(IMDIV(C2,B2),4)*100</f>
+        <v>51.519999999999996</v>
+      </c>
+      <c r="S2" s="30">
+        <f>ROUND(IMDIV(I2,J2),2)</f>
+        <v>79.22</v>
+      </c>
+      <c r="T2" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="45">
+        <f>((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>1.016424299952539</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="29">
+        <v>25</v>
+      </c>
+      <c r="C3" s="29">
+        <v>13</v>
+      </c>
+      <c r="D3" s="29">
+        <v>4</v>
+      </c>
+      <c r="E3" s="29">
+        <v>1</v>
+      </c>
+      <c r="F3" s="29">
+        <v>33</v>
+      </c>
+      <c r="G3" s="29">
+        <v>106</v>
+      </c>
+      <c r="H3" s="29">
+        <v>10</v>
+      </c>
+      <c r="I3" s="29">
+        <v>2884</v>
+      </c>
+      <c r="J3" s="29">
+        <v>49</v>
+      </c>
+      <c r="K3" s="30">
+        <f>ROUND(IMDIV(B3,J3),2)</f>
+        <v>0.51</v>
+      </c>
+      <c r="L3" s="31">
+        <f>E3/J3</f>
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="M3" s="31">
+        <f>D3/J3</f>
+        <v>8.1632653061224483E-2</v>
+      </c>
+      <c r="N3" s="30">
+        <f>ROUND(IMDIV(F3,J3),2)</f>
+        <v>0.67</v>
+      </c>
+      <c r="O3" s="30">
+        <f>ROUND(IMDIV(G3,J3),2)</f>
+        <v>2.16</v>
+      </c>
+      <c r="P3" s="30">
+        <f>ROUND(IMDIV(H3,J3),2)</f>
+        <v>0.2</v>
+      </c>
+      <c r="Q3" s="30">
+        <f>ROUND(IMDIV(B3,F3),2)</f>
+        <v>0.76</v>
+      </c>
+      <c r="R3" s="30">
+        <f>ROUND(IMDIV(C3,B3),4)*100</f>
+        <v>52</v>
+      </c>
+      <c r="S3" s="30">
+        <f>ROUND(IMDIV(I3,J3),2)</f>
+        <v>58.86</v>
+      </c>
+      <c r="T3" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="45">
+        <f>((K3/2.5)+(M3/4)+(L3/5)-(N3)+(S3/215)+(P3/20))+1</f>
+        <v>0.84225723777883243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="9">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9">
+        <v>18</v>
+      </c>
+      <c r="D4" s="9">
+        <v>8</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>32</v>
+      </c>
+      <c r="G4" s="9">
+        <v>112</v>
+      </c>
+      <c r="H4" s="9">
+        <v>10</v>
+      </c>
+      <c r="I4" s="9">
+        <v>4352</v>
+      </c>
+      <c r="J4" s="9">
+        <v>49</v>
+      </c>
+      <c r="K4" s="9">
+        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <v>0.63</v>
+      </c>
+      <c r="L4" s="11">
+        <f>E4/J4</f>
+        <v>4.0816326530612242E-2</v>
+      </c>
+      <c r="M4" s="11">
+        <f>D4/J4</f>
+        <v>0.16326530612244897</v>
+      </c>
+      <c r="N4" s="9">
+        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <v>0.65</v>
+      </c>
+      <c r="O4" s="9">
+        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <v>2.29</v>
+      </c>
+      <c r="P4" s="9">
+        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="9">
+        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <v>0.97</v>
+      </c>
+      <c r="R4" s="9">
+        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <v>58.06</v>
+      </c>
+      <c r="S4" s="9">
+        <f>ROUND(IMDIV(I4,J4),2)</f>
+        <v>88.82</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="45">
+        <f>((K4/2.5)+(M4/4)+(L4/5)-(N4)+(S4/215)+(P4/20))+1</f>
+        <v>1.074095870906502</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="9">
+        <v>35</v>
+      </c>
+      <c r="C5" s="9">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9">
+        <v>8</v>
+      </c>
+      <c r="E5" s="9">
+        <v>5</v>
+      </c>
+      <c r="F5" s="9">
+        <v>26</v>
+      </c>
+      <c r="G5" s="9">
+        <v>116</v>
+      </c>
+      <c r="H5" s="9">
+        <v>2</v>
+      </c>
+      <c r="I5" s="9">
+        <v>2821</v>
+      </c>
+      <c r="J5" s="9">
+        <v>49</v>
+      </c>
+      <c r="K5" s="9">
+        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <v>0.71</v>
+      </c>
+      <c r="L5" s="11">
+        <f>E5/J5</f>
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="M5" s="11">
+        <f>D5/J5</f>
+        <v>0.16326530612244897</v>
+      </c>
+      <c r="N5" s="9">
+        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <v>0.53</v>
+      </c>
+      <c r="O5" s="9">
+        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <v>2.37</v>
+      </c>
+      <c r="P5" s="9">
+        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <v>0.04</v>
+      </c>
+      <c r="Q5" s="9">
+        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <v>1.35</v>
+      </c>
+      <c r="R5" s="9">
+        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <v>40</v>
+      </c>
+      <c r="S5" s="9">
+        <f>ROUND(IMDIV(I5,J5),2)</f>
+        <v>57.57</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="45">
+        <f>((K5/2.5)+(M5/4)+(L5/5)-(N5)+(S5/215)+(P5/20))+1</f>
+        <v>1.0849919316563834</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6" t="e">
-        <f t="shared" ref="K2:K5" si="0">ROUND(IMDIV(B2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L2" s="7" t="e">
-        <f t="shared" ref="L2:L5" si="1">E2/J2</f>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6" t="e">
+        <f>ROUND(IMDIV(B6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L6" s="7" t="e">
+        <f>E6/J6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M2" s="7" t="e">
-        <f t="shared" ref="M2:M5" si="2">D2/J2</f>
+      <c r="M6" s="7" t="e">
+        <f>D6/J6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N2" s="6" t="e">
-        <f t="shared" ref="N2:N5" si="3">ROUND(IMDIV(F2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="O2" s="6" t="e">
-        <f t="shared" ref="O2:O5" si="4">ROUND(IMDIV(G2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="P2" s="6" t="e">
-        <f t="shared" ref="P2:P5" si="5">ROUND(IMDIV(H2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q2" s="6" t="e">
-        <f t="shared" ref="Q2:Q5" si="6">ROUND(IMDIV(B2,F2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R2" s="6" t="e">
-        <f t="shared" ref="R2:R5" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="S2" s="6" t="e">
-        <f t="shared" ref="S2:S5" si="8">ROUND(IMDIV(I2,J2),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="T2" s="6" t="s">
+      <c r="N6" s="6" t="e">
+        <f>ROUND(IMDIV(F6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O6" s="6" t="e">
+        <f>ROUND(IMDIV(G6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P6" s="6" t="e">
+        <f>ROUND(IMDIV(H6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q6" s="6" t="e">
+        <f>ROUND(IMDIV(B6,F6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R6" s="6" t="e">
+        <f>ROUND(IMDIV(C6,B6),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S6" s="6" t="e">
+        <f>ROUND(IMDIV(I6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="45" t="e">
-        <f t="shared" ref="V2:V5" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
+      <c r="V6" s="45" t="e">
+        <f>((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L3" s="7" t="e">
-        <f t="shared" si="1"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="e">
+        <f>ROUND(IMDIV(B7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L7" s="7" t="e">
+        <f>E7/J7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M3" s="7" t="e">
-        <f t="shared" si="2"/>
+      <c r="M7" s="7" t="e">
+        <f>D7/J7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N3" s="6" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O3" s="6" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P3" s="6" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q3" s="6" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R3" s="6" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S3" s="6" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T3" s="6" t="s">
+      <c r="N7" s="6" t="e">
+        <f>ROUND(IMDIV(F7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O7" s="6" t="e">
+        <f>ROUND(IMDIV(G7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P7" s="6" t="e">
+        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q7" s="6" t="e">
+        <f>ROUND(IMDIV(B7,F7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R7" s="6" t="e">
+        <f>ROUND(IMDIV(C7,B7),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S7" s="6" t="e">
+        <f>ROUND(IMDIV(I7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="T7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="30" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L4" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M4" s="31" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O4" s="30" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P4" s="30" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q4" s="30" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R4" s="30" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S4" s="30" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T4" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="V4" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="30" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L5" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M5" s="31" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O5" s="30" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P5" s="30" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q5" s="30" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R5" s="30" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S5" s="30" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T5" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="V5" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9" t="e">
-        <f t="shared" ref="K6:K9" si="10">ROUND(IMDIV(B6,J6),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L6" s="11" t="e">
-        <f t="shared" ref="L6:L9" si="11">E6/J6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M6" s="11" t="e">
-        <f t="shared" ref="M6:M9" si="12">D6/J6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="9" t="e">
-        <f t="shared" ref="N6:N9" si="13">ROUND(IMDIV(F6,J6),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="O6" s="9" t="e">
-        <f t="shared" ref="O6:O9" si="14">ROUND(IMDIV(G6,J6),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="P6" s="9" t="e">
-        <f t="shared" ref="P6:P9" si="15">ROUND(IMDIV(H6,J6),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q6" s="9" t="e">
-        <f t="shared" ref="Q6:Q9" si="16">ROUND(IMDIV(B6,F6),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R6" s="9" t="e">
-        <f t="shared" ref="R6:R9" si="17">ROUND(IMDIV(C6,B6),4)*100</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="S6" s="9" t="e">
-        <f t="shared" ref="S6:S9" si="18">ROUND(IMDIV(I6,J6),2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="V6" s="45" t="e">
-        <f t="shared" ref="V6:V9" si="19">((K6/2.5)+(M6/4)+(L6/5)-(N6)+(S6/215)+(P6/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9" t="e">
-        <f t="shared" si="10"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L7" s="11" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M7" s="11" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="9" t="e">
-        <f t="shared" si="13"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O7" s="9" t="e">
-        <f t="shared" si="14"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P7" s="9" t="e">
-        <f t="shared" si="15"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q7" s="9" t="e">
-        <f t="shared" si="16"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R7" s="9" t="e">
-        <f t="shared" si="17"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S7" s="9" t="e">
-        <f t="shared" si="18"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>24</v>
-      </c>
       <c r="V7" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+        <f>((K7/2.5)+(M7/4)+(L7/5)-(N7)+(S7/215)+(P7/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
         <v>37</v>
       </c>
@@ -7441,39 +7638,39 @@
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
       <c r="K8" s="27" t="e">
-        <f t="shared" si="10"/>
+        <f>ROUND(IMDIV(B8,J8),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="L8" s="28" t="e">
-        <f t="shared" si="11"/>
+        <f>E8/J8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M8" s="28" t="e">
-        <f t="shared" si="12"/>
+        <f>D8/J8</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N8" s="27" t="e">
-        <f t="shared" si="13"/>
+        <f>ROUND(IMDIV(F8,J8),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="O8" s="27" t="e">
-        <f t="shared" si="14"/>
+        <f>ROUND(IMDIV(G8,J8),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="P8" s="27" t="e">
-        <f t="shared" si="15"/>
+        <f>ROUND(IMDIV(H8,J8),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="Q8" s="27" t="e">
-        <f t="shared" si="16"/>
+        <f>ROUND(IMDIV(B8,F8),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="R8" s="27" t="e">
-        <f t="shared" si="17"/>
+        <f>ROUND(IMDIV(C8,B8),4)*100</f>
         <v>#NUM!</v>
       </c>
       <c r="S8" s="27" t="e">
-        <f t="shared" si="18"/>
+        <f>ROUND(IMDIV(I8,J8),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="T8" s="26" t="s">
@@ -7483,11 +7680,11 @@
         <v>24</v>
       </c>
       <c r="V8" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+        <f>((K8/2.5)+(M8/4)+(L8/5)-(N8)+(S8/215)+(P8/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="s">
         <v>38</v>
       </c>
@@ -7501,39 +7698,39 @@
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
       <c r="K9" s="27" t="e">
-        <f t="shared" si="10"/>
+        <f>ROUND(IMDIV(B9,J9),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="L9" s="28" t="e">
-        <f t="shared" si="11"/>
+        <f>E9/J9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M9" s="28" t="e">
-        <f t="shared" si="12"/>
+        <f>D9/J9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N9" s="27" t="e">
-        <f t="shared" si="13"/>
+        <f>ROUND(IMDIV(F9,J9),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="O9" s="27" t="e">
-        <f t="shared" si="14"/>
+        <f>ROUND(IMDIV(G9,J9),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="P9" s="27" t="e">
-        <f t="shared" si="15"/>
+        <f>ROUND(IMDIV(H9,J9),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="Q9" s="27" t="e">
-        <f t="shared" si="16"/>
+        <f>ROUND(IMDIV(B9,F9),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="R9" s="27" t="e">
-        <f t="shared" si="17"/>
+        <f>ROUND(IMDIV(C9,B9),4)*100</f>
         <v>#NUM!</v>
       </c>
       <c r="S9" s="27" t="e">
-        <f t="shared" si="18"/>
+        <f>ROUND(IMDIV(I9,J9),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="T9" s="26" t="s">
@@ -7543,11 +7740,11 @@
         <v>24</v>
       </c>
       <c r="V9" s="45" t="e">
-        <f t="shared" si="19"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+        <f>((K9/2.5)+(M9/4)+(L9/5)-(N9)+(S9/215)+(P9/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="52" t="s">
         <v>58</v>
       </c>
@@ -7573,7 +7770,7 @@
       <c r="U10" s="61"/>
       <c r="V10" s="55"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="76" t="s">
         <v>63</v>
       </c>
@@ -7623,24 +7820,46 @@
       <c r="U11" s="61"/>
       <c r="V11" s="55"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="66">
+      <c r="B12" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="81">
         <v>0</v>
       </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="67"/>
+      <c r="D12" s="67">
+        <v>79.22</v>
+      </c>
+      <c r="E12" s="68">
+        <v>1.016424299952539</v>
+      </c>
+      <c r="F12" s="67">
+        <v>0.67</v>
+      </c>
+      <c r="G12" s="67">
+        <v>3</v>
+      </c>
+      <c r="H12" s="67">
+        <v>7</v>
+      </c>
+      <c r="I12" s="67">
+        <v>0.67</v>
+      </c>
+      <c r="J12" s="67">
+        <v>50</v>
+      </c>
+      <c r="K12" s="67">
+        <v>0.04</v>
+      </c>
+      <c r="L12" s="67">
+        <v>1</v>
+      </c>
+      <c r="M12" s="67">
+        <v>51.519999999999996</v>
+      </c>
       <c r="N12" s="53"/>
       <c r="O12" s="53"/>
       <c r="P12" s="53"/>
@@ -7651,24 +7870,46 @@
       <c r="U12" s="61"/>
       <c r="V12" s="55"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="62"/>
+      <c r="B13" s="62" t="s">
+        <v>72</v>
+      </c>
       <c r="C13" s="69">
-        <v>0</v>
-      </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="67"/>
-      <c r="M13" s="67"/>
+        <v>-8</v>
+      </c>
+      <c r="D13" s="67">
+        <v>58.86</v>
+      </c>
+      <c r="E13" s="68">
+        <v>0.84225723777883243</v>
+      </c>
+      <c r="F13" s="67">
+        <v>0.51</v>
+      </c>
+      <c r="G13" s="67">
+        <v>1</v>
+      </c>
+      <c r="H13" s="67">
+        <v>4</v>
+      </c>
+      <c r="I13" s="67">
+        <v>0.67</v>
+      </c>
+      <c r="J13" s="67">
+        <v>106</v>
+      </c>
+      <c r="K13" s="67">
+        <v>0.2</v>
+      </c>
+      <c r="L13" s="67">
+        <v>0.76</v>
+      </c>
+      <c r="M13" s="67">
+        <v>52</v>
+      </c>
       <c r="N13" s="53"/>
       <c r="O13" s="53"/>
       <c r="P13" s="53"/>
@@ -7679,22 +7920,22 @@
       <c r="U13" s="61"/>
       <c r="V13" s="55"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
       <c r="N14" s="53"/>
       <c r="O14" s="53"/>
       <c r="P14" s="53"/>
@@ -7705,24 +7946,46 @@
       <c r="U14" s="5"/>
       <c r="V14" s="55"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="66">
-        <v>0</v>
-      </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="67"/>
+      <c r="B15" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="69">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="62">
+        <v>88.82</v>
+      </c>
+      <c r="E15" s="62">
+        <v>1.07</v>
+      </c>
+      <c r="F15" s="62">
+        <v>0.63</v>
+      </c>
+      <c r="G15" s="72">
+        <v>2</v>
+      </c>
+      <c r="H15" s="72">
+        <v>8</v>
+      </c>
+      <c r="I15" s="62">
+        <v>0.65</v>
+      </c>
+      <c r="J15" s="72">
+        <v>112</v>
+      </c>
+      <c r="K15" s="67">
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="67">
+        <v>0.97</v>
+      </c>
+      <c r="M15" s="62">
+        <v>58.06</v>
+      </c>
       <c r="N15" s="53"/>
       <c r="O15" s="53"/>
       <c r="P15" s="53"/>
@@ -7733,24 +7996,46 @@
       <c r="U15" s="5"/>
       <c r="V15" s="55"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="69">
-        <v>0</v>
-      </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="67"/>
-      <c r="M16" s="67"/>
+      <c r="B16" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="67">
+        <v>57.57</v>
+      </c>
+      <c r="E16" s="68">
+        <v>1.0849919316563834</v>
+      </c>
+      <c r="F16" s="67">
+        <v>0.71</v>
+      </c>
+      <c r="G16" s="72">
+        <v>5</v>
+      </c>
+      <c r="H16" s="72">
+        <v>8</v>
+      </c>
+      <c r="I16" s="67">
+        <v>0.53</v>
+      </c>
+      <c r="J16" s="72">
+        <v>116</v>
+      </c>
+      <c r="K16" s="67">
+        <v>0.04</v>
+      </c>
+      <c r="L16" s="67">
+        <v>1.35</v>
+      </c>
+      <c r="M16" s="67">
+        <v>40</v>
+      </c>
       <c r="N16" s="57"/>
       <c r="O16" s="57"/>
       <c r="P16" s="57"/>
@@ -7761,7 +8046,7 @@
       <c r="U16" s="57"/>
       <c r="V16" s="55"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="60"/>
       <c r="B17" s="53"/>
       <c r="C17" s="53"/>
@@ -7785,7 +8070,7 @@
       <c r="U17" s="57"/>
       <c r="V17" s="55"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>61</v>
       </c>
@@ -7811,7 +8096,7 @@
       <c r="U18" s="57"/>
       <c r="V18" s="55"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="78" t="s">
         <v>64</v>
       </c>
@@ -7861,7 +8146,7 @@
       <c r="U19" s="57"/>
       <c r="V19" s="55"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="65" t="s">
         <v>28</v>
       </c>
@@ -7889,7 +8174,7 @@
       <c r="U20" s="61"/>
       <c r="V20" s="55"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="65" t="s">
         <v>27</v>
       </c>
@@ -7917,22 +8202,22 @@
       <c r="U21" s="61"/>
       <c r="V21" s="55"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="73"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
       <c r="N22" s="53"/>
       <c r="O22" s="53"/>
       <c r="P22" s="53"/>
@@ -7943,7 +8228,7 @@
       <c r="U22" s="5"/>
       <c r="V22" s="55"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="65" t="s">
         <v>37</v>
       </c>
@@ -7962,7 +8247,7 @@
       <c r="L23" s="67"/>
       <c r="M23" s="67"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="65" t="s">
         <v>38</v>
       </c>
@@ -7982,21 +8267,25 @@
       <c r="M24" s="67"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V16">
+    <sortCondition sortBy="cellColor" ref="A4:A16" dxfId="1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D112C103-7A2C-4701-8F60-5B846BF871DD}">
-  <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:V20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8064,7 +8353,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>28</v>
       </c>
@@ -8078,39 +8367,39 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6" t="e">
-        <f t="shared" ref="K2:K9" si="0">ROUND(IMDIV(B2,J2),2)</f>
+        <f t="shared" ref="K2:K3" si="0">ROUND(IMDIV(B2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="L2" s="7" t="e">
-        <f t="shared" ref="L2:L9" si="1">E2/J2</f>
+        <f t="shared" ref="L2:L3" si="1">E2/J2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M2" s="7" t="e">
-        <f t="shared" ref="M2:M9" si="2">D2/J2</f>
+        <f t="shared" ref="M2:M3" si="2">D2/J2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N2" s="6" t="e">
-        <f t="shared" ref="N2:N9" si="3">ROUND(IMDIV(F2,J2),2)</f>
+        <f t="shared" ref="N2:N3" si="3">ROUND(IMDIV(F2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="O2" s="6" t="e">
-        <f t="shared" ref="O2:O9" si="4">ROUND(IMDIV(G2,J2),2)</f>
+        <f t="shared" ref="O2:O3" si="4">ROUND(IMDIV(G2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="P2" s="6" t="e">
-        <f t="shared" ref="P2:P9" si="5">ROUND(IMDIV(H2,J2),2)</f>
+        <f t="shared" ref="P2:P3" si="5">ROUND(IMDIV(H2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="Q2" s="6" t="e">
-        <f t="shared" ref="Q2:Q9" si="6">ROUND(IMDIV(B2,F2),2)</f>
+        <f t="shared" ref="Q2:Q3" si="6">ROUND(IMDIV(B2,F2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="R2" s="6" t="e">
-        <f t="shared" ref="R2:R9" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
+        <f t="shared" ref="R2:R3" si="7">ROUND(IMDIV(C2,B2),4)*100</f>
         <v>#NUM!</v>
       </c>
       <c r="S2" s="6" t="e">
-        <f t="shared" ref="S2:S9" si="8">ROUND(IMDIV(I2,J2),2)</f>
+        <f t="shared" ref="S2:S7" si="8">ROUND(IMDIV(I2,J2),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -8120,11 +8409,11 @@
         <v>24</v>
       </c>
       <c r="V2" s="45" t="e">
-        <f t="shared" ref="V2:V9" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+        <f t="shared" ref="V2:V7" si="9">((K2/2.5)+(M2/4)+(L2/5)-(N2)+(S2/215)+(P2/20))+1</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>27</v>
       </c>
@@ -8184,59 +8473,59 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="30" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L4" s="31" t="e">
-        <f t="shared" si="1"/>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9" t="e">
+        <f>ROUND(IMDIV(B4,J4),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L4" s="11" t="e">
+        <f>E4/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M4" s="31" t="e">
-        <f t="shared" si="2"/>
+      <c r="M4" s="11" t="e">
+        <f>D4/J4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N4" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O4" s="30" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P4" s="30" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q4" s="30" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R4" s="30" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S4" s="30" t="e">
+      <c r="N4" s="9" t="e">
+        <f>ROUND(IMDIV(F4,J4),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O4" s="9" t="e">
+        <f>ROUND(IMDIV(G4,J4),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P4" s="9" t="e">
+        <f>ROUND(IMDIV(H4,J4),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q4" s="9" t="e">
+        <f>ROUND(IMDIV(B4,F4),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R4" s="9" t="e">
+        <f>ROUND(IMDIV(C4,B4),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S4" s="9" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="T4" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="29" t="s">
+      <c r="T4" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U4" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V4" s="45" t="e">
@@ -8244,59 +8533,59 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A5" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="30" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L5" s="31" t="e">
-        <f t="shared" si="1"/>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="e">
+        <f>ROUND(IMDIV(B5,J5),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L5" s="11" t="e">
+        <f>E5/J5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M5" s="31" t="e">
-        <f t="shared" si="2"/>
+      <c r="M5" s="11" t="e">
+        <f>D5/J5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N5" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O5" s="30" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P5" s="30" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q5" s="30" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R5" s="30" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S5" s="30" t="e">
+      <c r="N5" s="9" t="e">
+        <f>ROUND(IMDIV(F5,J5),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O5" s="9" t="e">
+        <f>ROUND(IMDIV(G5,J5),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P5" s="9" t="e">
+        <f>ROUND(IMDIV(H5,J5),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q5" s="9" t="e">
+        <f>ROUND(IMDIV(B5,F5),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R5" s="9" t="e">
+        <f>ROUND(IMDIV(C5,B5),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S5" s="9" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="T5" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="29" t="s">
+      <c r="T5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="U5" s="10" t="s">
         <v>24</v>
       </c>
       <c r="V5" s="45" t="e">
@@ -8304,59 +8593,59 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L6" s="11" t="e">
-        <f t="shared" si="1"/>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="27" t="e">
+        <f>ROUND(IMDIV(B6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L6" s="28" t="e">
+        <f>E6/J6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M6" s="11" t="e">
-        <f t="shared" si="2"/>
+      <c r="M6" s="28" t="e">
+        <f>D6/J6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N6" s="9" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O6" s="9" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P6" s="9" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q6" s="9" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R6" s="9" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S6" s="9" t="e">
+      <c r="N6" s="27" t="e">
+        <f>ROUND(IMDIV(F6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O6" s="27" t="e">
+        <f>ROUND(IMDIV(G6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P6" s="27" t="e">
+        <f>ROUND(IMDIV(H6,J6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q6" s="27" t="e">
+        <f>ROUND(IMDIV(B6,F6),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R6" s="27" t="e">
+        <f>ROUND(IMDIV(C6,B6),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S6" s="27" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="T6" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" s="10" t="s">
+      <c r="T6" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" s="26" t="s">
         <v>24</v>
       </c>
       <c r="V6" s="45" t="e">
@@ -8364,59 +8653,59 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L7" s="11" t="e">
-        <f t="shared" si="1"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="27" t="e">
+        <f>ROUND(IMDIV(B7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="L7" s="28" t="e">
+        <f>E7/J7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M7" s="11" t="e">
-        <f t="shared" si="2"/>
+      <c r="M7" s="28" t="e">
+        <f>D7/J7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N7" s="9" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O7" s="9" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P7" s="9" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q7" s="9" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R7" s="9" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S7" s="9" t="e">
+      <c r="N7" s="27" t="e">
+        <f>ROUND(IMDIV(F7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="O7" s="27" t="e">
+        <f>ROUND(IMDIV(G7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="P7" s="27" t="e">
+        <f>ROUND(IMDIV(H7,J7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Q7" s="27" t="e">
+        <f>ROUND(IMDIV(B7,F7),2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="R7" s="27" t="e">
+        <f>ROUND(IMDIV(C7,B7),4)*100</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="S7" s="27" t="e">
         <f t="shared" si="8"/>
         <v>#NUM!</v>
       </c>
-      <c r="T7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7" s="10" t="s">
+      <c r="T7" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="U7" s="26" t="s">
         <v>24</v>
       </c>
       <c r="V7" s="45" t="e">
@@ -8424,137 +8713,67 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A8" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="27" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L8" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="28" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="27" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O8" s="27" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P8" s="27" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q8" s="27" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R8" s="27" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S8" s="27" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T8" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="V8" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="27" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="L9" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M9" s="28" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N9" s="27" t="e">
-        <f t="shared" si="3"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="O9" s="27" t="e">
-        <f t="shared" si="4"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="P9" s="27" t="e">
-        <f t="shared" si="5"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q9" s="27" t="e">
-        <f t="shared" si="6"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R9" s="27" t="e">
-        <f t="shared" si="7"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="S9" s="27" t="e">
-        <f t="shared" si="8"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="T9" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="U9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="V9" s="45" t="e">
-        <f t="shared" si="9"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A10" s="60"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="60"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="53"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="53"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="55"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="60"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="53"/>
+      <c r="Q9" s="53"/>
+      <c r="R9" s="53"/>
+      <c r="S9" s="53"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="61"/>
+      <c r="V9" s="55"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
       <c r="K10" s="53"/>
       <c r="L10" s="54"/>
       <c r="M10" s="54"/>
@@ -8564,178 +8783,180 @@
       <c r="Q10" s="53"/>
       <c r="R10" s="53"/>
       <c r="S10" s="53"/>
-      <c r="T10" s="80"/>
+      <c r="T10" s="53"/>
       <c r="U10" s="61"/>
       <c r="V10" s="55"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A11" s="60"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="64" t="s">
+        <v>17</v>
+      </c>
       <c r="N11" s="53"/>
       <c r="O11" s="53"/>
       <c r="P11" s="53"/>
       <c r="Q11" s="53"/>
       <c r="R11" s="53"/>
       <c r="S11" s="53"/>
-      <c r="T11" s="80"/>
+      <c r="T11" s="53"/>
       <c r="U11" s="61"/>
       <c r="V11" s="55"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A12" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="65"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="66">
+        <v>0</v>
+      </c>
+      <c r="D12" s="67"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
       <c r="N12" s="53"/>
       <c r="O12" s="53"/>
       <c r="P12" s="53"/>
       <c r="Q12" s="53"/>
       <c r="R12" s="53"/>
       <c r="S12" s="53"/>
-      <c r="T12" s="53"/>
-      <c r="U12" s="61"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
       <c r="V12" s="55"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" s="77" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="62" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="62" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="64" t="s">
-        <v>17</v>
-      </c>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="65"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="69">
+        <v>0</v>
+      </c>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
       <c r="N13" s="53"/>
       <c r="O13" s="53"/>
       <c r="P13" s="53"/>
       <c r="Q13" s="53"/>
       <c r="R13" s="53"/>
       <c r="S13" s="53"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="61"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
       <c r="V13" s="55"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A14" s="65"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="66">
-        <v>0</v>
-      </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="67"/>
-      <c r="M14" s="67"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="73"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
       <c r="V14" s="55"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="65"/>
       <c r="B15" s="62"/>
-      <c r="C15" s="69">
+      <c r="C15" s="66">
         <v>0</v>
       </c>
       <c r="D15" s="67"/>
       <c r="E15" s="68"/>
       <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
       <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
+      <c r="J15" s="72"/>
       <c r="K15" s="67"/>
       <c r="L15" s="67"/>
       <c r="M15" s="67"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="53"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="57"/>
       <c r="V15" s="55"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A16" s="77" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="73"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="65"/>
-      <c r="K16" s="65"/>
-      <c r="L16" s="65"/>
-      <c r="M16" s="65"/>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="65"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="69">
+        <v>0</v>
+      </c>
+      <c r="D16" s="67"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
       <c r="N16" s="57"/>
       <c r="O16" s="57"/>
       <c r="P16" s="57"/>
@@ -8746,22 +8967,20 @@
       <c r="U16" s="57"/>
       <c r="V16" s="55"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A17" s="65"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="66">
-        <v>0</v>
-      </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="67"/>
-      <c r="M17" s="67"/>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
       <c r="N17" s="57"/>
       <c r="O17" s="57"/>
       <c r="P17" s="57"/>
@@ -8772,67 +8991,64 @@
       <c r="U17" s="57"/>
       <c r="V17" s="55"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A18" s="65"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="69">
-        <v>0</v>
-      </c>
-      <c r="D18" s="67"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="57"/>
-      <c r="S18" s="57"/>
-      <c r="T18" s="57"/>
-      <c r="U18" s="57"/>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="60"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="61"/>
+      <c r="U18" s="61"/>
       <c r="V18" s="55"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A19" s="56"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="60"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="61"/>
+      <c r="U19" s="61"/>
       <c r="V19" s="55"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A20" s="60"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
       <c r="K20" s="53"/>
       <c r="L20" s="54"/>
       <c r="M20" s="54"/>
@@ -8842,56 +9058,9 @@
       <c r="Q20" s="53"/>
       <c r="R20" s="53"/>
       <c r="S20" s="53"/>
-      <c r="T20" s="61"/>
-      <c r="U20" s="61"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
       <c r="V20" s="55"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A21" s="60"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="61"/>
-      <c r="V21" s="55"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="53"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
